--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58118" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7A6DBF2-9B8C-49B7-A2ED-61F62ABB357D}"/>
+  <xr:revisionPtr revIDLastSave="58122" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22FBE9FF-C265-42DC-BD92-1EDB0ACFFBB6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12070,7 +12070,7 @@
     <t>Rta130826</t>
   </si>
   <si>
-    <t>TV 69888391</t>
+    <t>TV 69888391-sugeily</t>
   </si>
 </sst>
 </file>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58414" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49EEE31B-4287-4E2C-BF3C-1B7A29DD8427}"/>
+  <xr:revisionPtr revIDLastSave="58419" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF74FEDF-FBD7-42A1-8294-DDDDF3382D28}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1136,7 +1136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6234" uniqueCount="3651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6236" uniqueCount="3653">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -12088,7 +12088,13 @@
     <t>Tra150826</t>
   </si>
   <si>
-    <t>69754767-emily 1 pantalla hasta el 28 de agosto</t>
+    <t>69754767-emily 1 pantalla hasta el 30 de agosto</t>
+  </si>
+  <si>
+    <t>150826-2207</t>
+  </si>
+  <si>
+    <t>150826-2208</t>
   </si>
 </sst>
 </file>
@@ -31069,8 +31075,12 @@
       <c r="G98" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="H98" s="145"/>
-      <c r="I98" s="145"/>
+      <c r="H98" s="145" t="s">
+        <v>3651</v>
+      </c>
+      <c r="I98" s="145" t="s">
+        <v>3652</v>
+      </c>
       <c r="J98" s="30" t="s">
         <v>3157</v>
       </c>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58597" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C20FD43-9F1E-4539-AB3B-155862E6C8EE}"/>
+  <xr:revisionPtr revIDLastSave="58650" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD939D21-C95A-45A3-984B-BDFB9FC4F0D9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1140,6 +1140,43 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>HP</author>
+  </authors>
+  <commentList>
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{A2D76211-DA08-4E9C-A6AE-3FF481BA8F98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HP:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+iphone Ios 18.7.9
+Chat GPT Ios App
+17 de agosto 2026 a las 3.42pm
+panama city</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
@@ -1163,7 +1200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6240" uniqueCount="3643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6242" uniqueCount="3645">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -11860,9 +11897,6 @@
     <t>63465332 1 pantalla hasta el 13 de septiembre (Hilary)</t>
   </si>
   <si>
-    <t>eliminar sugeily</t>
-  </si>
-  <si>
     <t>hasta 12 de septiembre</t>
   </si>
   <si>
@@ -12092,6 +12126,15 @@
   </si>
   <si>
     <t xml:space="preserve">68582631-melanie 1 pantalla hasta el 15 de septiembre </t>
+  </si>
+  <si>
+    <t>10 usd hasta 16 de septiembre</t>
+  </si>
+  <si>
+    <t>64725455 1 pantalla hasta el 16 de septiembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quincenal 60957473-jose 1 pantalla hasta el 02 de septiembre </t>
   </si>
 </sst>
 </file>
@@ -13426,7 +13469,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="448">
+  <cellXfs count="451">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -13658,7 +13701,6 @@
     <xf numFmtId="2" fontId="2" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -13919,6 +13961,10 @@
     <xf numFmtId="0" fontId="120" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -13930,10 +13976,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF66CC"/>
       <color rgb="FF00FF00"/>
       <color rgb="FFFF6600"/>
       <color rgb="FF66FF99"/>
-      <color rgb="FFFF66CC"/>
       <color rgb="FF28871B"/>
       <color rgb="FFFF3300"/>
       <color rgb="FFFF00FF"/>
@@ -15328,161 +15374,6 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>2858319</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>68621</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="88830" cy="64034"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Imagen 86">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6030599-0AFE-1941-9C60-1CBEA80EFA05}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0E5FD612-A343-964B-B5B3-E573A94E88CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId8"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="16998" t="7377" r="27009" b="12816"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19139719" y="21982471"/>
-          <a:ext cx="88830" cy="64034"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>3094089</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>43016</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="78421" cy="69369"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Imagen 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1162267C-0201-0147-A223-BC0E54E17649}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A20F145E-3AD9-F240-B7CE-0B590521AEE3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId2"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="26000" t="6706" r="24667" b="6904"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="22933742" y="20933492"/>
-          <a:ext cx="78421" cy="69369"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>2965223</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>28348</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="113393" cy="113393"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Imagen 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98A51674-8445-4DD0-8A6D-E376E2A87AEB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19246908" y="13384752"/>
-          <a:ext cx="113393" cy="113393"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent6">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1156607</xdr:colOff>
       <xdr:row>413</xdr:row>
@@ -15503,7 +15394,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -15600,7 +15491,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -15629,7 +15520,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1116919</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>39687</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="119484" cy="94138"/>
@@ -15697,7 +15588,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -15838,7 +15729,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -15888,13 +15779,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId31"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -15935,7 +15826,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -16029,13 +15920,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16084,13 +15975,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16186,7 +16077,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -16233,7 +16124,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -16327,13 +16218,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16382,13 +16273,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16484,13 +16375,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16539,13 +16430,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -16597,7 +16488,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -16647,7 +16538,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -16835,7 +16726,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -16935,7 +16826,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -17217,13 +17108,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -17331,7 +17222,7 @@
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId31"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -17372,7 +17263,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -17419,7 +17310,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -17466,13 +17357,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -17665,13 +17556,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -17723,7 +17614,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -17770,7 +17661,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -17817,7 +17708,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -17864,7 +17755,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -17911,7 +17802,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -18055,7 +17946,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -18149,13 +18040,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -18207,7 +18098,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -18355,7 +18246,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -18402,13 +18293,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -18554,13 +18445,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId31"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -18601,7 +18492,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -18651,13 +18542,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId31"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -18701,13 +18592,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId31"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -18802,7 +18693,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -18899,13 +18790,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -18957,7 +18848,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -19007,7 +18898,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -19057,7 +18948,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -19104,7 +18995,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -19160,7 +19051,7 @@
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId31"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -19201,13 +19092,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
             <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
-              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId29"/>
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId34"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -19353,7 +19244,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -29853,7 +29744,7 @@
     <col min="1" max="1" width="22.7265625" customWidth="1"/>
     <col min="2" max="2" width="20.54296875" customWidth="1"/>
     <col min="3" max="3" width="31.90625" customWidth="1"/>
-    <col min="4" max="4" width="20.453125" style="392" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" style="391" customWidth="1"/>
     <col min="5" max="5" width="27.453125" style="30" customWidth="1"/>
     <col min="6" max="6" width="15.08984375" customWidth="1"/>
     <col min="7" max="7" width="46.90625" customWidth="1"/>
@@ -29879,7 +29770,7 @@
         <v>2096</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2174</v>
@@ -29895,10 +29786,10 @@
       <c r="B5" s="147">
         <v>69249040</v>
       </c>
-      <c r="C5" s="423" t="s">
+      <c r="C5" s="422" t="s">
         <v>2224</v>
       </c>
-      <c r="D5" s="390" t="s">
+      <c r="D5" s="389" t="s">
         <v>2220</v>
       </c>
       <c r="E5" s="148"/>
@@ -29910,10 +29801,10 @@
       <c r="B6" s="147" t="s">
         <v>2997</v>
       </c>
-      <c r="C6" s="423" t="s">
+      <c r="C6" s="422" t="s">
         <v>2230</v>
       </c>
-      <c r="D6" s="390" t="s">
+      <c r="D6" s="389" t="s">
         <v>2996</v>
       </c>
       <c r="E6" s="148"/>
@@ -29932,7 +29823,7 @@
         <v>2221</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2173</v>
@@ -29948,10 +29839,10 @@
       <c r="B8" s="147">
         <v>64858241</v>
       </c>
-      <c r="C8" s="423" t="s">
+      <c r="C8" s="422" t="s">
         <v>2214</v>
       </c>
-      <c r="D8" s="390" t="s">
+      <c r="D8" s="389" t="s">
         <v>2298</v>
       </c>
       <c r="E8" s="148"/>
@@ -29963,10 +29854,10 @@
       <c r="B9" s="147">
         <v>62279384</v>
       </c>
-      <c r="C9" s="423" t="s">
+      <c r="C9" s="422" t="s">
         <v>2215</v>
       </c>
-      <c r="D9" s="390" t="s">
+      <c r="D9" s="389" t="s">
         <v>2216</v>
       </c>
       <c r="E9" s="148"/>
@@ -29984,7 +29875,7 @@
       <c r="D10" s="30" t="s">
         <v>2094</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="412" t="s">
         <v>2913</v>
       </c>
       <c r="F10" s="30" t="s">
@@ -30001,10 +29892,10 @@
       <c r="B11" s="147">
         <v>68853797</v>
       </c>
-      <c r="C11" s="423" t="s">
+      <c r="C11" s="422" t="s">
         <v>2239</v>
       </c>
-      <c r="D11" s="390" t="s">
+      <c r="D11" s="389" t="s">
         <v>3154</v>
       </c>
       <c r="E11" s="148"/>
@@ -30016,10 +29907,10 @@
       <c r="B12" s="147">
         <v>68241069</v>
       </c>
-      <c r="C12" s="423" t="s">
+      <c r="C12" s="422" t="s">
         <v>2108</v>
       </c>
-      <c r="D12" s="390" t="s">
+      <c r="D12" s="389" t="s">
         <v>2364</v>
       </c>
       <c r="E12" s="148"/>
@@ -30054,10 +29945,10 @@
       <c r="B14" s="147">
         <v>69561522</v>
       </c>
-      <c r="C14" s="423" t="s">
+      <c r="C14" s="422" t="s">
         <v>2067</v>
       </c>
-      <c r="D14" s="390" t="s">
+      <c r="D14" s="389" t="s">
         <v>2298</v>
       </c>
       <c r="E14" s="148" t="s">
@@ -30071,10 +29962,10 @@
       <c r="B15" s="147">
         <v>61381388</v>
       </c>
-      <c r="C15" s="423" t="s">
+      <c r="C15" s="422" t="s">
         <v>2068</v>
       </c>
-      <c r="D15" s="390" t="s">
+      <c r="D15" s="389" t="s">
         <v>2450</v>
       </c>
       <c r="E15" s="148"/>
@@ -30109,10 +30000,10 @@
       <c r="B17" s="147">
         <v>69692470</v>
       </c>
-      <c r="C17" s="423" t="s">
+      <c r="C17" s="422" t="s">
         <v>2366</v>
       </c>
-      <c r="D17" s="390" t="s">
+      <c r="D17" s="389" t="s">
         <v>2862</v>
       </c>
       <c r="E17" s="148"/>
@@ -30124,7 +30015,7 @@
       <c r="B18" s="147" t="s">
         <v>1237</v>
       </c>
-      <c r="C18" s="423" t="s">
+      <c r="C18" s="422" t="s">
         <v>1424</v>
       </c>
       <c r="D18" s="148" t="s">
@@ -30165,10 +30056,10 @@
       <c r="B20" s="163">
         <v>63183787</v>
       </c>
-      <c r="C20" s="424" t="s">
+      <c r="C20" s="423" t="s">
         <v>2219</v>
       </c>
-      <c r="D20" s="389" t="s">
+      <c r="D20" s="388" t="s">
         <v>3328</v>
       </c>
       <c r="E20" s="164"/>
@@ -30180,7 +30071,7 @@
       <c r="B21" s="163">
         <v>68783599</v>
       </c>
-      <c r="C21" s="424" t="s">
+      <c r="C21" s="423" t="s">
         <v>1400</v>
       </c>
       <c r="D21" s="164" t="s">
@@ -30220,7 +30111,7 @@
       <c r="B23" s="164">
         <v>68381893</v>
       </c>
-      <c r="C23" s="305" t="s">
+      <c r="C23" s="304" t="s">
         <v>1524</v>
       </c>
       <c r="D23" s="164" t="s">
@@ -30237,10 +30128,10 @@
       <c r="B24" s="163">
         <v>64079861</v>
       </c>
-      <c r="C24" s="424" t="s">
+      <c r="C24" s="423" t="s">
         <v>1825</v>
       </c>
-      <c r="D24" s="389" t="s">
+      <c r="D24" s="388" t="s">
         <v>2882</v>
       </c>
       <c r="E24" s="164" t="s">
@@ -30263,7 +30154,7 @@
       <c r="E25" s="30" t="s">
         <v>3245</v>
       </c>
-      <c r="F25" s="312" t="s">
+      <c r="F25" s="311" t="s">
         <v>2258</v>
       </c>
       <c r="G25" s="30" t="s">
@@ -30277,10 +30168,10 @@
       <c r="B26" s="163">
         <v>69624389</v>
       </c>
-      <c r="C26" s="424" t="s">
+      <c r="C26" s="423" t="s">
         <v>2519</v>
       </c>
-      <c r="D26" s="389" t="s">
+      <c r="D26" s="388" t="s">
         <v>2847</v>
       </c>
       <c r="E26" s="164"/>
@@ -30292,10 +30183,10 @@
       <c r="B27" s="163">
         <v>62782770</v>
       </c>
-      <c r="C27" s="424" t="s">
+      <c r="C27" s="423" t="s">
         <v>2520</v>
       </c>
-      <c r="D27" s="389" t="s">
+      <c r="D27" s="388" t="s">
         <v>3435</v>
       </c>
       <c r="E27" s="164"/>
@@ -30323,13 +30214,13 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="407" customFormat="1">
-      <c r="D29" s="408"/>
-      <c r="E29" s="386"/>
-    </row>
-    <row r="30" spans="1:9" s="407" customFormat="1">
-      <c r="D30" s="408"/>
-      <c r="E30" s="386"/>
+    <row r="29" spans="1:9" s="406" customFormat="1">
+      <c r="D29" s="407"/>
+      <c r="E29" s="385"/>
+    </row>
+    <row r="30" spans="1:9" s="406" customFormat="1">
+      <c r="D30" s="407"/>
+      <c r="E30" s="385"/>
     </row>
     <row r="31" spans="1:9" s="30" customFormat="1">
       <c r="A31" t="s">
@@ -30357,15 +30248,15 @@
     </row>
     <row r="32" spans="1:9" s="147" customFormat="1">
       <c r="A32" s="149" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="B32" s="149" t="s">
         <v>1737</v>
       </c>
-      <c r="C32" s="423" t="s">
+      <c r="C32" s="422" t="s">
         <v>2078</v>
       </c>
-      <c r="D32" s="390" t="s">
+      <c r="D32" s="389" t="s">
         <v>2079</v>
       </c>
       <c r="E32" s="148"/>
@@ -30374,13 +30265,13 @@
       <c r="A33" s="149" t="s">
         <v>3228</v>
       </c>
-      <c r="B33" s="302">
+      <c r="B33" s="301">
         <v>62439069</v>
       </c>
-      <c r="C33" s="423" t="s">
+      <c r="C33" s="422" t="s">
         <v>2082</v>
       </c>
-      <c r="D33" s="390" t="s">
+      <c r="D33" s="389" t="s">
         <v>2569</v>
       </c>
       <c r="E33" s="148"/>
@@ -30389,7 +30280,7 @@
       <c r="A36" t="s">
         <v>2625</v>
       </c>
-      <c r="B36" s="425" t="s">
+      <c r="B36" s="424" t="s">
         <v>2311</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -30407,13 +30298,13 @@
       <c r="G36" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="H36" s="414" t="s">
+      <c r="H36" s="413" t="s">
         <v>2722</v>
       </c>
       <c r="I36" s="32" t="s">
         <v>3295</v>
       </c>
-      <c r="J36" s="414" t="s">
+      <c r="J36" s="413" t="s">
         <v>2912</v>
       </c>
       <c r="K36" s="30" t="s">
@@ -30421,16 +30312,16 @@
       </c>
     </row>
     <row r="37" spans="1:11" s="163" customFormat="1">
-      <c r="A37" s="272" t="s">
+      <c r="A37" s="271" t="s">
         <v>3425</v>
       </c>
-      <c r="B37" s="272" t="s">
+      <c r="B37" s="271" t="s">
         <v>1436</v>
       </c>
-      <c r="C37" s="424" t="s">
+      <c r="C37" s="423" t="s">
         <v>1751</v>
       </c>
-      <c r="D37" s="389" t="s">
+      <c r="D37" s="388" t="s">
         <v>1752</v>
       </c>
       <c r="E37" s="164" t="s">
@@ -30438,16 +30329,16 @@
       </c>
     </row>
     <row r="38" spans="1:11" s="163" customFormat="1">
-      <c r="A38" s="272" t="s">
+      <c r="A38" s="271" t="s">
         <v>2938</v>
       </c>
-      <c r="B38" s="272">
+      <c r="B38" s="271">
         <v>64341760</v>
       </c>
-      <c r="C38" s="426" t="s">
+      <c r="C38" s="425" t="s">
         <v>1754</v>
       </c>
-      <c r="D38" s="389" t="s">
+      <c r="D38" s="388" t="s">
         <v>2201</v>
       </c>
       <c r="E38" s="164" t="s">
@@ -30477,34 +30368,34 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="258" customFormat="1">
-      <c r="A40" s="315" t="s">
+    <row r="40" spans="1:11" s="257" customFormat="1">
+      <c r="A40" s="314" t="s">
         <v>2636</v>
       </c>
-      <c r="B40" s="272">
+      <c r="B40" s="271">
         <v>69918065</v>
       </c>
-      <c r="C40" s="426" t="s">
+      <c r="C40" s="425" t="s">
         <v>1744</v>
       </c>
-      <c r="D40" s="272" t="s">
+      <c r="D40" s="271" t="s">
         <v>2809</v>
       </c>
-      <c r="E40" s="256" t="s">
+      <c r="E40" s="255" t="s">
         <v>1745</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="258" customFormat="1">
-      <c r="A41" s="272" t="s">
+    <row r="41" spans="1:11" s="257" customFormat="1">
+      <c r="A41" s="271" t="s">
         <v>3463</v>
       </c>
-      <c r="B41" s="272">
+      <c r="B41" s="271">
         <v>60432412</v>
       </c>
-      <c r="C41" s="424" t="s">
+      <c r="C41" s="423" t="s">
         <v>1749</v>
       </c>
-      <c r="D41" s="389" t="s">
+      <c r="D41" s="388" t="s">
         <v>2831</v>
       </c>
       <c r="E41" s="164" t="s">
@@ -30512,7 +30403,7 @@
       </c>
     </row>
     <row r="42" spans="1:11" s="30" customFormat="1">
-      <c r="A42" s="441" t="s">
+      <c r="A42" s="440" t="s">
         <v>3137</v>
       </c>
       <c r="B42">
@@ -30533,9 +30424,9 @@
       <c r="G42" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="H42" s="220"/>
-      <c r="I42" s="220"/>
-      <c r="J42" s="220"/>
+      <c r="H42" s="219"/>
+      <c r="I42" s="219"/>
+      <c r="J42" s="219"/>
     </row>
     <row r="43" spans="1:11" s="149" customFormat="1">
       <c r="A43" s="149" t="s">
@@ -30544,13 +30435,13 @@
       <c r="B43" s="149" t="s">
         <v>2000</v>
       </c>
-      <c r="C43" s="423" t="s">
+      <c r="C43" s="422" t="s">
         <v>1494</v>
       </c>
       <c r="D43" s="149" t="s">
         <v>2704</v>
       </c>
-      <c r="E43" s="228" t="s">
+      <c r="E43" s="227" t="s">
         <v>1422</v>
       </c>
     </row>
@@ -30561,13 +30452,13 @@
       <c r="B44" s="149">
         <v>64476521</v>
       </c>
-      <c r="C44" s="423" t="s">
+      <c r="C44" s="422" t="s">
         <v>1496</v>
       </c>
       <c r="D44" s="149" t="s">
         <v>2837</v>
       </c>
-      <c r="E44" s="228" t="s">
+      <c r="E44" s="227" t="s">
         <v>1422</v>
       </c>
     </row>
@@ -30584,7 +30475,7 @@
       <c r="D48" s="4" t="s">
         <v>1403</v>
       </c>
-      <c r="E48" s="257" t="s">
+      <c r="E48" s="256" t="s">
         <v>3389</v>
       </c>
       <c r="F48" s="32" t="s">
@@ -30602,10 +30493,10 @@
       <c r="B49" s="147" t="s">
         <v>2980</v>
       </c>
-      <c r="C49" s="429" t="s">
+      <c r="C49" s="428" t="s">
         <v>1419</v>
       </c>
-      <c r="D49" s="390" t="s">
+      <c r="D49" s="389" t="s">
         <v>2955</v>
       </c>
       <c r="E49" s="148" t="s">
@@ -30619,10 +30510,10 @@
       <c r="B50" s="147">
         <v>62928817</v>
       </c>
-      <c r="C50" s="429" t="s">
+      <c r="C50" s="428" t="s">
         <v>1421</v>
       </c>
-      <c r="D50" s="390" t="s">
+      <c r="D50" s="389" t="s">
         <v>2746</v>
       </c>
       <c r="E50" s="148" t="s">
@@ -30643,7 +30534,7 @@
         <v>2748</v>
       </c>
       <c r="E54" s="30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="F54" s="30" t="s">
         <v>2115</v>
@@ -30651,13 +30542,13 @@
       <c r="G54" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="H54" s="218" t="s">
+      <c r="H54" s="217" t="s">
         <v>2825</v>
       </c>
       <c r="I54" s="192" t="s">
         <v>3140</v>
       </c>
-      <c r="J54" s="301" t="s">
+      <c r="J54" s="300" t="s">
         <v>3005</v>
       </c>
       <c r="K54" s="30" t="s">
@@ -30671,10 +30562,10 @@
       <c r="B55" s="163">
         <v>63487773</v>
       </c>
-      <c r="C55" s="426" t="s">
+      <c r="C55" s="425" t="s">
         <v>1807</v>
       </c>
-      <c r="D55" s="389" t="s">
+      <c r="D55" s="388" t="s">
         <v>2840</v>
       </c>
       <c r="E55" s="164"/>
@@ -30686,10 +30577,10 @@
       <c r="B56" s="163">
         <v>68845841</v>
       </c>
-      <c r="C56" s="424" t="s">
+      <c r="C56" s="423" t="s">
         <v>2039</v>
       </c>
-      <c r="D56" s="389" t="s">
+      <c r="D56" s="388" t="s">
         <v>2363</v>
       </c>
       <c r="E56" s="164"/>
@@ -30736,10 +30627,10 @@
       <c r="B58" s="147" t="s">
         <v>3088</v>
       </c>
-      <c r="C58" s="423" t="s">
+      <c r="C58" s="422" t="s">
         <v>1517</v>
       </c>
-      <c r="D58" s="390" t="s">
+      <c r="D58" s="389" t="s">
         <v>3072</v>
       </c>
       <c r="E58" s="148" t="s">
@@ -30753,10 +30644,10 @@
       <c r="B59" s="163">
         <v>64486692</v>
       </c>
-      <c r="C59" s="424" t="s">
+      <c r="C59" s="423" t="s">
         <v>2150</v>
       </c>
-      <c r="D59" s="389" t="s">
+      <c r="D59" s="388" t="s">
         <v>3077</v>
       </c>
       <c r="E59" s="164"/>
@@ -30775,7 +30666,7 @@
         <v>2800</v>
       </c>
       <c r="E60" s="30" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="F60" s="30" t="s">
         <v>2167</v>
@@ -30789,7 +30680,7 @@
       <c r="I60" s="30" t="s">
         <v>3185</v>
       </c>
-      <c r="J60" s="218" t="s">
+      <c r="J60" s="217" t="s">
         <v>2901</v>
       </c>
       <c r="K60" s="30" t="s">
@@ -30803,10 +30694,10 @@
       <c r="B61" s="147" t="s">
         <v>2995</v>
       </c>
-      <c r="C61" s="423" t="s">
+      <c r="C61" s="422" t="s">
         <v>2211</v>
       </c>
-      <c r="D61" s="390" t="s">
+      <c r="D61" s="389" t="s">
         <v>2994</v>
       </c>
       <c r="E61" s="148"/>
@@ -30818,10 +30709,10 @@
       <c r="B62" s="147">
         <v>64507039</v>
       </c>
-      <c r="C62" s="423" t="s">
+      <c r="C62" s="422" t="s">
         <v>2153</v>
       </c>
-      <c r="D62" s="390" t="s">
+      <c r="D62" s="389" t="s">
         <v>3073</v>
       </c>
       <c r="E62" s="148"/>
@@ -30868,39 +30759,39 @@
       <c r="B64" s="163">
         <v>68381893</v>
       </c>
-      <c r="C64" s="424" t="s">
+      <c r="C64" s="423" t="s">
         <v>2072</v>
       </c>
-      <c r="D64" s="389" t="s">
+      <c r="D64" s="388" t="s">
         <v>2138</v>
       </c>
       <c r="E64" s="164" t="s">
         <v>2191</v>
       </c>
     </row>
-    <row r="65" spans="1:11" s="258" customFormat="1">
-      <c r="A65" s="272" t="s">
+    <row r="65" spans="1:11" s="257" customFormat="1">
+      <c r="A65" s="271" t="s">
         <v>85</v>
       </c>
-      <c r="B65" s="272">
+      <c r="B65" s="271">
         <v>62360487</v>
       </c>
-      <c r="C65" s="424" t="s">
+      <c r="C65" s="423" t="s">
         <v>1741</v>
       </c>
-      <c r="D65" s="272" t="s">
+      <c r="D65" s="271" t="s">
         <v>2103</v>
       </c>
-      <c r="E65" s="303"/>
+      <c r="E65" s="302"/>
     </row>
     <row r="66" spans="1:11" s="139" customFormat="1">
-      <c r="A66" s="439" t="s">
+      <c r="A66" s="438" t="s">
         <v>3369</v>
       </c>
-      <c r="B66" s="430" t="s">
+      <c r="B66" s="429" t="s">
         <v>1486</v>
       </c>
-      <c r="C66" s="431" t="s">
+      <c r="C66" s="430" t="s">
         <v>1405</v>
       </c>
       <c r="D66" s="139" t="s">
@@ -30924,7 +30815,7 @@
       <c r="J66" s="30" t="s">
         <v>3279</v>
       </c>
-      <c r="K66" s="273" t="s">
+      <c r="K66" s="272" t="s">
         <v>2918</v>
       </c>
     </row>
@@ -30935,7 +30826,7 @@
       <c r="B67" s="164" t="s">
         <v>1174</v>
       </c>
-      <c r="C67" s="305" t="s">
+      <c r="C67" s="304" t="s">
         <v>1451</v>
       </c>
       <c r="D67" s="164" t="s">
@@ -30946,13 +30837,13 @@
       </c>
     </row>
     <row r="68" spans="1:11" s="164" customFormat="1">
-      <c r="A68" s="432" t="s">
+      <c r="A68" s="431" t="s">
         <v>3463</v>
       </c>
       <c r="B68" s="163" t="s">
         <v>1794</v>
       </c>
-      <c r="C68" s="424" t="s">
+      <c r="C68" s="423" t="s">
         <v>1530</v>
       </c>
       <c r="D68" s="164" t="s">
@@ -30961,8 +30852,8 @@
       <c r="E68" s="164" t="s">
         <v>1422</v>
       </c>
-      <c r="F68" s="256"/>
-      <c r="H68" s="256"/>
+      <c r="F68" s="255"/>
+      <c r="H68" s="255"/>
     </row>
     <row r="69" spans="1:11" s="30" customFormat="1">
       <c r="A69" s="4" t="s">
@@ -31000,13 +30891,13 @@
       </c>
     </row>
     <row r="70" spans="1:11" s="164" customFormat="1">
-      <c r="A70" s="256" t="s">
+      <c r="A70" s="255" t="s">
         <v>3230</v>
       </c>
-      <c r="B70" s="256">
+      <c r="B70" s="255">
         <v>62535724</v>
       </c>
-      <c r="C70" s="305" t="s">
+      <c r="C70" s="304" t="s">
         <v>1757</v>
       </c>
       <c r="D70" s="164" t="s">
@@ -31017,16 +30908,16 @@
       </c>
     </row>
     <row r="71" spans="1:11" s="163" customFormat="1">
-      <c r="A71" s="272" t="s">
-        <v>2721</v>
+      <c r="A71" s="271" t="s">
+        <v>148</v>
       </c>
       <c r="B71" s="163">
         <v>62090364</v>
       </c>
-      <c r="C71" s="424" t="s">
+      <c r="C71" s="423" t="s">
         <v>2026</v>
       </c>
-      <c r="D71" s="389" t="s">
+      <c r="D71" s="388" t="s">
         <v>2390</v>
       </c>
       <c r="E71" s="164" t="s">
@@ -31064,7 +30955,7 @@
       <c r="J72" s="30" t="s">
         <v>3318</v>
       </c>
-      <c r="K72" s="414" t="s">
+      <c r="K72" s="413" t="s">
         <v>2836</v>
       </c>
     </row>
@@ -31075,7 +30966,7 @@
       <c r="B73" s="164">
         <v>60450256</v>
       </c>
-      <c r="C73" s="305" t="s">
+      <c r="C73" s="304" t="s">
         <v>2171</v>
       </c>
       <c r="D73" s="164" t="s">
@@ -31089,10 +30980,10 @@
       <c r="B74" s="163">
         <v>68017100</v>
       </c>
-      <c r="C74" s="424" t="s">
+      <c r="C74" s="423" t="s">
         <v>2088</v>
       </c>
-      <c r="D74" s="389" t="s">
+      <c r="D74" s="388" t="s">
         <v>2233</v>
       </c>
       <c r="E74" s="164"/>
@@ -31101,7 +30992,7 @@
       <c r="A75" s="75" t="s">
         <v>3228</v>
       </c>
-      <c r="B75" s="425" t="s">
+      <c r="B75" s="424" t="s">
         <v>1983</v>
       </c>
       <c r="C75" s="22" t="s">
@@ -31119,7 +31010,7 @@
       <c r="G75" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="H75" s="218" t="s">
+      <c r="H75" s="217" t="s">
         <v>2888</v>
       </c>
       <c r="I75" s="30" t="s">
@@ -31139,10 +31030,10 @@
       <c r="B76" s="147">
         <v>64622116</v>
       </c>
-      <c r="C76" s="423" t="s">
+      <c r="C76" s="422" t="s">
         <v>1950</v>
       </c>
-      <c r="D76" s="390" t="s">
+      <c r="D76" s="389" t="s">
         <v>3076</v>
       </c>
       <c r="E76" s="148"/>
@@ -31154,10 +31045,10 @@
       <c r="B77" s="147">
         <v>66850767</v>
       </c>
-      <c r="C77" s="423" t="s">
+      <c r="C77" s="422" t="s">
         <v>2187</v>
       </c>
-      <c r="D77" s="390" t="s">
+      <c r="D77" s="389" t="s">
         <v>3517</v>
       </c>
       <c r="E77" s="148"/>
@@ -31185,19 +31076,19 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:11" s="407" customFormat="1">
-      <c r="D79" s="408"/>
-      <c r="E79" s="386"/>
-    </row>
-    <row r="80" spans="1:11" s="407" customFormat="1">
-      <c r="D80" s="408"/>
-      <c r="E80" s="386"/>
+    <row r="79" spans="1:11" s="406" customFormat="1">
+      <c r="D79" s="407"/>
+      <c r="E79" s="385"/>
+    </row>
+    <row r="80" spans="1:11" s="406" customFormat="1">
+      <c r="D80" s="407"/>
+      <c r="E80" s="385"/>
     </row>
     <row r="81" spans="1:11" s="30" customFormat="1">
       <c r="A81" t="s">
         <v>3137</v>
       </c>
-      <c r="B81" s="433" t="s">
+      <c r="B81" s="432" t="s">
         <v>2165</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -31225,77 +31116,76 @@
         <v>3277</v>
       </c>
       <c r="K81" s="30" t="s">
-        <v>3575</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" s="407" customFormat="1">
-      <c r="D82" s="408"/>
-      <c r="E82" s="386"/>
-    </row>
-    <row r="83" spans="1:11" s="407" customFormat="1">
-      <c r="D83" s="408"/>
-    </row>
-    <row r="84" spans="1:11" s="30" customFormat="1">
-      <c r="A84" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" s="406" customFormat="1">
+      <c r="D82" s="407"/>
+      <c r="E82" s="385"/>
+    </row>
+    <row r="83" spans="1:11" s="406" customFormat="1">
+      <c r="D83" s="407"/>
+    </row>
+    <row r="92" spans="1:11" s="30" customFormat="1">
+      <c r="A92" s="30" t="s">
         <v>3141</v>
       </c>
-      <c r="B84" s="425" t="s">
+      <c r="B92" s="287" t="s">
         <v>2724</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C92" s="254" t="s">
         <v>1726</v>
       </c>
-      <c r="D84" s="30" t="s">
+      <c r="D92" s="30" t="s">
         <v>2841</v>
       </c>
-      <c r="E84" s="30" t="s">
+      <c r="E92" s="30" t="s">
         <v>2717</v>
       </c>
-      <c r="F84" s="30" t="s">
+      <c r="F92" s="30" t="s">
         <v>2229</v>
       </c>
-      <c r="G84" s="30" t="s">
+      <c r="G92" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="H84" s="32" t="s">
+      <c r="H92" s="32" t="s">
         <v>2902</v>
       </c>
-      <c r="I84" s="30" t="s">
+      <c r="I92" s="30" t="s">
         <v>3197</v>
       </c>
-      <c r="J84" s="414" t="s">
-        <v>3565</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" s="163" customFormat="1">
-      <c r="A85" s="163" t="s">
+      <c r="J92" s="446" t="s">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" s="164" customFormat="1">
+      <c r="A93" s="164" t="s">
         <v>2943</v>
       </c>
-      <c r="B85" s="163">
+      <c r="B93" s="164">
         <v>67610749</v>
       </c>
-      <c r="C85" s="424" t="s">
+      <c r="C93" s="304" t="s">
         <v>2041</v>
       </c>
-      <c r="D85" s="389" t="s">
+      <c r="D93" s="164" t="s">
         <v>3476</v>
       </c>
-      <c r="E85" s="164"/>
-    </row>
-    <row r="86" spans="1:11" s="163" customFormat="1">
-      <c r="A86" s="272" t="s">
-        <v>3591</v>
-      </c>
-      <c r="B86" s="272" t="s">
+    </row>
+    <row r="94" spans="1:11" s="163" customFormat="1">
+      <c r="A94" s="271" t="s">
+        <v>3590</v>
+      </c>
+      <c r="B94" s="271" t="s">
         <v>1498</v>
       </c>
-      <c r="C86" s="424" t="s">
+      <c r="C94" s="423" t="s">
         <v>1782</v>
       </c>
-      <c r="D86" s="389" t="s">
+      <c r="D94" s="388" t="s">
         <v>3188</v>
       </c>
-      <c r="E86" s="164"/>
+      <c r="E94" s="164"/>
     </row>
     <row r="95" spans="1:11" s="30" customFormat="1">
       <c r="A95" s="30" t="s">
@@ -31304,10 +31194,10 @@
       <c r="B95" s="30">
         <v>6039752</v>
       </c>
-      <c r="C95" s="30" t="s">
+      <c r="C95" s="254" t="s">
         <v>1382</v>
       </c>
-      <c r="D95" s="255" t="s">
+      <c r="D95" s="254" t="s">
         <v>3266</v>
       </c>
       <c r="E95" s="30" t="s">
@@ -31320,29 +31210,29 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:11" s="147" customFormat="1">
-      <c r="A96" s="147" t="s">
+    <row r="96" spans="1:11" s="449" customFormat="1">
+      <c r="A96" s="449" t="s">
         <v>2445</v>
       </c>
-      <c r="B96" s="147">
+      <c r="B96" s="449">
         <v>64226974</v>
       </c>
-      <c r="C96" s="423" t="s">
+      <c r="C96" s="450" t="s">
         <v>2075</v>
       </c>
-      <c r="D96" s="390" t="s">
+      <c r="D96" s="449" t="s">
         <v>2076</v>
       </c>
       <c r="E96" s="148"/>
     </row>
-    <row r="97" spans="1:11" s="147" customFormat="1">
-      <c r="A97" s="147" t="s">
+    <row r="97" spans="1:11" s="449" customFormat="1">
+      <c r="A97" s="449" t="s">
         <v>2938</v>
       </c>
-      <c r="B97" s="147">
+      <c r="B97" s="449">
         <v>62646973</v>
       </c>
-      <c r="C97" s="423" t="s">
+      <c r="C97" s="450" t="s">
         <v>2022</v>
       </c>
       <c r="D97" s="148" t="s">
@@ -31354,14 +31244,14 @@
       <c r="A98" s="32" t="s">
         <v>2549</v>
       </c>
-      <c r="B98" s="288" t="s">
+      <c r="B98" s="287" t="s">
         <v>1288</v>
       </c>
-      <c r="C98" s="255" t="s">
+      <c r="C98" s="254" t="s">
         <v>1949</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="E98" s="30" t="s">
         <v>2680</v>
@@ -31373,25 +31263,25 @@
         <v>201</v>
       </c>
       <c r="H98" s="30" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="I98" s="30" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="J98" s="30" t="s">
         <v>3118</v>
       </c>
       <c r="K98" s="30" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="99" spans="1:11" s="152" customFormat="1">
-      <c r="D99" s="417"/>
-      <c r="E99" s="226"/>
+      <c r="D99" s="416"/>
+      <c r="E99" s="225"/>
     </row>
     <row r="100" spans="1:11" s="152" customFormat="1">
-      <c r="D100" s="417"/>
-      <c r="E100" s="226"/>
+      <c r="D100" s="416"/>
+      <c r="E100" s="225"/>
     </row>
     <row r="101" spans="1:11" s="30" customFormat="1">
       <c r="A101" s="30" t="s">
@@ -31404,10 +31294,10 @@
         <v>2087</v>
       </c>
       <c r="D101" s="30" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="E101" s="30" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="F101" s="30" t="s">
         <v>2178</v>
@@ -31415,14 +31305,14 @@
       <c r="G101" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="H101" s="414" t="s">
+      <c r="H101" s="413" t="s">
         <v>3531</v>
       </c>
       <c r="I101" s="32" t="s">
         <v>3532</v>
       </c>
-      <c r="J101" s="446" t="s">
-        <v>3642</v>
+      <c r="J101" s="445" t="s">
+        <v>3641</v>
       </c>
       <c r="K101" s="30" t="s">
         <v>3533</v>
@@ -31435,10 +31325,10 @@
       <c r="B102" s="147">
         <v>60533053</v>
       </c>
-      <c r="C102" s="423" t="s">
+      <c r="C102" s="422" t="s">
         <v>2159</v>
       </c>
-      <c r="D102" s="390" t="s">
+      <c r="D102" s="389" t="s">
         <v>2389</v>
       </c>
       <c r="E102" s="148"/>
@@ -31450,10 +31340,10 @@
       <c r="B103" s="147">
         <v>64720128</v>
       </c>
-      <c r="C103" s="429" t="s">
+      <c r="C103" s="428" t="s">
         <v>1492</v>
       </c>
-      <c r="D103" s="390" t="s">
+      <c r="D103" s="389" t="s">
         <v>1901</v>
       </c>
       <c r="E103" s="147" t="s">
@@ -31502,24 +31392,24 @@
       <c r="B105" s="147">
         <v>63145336</v>
       </c>
-      <c r="C105" s="423" t="s">
+      <c r="C105" s="422" t="s">
         <v>2038</v>
       </c>
       <c r="D105" s="147" t="s">
         <v>2146</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="284" customFormat="1">
+    <row r="106" spans="1:11" s="283" customFormat="1">
       <c r="A106" s="148" t="s">
         <v>3463</v>
       </c>
       <c r="B106" s="148">
         <v>68971798</v>
       </c>
-      <c r="C106" s="422" t="s">
+      <c r="C106" s="421" t="s">
         <v>2020</v>
       </c>
-      <c r="D106" s="228" t="s">
+      <c r="D106" s="227" t="s">
         <v>2021</v>
       </c>
     </row>
@@ -31551,11 +31441,11 @@
       <c r="I107" s="32" t="s">
         <v>3453</v>
       </c>
-      <c r="J107" s="218" t="s">
+      <c r="J107" s="217" t="s">
         <v>2710</v>
       </c>
-      <c r="K107" s="216" t="s">
-        <v>3621</v>
+      <c r="K107" s="215" t="s">
+        <v>3620</v>
       </c>
     </row>
     <row r="108" spans="1:11" s="147" customFormat="1">
@@ -31565,7 +31455,7 @@
       <c r="B108" s="147">
         <v>65509692</v>
       </c>
-      <c r="C108" s="423" t="s">
+      <c r="C108" s="422" t="s">
         <v>880</v>
       </c>
       <c r="D108" s="147" t="s">
@@ -31574,7 +31464,7 @@
       <c r="E108" s="147" t="s">
         <v>881</v>
       </c>
-      <c r="F108" s="423"/>
+      <c r="F108" s="422"/>
     </row>
     <row r="109" spans="1:11" s="147" customFormat="1">
       <c r="A109" s="147" t="s">
@@ -31583,7 +31473,7 @@
       <c r="B109" s="147" t="s">
         <v>923</v>
       </c>
-      <c r="C109" s="429" t="s">
+      <c r="C109" s="428" t="s">
         <v>883</v>
       </c>
       <c r="D109" s="147" t="s">
@@ -31592,7 +31482,7 @@
       <c r="E109" s="147" t="s">
         <v>881</v>
       </c>
-      <c r="F109" s="423"/>
+      <c r="F109" s="422"/>
     </row>
     <row r="110" spans="1:11" s="30" customFormat="1">
       <c r="A110" s="30" t="s">
@@ -31605,7 +31495,7 @@
         <v>701</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="E110" s="30" t="s">
         <v>1104</v>
@@ -31617,13 +31507,13 @@
         <v>1579</v>
       </c>
       <c r="H110" s="30" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="I110" s="30" t="s">
-        <v>3619</v>
-      </c>
-      <c r="J110" s="414" t="s">
-        <v>3592</v>
+        <v>3618</v>
+      </c>
+      <c r="J110" s="413" t="s">
+        <v>3591</v>
       </c>
       <c r="K110" s="30" t="s">
         <v>2974</v>
@@ -31645,16 +31535,16 @@
       <c r="E111" s="147" t="s">
         <v>879</v>
       </c>
-      <c r="F111" s="423"/>
+      <c r="F111" s="422"/>
     </row>
     <row r="112" spans="1:11" s="148" customFormat="1">
-      <c r="A112" s="228" t="s">
+      <c r="A112" s="227" t="s">
         <v>3141</v>
       </c>
       <c r="B112" s="148">
         <v>67381873</v>
       </c>
-      <c r="C112" s="422" t="s">
+      <c r="C112" s="421" t="s">
         <v>3271</v>
       </c>
       <c r="D112" s="148" t="s">
@@ -31663,11 +31553,11 @@
       <c r="E112" s="148" t="s">
         <v>879</v>
       </c>
-      <c r="F112" s="422"/>
+      <c r="F112" s="421"/>
     </row>
     <row r="113" spans="1:11" s="106" customFormat="1">
-      <c r="A113" s="253" t="s">
-        <v>3591</v>
+      <c r="A113" s="252" t="s">
+        <v>3590</v>
       </c>
       <c r="B113" s="32" t="s">
         <v>1442</v>
@@ -31700,20 +31590,20 @@
         <v>3286</v>
       </c>
     </row>
-    <row r="114" spans="1:11" s="434" customFormat="1">
-      <c r="A114" s="427" t="s">
-        <v>2943</v>
+    <row r="114" spans="1:11" s="433" customFormat="1">
+      <c r="A114" s="426" t="s">
+        <v>158</v>
       </c>
       <c r="B114" s="147">
         <v>64140721</v>
       </c>
-      <c r="C114" s="428" t="s">
+      <c r="C114" s="427" t="s">
         <v>899</v>
       </c>
-      <c r="D114" s="434" t="s">
+      <c r="D114" s="433" t="s">
         <v>3072</v>
       </c>
-      <c r="E114" s="435" t="s">
+      <c r="E114" s="434" t="s">
         <v>46</v>
       </c>
     </row>
@@ -31724,7 +31614,7 @@
       <c r="B115" s="147">
         <v>69964218</v>
       </c>
-      <c r="C115" s="429" t="s">
+      <c r="C115" s="428" t="s">
         <v>1783</v>
       </c>
       <c r="D115" s="147" t="s">
@@ -31745,7 +31635,7 @@
         <v>3527</v>
       </c>
       <c r="E116" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="F116" s="30" t="s">
         <v>1977</v>
@@ -31763,22 +31653,22 @@
         <v>3282</v>
       </c>
       <c r="K116" s="139" t="s">
-        <v>3620</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" s="407" customFormat="1">
-      <c r="D117" s="408"/>
-      <c r="E117" s="386"/>
-    </row>
-    <row r="118" spans="1:11" s="407" customFormat="1">
-      <c r="D118" s="408"/>
-      <c r="E118" s="386"/>
+        <v>3619</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" s="406" customFormat="1">
+      <c r="D117" s="407"/>
+      <c r="E117" s="385"/>
+    </row>
+    <row r="118" spans="1:11" s="406" customFormat="1">
+      <c r="D118" s="407"/>
+      <c r="E118" s="385"/>
     </row>
     <row r="119" spans="1:11" s="30" customFormat="1">
       <c r="A119" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B119" s="288" t="s">
+      <c r="B119" s="287" t="s">
         <v>1974</v>
       </c>
       <c r="C119" s="134" t="s">
@@ -31796,9 +31686,9 @@
       <c r="G119" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="H119" s="446"/>
-      <c r="I119" s="447"/>
-      <c r="J119" s="446"/>
+      <c r="H119" s="445"/>
+      <c r="I119" s="446"/>
+      <c r="J119" s="445"/>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
@@ -31886,7 +31776,7 @@
       <c r="C127" t="s">
         <v>2031</v>
       </c>
-      <c r="D127" s="392" t="s">
+      <c r="D127" s="391" t="s">
         <v>3436</v>
       </c>
       <c r="E127" s="30" t="s">
@@ -31903,7 +31793,7 @@
       <c r="C128" s="22" t="s">
         <v>2032</v>
       </c>
-      <c r="D128" s="392" t="s">
+      <c r="D128" s="391" t="s">
         <v>2063</v>
       </c>
       <c r="E128" s="30" t="s">
@@ -31914,12 +31804,12 @@
       </c>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="308"/>
+      <c r="A129" s="307"/>
       <c r="B129" s="97"/>
       <c r="C129" t="s">
         <v>2033</v>
       </c>
-      <c r="D129" s="392" t="s">
+      <c r="D129" s="391" t="s">
         <v>3437</v>
       </c>
       <c r="E129" s="30" t="s">
@@ -31936,7 +31826,7 @@
       <c r="C130" t="s">
         <v>2034</v>
       </c>
-      <c r="D130" s="392" t="s">
+      <c r="D130" s="391" t="s">
         <v>2028</v>
       </c>
       <c r="E130" s="30" t="s">
@@ -31953,7 +31843,7 @@
       <c r="C131" s="3" t="s">
         <v>3082</v>
       </c>
-      <c r="D131" s="392" t="s">
+      <c r="D131" s="391" t="s">
         <v>3138</v>
       </c>
       <c r="E131" s="30" t="s">
@@ -31970,7 +31860,7 @@
       <c r="C132" t="s">
         <v>2347</v>
       </c>
-      <c r="D132" s="392" t="s">
+      <c r="D132" s="391" t="s">
         <v>2863</v>
       </c>
       <c r="E132" s="30" t="s">
@@ -31981,7 +31871,7 @@
       <c r="C133" s="7" t="s">
         <v>2035</v>
       </c>
-      <c r="D133" s="392" t="s">
+      <c r="D133" s="391" t="s">
         <v>3477</v>
       </c>
       <c r="E133" s="30" t="s">
@@ -31989,16 +31879,16 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="285" t="s">
+      <c r="A134" s="284" t="s">
         <v>3119</v>
       </c>
-      <c r="B134" s="285" t="s">
+      <c r="B134" s="284" t="s">
         <v>1215</v>
       </c>
       <c r="C134" t="s">
         <v>2036</v>
       </c>
-      <c r="D134" s="392" t="s">
+      <c r="D134" s="391" t="s">
         <v>2037</v>
       </c>
       <c r="E134" s="30" t="s">
@@ -32020,7 +31910,7 @@
       <c r="C137" s="22" t="s">
         <v>1348</v>
       </c>
-      <c r="D137" s="392" t="s">
+      <c r="D137" s="391" t="s">
         <v>2109</v>
       </c>
       <c r="E137" s="30" t="s">
@@ -32040,7 +31930,7 @@
       <c r="C138" s="22" t="s">
         <v>1349</v>
       </c>
-      <c r="D138" s="392" t="s">
+      <c r="D138" s="391" t="s">
         <v>2403</v>
       </c>
       <c r="E138" s="30" t="s">
@@ -32060,7 +31950,7 @@
       <c r="C139" s="22" t="s">
         <v>2669</v>
       </c>
-      <c r="D139" s="392" t="s">
+      <c r="D139" s="391" t="s">
         <v>3083</v>
       </c>
       <c r="E139" s="30" t="s">
@@ -32077,7 +31967,7 @@
       <c r="D140" s="22" t="s">
         <v>2577</v>
       </c>
-      <c r="E140" s="413" t="s">
+      <c r="E140" s="412" t="s">
         <v>2835</v>
       </c>
       <c r="F140" t="s">
@@ -32094,7 +31984,7 @@
       <c r="C141" t="s">
         <v>1617</v>
       </c>
-      <c r="D141" s="392" t="s">
+      <c r="D141" s="391" t="s">
         <v>2578</v>
       </c>
       <c r="E141" s="30" t="s">
@@ -32114,7 +32004,7 @@
       <c r="C142" s="3" t="s">
         <v>2690</v>
       </c>
-      <c r="D142" s="392" t="s">
+      <c r="D142" s="391" t="s">
         <v>2691</v>
       </c>
       <c r="E142" s="30" t="s">
@@ -32134,7 +32024,7 @@
       <c r="C143" t="s">
         <v>1774</v>
       </c>
-      <c r="D143" s="392" t="s">
+      <c r="D143" s="391" t="s">
         <v>1773</v>
       </c>
       <c r="E143" s="30" t="s">
@@ -32154,10 +32044,10 @@
       <c r="C144" t="s">
         <v>2385</v>
       </c>
-      <c r="D144" s="392" t="s">
+      <c r="D144" s="391" t="s">
         <v>2386</v>
       </c>
-      <c r="E144" s="413" t="s">
+      <c r="E144" s="412" t="s">
         <v>2815</v>
       </c>
       <c r="F144" t="s">
@@ -32174,7 +32064,7 @@
       <c r="C146" t="s">
         <v>2501</v>
       </c>
-      <c r="D146" s="392" t="s">
+      <c r="D146" s="391" t="s">
         <v>2502</v>
       </c>
       <c r="E146" s="30" t="s">
@@ -32184,8 +32074,8 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="149" spans="1:6" s="286" customFormat="1" ht="23.5">
-      <c r="C149" s="286" t="s">
+    <row r="149" spans="1:6" s="285" customFormat="1" ht="23.5">
+      <c r="C149" s="285" t="s">
         <v>2046</v>
       </c>
     </row>
@@ -32199,7 +32089,7 @@
       <c r="C150" t="s">
         <v>2045</v>
       </c>
-      <c r="D150" s="392" t="s">
+      <c r="D150" s="391" t="s">
         <v>2209</v>
       </c>
       <c r="E150" s="30" t="s">
@@ -32219,7 +32109,7 @@
       <c r="C151" t="s">
         <v>2048</v>
       </c>
-      <c r="D151" s="392" t="s">
+      <c r="D151" s="391" t="s">
         <v>2948</v>
       </c>
       <c r="E151" s="30" t="s">
@@ -32239,7 +32129,7 @@
       <c r="C152" s="21" t="s">
         <v>2367</v>
       </c>
-      <c r="D152" s="392" t="s">
+      <c r="D152" s="391" t="s">
         <v>2956</v>
       </c>
       <c r="E152" s="30" t="s">
@@ -32261,10 +32151,10 @@
       <c r="C156" s="57" t="s">
         <v>2810</v>
       </c>
-      <c r="D156" s="392" t="s">
+      <c r="D156" s="391" t="s">
         <v>3438</v>
       </c>
-      <c r="E156" s="413" t="s">
+      <c r="E156" s="412" t="s">
         <v>2851</v>
       </c>
     </row>
@@ -32278,10 +32168,10 @@
       <c r="C157" s="4" t="s">
         <v>2152</v>
       </c>
-      <c r="D157" s="392" t="s">
+      <c r="D157" s="391" t="s">
         <v>2890</v>
       </c>
-      <c r="E157" s="413" t="s">
+      <c r="E157" s="412" t="s">
         <v>2851</v>
       </c>
     </row>
@@ -32295,10 +32185,10 @@
       <c r="C158" s="6" t="s">
         <v>1583</v>
       </c>
-      <c r="D158" s="392" t="s">
+      <c r="D158" s="391" t="s">
         <v>1786</v>
       </c>
-      <c r="E158" s="413" t="s">
+      <c r="E158" s="412" t="s">
         <v>2851</v>
       </c>
     </row>
@@ -32312,15 +32202,15 @@
       <c r="C159" s="6" t="s">
         <v>1818</v>
       </c>
-      <c r="D159" s="392" t="s">
+      <c r="D159" s="391" t="s">
         <v>2060</v>
       </c>
-      <c r="E159" s="413" t="s">
+      <c r="E159" s="412" t="s">
         <v>2851</v>
       </c>
     </row>
-    <row r="161" spans="1:6" s="327" customFormat="1" ht="23.5">
-      <c r="C161" s="327" t="s">
+    <row r="161" spans="1:6" s="326" customFormat="1" ht="23.5">
+      <c r="C161" s="326" t="s">
         <v>2726</v>
       </c>
     </row>
@@ -32336,7 +32226,7 @@
       <c r="C163" s="1" t="s">
         <v>3181</v>
       </c>
-      <c r="D163" s="392" t="s">
+      <c r="D163" s="391" t="s">
         <v>3183</v>
       </c>
     </row>
@@ -32350,7 +32240,7 @@
       <c r="C165" t="s">
         <v>2343</v>
       </c>
-      <c r="D165" s="392" t="s">
+      <c r="D165" s="391" t="s">
         <v>3158</v>
       </c>
       <c r="E165" s="30" t="s">
@@ -32370,7 +32260,7 @@
       <c r="C166" t="s">
         <v>2346</v>
       </c>
-      <c r="D166" s="392" t="s">
+      <c r="D166" s="391" t="s">
         <v>2507</v>
       </c>
       <c r="E166" s="30" t="s">
@@ -32387,7 +32277,7 @@
       <c r="C167" t="s">
         <v>2345</v>
       </c>
-      <c r="D167" s="392" t="s">
+      <c r="D167" s="391" t="s">
         <v>3212</v>
       </c>
       <c r="E167" s="30" t="s">
@@ -32404,7 +32294,7 @@
       <c r="C168" t="s">
         <v>2355</v>
       </c>
-      <c r="D168" s="392" t="s">
+      <c r="D168" s="391" t="s">
         <v>2864</v>
       </c>
       <c r="E168" s="30" t="s">
@@ -32412,21 +32302,24 @@
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="A169" s="97" t="s">
-        <v>1195</v>
+      <c r="A169" s="440" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B169">
+        <v>62491046</v>
       </c>
       <c r="C169" t="s">
         <v>2356</v>
       </c>
-      <c r="D169" s="392" t="s">
-        <v>3611</v>
+      <c r="D169" s="391" t="s">
+        <v>3610</v>
       </c>
       <c r="E169" s="30" t="s">
         <v>3200</v>
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="441" t="s">
+      <c r="A170" s="440" t="s">
         <v>2554</v>
       </c>
       <c r="B170" t="s">
@@ -32435,7 +32328,7 @@
       <c r="C170" t="s">
         <v>2357</v>
       </c>
-      <c r="D170" s="392" t="s">
+      <c r="D170" s="391" t="s">
         <v>2687</v>
       </c>
       <c r="E170" s="30" t="s">
@@ -32452,7 +32345,7 @@
       <c r="C171" s="21" t="s">
         <v>2358</v>
       </c>
-      <c r="D171" s="392" t="s">
+      <c r="D171" s="391" t="s">
         <v>2957</v>
       </c>
       <c r="E171" s="30" t="s">
@@ -32469,7 +32362,7 @@
       <c r="C172" t="s">
         <v>2727</v>
       </c>
-      <c r="D172" s="392" t="s">
+      <c r="D172" s="391" t="s">
         <v>2827</v>
       </c>
       <c r="E172" s="30" t="s">
@@ -32486,7 +32379,7 @@
       <c r="C173" t="s">
         <v>2729</v>
       </c>
-      <c r="D173" s="392" t="s">
+      <c r="D173" s="391" t="s">
         <v>2728</v>
       </c>
       <c r="E173" s="30" t="s">
@@ -32503,7 +32396,7 @@
       <c r="C174" t="s">
         <v>2868</v>
       </c>
-      <c r="D174" s="392" t="s">
+      <c r="D174" s="391" t="s">
         <v>2855</v>
       </c>
       <c r="E174" s="30" t="s">
@@ -32520,7 +32413,7 @@
       <c r="C175" t="s">
         <v>2730</v>
       </c>
-      <c r="D175" s="392" t="s">
+      <c r="D175" s="391" t="s">
         <v>3372</v>
       </c>
       <c r="E175" s="30" t="s">
@@ -32537,7 +32430,7 @@
       <c r="C176" t="s">
         <v>3516</v>
       </c>
-      <c r="D176" s="392" t="s">
+      <c r="D176" s="391" t="s">
         <v>3535</v>
       </c>
       <c r="E176" s="30" t="s">
@@ -32554,7 +32447,7 @@
       <c r="C177" t="s">
         <v>3350</v>
       </c>
-      <c r="D177" s="392" t="s">
+      <c r="D177" s="391" t="s">
         <v>2688</v>
       </c>
       <c r="E177" s="30" t="s">
@@ -32571,7 +32464,7 @@
       <c r="C178" t="s">
         <v>2405</v>
       </c>
-      <c r="D178" s="392" t="s">
+      <c r="D178" s="391" t="s">
         <v>2404</v>
       </c>
       <c r="E178" s="30" t="s">
@@ -32588,7 +32481,7 @@
       <c r="C179" t="s">
         <v>2406</v>
       </c>
-      <c r="D179" s="392" t="s">
+      <c r="D179" s="391" t="s">
         <v>2404</v>
       </c>
       <c r="E179" s="30" t="s">
@@ -32605,7 +32498,7 @@
       <c r="C180" t="s">
         <v>2845</v>
       </c>
-      <c r="D180" s="392" t="s">
+      <c r="D180" s="391" t="s">
         <v>2870</v>
       </c>
       <c r="E180" s="30" t="s">
@@ -32622,7 +32515,7 @@
       <c r="C181" s="21" t="s">
         <v>3087</v>
       </c>
-      <c r="D181" s="392" t="s">
+      <c r="D181" s="391" t="s">
         <v>3086</v>
       </c>
       <c r="E181" s="30" t="s">
@@ -32639,7 +32532,7 @@
       <c r="C182" t="s">
         <v>2453</v>
       </c>
-      <c r="D182" s="392" t="s">
+      <c r="D182" s="391" t="s">
         <v>3167</v>
       </c>
       <c r="E182" s="30" t="s">
@@ -32656,7 +32549,7 @@
       <c r="C183" t="s">
         <v>2456</v>
       </c>
-      <c r="D183" s="392" t="s">
+      <c r="D183" s="391" t="s">
         <v>2685</v>
       </c>
       <c r="E183" s="30" t="s">
@@ -32673,7 +32566,7 @@
       <c r="C184" t="s">
         <v>2454</v>
       </c>
-      <c r="D184" s="392" t="s">
+      <c r="D184" s="391" t="s">
         <v>2455</v>
       </c>
       <c r="E184" s="30" t="s">
@@ -32690,7 +32583,7 @@
       <c r="C185" t="s">
         <v>2468</v>
       </c>
-      <c r="D185" s="392" t="s">
+      <c r="D185" s="391" t="s">
         <v>2689</v>
       </c>
       <c r="E185" s="30" t="s">
@@ -32707,7 +32600,7 @@
       <c r="C186" t="s">
         <v>2469</v>
       </c>
-      <c r="D186" s="392" t="s">
+      <c r="D186" s="391" t="s">
         <v>2471</v>
       </c>
       <c r="E186" s="30" t="s">
@@ -32724,7 +32617,7 @@
       <c r="C187" t="s">
         <v>2470</v>
       </c>
-      <c r="D187" s="392" t="s">
+      <c r="D187" s="391" t="s">
         <v>3201</v>
       </c>
       <c r="E187" s="30" t="s">
@@ -32741,7 +32634,7 @@
       <c r="C188" t="s">
         <v>3173</v>
       </c>
-      <c r="D188" s="392" t="s">
+      <c r="D188" s="391" t="s">
         <v>3174</v>
       </c>
       <c r="E188" s="30" t="s">
@@ -32758,7 +32651,7 @@
       <c r="C189" s="1" t="s">
         <v>3175</v>
       </c>
-      <c r="D189" s="221" t="s">
+      <c r="D189" s="220" t="s">
         <v>3174</v>
       </c>
       <c r="E189" s="30" t="s">
@@ -32775,7 +32668,7 @@
       <c r="C190" s="3" t="s">
         <v>3176</v>
       </c>
-      <c r="D190" s="221" t="s">
+      <c r="D190" s="220" t="s">
         <v>3174</v>
       </c>
       <c r="E190" s="30" t="s">
@@ -32792,7 +32685,7 @@
       <c r="C191" s="3" t="s">
         <v>3177</v>
       </c>
-      <c r="D191" s="221" t="s">
+      <c r="D191" s="220" t="s">
         <v>3213</v>
       </c>
       <c r="E191" s="30" t="s">
@@ -32809,7 +32702,7 @@
       <c r="C192" s="22" t="s">
         <v>3178</v>
       </c>
-      <c r="D192" s="221" t="s">
+      <c r="D192" s="220" t="s">
         <v>3174</v>
       </c>
       <c r="E192" s="30" t="s">
@@ -32826,7 +32719,7 @@
       <c r="C193" t="s">
         <v>3221</v>
       </c>
-      <c r="D193" s="392" t="s">
+      <c r="D193" s="391" t="s">
         <v>3222</v>
       </c>
       <c r="E193" s="30" t="s">
@@ -32843,7 +32736,7 @@
       <c r="C194" t="s">
         <v>3223</v>
       </c>
-      <c r="D194" s="392" t="s">
+      <c r="D194" s="391" t="s">
         <v>3222</v>
       </c>
       <c r="E194" s="30" t="s">
@@ -32860,7 +32753,7 @@
       <c r="C195" s="3" t="s">
         <v>3224</v>
       </c>
-      <c r="D195" s="221" t="s">
+      <c r="D195" s="220" t="s">
         <v>3222</v>
       </c>
       <c r="E195" s="30" t="s">
@@ -32877,7 +32770,7 @@
       <c r="C196" t="s">
         <v>3225</v>
       </c>
-      <c r="D196" s="392" t="s">
+      <c r="D196" s="391" t="s">
         <v>3396</v>
       </c>
       <c r="E196" s="30" t="s">
@@ -32894,7 +32787,7 @@
       <c r="C197" t="s">
         <v>3363</v>
       </c>
-      <c r="D197" s="392" t="s">
+      <c r="D197" s="391" t="s">
         <v>3399</v>
       </c>
       <c r="E197" s="30" t="s">
@@ -32911,7 +32804,7 @@
       <c r="C198" t="s">
         <v>3297</v>
       </c>
-      <c r="D198" s="392" t="s">
+      <c r="D198" s="391" t="s">
         <v>3402</v>
       </c>
       <c r="E198" s="30" t="s">
@@ -32928,7 +32821,7 @@
       <c r="C199" t="s">
         <v>3298</v>
       </c>
-      <c r="D199" s="392" t="s">
+      <c r="D199" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E199" s="30" t="s">
@@ -32945,7 +32838,7 @@
       <c r="C200" t="s">
         <v>3299</v>
       </c>
-      <c r="D200" s="392" t="s">
+      <c r="D200" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E200" s="30" t="s">
@@ -32962,7 +32855,7 @@
       <c r="C201" t="s">
         <v>3300</v>
       </c>
-      <c r="D201" s="392" t="s">
+      <c r="D201" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E201" s="30" t="s">
@@ -32979,7 +32872,7 @@
       <c r="C202" t="s">
         <v>3301</v>
       </c>
-      <c r="D202" s="392" t="s">
+      <c r="D202" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E202" s="30" t="s">
@@ -32996,7 +32889,7 @@
       <c r="C203" t="s">
         <v>3302</v>
       </c>
-      <c r="D203" s="392" t="s">
+      <c r="D203" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E203" s="30" t="s">
@@ -33013,7 +32906,7 @@
       <c r="C204" t="s">
         <v>3303</v>
       </c>
-      <c r="D204" s="392" t="s">
+      <c r="D204" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E204" s="30" t="s">
@@ -33030,7 +32923,7 @@
       <c r="C205" s="1" t="s">
         <v>3400</v>
       </c>
-      <c r="D205" s="392" t="s">
+      <c r="D205" s="391" t="s">
         <v>3401</v>
       </c>
       <c r="E205" s="30" t="s">
@@ -33047,7 +32940,7 @@
       <c r="C206" t="s">
         <v>3304</v>
       </c>
-      <c r="D206" s="392" t="s">
+      <c r="D206" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E206" s="30" t="s">
@@ -33064,18 +32957,18 @@
       <c r="C207" t="s">
         <v>3305</v>
       </c>
-      <c r="D207" s="392" t="s">
+      <c r="D207" s="391" t="s">
         <v>3306</v>
       </c>
       <c r="E207" s="30" t="s">
         <v>3307</v>
       </c>
     </row>
-    <row r="210" spans="1:5" s="411" customFormat="1" ht="23.5">
-      <c r="C210" s="411" t="s">
+    <row r="210" spans="1:5" s="410" customFormat="1" ht="23.5">
+      <c r="C210" s="410" t="s">
         <v>3343</v>
       </c>
-      <c r="D210" s="411">
+      <c r="D210" s="410">
         <v>51957149094</v>
       </c>
     </row>
@@ -33089,7 +32982,7 @@
       <c r="C211" t="s">
         <v>3364</v>
       </c>
-      <c r="D211" s="392" t="s">
+      <c r="D211" s="391" t="s">
         <v>3365</v>
       </c>
       <c r="E211" s="30" t="s">
@@ -33106,7 +32999,7 @@
       <c r="C212" t="s">
         <v>3344</v>
       </c>
-      <c r="D212" s="392" t="s">
+      <c r="D212" s="391" t="s">
         <v>3357</v>
       </c>
       <c r="E212" s="30" t="s">
@@ -33123,7 +33016,7 @@
       <c r="C213" s="21" t="s">
         <v>3366</v>
       </c>
-      <c r="D213" s="392" t="s">
+      <c r="D213" s="391" t="s">
         <v>3489</v>
       </c>
       <c r="E213" s="30" t="s">
@@ -33140,7 +33033,7 @@
       <c r="C214" t="s">
         <v>3345</v>
       </c>
-      <c r="D214" s="392" t="s">
+      <c r="D214" s="391" t="s">
         <v>3358</v>
       </c>
       <c r="E214" s="30" t="s">
@@ -33157,7 +33050,7 @@
       <c r="C215" t="s">
         <v>3346</v>
       </c>
-      <c r="D215" s="392" t="s">
+      <c r="D215" s="391" t="s">
         <v>3478</v>
       </c>
       <c r="E215" s="30" t="s">
@@ -33174,7 +33067,7 @@
       <c r="C216" t="s">
         <v>3488</v>
       </c>
-      <c r="D216" s="392" t="s">
+      <c r="D216" s="391" t="s">
         <v>3502</v>
       </c>
       <c r="E216" s="30" t="s">
@@ -33191,7 +33084,7 @@
       <c r="C217" t="s">
         <v>3347</v>
       </c>
-      <c r="D217" s="392" t="s">
+      <c r="D217" s="391" t="s">
         <v>3484</v>
       </c>
       <c r="E217" s="30" t="s">
@@ -33208,7 +33101,7 @@
       <c r="C218" t="s">
         <v>3348</v>
       </c>
-      <c r="D218" s="392" t="s">
+      <c r="D218" s="391" t="s">
         <v>3501</v>
       </c>
       <c r="E218" s="30" t="s">
@@ -33225,7 +33118,7 @@
       <c r="C219" t="s">
         <v>3515</v>
       </c>
-      <c r="D219" s="392" t="s">
+      <c r="D219" s="391" t="s">
         <v>3518</v>
       </c>
       <c r="E219" s="30" t="s">
@@ -33242,7 +33135,7 @@
       <c r="C220" t="s">
         <v>3519</v>
       </c>
-      <c r="D220" s="392" t="s">
+      <c r="D220" s="391" t="s">
         <v>3520</v>
       </c>
       <c r="E220" s="30" t="s">
@@ -33274,10 +33167,10 @@
         <v>65583706</v>
       </c>
       <c r="C222" t="s">
-        <v>3612</v>
-      </c>
-      <c r="D222" s="392" t="s">
-        <v>3614</v>
+        <v>3611</v>
+      </c>
+      <c r="D222" s="391" t="s">
+        <v>3613</v>
       </c>
       <c r="E222" s="30" t="s">
         <v>3551</v>
@@ -33303,10 +33196,10 @@
     <row r="224" spans="1:5">
       <c r="A224" s="97"/>
       <c r="C224" t="s">
-        <v>3613</v>
-      </c>
-      <c r="D224" s="392" t="s">
-        <v>3616</v>
+        <v>3612</v>
+      </c>
+      <c r="D224" s="391" t="s">
+        <v>3615</v>
       </c>
       <c r="E224" s="30" t="s">
         <v>3551</v>
@@ -33323,7 +33216,7 @@
         <v>3549</v>
       </c>
       <c r="D225" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="E225" s="30" t="s">
         <v>3551</v>
@@ -33379,40 +33272,40 @@
       <c r="D241" s="22"/>
     </row>
     <row r="242" spans="1:5">
-      <c r="C242" s="300"/>
+      <c r="C242" s="299"/>
     </row>
     <row r="243" spans="1:5">
-      <c r="C243" s="300"/>
+      <c r="C243" s="299"/>
     </row>
     <row r="244" spans="1:5">
-      <c r="C244" s="221"/>
+      <c r="C244" s="220"/>
     </row>
     <row r="245" spans="1:5">
-      <c r="C245" s="300"/>
+      <c r="C245" s="299"/>
     </row>
     <row r="246" spans="1:5">
-      <c r="C246" s="300"/>
+      <c r="C246" s="299"/>
     </row>
     <row r="247" spans="1:5">
-      <c r="C247" s="300"/>
+      <c r="C247" s="299"/>
     </row>
     <row r="248" spans="1:5">
-      <c r="C248" s="300"/>
+      <c r="C248" s="299"/>
     </row>
     <row r="249" spans="1:5">
-      <c r="C249" s="300"/>
+      <c r="C249" s="299"/>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="4"/>
-      <c r="C250" s="300"/>
-    </row>
-    <row r="251" spans="1:5" s="382" customFormat="1" ht="23.5">
-      <c r="B251" s="382" t="s">
+      <c r="C250" s="299"/>
+    </row>
+    <row r="251" spans="1:5" s="381" customFormat="1" ht="23.5">
+      <c r="B251" s="381" t="s">
         <v>3078</v>
       </c>
-      <c r="C251" s="383"/>
-      <c r="D251" s="393"/>
-      <c r="E251" s="385"/>
+      <c r="C251" s="382"/>
+      <c r="D251" s="392"/>
+      <c r="E251" s="384"/>
     </row>
     <row r="252" spans="1:5">
       <c r="C252" t="s">
@@ -33442,7 +33335,7 @@
       <c r="C255" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="D255" s="392" t="s">
+      <c r="D255" s="391" t="s">
         <v>2118</v>
       </c>
     </row>
@@ -33501,7 +33394,7 @@
         <v>2043</v>
       </c>
       <c r="C262" s="7"/>
-      <c r="D262" s="394"/>
+      <c r="D262" s="393"/>
       <c r="E262" s="33"/>
       <c r="F262" s="7"/>
     </row>
@@ -33532,7 +33425,7 @@
       <c r="C311" s="138" t="s">
         <v>876</v>
       </c>
-      <c r="D311" s="391" t="s">
+      <c r="D311" s="390" t="s">
         <v>877</v>
       </c>
       <c r="E311" s="145" t="s">
@@ -33570,7 +33463,7 @@
       <c r="C313" s="138" t="s">
         <v>893</v>
       </c>
-      <c r="D313" s="391" t="s">
+      <c r="D313" s="390" t="s">
         <v>909</v>
       </c>
       <c r="E313" s="145" t="s">
@@ -33583,21 +33476,21 @@
         <v>93</v>
       </c>
     </row>
-    <row r="314" spans="1:8" s="230" customFormat="1">
-      <c r="C314" s="231" t="s">
+    <row r="314" spans="1:8" s="229" customFormat="1">
+      <c r="C314" s="230" t="s">
         <v>1170</v>
       </c>
-      <c r="D314" s="230" t="s">
+      <c r="D314" s="229" t="s">
         <v>1171</v>
       </c>
-      <c r="E314" s="232"/>
-      <c r="F314" s="230" t="s">
+      <c r="E314" s="231"/>
+      <c r="F314" s="229" t="s">
         <v>88</v>
       </c>
-      <c r="G314" s="230" t="s">
+      <c r="G314" s="229" t="s">
         <v>202</v>
       </c>
-      <c r="H314" s="232"/>
+      <c r="H314" s="231"/>
     </row>
     <row r="315" spans="1:8" s="82" customFormat="1" ht="13.5" customHeight="1">
       <c r="A315" s="82" t="s">
@@ -34404,7 +34297,7 @@
       <c r="C359" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D359" s="392" t="s">
+      <c r="D359" s="391" t="s">
         <v>133</v>
       </c>
       <c r="E359" s="30" t="s">
@@ -34522,7 +34415,7 @@
       <c r="C365" s="170" t="s">
         <v>614</v>
       </c>
-      <c r="D365" s="395" t="s">
+      <c r="D365" s="394" t="s">
         <v>995</v>
       </c>
       <c r="E365" s="77" t="s">
@@ -34624,27 +34517,27 @@
         <v>217</v>
       </c>
     </row>
-    <row r="372" spans="1:14" s="208" customFormat="1">
+    <row r="372" spans="1:14" s="207" customFormat="1">
       <c r="A372" s="185"/>
-      <c r="C372" s="209" t="s">
+      <c r="C372" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="D372" s="208" t="s">
+      <c r="D372" s="207" t="s">
         <v>874</v>
       </c>
-      <c r="E372" s="210" t="s">
+      <c r="E372" s="209" t="s">
         <v>1112</v>
       </c>
-      <c r="F372" s="208" t="s">
+      <c r="F372" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="G372" s="208" t="s">
+      <c r="G372" s="207" t="s">
         <v>243</v>
       </c>
       <c r="J372" s="185"/>
-      <c r="K372" s="211"/>
-      <c r="L372" s="212"/>
-      <c r="N372" s="213"/>
+      <c r="K372" s="210"/>
+      <c r="L372" s="211"/>
+      <c r="N372" s="212"/>
     </row>
     <row r="373" spans="1:14" s="82" customFormat="1">
       <c r="C373" s="93" t="s">
@@ -34712,7 +34605,7 @@
       <c r="C376" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="D376" s="395" t="s">
+      <c r="D376" s="394" t="s">
         <v>971</v>
       </c>
       <c r="E376" s="77"/>
@@ -34781,7 +34674,7 @@
       <c r="C380" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D380" s="394"/>
+      <c r="D380" s="393"/>
       <c r="E380" s="33"/>
     </row>
     <row r="381" spans="1:14" ht="15.4" customHeight="1">
@@ -34848,7 +34741,7 @@
       <c r="C384" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D384" s="392" t="s">
+      <c r="D384" s="391" t="s">
         <v>192</v>
       </c>
     </row>
@@ -34893,7 +34786,7 @@
       <c r="C388" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D388" s="392" t="s">
+      <c r="D388" s="391" t="s">
         <v>329</v>
       </c>
       <c r="E388" s="30" t="s">
@@ -34916,7 +34809,7 @@
       <c r="C389" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D389" s="392" t="s">
+      <c r="D389" s="391" t="s">
         <v>120</v>
       </c>
       <c r="E389" s="30" t="s">
@@ -34935,7 +34828,7 @@
       <c r="C390" t="s">
         <v>236</v>
       </c>
-      <c r="D390" s="392" t="s">
+      <c r="D390" s="391" t="s">
         <v>337</v>
       </c>
       <c r="E390" s="30"/>
@@ -34955,7 +34848,7 @@
       <c r="C391" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D391" s="392" t="s">
+      <c r="D391" s="391" t="s">
         <v>173</v>
       </c>
       <c r="E391" s="30" t="s">
@@ -34998,7 +34891,7 @@
       <c r="C393" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D393" s="392" t="s">
+      <c r="D393" s="391" t="s">
         <v>176</v>
       </c>
       <c r="E393" s="30" t="s">
@@ -35208,7 +35101,7 @@
       <c r="C402" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D402" s="392" t="s">
+      <c r="D402" s="391" t="s">
         <v>211</v>
       </c>
       <c r="E402" s="30" t="s">
@@ -35235,7 +35128,7 @@
       <c r="C403" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="D403" s="392" t="s">
+      <c r="D403" s="391" t="s">
         <v>213</v>
       </c>
       <c r="E403" s="30" t="s">
@@ -35255,7 +35148,7 @@
       <c r="C404" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D404" s="392" t="s">
+      <c r="D404" s="391" t="s">
         <v>215</v>
       </c>
       <c r="E404" s="30"/>
@@ -35367,7 +35260,7 @@
       <c r="H409" s="90"/>
     </row>
     <row r="410" spans="1:9" s="82" customFormat="1">
-      <c r="B410" s="254" t="s">
+      <c r="B410" s="253" t="s">
         <v>1521</v>
       </c>
       <c r="C410" s="81" t="s">
@@ -35405,13 +35298,13 @@
       </c>
     </row>
     <row r="412" spans="1:9" s="32" customFormat="1">
-      <c r="C412" s="227" t="s">
+      <c r="C412" s="226" t="s">
         <v>1186</v>
       </c>
       <c r="D412" s="32" t="s">
         <v>1187</v>
       </c>
-      <c r="E412" s="215" t="s">
+      <c r="E412" s="214" t="s">
         <v>1224</v>
       </c>
       <c r="F412" s="32" t="s">
@@ -35431,7 +35324,7 @@
       <c r="C413" t="s">
         <v>10</v>
       </c>
-      <c r="D413" s="392" t="s">
+      <c r="D413" s="391" t="s">
         <v>11</v>
       </c>
       <c r="E413" s="30" t="s">
@@ -35466,7 +35359,7 @@
       <c r="C415" s="115" t="s">
         <v>1632</v>
       </c>
-      <c r="D415" s="396" t="s">
+      <c r="D415" s="395" t="s">
         <v>1633</v>
       </c>
       <c r="E415" s="95" t="s">
@@ -35480,7 +35373,7 @@
       <c r="C416" s="115" t="s">
         <v>1632</v>
       </c>
-      <c r="D416" s="396" t="s">
+      <c r="D416" s="395" t="s">
         <v>1639</v>
       </c>
       <c r="E416" s="95" t="s">
@@ -35497,7 +35390,7 @@
       <c r="C417" s="114" t="s">
         <v>1663</v>
       </c>
-      <c r="D417" s="396" t="s">
+      <c r="D417" s="395" t="s">
         <v>1664</v>
       </c>
       <c r="E417" s="95" t="s">
@@ -35514,7 +35407,7 @@
       <c r="C418" s="114" t="s">
         <v>1663</v>
       </c>
-      <c r="D418" s="397" t="s">
+      <c r="D418" s="396" t="s">
         <v>1670</v>
       </c>
       <c r="E418" s="95" t="s">
@@ -35531,7 +35424,7 @@
       <c r="C419" s="114" t="s">
         <v>1663</v>
       </c>
-      <c r="D419" s="397" t="s">
+      <c r="D419" s="396" t="s">
         <v>1702</v>
       </c>
       <c r="E419" s="95" t="s">
@@ -35548,7 +35441,7 @@
       <c r="C420" s="114" t="s">
         <v>1663</v>
       </c>
-      <c r="D420" s="397" t="s">
+      <c r="D420" s="396" t="s">
         <v>1796</v>
       </c>
       <c r="E420" s="95" t="s">
@@ -35565,7 +35458,7 @@
       <c r="C421" s="114" t="s">
         <v>1848</v>
       </c>
-      <c r="D421" s="396" t="s">
+      <c r="D421" s="395" t="s">
         <v>1849</v>
       </c>
       <c r="E421" s="95"/>
@@ -35581,7 +35474,7 @@
       <c r="C422" s="114" t="s">
         <v>1848</v>
       </c>
-      <c r="D422" s="396" t="s">
+      <c r="D422" s="395" t="s">
         <v>1895</v>
       </c>
       <c r="E422" s="95" t="s">
@@ -35593,7 +35486,7 @@
       <c r="A424" s="7"/>
       <c r="B424" s="7"/>
       <c r="C424" s="8"/>
-      <c r="D424" s="394"/>
+      <c r="D424" s="393"/>
       <c r="E424" s="33"/>
       <c r="F424" s="7"/>
     </row>
@@ -35637,14 +35530,14 @@
         <v>796</v>
       </c>
       <c r="C427" s="111"/>
-      <c r="D427" s="398"/>
+      <c r="D427" s="397"/>
       <c r="F427" s="111"/>
     </row>
     <row r="428" spans="1:6" s="111" customFormat="1">
       <c r="A428"/>
       <c r="B428"/>
       <c r="C428"/>
-      <c r="D428" s="392"/>
+      <c r="D428" s="391"/>
       <c r="E428" s="30"/>
       <c r="F428"/>
     </row>
@@ -35672,7 +35565,7 @@
       <c r="C431" s="111" t="s">
         <v>549</v>
       </c>
-      <c r="D431" s="398" t="s">
+      <c r="D431" s="397" t="s">
         <v>568</v>
       </c>
       <c r="E431" s="112"/>
@@ -35707,7 +35600,7 @@
       <c r="C434" s="111" t="s">
         <v>671</v>
       </c>
-      <c r="D434" s="398"/>
+      <c r="D434" s="397"/>
       <c r="E434" s="112" t="s">
         <v>780</v>
       </c>
@@ -35739,7 +35632,7 @@
       <c r="B437" s="111" t="s">
         <v>579</v>
       </c>
-      <c r="D437" s="398"/>
+      <c r="D437" s="397"/>
       <c r="E437" s="112"/>
     </row>
     <row r="439" spans="1:6" s="112" customFormat="1" ht="11.15" customHeight="1">
@@ -35766,7 +35659,7 @@
       <c r="C440" s="111" t="s">
         <v>356</v>
       </c>
-      <c r="D440" s="398"/>
+      <c r="D440" s="397"/>
       <c r="E440" s="112"/>
     </row>
     <row r="442" spans="1:6" s="112" customFormat="1" ht="11.15" customHeight="1">
@@ -35799,7 +35692,7 @@
       <c r="C443" s="111" t="s">
         <v>676</v>
       </c>
-      <c r="D443" s="398" t="s">
+      <c r="D443" s="397" t="s">
         <v>677</v>
       </c>
       <c r="E443" s="112" t="s">
@@ -35832,7 +35725,7 @@
       </c>
       <c r="B446" s="111"/>
       <c r="C446" s="111"/>
-      <c r="D446" s="398"/>
+      <c r="D446" s="397"/>
       <c r="E446" s="112"/>
       <c r="F446" s="111"/>
     </row>
@@ -35862,7 +35755,7 @@
       </c>
       <c r="B449" s="111"/>
       <c r="C449" s="111"/>
-      <c r="D449" s="398"/>
+      <c r="D449" s="397"/>
       <c r="E449" s="112"/>
       <c r="F449" s="111"/>
     </row>
@@ -36003,7 +35896,7 @@
     <hyperlink ref="C37" r:id="rId132" xr:uid="{3174E757-D351-46EF-8FF8-36AD7447E0E4}"/>
     <hyperlink ref="C38" r:id="rId133" xr:uid="{A2DD97D4-49A4-41AD-87E6-3EACF84B6039}"/>
     <hyperlink ref="C70" r:id="rId134" xr:uid="{677754D0-C565-4190-A085-74C79816DA3A}"/>
-    <hyperlink ref="C86" r:id="rId135" xr:uid="{669D6C8C-CF64-4B4B-9322-15B6F2E4A206}"/>
+    <hyperlink ref="C94" r:id="rId135" xr:uid="{669D6C8C-CF64-4B4B-9322-15B6F2E4A206}"/>
     <hyperlink ref="C115" r:id="rId136" xr:uid="{D00B3092-B2EE-4646-9C5E-54807683A37C}"/>
     <hyperlink ref="C55" r:id="rId137" xr:uid="{973D83A6-575F-4359-8328-05A28DDF25C9}"/>
     <hyperlink ref="C24" r:id="rId138" xr:uid="{FE23252C-9E3F-4DC1-A463-0FC5C576DC88}"/>
@@ -36017,7 +35910,7 @@
     <hyperlink ref="C105" r:id="rId146" xr:uid="{51A0DCDF-B166-46C9-AFD0-C821EE146A94}"/>
     <hyperlink ref="C54" r:id="rId147" xr:uid="{A40BB4AD-3A49-45A0-8099-CEAC1B9A75AB}"/>
     <hyperlink ref="C56" r:id="rId148" xr:uid="{782528FA-CF6E-4C1A-A91F-B9A9BE60A608}"/>
-    <hyperlink ref="C85" r:id="rId149" xr:uid="{48AA4291-C2A0-410B-9F18-DCD497D7D229}"/>
+    <hyperlink ref="C93" r:id="rId149" xr:uid="{48AA4291-C2A0-410B-9F18-DCD497D7D229}"/>
     <hyperlink ref="C14" r:id="rId150" xr:uid="{0B9BC1FA-777F-4893-8CF4-82697BE54A32}"/>
     <hyperlink ref="C15" r:id="rId151" xr:uid="{BCA3DF1A-B691-43F0-A38B-8A9CC37966CE}"/>
     <hyperlink ref="C64" r:id="rId152" xr:uid="{4C471FD1-B3C4-4EDE-A5AF-F4B3D5022588}"/>
@@ -36080,11 +35973,13 @@
     <hyperlink ref="C259" r:id="rId209" xr:uid="{C7A760BE-8FAA-43C2-A998-89CA8D3B1967}"/>
     <hyperlink ref="D259" r:id="rId210" xr:uid="{20E3234B-A686-4676-8267-8E598D205A1F}"/>
     <hyperlink ref="D260" r:id="rId211" xr:uid="{91962554-3B4C-4770-9432-D3A75C9F8974}"/>
+    <hyperlink ref="C95" r:id="rId212" xr:uid="{919A4BCF-AB98-4B6B-99D6-2749BA7C832F}"/>
+    <hyperlink ref="C92" r:id="rId213" xr:uid="{05FF51FE-70DD-4376-94E7-9F7EB15D512F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId212"/>
-  <drawing r:id="rId213"/>
-  <legacyDrawing r:id="rId214"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId214"/>
+  <drawing r:id="rId215"/>
+  <legacyDrawing r:id="rId216"/>
 </worksheet>
 </file>
 
@@ -36107,13 +36002,13 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="222" customFormat="1" ht="15.5">
-      <c r="C2" s="222" t="s">
+    <row r="2" spans="1:9" s="221" customFormat="1" ht="15.5">
+      <c r="C2" s="221" t="s">
         <v>2646</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="222" customFormat="1" ht="15.5">
-      <c r="C4" s="222" t="s">
+    <row r="4" spans="1:9" s="221" customFormat="1" ht="15.5">
+      <c r="C4" s="221" t="s">
         <v>2647</v>
       </c>
     </row>
@@ -36406,7 +36301,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="183" customFormat="1">
-      <c r="A18" s="193" t="s">
+      <c r="A18" s="278" t="s">
         <v>2721</v>
       </c>
       <c r="B18" s="193">
@@ -36453,10 +36348,10 @@
       <c r="G20" s="76" t="s">
         <v>427</v>
       </c>
-      <c r="H20" s="223" t="s">
+      <c r="H20" s="222" t="s">
         <v>1488</v>
       </c>
-      <c r="I20" s="223" t="s">
+      <c r="I20" s="222" t="s">
         <v>412</v>
       </c>
     </row>
@@ -36711,8 +36606,8 @@
       <c r="I30" s="193"/>
     </row>
     <row r="31" spans="1:9" s="183" customFormat="1">
-      <c r="A31" s="49" t="s">
-        <v>2832</v>
+      <c r="A31" s="183" t="s">
+        <v>3463</v>
       </c>
       <c r="B31" s="183">
         <v>62385671</v>
@@ -36846,7 +36741,7 @@
       <c r="I36" s="193"/>
     </row>
     <row r="37" spans="1:9" s="183" customFormat="1">
-      <c r="A37" s="183" t="s">
+      <c r="A37" s="49" t="s">
         <v>2391</v>
       </c>
       <c r="B37" s="183">
@@ -37014,7 +36909,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="183" customFormat="1">
-      <c r="A44" s="237" t="s">
+      <c r="A44" s="236" t="s">
         <v>3209</v>
       </c>
       <c r="B44" s="183">
@@ -37079,10 +36974,10 @@
         <v>64403333</v>
       </c>
       <c r="C46" s="194" t="s">
-        <v>3638</v>
-      </c>
-      <c r="D46" s="445" t="s">
         <v>3637</v>
+      </c>
+      <c r="D46" s="444" t="s">
+        <v>3636</v>
       </c>
       <c r="E46" s="183" t="s">
         <v>365</v>
@@ -37110,7 +37005,7 @@
       <c r="C48" s="76" t="s">
         <v>1182</v>
       </c>
-      <c r="D48" s="223" t="s">
+      <c r="D48" s="222" t="s">
         <v>1333</v>
       </c>
       <c r="E48" s="76" t="s">
@@ -37119,7 +37014,7 @@
       <c r="F48" s="76" t="s">
         <v>3289</v>
       </c>
-      <c r="G48" s="223" t="s">
+      <c r="G48" s="222" t="s">
         <v>1488</v>
       </c>
       <c r="H48" s="76" t="s">
@@ -37709,7 +37604,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" s="183" customFormat="1">
-      <c r="A73" s="237" t="s">
+      <c r="A73" s="236" t="s">
         <v>2923</v>
       </c>
       <c r="B73" s="193" t="s">
@@ -37767,7 +37662,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" s="76" customFormat="1">
-      <c r="C76" s="378" t="s">
+      <c r="C76" s="377" t="s">
         <v>2547</v>
       </c>
       <c r="D76" s="195" t="s">
@@ -37880,7 +37775,7 @@
       <c r="H83" s="76" t="s">
         <v>1384</v>
       </c>
-      <c r="I83" s="223"/>
+      <c r="I83" s="222"/>
     </row>
     <row r="84" spans="1:9" s="183" customFormat="1">
       <c r="A84" s="183" t="s">
@@ -38041,7 +37936,7 @@
         <v>1790</v>
       </c>
       <c r="E90" s="76" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F90" s="195" t="s">
         <v>2628</v>
@@ -38065,7 +37960,7 @@
         <v>2478</v>
       </c>
       <c r="E91" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F91" s="193" t="s">
         <v>2628</v>
@@ -38089,7 +37984,7 @@
         <v>1273</v>
       </c>
       <c r="E92" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F92" s="193" t="s">
         <v>2628</v>
@@ -38113,7 +38008,7 @@
         <v>2516</v>
       </c>
       <c r="E93" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F93" s="193" t="s">
         <v>2628</v>
@@ -38124,7 +38019,7 @@
       <c r="I93" s="193"/>
     </row>
     <row r="94" spans="1:9" s="183" customFormat="1">
-      <c r="A94" s="437" t="s">
+      <c r="A94" s="436" t="s">
         <v>3369</v>
       </c>
       <c r="B94" s="193">
@@ -38137,7 +38032,7 @@
         <v>2421</v>
       </c>
       <c r="E94" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F94" s="193" t="s">
         <v>2628</v>
@@ -38161,7 +38056,7 @@
         <v>2697</v>
       </c>
       <c r="E95" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F95" s="193" t="s">
         <v>2628</v>
@@ -38178,14 +38073,14 @@
       <c r="B97" s="76">
         <v>64147946</v>
       </c>
-      <c r="C97" s="379" t="s">
+      <c r="C97" s="378" t="s">
         <v>3009</v>
       </c>
       <c r="D97" s="195" t="s">
         <v>2629</v>
       </c>
       <c r="E97" s="76" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F97" s="195" t="s">
         <v>2630</v>
@@ -38212,7 +38107,7 @@
         <v>2635</v>
       </c>
       <c r="E98" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F98" s="193" t="s">
         <v>2630</v>
@@ -38239,7 +38134,7 @@
         <v>2424</v>
       </c>
       <c r="E99" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F99" s="193" t="s">
         <v>2630</v>
@@ -38266,7 +38161,7 @@
         <v>3143</v>
       </c>
       <c r="E100" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F100" s="183" t="s">
         <v>2630</v>
@@ -38292,7 +38187,7 @@
         <v>2149</v>
       </c>
       <c r="E101" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F101" s="183" t="s">
         <v>2630</v>
@@ -38318,7 +38213,7 @@
         <v>2624</v>
       </c>
       <c r="E102" s="183" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F102" s="183" t="s">
         <v>2630</v>
@@ -38354,7 +38249,7 @@
       <c r="E104" s="76" t="s">
         <v>1384</v>
       </c>
-      <c r="F104" s="195" t="s">
+      <c r="F104" s="448" t="s">
         <v>2927</v>
       </c>
       <c r="G104" s="76" t="s">
@@ -38510,7 +38405,7 @@
       <c r="E111" s="76" t="s">
         <v>1716</v>
       </c>
-      <c r="F111" s="195" t="s">
+      <c r="F111" s="448" t="s">
         <v>2928</v>
       </c>
       <c r="G111" s="76" t="s">
@@ -38591,7 +38486,7 @@
       <c r="I114" s="193"/>
     </row>
     <row r="115" spans="1:9" s="183" customFormat="1">
-      <c r="A115" s="183" t="s">
+      <c r="A115" s="49" t="s">
         <v>2721</v>
       </c>
       <c r="B115" s="183">
@@ -38651,7 +38546,7 @@
       <c r="D118" s="76" t="s">
         <v>2436</v>
       </c>
-      <c r="E118" s="76" t="s">
+      <c r="E118" s="286" t="s">
         <v>2947</v>
       </c>
       <c r="F118" s="195" t="s">
@@ -38781,10 +38676,10 @@
         <v>62723048</v>
       </c>
       <c r="C123" s="194" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="D123" s="193" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="E123" s="183" t="s">
         <v>2947</v>
@@ -38819,7 +38714,7 @@
       <c r="F125" s="76" t="s">
         <v>2962</v>
       </c>
-      <c r="G125" s="223" t="s">
+      <c r="G125" s="222" t="s">
         <v>1488</v>
       </c>
       <c r="H125" s="102" t="s">
@@ -38862,10 +38757,10 @@
         <v>64543204</v>
       </c>
       <c r="C127" s="194" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="D127" s="183" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="E127" s="183" t="s">
         <v>1384</v>
@@ -39072,16 +38967,16 @@
     </row>
     <row r="136" spans="1:9" s="183" customFormat="1">
       <c r="A136" s="193" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="B136" s="193">
         <v>60125401</v>
       </c>
       <c r="C136" s="194" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="D136" s="193" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="E136" s="183" t="s">
         <v>2683</v>
@@ -39287,7 +39182,7 @@
       <c r="I144" s="193"/>
     </row>
     <row r="146" spans="1:9" s="76" customFormat="1">
-      <c r="A146" s="195" t="s">
+      <c r="A146" s="278" t="s">
         <v>2391</v>
       </c>
       <c r="B146" s="195">
@@ -39395,7 +39290,7 @@
       <c r="I149" s="193"/>
     </row>
     <row r="150" spans="1:9" s="183" customFormat="1">
-      <c r="A150" s="193" t="s">
+      <c r="A150" s="278" t="s">
         <v>2721</v>
       </c>
       <c r="B150" s="193">
@@ -39432,7 +39327,7 @@
         <v>1126</v>
       </c>
       <c r="D151" s="193" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="E151" s="183" t="s">
         <v>2683</v>
@@ -39626,7 +39521,7 @@
       <c r="E160" s="76" t="s">
         <v>2683</v>
       </c>
-      <c r="F160" s="195" t="s">
+      <c r="F160" s="448" t="s">
         <v>2947</v>
       </c>
       <c r="G160" s="76" t="s">
@@ -39772,15 +39667,15 @@
       </c>
       <c r="I165" s="193"/>
     </row>
-    <row r="175" spans="1:9" s="377" customFormat="1" ht="15.5">
-      <c r="A175" s="376"/>
-      <c r="B175" s="376"/>
-      <c r="C175" s="376" t="s">
+    <row r="175" spans="1:9" s="376" customFormat="1" ht="15.5">
+      <c r="A175" s="375"/>
+      <c r="B175" s="375"/>
+      <c r="C175" s="375" t="s">
         <v>2969</v>
       </c>
-      <c r="D175" s="376"/>
-      <c r="F175" s="376"/>
-      <c r="I175" s="376"/>
+      <c r="D175" s="375"/>
+      <c r="F175" s="375"/>
+      <c r="I175" s="375"/>
     </row>
     <row r="176" spans="1:9">
       <c r="C176"/>
@@ -39790,13 +39685,13 @@
       <c r="F178"/>
       <c r="I178"/>
     </row>
-    <row r="179" spans="1:9" s="399" customFormat="1" ht="23.5">
-      <c r="B179" s="399" t="s">
+    <row r="179" spans="1:9" s="398" customFormat="1" ht="23.5">
+      <c r="B179" s="398" t="s">
         <v>3207</v>
       </c>
-      <c r="C179" s="400"/>
-      <c r="D179" s="401"/>
-      <c r="E179" s="402"/>
+      <c r="C179" s="399"/>
+      <c r="D179" s="400"/>
+      <c r="E179" s="401"/>
     </row>
     <row r="180" spans="1:9">
       <c r="A180"/>
@@ -39873,7 +39768,7 @@
       <c r="D186" s="1" t="s">
         <v>3451</v>
       </c>
-      <c r="F186" s="418"/>
+      <c r="F186" s="417"/>
     </row>
     <row r="187" spans="1:9">
       <c r="C187" s="1" t="s">
@@ -39896,7 +39791,7 @@
         <v>716</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -39904,7 +39799,7 @@
         <v>284</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -39912,7 +39807,7 @@
         <v>2540</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -40103,31 +39998,31 @@
       </c>
     </row>
     <row r="233" spans="1:9" s="7" customFormat="1">
-      <c r="A233" s="307" t="s">
+      <c r="A233" s="306" t="s">
         <v>787</v>
       </c>
-      <c r="B233" s="307">
+      <c r="B233" s="306">
         <v>67697112</v>
       </c>
       <c r="C233" s="8" t="s">
         <v>1540</v>
       </c>
-      <c r="D233" s="307" t="s">
+      <c r="D233" s="306" t="s">
         <v>2260</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>2189</v>
       </c>
-      <c r="F233" s="307" t="s">
+      <c r="F233" s="306" t="s">
         <v>1570</v>
       </c>
-      <c r="G233" s="307" t="s">
+      <c r="G233" s="306" t="s">
         <v>1488</v>
       </c>
       <c r="H233" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="I233" s="307"/>
+      <c r="I233" s="306"/>
     </row>
     <row r="234" spans="1:9">
       <c r="A234"/>
@@ -41318,7 +41213,7 @@
       <c r="J3"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="221" t="s">
+      <c r="A4" s="220" t="s">
         <v>3119</v>
       </c>
       <c r="B4" t="s">
@@ -41343,7 +41238,7 @@
         <v>3002</v>
       </c>
       <c r="I4" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41369,10 +41264,10 @@
       <c r="G5" t="s">
         <v>520</v>
       </c>
-      <c r="H5" s="221" t="s">
+      <c r="H5" s="220" t="s">
         <v>3164</v>
       </c>
-      <c r="I5" s="221" t="s">
+      <c r="I5" s="220" t="s">
         <v>3362</v>
       </c>
       <c r="J5" t="s">
@@ -41427,13 +41322,13 @@
         <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2161</v>
       </c>
       <c r="D8" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="E8" t="s">
         <v>2480</v>
@@ -41445,7 +41340,7 @@
         <v>253</v>
       </c>
       <c r="H8" s="105" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="I8" t="s">
         <v>3295</v>
@@ -41584,7 +41479,7 @@
         <v>3500</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="19" customFormat="1"/>
@@ -41662,7 +41557,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="282" t="s">
+      <c r="A5" s="281" t="s">
         <v>2264</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -41680,10 +41575,10 @@
       <c r="G5" t="s">
         <v>522</v>
       </c>
-      <c r="H5" s="368" t="s">
+      <c r="H5" s="367" t="s">
         <v>2264</v>
       </c>
-      <c r="I5" s="282" t="s">
+      <c r="I5" s="281" t="s">
         <v>2264</v>
       </c>
     </row>
@@ -41717,7 +41612,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="279" t="s">
+      <c r="A7" s="278" t="s">
         <v>2844</v>
       </c>
       <c r="B7" s="10" t="s">
@@ -41741,7 +41636,7 @@
       <c r="H7" t="s">
         <v>3285</v>
       </c>
-      <c r="I7" s="279" t="s">
+      <c r="I7" s="278" t="s">
         <v>2857</v>
       </c>
     </row>
@@ -41801,7 +41696,7 @@
       <c r="G12" t="s">
         <v>522</v>
       </c>
-      <c r="H12" s="279" t="s">
+      <c r="H12" s="278" t="s">
         <v>2865</v>
       </c>
       <c r="I12" t="s">
@@ -41841,33 +41736,33 @@
       <c r="G15" t="s">
         <v>522</v>
       </c>
-      <c r="H15" s="279" t="s">
+      <c r="H15" s="278" t="s">
         <v>2842</v>
       </c>
-      <c r="I15" s="282" t="s">
+      <c r="I15" s="281" t="s">
         <v>2264</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="282"/>
-      <c r="B16" s="282"/>
-      <c r="C16" s="282" t="s">
+      <c r="A16" s="281"/>
+      <c r="B16" s="281"/>
+      <c r="C16" s="281" t="s">
         <v>2387</v>
       </c>
-      <c r="D16" s="282" t="s">
+      <c r="D16" s="281" t="s">
         <v>2860</v>
       </c>
-      <c r="E16" s="282" t="s">
+      <c r="E16" s="281" t="s">
         <v>976</v>
       </c>
-      <c r="F16" s="282" t="s">
+      <c r="F16" s="281" t="s">
         <v>2388</v>
       </c>
       <c r="G16" s="97" t="s">
         <v>522</v>
       </c>
-      <c r="H16" s="282"/>
-      <c r="I16" s="282"/>
+      <c r="H16" s="281"/>
+      <c r="I16" s="281"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
@@ -41914,7 +41809,7 @@
       <c r="G18" t="s">
         <v>522</v>
       </c>
-      <c r="H18" s="412" t="s">
+      <c r="H18" s="411" t="s">
         <v>2758</v>
       </c>
       <c r="I18" s="10" t="s">
@@ -41943,7 +41838,7 @@
       <c r="G19" t="s">
         <v>522</v>
       </c>
-      <c r="H19" s="279" t="s">
+      <c r="H19" s="278" t="s">
         <v>2866</v>
       </c>
       <c r="I19" s="10" t="s">
@@ -42046,7 +41941,7 @@
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="279" t="s">
+      <c r="A25" s="278" t="s">
         <v>2257</v>
       </c>
       <c r="B25" s="10">
@@ -42067,10 +41962,10 @@
       <c r="G25" t="s">
         <v>522</v>
       </c>
-      <c r="H25" s="279" t="s">
+      <c r="H25" s="278" t="s">
         <v>2668</v>
       </c>
-      <c r="I25" s="282"/>
+      <c r="I25" s="281"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="10" t="s">
@@ -42095,17 +41990,17 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="317" customFormat="1" ht="23.5">
-      <c r="A36" s="316"/>
-      <c r="B36" s="319" t="s">
+    <row r="36" spans="1:10" s="316" customFormat="1" ht="23.5">
+      <c r="A36" s="315"/>
+      <c r="B36" s="318" t="s">
         <v>2580</v>
       </c>
-      <c r="C36" s="316"/>
-      <c r="D36" s="316"/>
-      <c r="E36" s="316"/>
-      <c r="F36" s="316"/>
-      <c r="H36" s="318"/>
-      <c r="I36" s="316"/>
+      <c r="C36" s="315"/>
+      <c r="D36" s="315"/>
+      <c r="E36" s="315"/>
+      <c r="F36" s="315"/>
+      <c r="H36" s="317"/>
+      <c r="I36" s="315"/>
     </row>
     <row r="37" spans="1:10">
       <c r="C37" s="10" t="s">
@@ -42120,20 +42015,20 @@
       <c r="G38"/>
       <c r="J38" s="10"/>
     </row>
-    <row r="39" spans="1:10" s="322" customFormat="1" ht="23.5">
-      <c r="A39" s="320"/>
-      <c r="B39" s="321" t="s">
+    <row r="39" spans="1:10" s="321" customFormat="1" ht="23.5">
+      <c r="A39" s="319"/>
+      <c r="B39" s="320" t="s">
         <v>2604</v>
       </c>
-      <c r="C39" s="320"/>
-      <c r="D39" s="320"/>
-      <c r="E39" s="320"/>
-      <c r="F39" s="320"/>
-      <c r="H39" s="323"/>
-      <c r="I39" s="320"/>
+      <c r="C39" s="319"/>
+      <c r="D39" s="319"/>
+      <c r="E39" s="319"/>
+      <c r="F39" s="319"/>
+      <c r="H39" s="322"/>
+      <c r="I39" s="319"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="279" t="s">
+      <c r="A40" s="278" t="s">
         <v>352</v>
       </c>
       <c r="B40" s="10">
@@ -42156,7 +42051,7 @@
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="279" t="s">
+      <c r="A41" s="278" t="s">
         <v>2587</v>
       </c>
       <c r="B41" s="10">
@@ -42179,7 +42074,7 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="279" t="s">
+      <c r="A42" s="278" t="s">
         <v>2498</v>
       </c>
       <c r="B42" s="10">
@@ -42263,10 +42158,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="G4"/>
-      <c r="I4" s="221"/>
+      <c r="I4" s="220"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="279" t="s">
+      <c r="A5" s="278" t="s">
         <v>2044</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -42371,8 +42266,8 @@
       <c r="G8" t="s">
         <v>980</v>
       </c>
-      <c r="H8" s="282"/>
-      <c r="I8" s="282"/>
+      <c r="H8" s="281"/>
+      <c r="I8" s="281"/>
     </row>
     <row r="9" spans="1:10">
       <c r="C9" s="22"/>
@@ -42408,31 +42303,31 @@
     <col min="3" max="3" width="28.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="369" customFormat="1" ht="31">
-      <c r="A1" s="369" t="e" vm="1">
+    <row r="1" spans="1:9" s="368" customFormat="1" ht="31">
+      <c r="A1" s="368" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="370"/>
-      <c r="C1" s="369" t="s">
+      <c r="B1" s="369"/>
+      <c r="C1" s="368" t="s">
         <v>2897</v>
       </c>
-      <c r="G1" s="369" t="e" vm="1">
+      <c r="G1" s="368" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="H1" s="370"/>
-      <c r="I1" s="370"/>
-    </row>
-    <row r="2" spans="1:9" s="374" customFormat="1" ht="18.5">
-      <c r="A2" s="371" t="s">
+      <c r="H1" s="369"/>
+      <c r="I1" s="369"/>
+    </row>
+    <row r="2" spans="1:9" s="373" customFormat="1" ht="18.5">
+      <c r="A2" s="370" t="s">
         <v>2898</v>
       </c>
-      <c r="B2" s="372" t="s">
+      <c r="B2" s="371" t="s">
         <v>977</v>
       </c>
-      <c r="C2" s="373" t="s">
+      <c r="C2" s="372" t="s">
         <v>361</v>
       </c>
-      <c r="D2" s="374" t="s">
+      <c r="D2" s="373" t="s">
         <v>3131</v>
       </c>
     </row>
@@ -42538,7 +42433,7 @@
       <c r="I9" s="10"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="279" t="s">
+      <c r="A10" s="278" t="s">
         <v>2128</v>
       </c>
       <c r="B10" s="10">
@@ -42589,7 +42484,7 @@
         <v>65124748</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2968</v>
@@ -42610,7 +42505,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2968</v>
@@ -42771,8 +42666,8 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FC023C-A370-4023-8ADE-A4883D317B37}">
-  <dimension ref="A1:E4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FC023C-A370-4023-8ADE-A4883D317B37}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="10" customWidth="1"/>
@@ -42781,32 +42676,39 @@
     <col min="4" max="4" width="26.08984375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="443" customFormat="1" ht="42.5" customHeight="1">
-      <c r="A1" s="442"/>
-      <c r="B1" s="442" t="s">
-        <v>3625</v>
-      </c>
-      <c r="C1" s="442"/>
-    </row>
-    <row r="4" spans="1:5">
+    <row r="1" spans="1:7" s="442" customFormat="1" ht="42.5" customHeight="1">
+      <c r="A1" s="441"/>
+      <c r="B1" s="441" t="s">
+        <v>3624</v>
+      </c>
+      <c r="C1" s="441"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="10" t="s">
         <v>148</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>3625</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>3626</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" t="s">
         <v>3627</v>
       </c>
-      <c r="E4" t="s">
-        <v>3628</v>
+      <c r="F4" s="10" t="s">
+        <v>3642</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>3643</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -42820,19 +42722,19 @@
     <col min="3" max="3" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="374" customFormat="1" ht="18.5">
-      <c r="B1" s="374" t="s">
+    <row r="1" spans="1:6" s="373" customFormat="1" ht="18.5">
+      <c r="B1" s="373" t="s">
         <v>3007</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="249" customFormat="1">
-      <c r="A2" s="249" t="s">
+    <row r="2" spans="1:6" s="248" customFormat="1">
+      <c r="A2" s="248" t="s">
         <v>3008</v>
       </c>
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="248" t="s">
         <v>705</v>
       </c>
-      <c r="C2" s="249" t="s">
+      <c r="C2" s="248" t="s">
         <v>3010</v>
       </c>
     </row>
@@ -42920,10 +42822,10 @@
       <c r="B15" t="s">
         <v>3015</v>
       </c>
-      <c r="C15" s="249" t="s">
+      <c r="C15" s="248" t="s">
         <v>3010</v>
       </c>
-      <c r="D15" s="230" t="s">
+      <c r="D15" s="229" t="s">
         <v>2786</v>
       </c>
       <c r="E15" s="181" t="s">
@@ -43005,7 +42907,7 @@
       <c r="B27" t="s">
         <v>297</v>
       </c>
-      <c r="C27" s="249" t="s">
+      <c r="C27" s="248" t="s">
         <v>3010</v>
       </c>
       <c r="D27" s="181" t="s">
@@ -43107,90 +43009,90 @@
     <col min="13" max="13" width="47.36328125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="331" customFormat="1" ht="26">
-      <c r="C1" s="332" t="s">
+    <row r="1" spans="1:13" s="330" customFormat="1" ht="26">
+      <c r="C1" s="331" t="s">
         <v>2775</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="334" customFormat="1">
-      <c r="A2" s="333" t="s">
+    <row r="2" spans="1:13" s="333" customFormat="1">
+      <c r="A2" s="332" t="s">
         <v>2776</v>
       </c>
-      <c r="B2" s="334" t="s">
+      <c r="B2" s="333" t="s">
         <v>2796</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="334" customFormat="1" ht="18" customHeight="1">
-      <c r="A3" s="334" t="s">
+    <row r="3" spans="1:13" s="333" customFormat="1" ht="18" customHeight="1">
+      <c r="A3" s="333" t="s">
         <v>2777</v>
       </c>
-      <c r="B3" s="366" t="s">
+      <c r="B3" s="365" t="s">
         <v>2797</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="334" customFormat="1">
-      <c r="A4" s="334" t="s">
+    <row r="4" spans="1:13" s="333" customFormat="1">
+      <c r="A4" s="333" t="s">
         <v>2778</v>
       </c>
-      <c r="B4" s="334" t="s">
+      <c r="B4" s="333" t="s">
         <v>2592</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="336" customFormat="1">
-      <c r="A5" s="335" t="s">
+    <row r="5" spans="1:13" s="335" customFormat="1">
+      <c r="A5" s="334" t="s">
         <v>2779</v>
       </c>
-      <c r="B5" s="336" t="s">
+      <c r="B5" s="335" t="s">
         <v>2798</v>
       </c>
-      <c r="C5" s="336" t="s">
+      <c r="C5" s="335" t="s">
         <v>3458</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="336" customFormat="1">
-      <c r="A6" s="336" t="s">
+    <row r="6" spans="1:13" s="335" customFormat="1">
+      <c r="A6" s="335" t="s">
         <v>2777</v>
       </c>
-      <c r="B6" s="336" t="s">
+      <c r="B6" s="335" t="s">
         <v>3457</v>
       </c>
-      <c r="C6" s="336" t="s">
+      <c r="C6" s="335" t="s">
         <v>3457</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="336" customFormat="1">
-      <c r="A7" s="336" t="s">
+    <row r="7" spans="1:13" s="335" customFormat="1">
+      <c r="A7" s="335" t="s">
         <v>2778</v>
       </c>
-      <c r="B7" s="336" t="s">
+      <c r="B7" s="335" t="s">
         <v>2799</v>
       </c>
-      <c r="C7" s="336" t="s">
+      <c r="C7" s="335" t="s">
         <v>2799</v>
       </c>
-      <c r="D7" s="337"/>
-      <c r="H7" s="337"/>
-      <c r="I7" s="337"/>
-      <c r="L7" s="337"/>
-      <c r="M7" s="337"/>
-    </row>
-    <row r="8" spans="1:13" s="338" customFormat="1">
-      <c r="A8" s="339" t="s">
+      <c r="D7" s="336"/>
+      <c r="H7" s="336"/>
+      <c r="I7" s="336"/>
+      <c r="L7" s="336"/>
+      <c r="M7" s="336"/>
+    </row>
+    <row r="8" spans="1:13" s="337" customFormat="1">
+      <c r="A8" s="338" t="s">
         <v>2780</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="338" customFormat="1">
-      <c r="A9" s="338" t="s">
+    <row r="9" spans="1:13" s="337" customFormat="1">
+      <c r="A9" s="337" t="s">
         <v>2777</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="338" customFormat="1">
-      <c r="A10" s="338" t="s">
+    <row r="10" spans="1:13" s="337" customFormat="1">
+      <c r="A10" s="337" t="s">
         <v>2778</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="168" customFormat="1">
-      <c r="A11" s="340" t="s">
+      <c r="A11" s="339" t="s">
         <v>2781</v>
       </c>
     </row>
@@ -43203,409 +43105,409 @@
       <c r="A13" s="168" t="s">
         <v>2778</v>
       </c>
-      <c r="I13" s="341"/>
-      <c r="L13" s="341"/>
-      <c r="M13" s="341"/>
-    </row>
-    <row r="14" spans="1:13" s="351" customFormat="1">
-      <c r="A14" s="342" t="s">
+      <c r="I13" s="340"/>
+      <c r="L13" s="340"/>
+      <c r="M13" s="340"/>
+    </row>
+    <row r="14" spans="1:13" s="350" customFormat="1">
+      <c r="A14" s="341" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="342" t="s">
+      <c r="B14" s="341" t="s">
         <v>2788</v>
       </c>
-      <c r="C14" s="342" t="s">
+      <c r="C14" s="341" t="s">
         <v>2793</v>
       </c>
-      <c r="D14" s="342" t="s">
+      <c r="D14" s="341" t="s">
         <v>2798</v>
       </c>
-      <c r="E14" s="342" t="s">
+      <c r="E14" s="341" t="s">
         <v>2798</v>
       </c>
-      <c r="F14" s="342" t="s">
+      <c r="F14" s="341" t="s">
         <v>2807</v>
       </c>
-      <c r="G14" s="342" t="s">
+      <c r="G14" s="341" t="s">
         <v>2811</v>
       </c>
-      <c r="H14" s="342" t="s">
+      <c r="H14" s="341" t="s">
         <v>3465</v>
       </c>
-      <c r="I14" s="342" t="s">
+      <c r="I14" s="341" t="s">
         <v>3468</v>
       </c>
-      <c r="L14" s="342"/>
-      <c r="M14" s="342"/>
-    </row>
-    <row r="15" spans="1:13" s="344" customFormat="1">
-      <c r="A15" s="344" t="s">
+      <c r="L14" s="341"/>
+      <c r="M14" s="341"/>
+    </row>
+    <row r="15" spans="1:13" s="343" customFormat="1">
+      <c r="A15" s="343" t="s">
         <v>2777</v>
       </c>
-      <c r="B15" s="343" t="s">
+      <c r="B15" s="342" t="s">
         <v>2791</v>
       </c>
-      <c r="C15" s="343" t="s">
+      <c r="C15" s="342" t="s">
         <v>2794</v>
       </c>
-      <c r="D15" s="343" t="s">
+      <c r="D15" s="342" t="s">
         <v>2791</v>
       </c>
-      <c r="E15" s="343" t="s">
+      <c r="E15" s="342" t="s">
         <v>2794</v>
       </c>
-      <c r="F15" s="343" t="s">
+      <c r="F15" s="342" t="s">
         <v>2808</v>
       </c>
-      <c r="G15" s="343" t="s">
+      <c r="G15" s="342" t="s">
         <v>2812</v>
       </c>
-      <c r="H15" s="343" t="s">
+      <c r="H15" s="342" t="s">
         <v>3466</v>
       </c>
-      <c r="I15" s="343" t="s">
+      <c r="I15" s="342" t="s">
         <v>3469</v>
       </c>
-      <c r="L15" s="343"/>
-      <c r="M15" s="343"/>
-    </row>
-    <row r="16" spans="1:13" s="344" customFormat="1">
-      <c r="A16" s="344" t="s">
+      <c r="L15" s="342"/>
+      <c r="M15" s="342"/>
+    </row>
+    <row r="16" spans="1:13" s="343" customFormat="1">
+      <c r="A16" s="343" t="s">
         <v>2778</v>
       </c>
-      <c r="B16" s="343" t="s">
+      <c r="B16" s="342" t="s">
         <v>2792</v>
       </c>
-      <c r="C16" s="343" t="s">
+      <c r="C16" s="342" t="s">
         <v>2795</v>
       </c>
-      <c r="D16" s="343" t="s">
+      <c r="D16" s="342" t="s">
         <v>2792</v>
       </c>
-      <c r="E16" s="343" t="s">
+      <c r="E16" s="342" t="s">
         <v>2795</v>
       </c>
-      <c r="F16" s="343" t="s">
+      <c r="F16" s="342" t="s">
         <v>2795</v>
       </c>
-      <c r="G16" s="343" t="s">
+      <c r="G16" s="342" t="s">
         <v>2813</v>
       </c>
-      <c r="H16" s="343" t="s">
+      <c r="H16" s="342" t="s">
         <v>3467</v>
       </c>
-      <c r="I16" s="343" t="s">
+      <c r="I16" s="342" t="s">
         <v>1384</v>
       </c>
-      <c r="L16" s="343"/>
-      <c r="M16" s="343"/>
-    </row>
-    <row r="17" spans="1:13" s="334" customFormat="1">
-      <c r="A17" s="419" t="s">
+      <c r="L16" s="342"/>
+      <c r="M16" s="342"/>
+    </row>
+    <row r="17" spans="1:13" s="333" customFormat="1">
+      <c r="A17" s="418" t="s">
         <v>2782</v>
       </c>
-      <c r="B17" s="420" t="s">
+      <c r="B17" s="419" t="s">
         <v>3454</v>
       </c>
-      <c r="C17" s="420"/>
-      <c r="D17" s="420"/>
-      <c r="E17" s="420"/>
-      <c r="F17" s="420"/>
-      <c r="G17" s="420"/>
-      <c r="H17" s="420"/>
-      <c r="I17" s="420"/>
-      <c r="L17" s="420"/>
-      <c r="M17" s="420"/>
-    </row>
-    <row r="18" spans="1:13" s="334" customFormat="1">
-      <c r="A18" s="334" t="s">
+      <c r="C17" s="419"/>
+      <c r="D17" s="419"/>
+      <c r="E17" s="419"/>
+      <c r="F17" s="419"/>
+      <c r="G17" s="419"/>
+      <c r="H17" s="419"/>
+      <c r="I17" s="419"/>
+      <c r="L17" s="419"/>
+      <c r="M17" s="419"/>
+    </row>
+    <row r="18" spans="1:13" s="333" customFormat="1">
+      <c r="A18" s="333" t="s">
         <v>2777</v>
       </c>
-      <c r="B18" s="420" t="s">
+      <c r="B18" s="419" t="s">
         <v>3455</v>
       </c>
-      <c r="C18" s="420"/>
-      <c r="D18" s="420"/>
-      <c r="E18" s="420"/>
-      <c r="F18" s="420"/>
-      <c r="G18" s="420"/>
-      <c r="H18" s="420"/>
-      <c r="I18" s="420"/>
-      <c r="L18" s="420"/>
-      <c r="M18" s="420"/>
-    </row>
-    <row r="19" spans="1:13" s="334" customFormat="1">
-      <c r="A19" s="334" t="s">
+      <c r="C18" s="419"/>
+      <c r="D18" s="419"/>
+      <c r="E18" s="419"/>
+      <c r="F18" s="419"/>
+      <c r="G18" s="419"/>
+      <c r="H18" s="419"/>
+      <c r="I18" s="419"/>
+      <c r="L18" s="419"/>
+      <c r="M18" s="419"/>
+    </row>
+    <row r="19" spans="1:13" s="333" customFormat="1">
+      <c r="A19" s="333" t="s">
         <v>2778</v>
       </c>
-      <c r="B19" s="420" t="s">
+      <c r="B19" s="419" t="s">
         <v>3456</v>
       </c>
-      <c r="C19" s="420"/>
-      <c r="D19" s="420"/>
-      <c r="E19" s="420"/>
-      <c r="F19" s="420"/>
-      <c r="G19" s="420"/>
-      <c r="H19" s="420"/>
-      <c r="I19" s="420"/>
-      <c r="L19" s="420"/>
-      <c r="M19" s="420"/>
-    </row>
-    <row r="20" spans="1:13" s="347" customFormat="1">
-      <c r="A20" s="345" t="s">
+      <c r="C19" s="419"/>
+      <c r="D19" s="419"/>
+      <c r="E19" s="419"/>
+      <c r="F19" s="419"/>
+      <c r="G19" s="419"/>
+      <c r="H19" s="419"/>
+      <c r="I19" s="419"/>
+      <c r="L19" s="419"/>
+      <c r="M19" s="419"/>
+    </row>
+    <row r="20" spans="1:13" s="346" customFormat="1">
+      <c r="A20" s="344" t="s">
         <v>2783</v>
       </c>
-      <c r="B20" s="345" t="s">
+      <c r="B20" s="344" t="s">
         <v>3057</v>
       </c>
-      <c r="C20" s="346"/>
-      <c r="D20" s="346"/>
-      <c r="E20" s="346"/>
-      <c r="F20" s="346"/>
-      <c r="G20" s="346"/>
-      <c r="H20" s="346"/>
-      <c r="I20" s="346"/>
-      <c r="L20" s="346"/>
-      <c r="M20" s="346"/>
-    </row>
-    <row r="21" spans="1:13" s="347" customFormat="1">
-      <c r="A21" s="347" t="s">
+      <c r="C20" s="345"/>
+      <c r="D20" s="345"/>
+      <c r="E20" s="345"/>
+      <c r="F20" s="345"/>
+      <c r="G20" s="345"/>
+      <c r="H20" s="345"/>
+      <c r="I20" s="345"/>
+      <c r="L20" s="345"/>
+      <c r="M20" s="345"/>
+    </row>
+    <row r="21" spans="1:13" s="346" customFormat="1">
+      <c r="A21" s="346" t="s">
         <v>2777</v>
       </c>
-      <c r="B21" s="346" t="s">
+      <c r="B21" s="345" t="s">
         <v>3058</v>
       </c>
-      <c r="D21" s="346"/>
-      <c r="E21" s="346"/>
-      <c r="F21" s="346"/>
-      <c r="G21" s="346"/>
-      <c r="H21" s="346"/>
-      <c r="I21" s="346"/>
-      <c r="L21" s="346"/>
-      <c r="M21" s="346"/>
-    </row>
-    <row r="22" spans="1:13" s="347" customFormat="1" ht="12.4" customHeight="1">
-      <c r="A22" s="347" t="s">
+      <c r="D21" s="345"/>
+      <c r="E21" s="345"/>
+      <c r="F21" s="345"/>
+      <c r="G21" s="345"/>
+      <c r="H21" s="345"/>
+      <c r="I21" s="345"/>
+      <c r="L21" s="345"/>
+      <c r="M21" s="345"/>
+    </row>
+    <row r="22" spans="1:13" s="346" customFormat="1" ht="12.4" customHeight="1">
+      <c r="A22" s="346" t="s">
         <v>2778</v>
       </c>
-      <c r="B22" s="347" t="s">
+      <c r="B22" s="346" t="s">
         <v>3059</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="350" customFormat="1">
-      <c r="A23" s="348" t="s">
+    <row r="23" spans="1:13" s="349" customFormat="1">
+      <c r="A23" s="347" t="s">
         <v>1031</v>
       </c>
-      <c r="B23" s="349"/>
-      <c r="C23" s="349"/>
-      <c r="D23" s="349"/>
-      <c r="E23" s="349"/>
-      <c r="F23" s="349"/>
-      <c r="G23" s="349"/>
-      <c r="H23" s="349"/>
-      <c r="I23" s="349"/>
-      <c r="L23" s="349"/>
-      <c r="M23" s="349"/>
-    </row>
-    <row r="24" spans="1:13" s="350" customFormat="1">
-      <c r="A24" s="350" t="s">
+      <c r="B23" s="348"/>
+      <c r="C23" s="348"/>
+      <c r="D23" s="348"/>
+      <c r="E23" s="348"/>
+      <c r="F23" s="348"/>
+      <c r="G23" s="348"/>
+      <c r="H23" s="348"/>
+      <c r="I23" s="348"/>
+      <c r="L23" s="348"/>
+      <c r="M23" s="348"/>
+    </row>
+    <row r="24" spans="1:13" s="349" customFormat="1">
+      <c r="A24" s="349" t="s">
         <v>2777</v>
       </c>
-      <c r="B24" s="349"/>
-      <c r="D24" s="349"/>
-      <c r="E24" s="349"/>
-      <c r="F24" s="349"/>
-      <c r="G24" s="349"/>
-      <c r="H24" s="349"/>
-      <c r="I24" s="349"/>
-      <c r="L24" s="349"/>
-      <c r="M24" s="349"/>
-    </row>
-    <row r="25" spans="1:13" s="350" customFormat="1">
-      <c r="A25" s="350" t="s">
+      <c r="B24" s="348"/>
+      <c r="D24" s="348"/>
+      <c r="E24" s="348"/>
+      <c r="F24" s="348"/>
+      <c r="G24" s="348"/>
+      <c r="H24" s="348"/>
+      <c r="I24" s="348"/>
+      <c r="L24" s="348"/>
+      <c r="M24" s="348"/>
+    </row>
+    <row r="25" spans="1:13" s="349" customFormat="1">
+      <c r="A25" s="349" t="s">
         <v>2778</v>
       </c>
-      <c r="B25" s="349"/>
-      <c r="D25" s="349"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
-      <c r="G25" s="349"/>
-      <c r="H25" s="349"/>
-      <c r="I25" s="349"/>
-      <c r="L25" s="349"/>
-      <c r="M25" s="349"/>
-    </row>
-    <row r="26" spans="1:13" s="353" customFormat="1">
-      <c r="A26" s="352" t="s">
+      <c r="B25" s="348"/>
+      <c r="D25" s="348"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
+      <c r="G25" s="348"/>
+      <c r="H25" s="348"/>
+      <c r="I25" s="348"/>
+      <c r="L25" s="348"/>
+      <c r="M25" s="348"/>
+    </row>
+    <row r="26" spans="1:13" s="352" customFormat="1">
+      <c r="A26" s="351" t="s">
         <v>2784</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="353" customFormat="1">
-      <c r="A27" s="353" t="s">
+    <row r="27" spans="1:13" s="352" customFormat="1">
+      <c r="A27" s="352" t="s">
         <v>2777</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="353" customFormat="1">
-      <c r="A28" s="353" t="s">
+    <row r="28" spans="1:13" s="352" customFormat="1">
+      <c r="A28" s="352" t="s">
         <v>2778</v>
       </c>
-      <c r="B28" s="354"/>
-      <c r="C28" s="354"/>
-      <c r="D28" s="354"/>
-      <c r="E28" s="354"/>
-      <c r="F28" s="354"/>
-      <c r="G28" s="354"/>
-      <c r="H28" s="354"/>
-      <c r="I28" s="354"/>
-      <c r="L28" s="354"/>
-      <c r="M28" s="354"/>
-    </row>
-    <row r="29" spans="1:13" s="364" customFormat="1">
-      <c r="A29" s="355" t="s">
+      <c r="B28" s="353"/>
+      <c r="C28" s="353"/>
+      <c r="D28" s="353"/>
+      <c r="E28" s="353"/>
+      <c r="F28" s="353"/>
+      <c r="G28" s="353"/>
+      <c r="H28" s="353"/>
+      <c r="I28" s="353"/>
+      <c r="L28" s="353"/>
+      <c r="M28" s="353"/>
+    </row>
+    <row r="29" spans="1:13" s="363" customFormat="1">
+      <c r="A29" s="354" t="s">
         <v>2785</v>
       </c>
-      <c r="B29" s="355" t="s">
+      <c r="B29" s="354" t="s">
         <v>2788</v>
       </c>
-      <c r="C29" s="355" t="s">
+      <c r="C29" s="354" t="s">
         <v>3194</v>
       </c>
-      <c r="D29" s="355"/>
-      <c r="E29" s="355"/>
-      <c r="F29" s="355"/>
-      <c r="G29" s="355"/>
-      <c r="H29" s="355"/>
-      <c r="I29" s="355"/>
-      <c r="L29" s="355"/>
-      <c r="M29" s="355"/>
-    </row>
-    <row r="30" spans="1:13" s="357" customFormat="1">
-      <c r="A30" s="357" t="s">
+      <c r="D29" s="354"/>
+      <c r="E29" s="354"/>
+      <c r="F29" s="354"/>
+      <c r="G29" s="354"/>
+      <c r="H29" s="354"/>
+      <c r="I29" s="354"/>
+      <c r="L29" s="354"/>
+      <c r="M29" s="354"/>
+    </row>
+    <row r="30" spans="1:13" s="356" customFormat="1">
+      <c r="A30" s="356" t="s">
         <v>2777</v>
       </c>
-      <c r="B30" s="356" t="s">
+      <c r="B30" s="355" t="s">
         <v>2789</v>
       </c>
-      <c r="C30" s="356" t="s">
+      <c r="C30" s="355" t="s">
         <v>3195</v>
       </c>
-      <c r="D30" s="356"/>
-      <c r="E30" s="356"/>
-      <c r="F30" s="356"/>
-      <c r="G30" s="356"/>
-      <c r="H30" s="356"/>
-      <c r="I30" s="356"/>
-      <c r="L30" s="356"/>
-      <c r="M30" s="356"/>
-    </row>
-    <row r="31" spans="1:13" s="357" customFormat="1">
-      <c r="A31" s="357" t="s">
+      <c r="D30" s="355"/>
+      <c r="E30" s="355"/>
+      <c r="F30" s="355"/>
+      <c r="G30" s="355"/>
+      <c r="H30" s="355"/>
+      <c r="I30" s="355"/>
+      <c r="L30" s="355"/>
+      <c r="M30" s="355"/>
+    </row>
+    <row r="31" spans="1:13" s="356" customFormat="1">
+      <c r="A31" s="356" t="s">
         <v>2778</v>
       </c>
-      <c r="B31" s="356" t="s">
+      <c r="B31" s="355" t="s">
         <v>2790</v>
       </c>
-      <c r="C31" s="356" t="s">
+      <c r="C31" s="355" t="s">
         <v>2790</v>
       </c>
-      <c r="D31" s="356"/>
-      <c r="E31" s="356"/>
-      <c r="F31" s="356"/>
-      <c r="G31" s="356"/>
-      <c r="H31" s="356"/>
-      <c r="I31" s="356"/>
-      <c r="L31" s="356"/>
-      <c r="M31" s="356"/>
-    </row>
-    <row r="32" spans="1:13" s="365" customFormat="1">
-      <c r="A32" s="358" t="s">
+      <c r="D31" s="355"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
+      <c r="G31" s="355"/>
+      <c r="H31" s="355"/>
+      <c r="I31" s="355"/>
+      <c r="L31" s="355"/>
+      <c r="M31" s="355"/>
+    </row>
+    <row r="32" spans="1:13" s="364" customFormat="1">
+      <c r="A32" s="357" t="s">
         <v>2786</v>
       </c>
-      <c r="B32" s="358"/>
-      <c r="C32" s="358"/>
-      <c r="D32" s="358"/>
-      <c r="E32" s="358"/>
-      <c r="F32" s="358"/>
-      <c r="G32" s="358"/>
-      <c r="H32" s="358"/>
-      <c r="I32" s="358"/>
-      <c r="L32" s="358"/>
-      <c r="M32" s="358"/>
-    </row>
-    <row r="33" spans="1:13" s="360" customFormat="1">
-      <c r="A33" s="360" t="s">
+      <c r="B32" s="357"/>
+      <c r="C32" s="357"/>
+      <c r="D32" s="357"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
+      <c r="G32" s="357"/>
+      <c r="H32" s="357"/>
+      <c r="I32" s="357"/>
+      <c r="L32" s="357"/>
+      <c r="M32" s="357"/>
+    </row>
+    <row r="33" spans="1:13" s="359" customFormat="1">
+      <c r="A33" s="359" t="s">
         <v>2777</v>
       </c>
-      <c r="B33" s="359"/>
-      <c r="C33" s="359"/>
-      <c r="D33" s="359"/>
-      <c r="E33" s="359"/>
-      <c r="F33" s="359"/>
-      <c r="G33" s="359"/>
-      <c r="H33" s="359"/>
-      <c r="I33" s="359"/>
-      <c r="L33" s="359"/>
-      <c r="M33" s="359"/>
-    </row>
-    <row r="34" spans="1:13" s="360" customFormat="1">
-      <c r="A34" s="360" t="s">
+      <c r="B33" s="358"/>
+      <c r="C33" s="358"/>
+      <c r="D33" s="358"/>
+      <c r="E33" s="358"/>
+      <c r="F33" s="358"/>
+      <c r="G33" s="358"/>
+      <c r="H33" s="358"/>
+      <c r="I33" s="358"/>
+      <c r="L33" s="358"/>
+      <c r="M33" s="358"/>
+    </row>
+    <row r="34" spans="1:13" s="359" customFormat="1">
+      <c r="A34" s="359" t="s">
         <v>2778</v>
       </c>
-      <c r="B34" s="359"/>
-      <c r="C34" s="359"/>
-      <c r="D34" s="359"/>
-      <c r="E34" s="359"/>
-      <c r="F34" s="359"/>
-      <c r="G34" s="359"/>
-      <c r="H34" s="359"/>
-      <c r="I34" s="359"/>
-      <c r="L34" s="359"/>
-      <c r="M34" s="359"/>
-    </row>
-    <row r="35" spans="1:13" s="363" customFormat="1">
-      <c r="A35" s="361" t="s">
+      <c r="B34" s="358"/>
+      <c r="C34" s="358"/>
+      <c r="D34" s="358"/>
+      <c r="E34" s="358"/>
+      <c r="F34" s="358"/>
+      <c r="G34" s="358"/>
+      <c r="H34" s="358"/>
+      <c r="I34" s="358"/>
+      <c r="L34" s="358"/>
+      <c r="M34" s="358"/>
+    </row>
+    <row r="35" spans="1:13" s="362" customFormat="1">
+      <c r="A35" s="360" t="s">
         <v>2787</v>
       </c>
-      <c r="B35" s="362"/>
-      <c r="C35" s="362"/>
-      <c r="D35" s="362"/>
-      <c r="E35" s="362"/>
-      <c r="F35" s="362"/>
-      <c r="G35" s="362"/>
-      <c r="H35" s="362"/>
-      <c r="I35" s="362"/>
-      <c r="L35" s="362"/>
-      <c r="M35" s="362"/>
-    </row>
-    <row r="36" spans="1:13" s="363" customFormat="1">
-      <c r="A36" s="363" t="s">
+      <c r="B35" s="361"/>
+      <c r="C35" s="361"/>
+      <c r="D35" s="361"/>
+      <c r="E35" s="361"/>
+      <c r="F35" s="361"/>
+      <c r="G35" s="361"/>
+      <c r="H35" s="361"/>
+      <c r="I35" s="361"/>
+      <c r="L35" s="361"/>
+      <c r="M35" s="361"/>
+    </row>
+    <row r="36" spans="1:13" s="362" customFormat="1">
+      <c r="A36" s="362" t="s">
         <v>2777</v>
       </c>
-      <c r="B36" s="362"/>
-      <c r="C36" s="362"/>
-      <c r="D36" s="362"/>
-      <c r="E36" s="362"/>
-      <c r="F36" s="362"/>
-      <c r="G36" s="362"/>
-      <c r="H36" s="362"/>
-      <c r="I36" s="362"/>
-      <c r="L36" s="362"/>
-      <c r="M36" s="362"/>
-    </row>
-    <row r="37" spans="1:13" s="363" customFormat="1">
-      <c r="A37" s="363" t="s">
+      <c r="B36" s="361"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
+      <c r="G36" s="361"/>
+      <c r="H36" s="361"/>
+      <c r="I36" s="361"/>
+      <c r="L36" s="361"/>
+      <c r="M36" s="361"/>
+    </row>
+    <row r="37" spans="1:13" s="362" customFormat="1">
+      <c r="A37" s="362" t="s">
         <v>2778</v>
       </c>
-      <c r="B37" s="362"/>
-      <c r="C37" s="362"/>
-      <c r="D37" s="362"/>
-      <c r="E37" s="362"/>
-      <c r="F37" s="362"/>
-      <c r="G37" s="362"/>
-      <c r="H37" s="362"/>
-      <c r="I37" s="362"/>
-      <c r="L37" s="362"/>
-      <c r="M37" s="362"/>
+      <c r="B37" s="361"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+      <c r="G37" s="361"/>
+      <c r="H37" s="361"/>
+      <c r="I37" s="361"/>
+      <c r="L37" s="361"/>
+      <c r="M37" s="361"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44193,10 +44095,10 @@
     </row>
     <row r="5" spans="1:14" ht="0.75" customHeight="1"/>
     <row r="6" spans="1:14" s="4" customFormat="1">
-      <c r="A6" s="387" t="s">
+      <c r="A6" s="386" t="s">
         <v>3097</v>
       </c>
-      <c r="B6" s="387" t="s">
+      <c r="B6" s="386" t="s">
         <v>3099</v>
       </c>
       <c r="C6" s="22" t="s">
@@ -44214,10 +44116,10 @@
       <c r="G6" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="387" t="s">
+      <c r="H6" s="386" t="s">
         <v>3100</v>
       </c>
-      <c r="I6" s="387" t="s">
+      <c r="I6" s="386" t="s">
         <v>3101</v>
       </c>
       <c r="N6" s="4" t="s">
@@ -44317,7 +44219,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44367,10 +44269,10 @@
         <v>247</v>
       </c>
       <c r="H11" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44396,9 +44298,9 @@
         <v>247</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3622</v>
-      </c>
-      <c r="I12" s="4" t="s">
+        <v>3621</v>
+      </c>
+      <c r="I12" s="314" t="s">
         <v>2952</v>
       </c>
     </row>
@@ -44424,11 +44326,11 @@
       <c r="G13" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H13" s="221" t="s">
+      <c r="H13" s="220" t="s">
         <v>3326</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44456,7 +44358,7 @@
       <c r="H14" s="4" t="s">
         <v>3544</v>
       </c>
-      <c r="I14" s="221" t="s">
+      <c r="I14" s="220" t="s">
         <v>3564</v>
       </c>
       <c r="L14" s="3"/>
@@ -44562,10 +44464,10 @@
         <v>2339</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>3578</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>3579</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>3580</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>247</v>
@@ -44574,7 +44476,7 @@
         <v>2869</v>
       </c>
       <c r="I18" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44629,7 +44531,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="314" t="s">
         <v>2391</v>
       </c>
       <c r="B21" s="4">
@@ -44699,7 +44601,7 @@
       <c r="H23" t="s">
         <v>3310</v>
       </c>
-      <c r="I23" s="315" t="s">
+      <c r="I23" s="314" t="s">
         <v>2820</v>
       </c>
       <c r="L23" s="6"/>
@@ -44749,7 +44651,7 @@
       <c r="G25" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H25" s="221" t="s">
+      <c r="H25" s="220" t="s">
         <v>3160</v>
       </c>
       <c r="I25" s="4" t="s">
@@ -44808,7 +44710,7 @@
         <v>160</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="I27" t="s">
         <v>3280</v>
@@ -44879,7 +44781,7 @@
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" t="s">
+      <c r="A30" s="49" t="s">
         <v>2391</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -44900,7 +44802,7 @@
       <c r="G30" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="H30" s="315" t="s">
+      <c r="H30" s="314" t="s">
         <v>2773</v>
       </c>
       <c r="I30" t="s">
@@ -45051,7 +44953,7 @@
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="388" t="s">
+      <c r="A36" s="387" t="s">
         <v>3110</v>
       </c>
       <c r="B36" t="s">
@@ -45072,7 +44974,7 @@
       <c r="G36" t="s">
         <v>160</v>
       </c>
-      <c r="H36" s="388" t="s">
+      <c r="H36" s="387" t="s">
         <v>3155</v>
       </c>
       <c r="I36" t="s">
@@ -45109,7 +45011,7 @@
       </c>
     </row>
     <row r="42" spans="1:11" s="97" customFormat="1">
-      <c r="C42" s="311" t="s">
+      <c r="C42" s="310" t="s">
         <v>2894</v>
       </c>
       <c r="D42" s="97" t="s">
@@ -45125,8 +45027,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="265" customFormat="1" ht="15.5">
-      <c r="C44" s="265" t="s">
+    <row r="44" spans="1:11" s="264" customFormat="1" ht="15.5">
+      <c r="C44" s="264" t="s">
         <v>1624</v>
       </c>
     </row>
@@ -45152,7 +45054,7 @@
       <c r="G45" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H45" s="315" t="s">
+      <c r="H45" s="314" t="s">
         <v>2644</v>
       </c>
       <c r="I45" s="49" t="s">
@@ -45161,7 +45063,7 @@
       <c r="J45" t="s">
         <v>3308</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" s="49" t="s">
         <v>2945</v>
       </c>
     </row>
@@ -45271,7 +45173,7 @@
       <c r="A53" t="s">
         <v>2250</v>
       </c>
-      <c r="C53" s="261" t="s">
+      <c r="C53" s="260" t="s">
         <v>319</v>
       </c>
       <c r="D53" t="s">
@@ -45564,13 +45466,13 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="106" customFormat="1">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="408" t="s">
         <v>2721</v>
       </c>
       <c r="B2" s="106" t="s">
         <v>2949</v>
       </c>
-      <c r="C2" s="280" t="s">
+      <c r="C2" s="279" t="s">
         <v>257</v>
       </c>
       <c r="D2" s="106" t="s">
@@ -45582,20 +45484,20 @@
       <c r="F2" s="106" t="s">
         <v>1279</v>
       </c>
-      <c r="G2" s="214" t="s">
+      <c r="G2" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="306" t="s">
+      <c r="H2" s="305" t="s">
         <v>3142</v>
       </c>
-      <c r="I2" s="381" t="s">
+      <c r="I2" s="380" t="s">
         <v>2924</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45618,7 +45520,7 @@
       <c r="F4" s="30" t="s">
         <v>2575</v>
       </c>
-      <c r="G4" s="257" t="s">
+      <c r="G4" s="256" t="s">
         <v>273</v>
       </c>
       <c r="H4" s="32" t="s">
@@ -45628,7 +45530,7 @@
         <v>3276</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="K4" s="139" t="s">
         <v>3351</v>
@@ -45654,16 +45556,16 @@
       <c r="F5" s="30" t="s">
         <v>1102</v>
       </c>
-      <c r="G5" s="214" t="s">
+      <c r="G5" s="213" t="s">
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>3460</v>
       </c>
-      <c r="I5" s="315" t="s">
+      <c r="I5" s="314" t="s">
         <v>2883</v>
       </c>
-      <c r="J5" s="218" t="s">
+      <c r="J5" s="217" t="s">
         <v>2744</v>
       </c>
       <c r="K5" s="30" t="s">
@@ -45693,10 +45595,10 @@
       <c r="G6" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="414" t="s">
+      <c r="H6" s="413" t="s">
         <v>2905</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="413" t="s">
         <v>3089</v>
       </c>
       <c r="J6" s="30" t="s">
@@ -45732,13 +45634,13 @@
       <c r="H7" s="32" t="s">
         <v>3288</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="217" t="s">
         <v>2953</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>3022</v>
       </c>
-      <c r="K7" s="218" t="s">
+      <c r="K7" s="217" t="s">
         <v>2718</v>
       </c>
       <c r="M7" s="36"/>
@@ -45766,13 +45668,13 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="I8" s="32" t="s">
         <v>3071</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="K8" s="139" t="s">
         <v>3117</v>
@@ -45780,7 +45682,7 @@
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
-      <c r="A9" s="310" t="s">
+      <c r="A9" s="309" t="s">
         <v>2432</v>
       </c>
       <c r="B9" s="32" t="s">
@@ -45843,7 +45745,7 @@
       <c r="I10" t="s">
         <v>3123</v>
       </c>
-      <c r="J10" s="220" t="s">
+      <c r="J10" s="219" t="s">
         <v>3504</v>
       </c>
       <c r="K10" s="107" t="s">
@@ -45877,7 +45779,7 @@
         <v>3360</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="J11" s="107" t="s">
         <v>2919</v>
@@ -45910,7 +45812,7 @@
         <v>248</v>
       </c>
       <c r="H12" s="106" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="I12" s="106" t="s">
         <v>3563</v>
@@ -45981,13 +45883,13 @@
       <c r="G14" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="444" t="s">
-        <v>3631</v>
-      </c>
-      <c r="I14" s="207" t="s">
+      <c r="H14" s="443" t="s">
+        <v>3630</v>
+      </c>
+      <c r="I14" s="447" t="s">
         <v>2401</v>
       </c>
-      <c r="J14" s="107" t="s">
+      <c r="J14" s="408" t="s">
         <v>2925</v>
       </c>
       <c r="M14" s="36"/>
@@ -46023,7 +45925,7 @@
       <c r="J15" t="s">
         <v>3296</v>
       </c>
-      <c r="K15" s="409" t="s">
+      <c r="K15" s="408" t="s">
         <v>2821</v>
       </c>
       <c r="M15" s="36"/>
@@ -46063,7 +45965,7 @@
       <c r="C17" s="134" t="s">
         <v>1692</v>
       </c>
-      <c r="D17" s="255" t="s">
+      <c r="D17" s="254" t="s">
         <v>2801</v>
       </c>
       <c r="E17" s="140" t="s">
@@ -46084,13 +45986,13 @@
       <c r="J17" s="30" t="s">
         <v>2942</v>
       </c>
-      <c r="K17" s="221" t="s">
+      <c r="K17" s="220" t="s">
         <v>3481</v>
       </c>
       <c r="M17" s="34"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="310" t="s">
+      <c r="A18" s="309" t="s">
         <v>2408</v>
       </c>
       <c r="B18" t="s">
@@ -46120,8 +46022,8 @@
       <c r="J18" t="s">
         <v>3274</v>
       </c>
-      <c r="K18" s="441" t="s">
-        <v>3632</v>
+      <c r="K18" s="440" t="s">
+        <v>3631</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46151,9 +46053,9 @@
         <v>3192</v>
       </c>
       <c r="I19" t="s">
-        <v>3617</v>
-      </c>
-      <c r="J19" s="221" t="s">
+        <v>3616</v>
+      </c>
+      <c r="J19" s="220" t="s">
         <v>3205</v>
       </c>
       <c r="K19" s="49" t="s">
@@ -46162,7 +46064,7 @@
       <c r="M19" s="36"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="310" t="s">
+      <c r="A20" s="309" t="s">
         <v>3119</v>
       </c>
       <c r="B20" t="s">
@@ -46183,7 +46085,7 @@
       <c r="G20" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="326" t="s">
+      <c r="H20" s="325" t="s">
         <v>3493</v>
       </c>
       <c r="I20" t="s">
@@ -46235,26 +46137,26 @@
       <c r="C29" s="138" t="s">
         <v>964</v>
       </c>
-      <c r="D29" s="329" t="s">
+      <c r="D29" s="328" t="s">
         <v>2760</v>
       </c>
-      <c r="E29" s="329" t="s">
+      <c r="E29" s="328" t="s">
         <v>2274</v>
       </c>
       <c r="F29" s="145" t="s">
         <v>2275</v>
       </c>
-      <c r="G29" s="330" t="s">
+      <c r="G29" s="329" t="s">
         <v>731</v>
       </c>
-      <c r="M29" s="328"/>
-    </row>
-    <row r="30" spans="1:13" s="262" customFormat="1" ht="21">
-      <c r="C30" s="262" t="s">
+      <c r="M29" s="327"/>
+    </row>
+    <row r="30" spans="1:13" s="261" customFormat="1" ht="21">
+      <c r="C30" s="261" t="s">
         <v>1607</v>
       </c>
-      <c r="E30" s="263"/>
-      <c r="M30" s="264"/>
+      <c r="E30" s="262"/>
+      <c r="M30" s="263"/>
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
@@ -46281,7 +46183,7 @@
       <c r="M31" s="165"/>
     </row>
     <row r="32" spans="1:13" s="107" customFormat="1">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="413" t="s">
         <v>2391</v>
       </c>
       <c r="B32" s="32" t="s">
@@ -46361,7 +46263,7 @@
       <c r="C35" s="22" t="s">
         <v>1119</v>
       </c>
-      <c r="D35" s="410" t="s">
+      <c r="D35" s="409" t="s">
         <v>2238</v>
       </c>
       <c r="E35" s="140" t="s">
@@ -46507,15 +46409,15 @@
         <v>3236</v>
       </c>
       <c r="I43" s="139"/>
-      <c r="K43" s="242"/>
+      <c r="K43" s="241"/>
       <c r="M43" s="36"/>
     </row>
-    <row r="44" spans="1:13" s="277" customFormat="1" ht="21">
-      <c r="C44" s="277" t="s">
+    <row r="44" spans="1:13" s="276" customFormat="1" ht="21">
+      <c r="C44" s="276" t="s">
         <v>2292</v>
       </c>
       <c r="E44" s="181"/>
-      <c r="M44" s="278"/>
+      <c r="M44" s="277"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="180" t="s">
@@ -46550,7 +46452,7 @@
       </c>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="220"/>
+      <c r="A49" s="219"/>
       <c r="B49" s="32"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -46567,7 +46469,7 @@
       <c r="M50" s="36"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="220"/>
+      <c r="A51" s="219"/>
       <c r="B51" s="32"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -46745,7 +46647,7 @@
       </c>
     </row>
     <row r="75" spans="1:38">
-      <c r="C75" s="243" t="s">
+      <c r="C75" s="242" t="s">
         <v>1132</v>
       </c>
       <c r="D75" t="s">
@@ -46854,7 +46756,7 @@
     <row r="84" spans="1:13" s="139" customFormat="1">
       <c r="A84" s="30"/>
       <c r="B84" s="30"/>
-      <c r="C84" s="260" t="s">
+      <c r="C84" s="259" t="s">
         <v>1015</v>
       </c>
       <c r="D84" s="139" t="s">
@@ -46874,7 +46776,7 @@
     </row>
     <row r="85" spans="1:13">
       <c r="B85" s="107"/>
-      <c r="C85" s="224" t="s">
+      <c r="C85" s="223" t="s">
         <v>953</v>
       </c>
       <c r="D85" s="107" t="s">
@@ -46915,7 +46817,7 @@
     <row r="87" spans="1:13">
       <c r="A87" s="30"/>
       <c r="B87" s="30"/>
-      <c r="C87" s="243" t="s">
+      <c r="C87" s="242" t="s">
         <v>1025</v>
       </c>
       <c r="D87" t="s">
@@ -46953,7 +46855,7 @@
     <row r="89" spans="1:13">
       <c r="A89" s="107"/>
       <c r="B89" s="30"/>
-      <c r="C89" s="260" t="s">
+      <c r="C89" s="259" t="s">
         <v>1076</v>
       </c>
       <c r="D89" s="30" t="s">
@@ -47048,7 +46950,7 @@
       <c r="D94" s="7" t="s">
         <v>1658</v>
       </c>
-      <c r="E94" s="270" t="s">
+      <c r="E94" s="269" t="s">
         <v>1557</v>
       </c>
       <c r="F94" s="7" t="s">
@@ -47057,15 +46959,15 @@
       <c r="G94" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="M94" s="271"/>
-    </row>
-    <row r="102" spans="2:5" s="382" customFormat="1" ht="23.5">
-      <c r="B102" s="382" t="s">
+      <c r="M94" s="270"/>
+    </row>
+    <row r="102" spans="2:5" s="381" customFormat="1" ht="23.5">
+      <c r="B102" s="381" t="s">
         <v>3078</v>
       </c>
-      <c r="C102" s="383"/>
-      <c r="D102" s="384"/>
-      <c r="E102" s="385"/>
+      <c r="C102" s="382"/>
+      <c r="D102" s="383"/>
+      <c r="E102" s="384"/>
     </row>
     <row r="103" spans="2:5">
       <c r="C103" t="s">
@@ -47193,10 +47095,10 @@
       <c r="A2" t="s">
         <v>2693</v>
       </c>
-      <c r="B2" s="367" t="s">
+      <c r="B2" s="366" t="s">
         <v>2802</v>
       </c>
-      <c r="C2" s="367" t="s">
+      <c r="C2" s="366" t="s">
         <v>2803</v>
       </c>
       <c r="F2"/>
@@ -47307,7 +47209,7 @@
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="C12" s="239" t="s">
+      <c r="C12" s="238" t="s">
         <v>2016</v>
       </c>
     </row>
@@ -47315,8 +47217,8 @@
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="240"/>
-      <c r="C13" s="240"/>
+      <c r="B13" s="239"/>
+      <c r="C13" s="239"/>
       <c r="D13" s="131" t="s">
         <v>1176</v>
       </c>
@@ -47326,7 +47228,7 @@
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="236"/>
+      <c r="B14" s="235"/>
       <c r="D14" s="132" t="s">
         <v>1175</v>
       </c>
@@ -47335,7 +47237,7 @@
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="241"/>
+      <c r="B15" s="240"/>
       <c r="D15" s="5" t="s">
         <v>1178</v>
       </c>
@@ -47344,13 +47246,13 @@
       <c r="A16">
         <v>5</v>
       </c>
-      <c r="B16" s="233"/>
+      <c r="B16" s="232"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
         <v>6</v>
       </c>
-      <c r="B17" s="241"/>
+      <c r="B17" s="240"/>
       <c r="D17" s="179"/>
       <c r="F17" s="9"/>
     </row>
@@ -47358,7 +47260,7 @@
       <c r="A18">
         <v>7</v>
       </c>
-      <c r="B18" s="241"/>
+      <c r="B18" s="240"/>
       <c r="F18" s="2" t="s">
         <v>35</v>
       </c>
@@ -47367,7 +47269,7 @@
       <c r="A19">
         <v>8</v>
       </c>
-      <c r="B19" s="233"/>
+      <c r="B19" s="232"/>
       <c r="F19" s="1" t="s">
         <v>966</v>
       </c>
@@ -47379,7 +47281,7 @@
       <c r="A20">
         <v>9</v>
       </c>
-      <c r="B20" s="233"/>
+      <c r="B20" s="232"/>
       <c r="D20"/>
       <c r="F20" s="2" t="s">
         <v>940</v>
@@ -47398,7 +47300,7 @@
       <c r="A21">
         <v>10</v>
       </c>
-      <c r="B21" s="233"/>
+      <c r="B21" s="232"/>
       <c r="F21" s="2" t="s">
         <v>941</v>
       </c>
@@ -47413,7 +47315,7 @@
       <c r="A22">
         <v>11</v>
       </c>
-      <c r="B22" s="234"/>
+      <c r="B22" s="233"/>
       <c r="F22" s="2" t="s">
         <v>1150</v>
       </c>
@@ -47428,7 +47330,7 @@
       <c r="A23">
         <v>12</v>
       </c>
-      <c r="B23" s="235"/>
+      <c r="B23" s="234"/>
       <c r="C23" t="s">
         <v>197</v>
       </c>
@@ -47449,7 +47351,7 @@
       <c r="A25">
         <v>14</v>
       </c>
-      <c r="B25" s="239"/>
+      <c r="B25" s="238"/>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:9" ht="15.5">
@@ -47457,7 +47359,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="87"/>
-      <c r="F26" s="436"/>
+      <c r="F26" s="435"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
@@ -47549,7 +47451,7 @@
       </c>
     </row>
     <row r="46" spans="2:6" ht="15" thickBot="1">
-      <c r="B46" s="219" t="s">
+      <c r="B46" s="218" t="s">
         <v>242</v>
       </c>
     </row>
@@ -47592,7 +47494,7 @@
       </c>
     </row>
     <row r="55" spans="2:3">
-      <c r="B55" s="283" t="s">
+      <c r="B55" s="282" t="s">
         <v>1968</v>
       </c>
     </row>
@@ -47667,7 +47569,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="1.5" customHeight="1">
-      <c r="H1" s="251"/>
+      <c r="H1" s="250"/>
     </row>
     <row r="2" spans="1:11" hidden="1"/>
     <row r="3" spans="1:11" s="12" customFormat="1" ht="62.5" customHeight="1">
@@ -47689,38 +47591,38 @@
     <row r="5" spans="1:11" s="106" customFormat="1">
       <c r="C5" s="22"/>
     </row>
-    <row r="6" spans="1:11" s="251" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A6" s="304" t="s">
+    <row r="6" spans="1:11" s="250" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A6" s="303" t="s">
         <v>144</v>
       </c>
-      <c r="B6" s="251" t="s">
+      <c r="B6" s="250" t="s">
+        <v>3568</v>
+      </c>
+      <c r="C6" s="249" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D6" s="250" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E6" s="250" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F6" s="250" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G6" s="250" t="s">
+        <v>360</v>
+      </c>
+      <c r="H6" s="250" t="s">
+        <v>3383</v>
+      </c>
+      <c r="I6" s="247" t="s">
+        <v>3582</v>
+      </c>
+      <c r="J6" s="437" t="s">
         <v>3569</v>
       </c>
-      <c r="C6" s="250" t="s">
-        <v>1327</v>
-      </c>
-      <c r="D6" s="251" t="s">
-        <v>2131</v>
-      </c>
-      <c r="E6" s="251" t="s">
-        <v>1559</v>
-      </c>
-      <c r="F6" s="251" t="s">
-        <v>1560</v>
-      </c>
-      <c r="G6" s="251" t="s">
-        <v>360</v>
-      </c>
-      <c r="H6" s="251" t="s">
-        <v>3383</v>
-      </c>
-      <c r="I6" s="248" t="s">
-        <v>3583</v>
-      </c>
-      <c r="J6" s="438" t="s">
-        <v>3570</v>
-      </c>
-      <c r="K6" s="251" t="s">
+      <c r="K6" s="250" t="s">
         <v>480</v>
       </c>
     </row>
@@ -47729,38 +47631,38 @@
       <c r="D7" s="205"/>
       <c r="H7" s="30"/>
     </row>
-    <row r="8" spans="1:11" s="269" customFormat="1">
-      <c r="A8" s="304" t="s">
+    <row r="8" spans="1:11" s="268" customFormat="1">
+      <c r="A8" s="303" t="s">
         <v>2938</v>
       </c>
-      <c r="B8" s="268">
+      <c r="B8" s="267">
         <v>65509692</v>
       </c>
-      <c r="C8" s="259" t="s">
+      <c r="C8" s="258" t="s">
         <v>716</v>
       </c>
-      <c r="D8" s="259" t="s">
+      <c r="D8" s="258" t="s">
         <v>2253</v>
       </c>
-      <c r="E8" s="269" t="s">
+      <c r="E8" s="268" t="s">
         <v>1055</v>
       </c>
-      <c r="F8" s="269" t="s">
+      <c r="F8" s="268" t="s">
         <v>3367</v>
       </c>
-      <c r="G8" s="269" t="s">
+      <c r="G8" s="268" t="s">
         <v>696</v>
       </c>
-      <c r="H8" s="299" t="s">
+      <c r="H8" s="298" t="s">
         <v>3327</v>
       </c>
-      <c r="I8" s="375" t="s">
+      <c r="I8" s="374" t="s">
         <v>2911</v>
       </c>
-      <c r="J8" s="269" t="s">
+      <c r="J8" s="268" t="s">
         <v>3505</v>
       </c>
-      <c r="K8" s="269" t="s">
+      <c r="K8" s="268" t="s">
         <v>717</v>
       </c>
     </row>
@@ -47796,96 +47698,96 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="263" customFormat="1">
-      <c r="A10" s="325" t="s">
+    <row r="10" spans="1:11" s="262" customFormat="1">
+      <c r="A10" s="324" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="268">
+      <c r="B10" s="267">
         <v>64403333</v>
       </c>
-      <c r="C10" s="274" t="s">
+      <c r="C10" s="273" t="s">
         <v>670</v>
       </c>
-      <c r="D10" s="268" t="s">
+      <c r="D10" s="267" t="s">
         <v>1238</v>
       </c>
-      <c r="E10" s="267" t="s">
+      <c r="E10" s="266" t="s">
         <v>1457</v>
       </c>
-      <c r="F10" s="267" t="s">
+      <c r="F10" s="266" t="s">
         <v>3397</v>
       </c>
-      <c r="G10" s="267" t="s">
+      <c r="G10" s="266" t="s">
         <v>962</v>
       </c>
-      <c r="K10" s="263" t="s">
+      <c r="K10" s="262" t="s">
         <v>1239</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="249" customFormat="1">
-      <c r="A11" s="304" t="s">
+    <row r="11" spans="1:11" s="248" customFormat="1">
+      <c r="A11" s="303" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="244" t="s">
+      <c r="B11" s="243" t="s">
         <v>2915</v>
       </c>
-      <c r="C11" s="259" t="s">
+      <c r="C11" s="258" t="s">
         <v>487</v>
       </c>
-      <c r="D11" s="244" t="s">
+      <c r="D11" s="243" t="s">
         <v>1231</v>
       </c>
-      <c r="E11" s="245" t="s">
+      <c r="E11" s="244" t="s">
         <v>1470</v>
       </c>
-      <c r="F11" s="245" t="s">
+      <c r="F11" s="244" t="s">
         <v>1471</v>
       </c>
-      <c r="G11" s="245" t="s">
+      <c r="G11" s="244" t="s">
         <v>696</v>
       </c>
-      <c r="H11" s="268" t="s">
+      <c r="H11" s="267" t="s">
         <v>3021</v>
       </c>
-      <c r="I11" s="375" t="s">
+      <c r="I11" s="374" t="s">
         <v>2640</v>
       </c>
-      <c r="J11" s="268" t="s">
-        <v>3623</v>
-      </c>
-      <c r="K11" s="249" t="s">
+      <c r="J11" s="267" t="s">
+        <v>3622</v>
+      </c>
+      <c r="K11" s="248" t="s">
         <v>1240</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="266" t="s">
+      <c r="A12" s="265" t="s">
         <v>2991</v>
       </c>
-      <c r="B12" s="266">
+      <c r="B12" s="265">
         <v>62272941</v>
       </c>
       <c r="C12" s="194" t="s">
         <v>496</v>
       </c>
-      <c r="D12" s="216" t="s">
+      <c r="D12" s="215" t="s">
         <v>2002</v>
       </c>
-      <c r="E12" s="217" t="s">
+      <c r="E12" s="216" t="s">
         <v>1441</v>
       </c>
-      <c r="F12" s="217" t="s">
+      <c r="F12" s="216" t="s">
         <v>1440</v>
       </c>
-      <c r="G12" s="217" t="s">
+      <c r="G12" s="216" t="s">
         <v>696</v>
       </c>
-      <c r="H12" s="375" t="s">
+      <c r="H12" s="374" t="s">
         <v>2867</v>
       </c>
-      <c r="I12" s="216" t="s">
+      <c r="I12" s="215" t="s">
         <v>3398</v>
       </c>
-      <c r="J12" s="273" t="s">
+      <c r="J12" s="280" t="s">
         <v>2929</v>
       </c>
       <c r="K12" s="183" t="s">
@@ -47893,394 +47795,394 @@
       </c>
     </row>
     <row r="13" spans="1:11" s="183" customFormat="1">
-      <c r="A13" s="381" t="s">
+      <c r="A13" s="380" t="s">
         <v>2426</v>
       </c>
-      <c r="B13" s="216">
+      <c r="B13" s="215">
         <v>64403333</v>
       </c>
-      <c r="C13" s="216" t="s">
+      <c r="C13" s="215" t="s">
         <v>532</v>
       </c>
-      <c r="D13" s="216" t="s">
+      <c r="D13" s="215" t="s">
         <v>1250</v>
       </c>
-      <c r="E13" s="217" t="s">
+      <c r="E13" s="216" t="s">
         <v>3090</v>
       </c>
-      <c r="F13" s="217" t="s">
+      <c r="F13" s="216" t="s">
         <v>3091</v>
       </c>
-      <c r="G13" s="217" t="s">
+      <c r="G13" s="216" t="s">
         <v>962</v>
       </c>
       <c r="K13" s="183" t="s">
         <v>1249</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="226" customFormat="1">
-      <c r="A14" s="226" t="s">
+    <row r="14" spans="1:11" s="225" customFormat="1">
+      <c r="A14" s="225" t="s">
         <v>3141</v>
       </c>
-      <c r="B14" s="226">
+      <c r="B14" s="225">
         <v>69964218</v>
       </c>
-      <c r="C14" s="225" t="s">
+      <c r="C14" s="224" t="s">
         <v>338</v>
       </c>
-      <c r="D14" s="226" t="s">
+      <c r="D14" s="225" t="s">
         <v>2572</v>
       </c>
-      <c r="E14" s="226" t="s">
+      <c r="E14" s="225" t="s">
         <v>1832</v>
       </c>
-      <c r="F14" s="226" t="s">
+      <c r="F14" s="225" t="s">
         <v>1834</v>
       </c>
-      <c r="G14" s="226" t="s">
+      <c r="G14" s="225" t="s">
         <v>696</v>
       </c>
-      <c r="H14" s="226" t="s">
+      <c r="H14" s="225" t="s">
         <v>2129</v>
       </c>
-      <c r="I14" s="226" t="s">
+      <c r="I14" s="225" t="s">
         <v>3315</v>
       </c>
-      <c r="J14" s="226" t="s">
+      <c r="J14" s="225" t="s">
         <v>3139</v>
       </c>
-      <c r="K14" s="226" t="s">
+      <c r="K14" s="225" t="s">
         <v>1359</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="183" customFormat="1">
-      <c r="A15" s="276" t="s">
+      <c r="A15" s="275" t="s">
         <v>2554</v>
       </c>
-      <c r="B15" s="216" t="s">
+      <c r="B15" s="215" t="s">
         <v>2058</v>
       </c>
       <c r="C15" s="191" t="s">
         <v>502</v>
       </c>
-      <c r="D15" s="216" t="s">
+      <c r="D15" s="215" t="s">
         <v>2057</v>
       </c>
-      <c r="E15" s="217" t="s">
+      <c r="E15" s="216" t="s">
         <v>3367</v>
       </c>
-      <c r="F15" s="217" t="s">
+      <c r="F15" s="216" t="s">
         <v>1481</v>
       </c>
-      <c r="G15" s="217" t="s">
+      <c r="G15" s="216" t="s">
         <v>696</v>
       </c>
-      <c r="H15" s="276" t="s">
+      <c r="H15" s="275" t="s">
         <v>3227</v>
       </c>
-      <c r="I15" s="216" t="s">
+      <c r="I15" s="215" t="s">
         <v>2921</v>
       </c>
-      <c r="J15" s="266" t="s">
+      <c r="J15" s="265" t="s">
         <v>3361</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1242</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="263" customFormat="1">
-      <c r="A16" s="218" t="s">
+    <row r="16" spans="1:11" s="262" customFormat="1">
+      <c r="A16" s="217" t="s">
         <v>2705</v>
       </c>
-      <c r="B16" s="268" t="s">
+      <c r="B16" s="267" t="s">
         <v>2706</v>
       </c>
-      <c r="C16" s="274" t="s">
+      <c r="C16" s="273" t="s">
         <v>1344</v>
       </c>
-      <c r="D16" s="263" t="s">
+      <c r="D16" s="262" t="s">
         <v>2571</v>
       </c>
-      <c r="E16" s="263" t="s">
+      <c r="E16" s="262" t="s">
         <v>3218</v>
       </c>
-      <c r="F16" s="263" t="s">
+      <c r="F16" s="262" t="s">
         <v>3219</v>
       </c>
-      <c r="G16" s="263" t="s">
+      <c r="G16" s="262" t="s">
         <v>696</v>
       </c>
-      <c r="H16" s="218" t="s">
+      <c r="H16" s="217" t="s">
         <v>3319</v>
       </c>
-      <c r="I16" s="381" t="s">
+      <c r="I16" s="380" t="s">
         <v>2658</v>
       </c>
-      <c r="J16" s="218" t="s">
+      <c r="J16" s="217" t="s">
         <v>2402</v>
       </c>
-      <c r="K16" s="263" t="s">
+      <c r="K16" s="262" t="s">
         <v>1487</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="268" customFormat="1">
-      <c r="A17" s="275" t="s">
+    <row r="17" spans="1:11" s="267" customFormat="1">
+      <c r="A17" s="274" t="s">
         <v>2696</v>
       </c>
-      <c r="B17" s="275">
+      <c r="B17" s="274">
         <v>64403333</v>
       </c>
-      <c r="C17" s="259" t="s">
+      <c r="C17" s="258" t="s">
         <v>1544</v>
       </c>
-      <c r="D17" s="268" t="s">
+      <c r="D17" s="267" t="s">
         <v>1506</v>
       </c>
-      <c r="E17" s="267" t="s">
+      <c r="E17" s="266" t="s">
         <v>1832</v>
       </c>
-      <c r="F17" s="267" t="s">
+      <c r="F17" s="266" t="s">
         <v>1833</v>
       </c>
-      <c r="G17" s="267" t="s">
+      <c r="G17" s="266" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="268" customFormat="1">
-      <c r="A18" s="269" t="s">
+    <row r="18" spans="1:11" s="267" customFormat="1">
+      <c r="A18" s="268" t="s">
         <v>3119</v>
       </c>
-      <c r="B18" s="269">
+      <c r="B18" s="268">
         <v>65325884</v>
       </c>
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="267" t="s">
         <v>582</v>
       </c>
-      <c r="D18" s="268" t="s">
+      <c r="D18" s="267" t="s">
         <v>2139</v>
       </c>
-      <c r="E18" s="268" t="s">
+      <c r="E18" s="267" t="s">
         <v>1944</v>
       </c>
-      <c r="F18" s="268" t="s">
+      <c r="F18" s="267" t="s">
         <v>1710</v>
       </c>
-      <c r="G18" s="267" t="s">
+      <c r="G18" s="266" t="s">
         <v>696</v>
       </c>
-      <c r="J18" s="291"/>
-      <c r="K18" s="268" t="s">
+      <c r="J18" s="290"/>
+      <c r="K18" s="267" t="s">
         <v>1747</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="268" customFormat="1">
-      <c r="A19" s="268" t="s">
+    <row r="19" spans="1:11" s="267" customFormat="1">
+      <c r="A19" s="217" t="s">
         <v>2391</v>
       </c>
-      <c r="B19" s="268" t="s">
+      <c r="B19" s="267" t="s">
         <v>2922</v>
       </c>
-      <c r="C19" s="268" t="s">
+      <c r="C19" s="267" t="s">
         <v>506</v>
       </c>
-      <c r="D19" s="268" t="s">
+      <c r="D19" s="267" t="s">
         <v>1926</v>
       </c>
-      <c r="E19" s="267" t="s">
+      <c r="E19" s="266" t="s">
         <v>2931</v>
       </c>
-      <c r="F19" s="268" t="s">
+      <c r="F19" s="267" t="s">
         <v>2917</v>
       </c>
-      <c r="G19" s="267" t="s">
+      <c r="G19" s="266" t="s">
         <v>696</v>
       </c>
-      <c r="H19" s="275" t="s">
+      <c r="H19" s="274" t="s">
         <v>3529</v>
       </c>
-      <c r="I19" s="268" t="s">
+      <c r="I19" s="267" t="s">
         <v>3322</v>
       </c>
-      <c r="J19" s="268" t="s">
+      <c r="J19" s="267" t="s">
         <v>3471</v>
       </c>
-      <c r="K19" s="268" t="s">
+      <c r="K19" s="267" t="s">
         <v>1707</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="268" t="s">
+      <c r="A20" s="267" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="263" t="s">
+      <c r="B20" s="262" t="s">
         <v>1919</v>
       </c>
-      <c r="C20" s="259" t="s">
+      <c r="C20" s="258" t="s">
         <v>763</v>
       </c>
-      <c r="D20" s="268" t="s">
+      <c r="D20" s="267" t="s">
         <v>1918</v>
       </c>
-      <c r="E20" s="268" t="s">
+      <c r="E20" s="267" t="s">
         <v>1772</v>
       </c>
-      <c r="F20" s="268" t="s">
+      <c r="F20" s="267" t="s">
         <v>1719</v>
       </c>
-      <c r="G20" s="267" t="s">
+      <c r="G20" s="266" t="s">
         <v>696</v>
       </c>
       <c r="H20" s="49" t="s">
         <v>2773</v>
       </c>
-      <c r="I20" s="263" t="s">
-        <v>3610</v>
+      <c r="I20" s="262" t="s">
+        <v>3609</v>
       </c>
       <c r="J20" s="49"/>
-      <c r="K20" s="268" t="s">
+      <c r="K20" s="267" t="s">
         <v>1720</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="263" customFormat="1">
-      <c r="A21" s="275" t="s">
+    <row r="21" spans="1:11" s="262" customFormat="1">
+      <c r="A21" s="274" t="s">
         <v>3137</v>
       </c>
-      <c r="B21" s="263" t="s">
+      <c r="B21" s="262" t="s">
         <v>2500</v>
       </c>
-      <c r="C21" s="259" t="s">
+      <c r="C21" s="258" t="s">
         <v>844</v>
       </c>
-      <c r="D21" s="268" t="s">
+      <c r="D21" s="267" t="s">
         <v>2472</v>
       </c>
-      <c r="E21" s="268" t="s">
+      <c r="E21" s="267" t="s">
         <v>1862</v>
       </c>
-      <c r="F21" s="268" t="s">
+      <c r="F21" s="267" t="s">
         <v>1863</v>
       </c>
-      <c r="G21" s="268" t="s">
+      <c r="G21" s="267" t="s">
         <v>696</v>
       </c>
-      <c r="H21" s="263" t="s">
+      <c r="H21" s="49" t="s">
         <v>2944</v>
       </c>
-      <c r="I21" s="268" t="s">
+      <c r="I21" s="267" t="s">
         <v>3204</v>
       </c>
-      <c r="J21" s="263" t="s">
+      <c r="J21" s="262" t="s">
         <v>3558</v>
       </c>
-      <c r="K21" s="268" t="s">
+      <c r="K21" s="267" t="s">
         <v>1838</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="263" customFormat="1">
-      <c r="A22" s="249" t="s">
+    <row r="22" spans="1:11" s="262" customFormat="1">
+      <c r="A22" s="248" t="s">
         <v>3491</v>
       </c>
-      <c r="B22" s="263" t="s">
+      <c r="B22" s="262" t="s">
         <v>2558</v>
       </c>
-      <c r="C22" s="263" t="s">
+      <c r="C22" s="262" t="s">
         <v>859</v>
       </c>
-      <c r="D22" s="263" t="s">
+      <c r="D22" s="262" t="s">
         <v>3028</v>
       </c>
-      <c r="E22" s="263" t="s">
+      <c r="E22" s="262" t="s">
         <v>1862</v>
       </c>
-      <c r="F22" s="263" t="s">
+      <c r="F22" s="262" t="s">
         <v>1863</v>
       </c>
-      <c r="G22" s="263" t="s">
+      <c r="G22" s="262" t="s">
         <v>696</v>
       </c>
-      <c r="H22" s="263" t="s">
+      <c r="H22" s="262" t="s">
         <v>3171</v>
       </c>
-      <c r="I22" s="263" t="s">
+      <c r="I22" s="262" t="s">
         <v>3162</v>
       </c>
-      <c r="J22" s="263" t="s">
+      <c r="J22" s="262" t="s">
         <v>3116</v>
       </c>
-      <c r="K22" s="263" t="s">
+      <c r="K22" s="262" t="s">
         <v>1884</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="268" customFormat="1">
-      <c r="A24" s="415" t="s">
+    <row r="24" spans="1:11" s="267" customFormat="1">
+      <c r="A24" s="414" t="s">
         <v>2771</v>
       </c>
-      <c r="B24" s="313" t="s">
+      <c r="B24" s="312" t="s">
         <v>2602</v>
       </c>
-      <c r="C24" s="263" t="s">
+      <c r="C24" s="262" t="s">
         <v>1885</v>
       </c>
-      <c r="D24" s="263" t="s">
+      <c r="D24" s="262" t="s">
         <v>2133</v>
       </c>
-      <c r="E24" s="268" t="s">
+      <c r="E24" s="267" t="s">
         <v>1862</v>
       </c>
-      <c r="F24" s="268" t="s">
+      <c r="F24" s="267" t="s">
         <v>1863</v>
       </c>
-      <c r="G24" s="268" t="s">
+      <c r="G24" s="267" t="s">
         <v>696</v>
       </c>
-      <c r="H24" s="268" t="s">
+      <c r="H24" s="267" t="s">
         <v>3231</v>
       </c>
-      <c r="I24" s="268" t="s">
-        <v>3588</v>
-      </c>
-      <c r="J24" s="268" t="s">
+      <c r="I24" s="267" t="s">
+        <v>3587</v>
+      </c>
+      <c r="J24" s="267" t="s">
         <v>3554</v>
       </c>
-      <c r="K24" s="263" t="s">
+      <c r="K24" s="262" t="s">
         <v>1886</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="263" customFormat="1">
-      <c r="A29" s="263" t="s">
+    <row r="29" spans="1:11" s="262" customFormat="1">
+      <c r="A29" s="262" t="s">
         <v>2943</v>
       </c>
-      <c r="B29" s="263">
+      <c r="B29" s="262">
         <v>69184177</v>
       </c>
-      <c r="C29" s="263" t="s">
+      <c r="C29" s="262" t="s">
         <v>853</v>
       </c>
-      <c r="D29" s="268" t="s">
+      <c r="D29" s="267" t="s">
         <v>2256</v>
       </c>
-      <c r="E29" s="263" t="s">
+      <c r="E29" s="262" t="s">
         <v>1862</v>
       </c>
-      <c r="F29" s="263" t="s">
+      <c r="F29" s="262" t="s">
         <v>1863</v>
       </c>
-      <c r="G29" s="263" t="s">
+      <c r="G29" s="262" t="s">
         <v>962</v>
       </c>
-      <c r="K29" s="268" t="s">
+      <c r="K29" s="267" t="s">
         <v>1883</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="263" customFormat="1">
+    <row r="31" spans="1:11" s="262" customFormat="1">
       <c r="A31" s="97" t="s">
         <v>2935</v>
       </c>
       <c r="B31" s="97"/>
-      <c r="C31" s="263" t="s">
+      <c r="C31" s="262" t="s">
         <v>851</v>
       </c>
-      <c r="D31" s="268" t="s">
+      <c r="D31" s="267" t="s">
         <v>2976</v>
       </c>
       <c r="E31" s="97" t="s">
@@ -48295,7 +48197,7 @@
       <c r="H31" s="97"/>
       <c r="I31" s="97"/>
       <c r="J31" s="97"/>
-      <c r="K31" s="268" t="s">
+      <c r="K31" s="267" t="s">
         <v>1865</v>
       </c>
     </row>
@@ -48309,13 +48211,13 @@
       <c r="D32" s="145" t="s">
         <v>2132</v>
       </c>
-      <c r="E32" s="289" t="s">
+      <c r="E32" s="288" t="s">
         <v>2936</v>
       </c>
-      <c r="F32" s="289" t="s">
+      <c r="F32" s="288" t="s">
         <v>2937</v>
       </c>
-      <c r="G32" s="289" t="s">
+      <c r="G32" s="288" t="s">
         <v>696</v>
       </c>
       <c r="H32" s="145"/>
@@ -48323,174 +48225,174 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="244" customFormat="1">
+    <row r="33" spans="1:11" s="243" customFormat="1">
       <c r="A33" s="145" t="s">
         <v>2935</v>
       </c>
-      <c r="C33" s="274" t="s">
+      <c r="C33" s="273" t="s">
         <v>642</v>
       </c>
-      <c r="D33" s="250" t="s">
+      <c r="D33" s="249" t="s">
         <v>3027</v>
       </c>
-      <c r="E33" s="246" t="s">
+      <c r="E33" s="245" t="s">
         <v>2576</v>
       </c>
-      <c r="F33" s="246" t="s">
+      <c r="F33" s="245" t="s">
         <v>1779</v>
       </c>
-      <c r="G33" s="246" t="s">
+      <c r="G33" s="245" t="s">
         <v>714</v>
       </c>
-      <c r="H33" s="268"/>
-      <c r="I33" s="268"/>
-    </row>
-    <row r="35" spans="1:11" s="268" customFormat="1">
+      <c r="H33" s="267"/>
+      <c r="I33" s="267"/>
+    </row>
+    <row r="35" spans="1:11" s="267" customFormat="1">
       <c r="A35" s="145" t="s">
         <v>2430</v>
       </c>
       <c r="B35" s="145" t="s">
         <v>2122</v>
       </c>
-      <c r="C35" s="268" t="s">
+      <c r="C35" s="267" t="s">
         <v>454</v>
       </c>
-      <c r="D35" s="268" t="s">
+      <c r="D35" s="267" t="s">
         <v>2429</v>
       </c>
-      <c r="E35" s="269" t="s">
+      <c r="E35" s="268" t="s">
         <v>1469</v>
       </c>
-      <c r="F35" s="269" t="s">
+      <c r="F35" s="268" t="s">
         <v>1502</v>
       </c>
-      <c r="G35" s="269" t="s">
+      <c r="G35" s="268" t="s">
         <v>265</v>
       </c>
-      <c r="J35" s="299"/>
-      <c r="K35" s="268" t="s">
+      <c r="J35" s="298"/>
+      <c r="K35" s="267" t="s">
         <v>1500</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="249" customFormat="1">
+    <row r="36" spans="1:11" s="248" customFormat="1">
       <c r="A36" s="97" t="s">
         <v>1153</v>
       </c>
       <c r="B36" s="97" t="s">
         <v>2122</v>
       </c>
-      <c r="C36" s="252" t="s">
+      <c r="C36" s="251" t="s">
         <v>557</v>
       </c>
-      <c r="D36" s="244" t="s">
+      <c r="D36" s="243" t="s">
         <v>1328</v>
       </c>
-      <c r="E36" s="245" t="s">
+      <c r="E36" s="244" t="s">
         <v>1935</v>
       </c>
-      <c r="F36" s="245" t="s">
+      <c r="F36" s="244" t="s">
         <v>1779</v>
       </c>
-      <c r="G36" s="245" t="s">
+      <c r="G36" s="244" t="s">
         <v>962</v>
       </c>
-      <c r="K36" s="249" t="s">
+      <c r="K36" s="248" t="s">
         <v>1253</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="249" customFormat="1">
+    <row r="37" spans="1:11" s="248" customFormat="1">
       <c r="A37" s="97" t="s">
         <v>1153</v>
       </c>
       <c r="B37" s="97" t="s">
         <v>2122</v>
       </c>
-      <c r="C37" s="247" t="s">
+      <c r="C37" s="246" t="s">
         <v>560</v>
       </c>
-      <c r="D37" s="249" t="s">
+      <c r="D37" s="248" t="s">
         <v>1259</v>
       </c>
-      <c r="E37" s="244" t="s">
+      <c r="E37" s="243" t="s">
         <v>1462</v>
       </c>
-      <c r="F37" s="245" t="s">
+      <c r="F37" s="244" t="s">
         <v>1461</v>
       </c>
-      <c r="G37" s="244" t="s">
+      <c r="G37" s="243" t="s">
         <v>962</v>
       </c>
-      <c r="K37" s="249" t="s">
+      <c r="K37" s="248" t="s">
         <v>1258</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="268" customFormat="1">
+    <row r="38" spans="1:11" s="267" customFormat="1">
       <c r="A38" s="145" t="s">
         <v>1153</v>
       </c>
       <c r="B38" s="145" t="s">
         <v>2122</v>
       </c>
-      <c r="C38" s="274" t="s">
+      <c r="C38" s="273" t="s">
         <v>504</v>
       </c>
-      <c r="D38" s="268" t="s">
+      <c r="D38" s="267" t="s">
         <v>1835</v>
       </c>
-      <c r="E38" s="268" t="s">
+      <c r="E38" s="267" t="s">
         <v>1636</v>
       </c>
-      <c r="F38" s="268" t="s">
+      <c r="F38" s="267" t="s">
         <v>1642</v>
       </c>
-      <c r="G38" s="268" t="s">
+      <c r="G38" s="267" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="268" customFormat="1">
+    <row r="39" spans="1:11" s="267" customFormat="1">
       <c r="A39" s="145" t="s">
         <v>2439</v>
       </c>
       <c r="B39" s="145" t="s">
         <v>2134</v>
       </c>
-      <c r="C39" s="268" t="s">
+      <c r="C39" s="267" t="s">
         <v>778</v>
       </c>
-      <c r="D39" s="268" t="s">
+      <c r="D39" s="267" t="s">
         <v>2135</v>
       </c>
       <c r="E39" s="145" t="s">
         <v>1677</v>
       </c>
       <c r="F39" s="145"/>
-      <c r="G39" s="289"/>
+      <c r="G39" s="288"/>
       <c r="H39" s="97"/>
-      <c r="I39" s="263"/>
-      <c r="K39" s="268" t="s">
+      <c r="I39" s="262"/>
+      <c r="K39" s="267" t="s">
         <v>1679</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="263" customFormat="1">
+    <row r="40" spans="1:11" s="262" customFormat="1">
       <c r="A40" s="97" t="s">
         <v>1153</v>
       </c>
       <c r="B40" s="97" t="s">
         <v>2122</v>
       </c>
-      <c r="C40" s="263" t="s">
+      <c r="C40" s="262" t="s">
         <v>1828</v>
       </c>
-      <c r="D40" s="263" t="s">
+      <c r="D40" s="262" t="s">
         <v>1506</v>
       </c>
-      <c r="E40" s="268" t="s">
+      <c r="E40" s="267" t="s">
         <v>1830</v>
       </c>
-      <c r="F40" s="268" t="s">
+      <c r="F40" s="267" t="s">
         <v>1831</v>
       </c>
-      <c r="G40" s="268" t="s">
+      <c r="G40" s="267" t="s">
         <v>962</v>
       </c>
     </row>
@@ -48515,7 +48417,7 @@
     <row r="49" spans="1:11" s="30" customFormat="1">
       <c r="E49" s="173"/>
       <c r="G49" s="173"/>
-      <c r="H49" s="290"/>
+      <c r="H49" s="289"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="30"/>
@@ -48544,13 +48446,13 @@
       <c r="K54" s="30"/>
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
-      <c r="C55" s="221"/>
+      <c r="C55" s="220"/>
       <c r="H55"/>
       <c r="I55"/>
       <c r="J55"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="J62" s="220"/>
+      <c r="J62" s="219"/>
     </row>
     <row r="66" spans="5:5">
       <c r="E66" s="30"/>
@@ -48692,7 +48594,7 @@
       <c r="I2" t="s">
         <v>3510</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="49" t="s">
         <v>2934</v>
       </c>
       <c r="L2" s="36" t="s">
@@ -48700,7 +48602,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="4" customFormat="1">
-      <c r="A3" s="440" t="s">
+      <c r="A3" s="439" t="s">
         <v>2923</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -48754,12 +48656,12 @@
         <v>326</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="H4" t="s">
         <v>2266</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="314" t="s">
         <v>2939</v>
       </c>
       <c r="J4" s="49" t="s">
@@ -48797,7 +48699,7 @@
       <c r="I5" s="75" t="s">
         <v>3390</v>
       </c>
-      <c r="J5" s="221" t="s">
+      <c r="J5" s="220" t="s">
         <v>2906</v>
       </c>
       <c r="L5" s="39"/>
@@ -48857,7 +48759,7 @@
         <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>3507</v>
@@ -48873,7 +48775,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="315" t="s">
+      <c r="A8" s="314" t="s">
         <v>2426</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -48895,7 +48797,7 @@
         <v>3004</v>
       </c>
       <c r="H8" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="I8" t="s">
         <v>2966</v>
@@ -48927,13 +48829,13 @@
       <c r="G9" t="s">
         <v>3360</v>
       </c>
-      <c r="H9" s="221" t="s">
+      <c r="H9" s="220" t="s">
         <v>3159</v>
       </c>
-      <c r="I9" s="315" t="s">
+      <c r="I9" s="314" t="s">
         <v>2838</v>
       </c>
-      <c r="J9" s="221" t="s">
+      <c r="J9" s="220" t="s">
         <v>3134</v>
       </c>
     </row>
@@ -48948,7 +48850,7 @@
         <v>2317</v>
       </c>
       <c r="D10" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="E10" t="s">
         <v>2286</v>
@@ -48960,7 +48862,7 @@
         <v>3374</v>
       </c>
       <c r="H10" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="I10" t="s">
         <v>3409</v>
@@ -49096,13 +48998,13 @@
     <row r="17" spans="2:12">
       <c r="L17" s="36"/>
     </row>
-    <row r="20" spans="2:12" s="403" customFormat="1" ht="23.5">
-      <c r="B20" s="403" t="s">
+    <row r="20" spans="2:12" s="402" customFormat="1" ht="23.5">
+      <c r="B20" s="402" t="s">
         <v>3252</v>
       </c>
-      <c r="C20" s="404"/>
-      <c r="D20" s="405"/>
-      <c r="E20" s="406"/>
+      <c r="C20" s="403"/>
+      <c r="D20" s="404"/>
+      <c r="E20" s="405"/>
     </row>
     <row r="21" spans="2:12">
       <c r="C21" t="s">
@@ -49130,31 +49032,31 @@
     </row>
     <row r="24" spans="2:12">
       <c r="C24" s="1"/>
-      <c r="D24" s="392"/>
+      <c r="D24" s="391"/>
       <c r="E24" s="30"/>
       <c r="L24"/>
     </row>
     <row r="25" spans="2:12">
-      <c r="C25" s="292"/>
-      <c r="D25" s="293"/>
+      <c r="C25" s="291"/>
+      <c r="D25" s="292"/>
     </row>
     <row r="26" spans="2:12">
-      <c r="C26" s="294"/>
-      <c r="D26" s="293"/>
+      <c r="C26" s="293"/>
+      <c r="D26" s="292"/>
     </row>
     <row r="27" spans="2:12" s="4" customFormat="1">
-      <c r="C27" s="295"/>
-      <c r="D27" s="293"/>
+      <c r="C27" s="294"/>
+      <c r="D27" s="292"/>
       <c r="H27"/>
       <c r="L27" s="39"/>
     </row>
     <row r="29" spans="2:12">
-      <c r="C29" s="296"/>
-      <c r="D29" s="296"/>
+      <c r="C29" s="295"/>
+      <c r="D29" s="295"/>
     </row>
     <row r="30" spans="2:12">
-      <c r="C30" s="297"/>
-      <c r="D30" s="296"/>
+      <c r="C30" s="296"/>
+      <c r="D30" s="295"/>
     </row>
     <row r="40" spans="3:12" s="24" customFormat="1" ht="34" customHeight="1">
       <c r="C40" s="40" t="s">
@@ -49492,15 +49394,15 @@
       <c r="D13" t="s">
         <v>2564</v>
       </c>
-      <c r="E13" s="441" t="s">
+      <c r="E13" s="440" t="s">
+        <v>3628</v>
+      </c>
+      <c r="F13" t="s">
         <v>3629</v>
       </c>
-      <c r="F13" t="s">
-        <v>3630</v>
-      </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="217" t="s">
         <v>2721</v>
       </c>
       <c r="B14" s="30">
@@ -49656,13 +49558,13 @@
       </c>
     </row>
     <row r="31" spans="1:6"/>
-    <row r="32" spans="1:6" s="314" customFormat="1" ht="15.5">
-      <c r="C32" s="314" t="s">
+    <row r="32" spans="1:6" s="313" customFormat="1" ht="15.5">
+      <c r="C32" s="313" t="s">
         <v>2482</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="C33" s="254" t="s">
+      <c r="C33" s="253" t="s">
         <v>2909</v>
       </c>
       <c r="D33" s="30" t="s">
@@ -49680,8 +49582,8 @@
         <v>2614</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="298" customFormat="1" ht="18">
-      <c r="C39" s="298" t="s">
+    <row r="39" spans="1:7" s="297" customFormat="1" ht="18">
+      <c r="C39" s="297" t="s">
         <v>2141</v>
       </c>
     </row>
@@ -49722,7 +49624,7 @@
       <c r="A43" s="97" t="s">
         <v>3032</v>
       </c>
-      <c r="C43" s="255" t="s">
+      <c r="C43" s="254" t="s">
         <v>1071</v>
       </c>
       <c r="D43" s="30" t="s">
@@ -49733,7 +49635,7 @@
       <c r="A44" s="97" t="s">
         <v>3032</v>
       </c>
-      <c r="C44" s="380" t="s">
+      <c r="C44" s="379" t="s">
         <v>1353</v>
       </c>
       <c r="D44" s="30" t="s">
@@ -49772,7 +49674,7 @@
       <c r="D47" s="30" t="s">
         <v>3473</v>
       </c>
-      <c r="F47" s="421" t="s">
+      <c r="F47" s="420" t="s">
         <v>3475</v>
       </c>
       <c r="G47" s="30" t="s">
@@ -49860,15 +49762,15 @@
       <c r="A56" s="97" t="s">
         <v>3033</v>
       </c>
-      <c r="C56" s="255" t="s">
+      <c r="C56" s="254" t="s">
         <v>2483</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>3034</v>
       </c>
     </row>
-    <row r="60" spans="1:5" s="416" customFormat="1" ht="18">
-      <c r="C60" s="416" t="s">
+    <row r="60" spans="1:5" s="415" customFormat="1" ht="18">
+      <c r="C60" s="415" t="s">
         <v>3423</v>
       </c>
     </row>
@@ -50344,7 +50246,7 @@
       </c>
     </row>
     <row r="112" spans="1:6" s="30" customFormat="1">
-      <c r="A112" s="218" t="s">
+      <c r="A112" s="217" t="s">
         <v>1269</v>
       </c>
       <c r="B112" s="30">
@@ -50812,8 +50714,8 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="155" spans="1:6" s="229" customFormat="1" ht="15.5">
-      <c r="C155" s="238"/>
+    <row r="155" spans="1:6" s="228" customFormat="1" ht="15.5">
+      <c r="C155" s="237"/>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="49" t="s">
@@ -50881,23 +50783,23 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="168" spans="1:6" s="309" customFormat="1">
-      <c r="A168" s="281" t="s">
+    <row r="168" spans="1:6" s="308" customFormat="1">
+      <c r="A168" s="280" t="s">
         <v>2362</v>
       </c>
-      <c r="B168" s="309">
+      <c r="B168" s="308">
         <v>62806425</v>
       </c>
       <c r="C168" s="102" t="s">
         <v>2301</v>
       </c>
-      <c r="D168" s="309" t="s">
+      <c r="D168" s="308" t="s">
         <v>1620</v>
       </c>
-      <c r="E168" s="309" t="s">
+      <c r="E168" s="308" t="s">
         <v>2397</v>
       </c>
-      <c r="F168" s="309" t="s">
+      <c r="F168" s="308" t="s">
         <v>2398</v>
       </c>
     </row>
@@ -50964,7 +50866,7 @@
       <c r="C173" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D173" s="221" t="s">
+      <c r="D173" s="220" t="s">
         <v>1417</v>
       </c>
       <c r="E173" t="s">
@@ -51188,7 +51090,7 @@
       <c r="B196" s="180">
         <v>60642249</v>
       </c>
-      <c r="C196" s="287" t="s">
+      <c r="C196" s="286" t="s">
         <v>1814</v>
       </c>
       <c r="D196" t="s">
@@ -51317,7 +51219,7 @@
       </c>
     </row>
     <row r="206" spans="1:6">
-      <c r="A206" s="281" t="s">
+      <c r="A206" s="280" t="s">
         <v>1690</v>
       </c>
       <c r="B206" s="139">
@@ -51841,10 +51743,10 @@
       <c r="B256" s="30">
         <v>60433915</v>
       </c>
-      <c r="C256" s="255" t="s">
+      <c r="C256" s="254" t="s">
         <v>2441</v>
       </c>
-      <c r="D256" s="255" t="s">
+      <c r="D256" s="254" t="s">
         <v>2979</v>
       </c>
       <c r="E256" t="s">
@@ -52615,7 +52517,7 @@
       <c r="E303" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="F303" s="324" t="s">
+      <c r="F303" s="323" t="s">
         <v>1034</v>
       </c>
       <c r="G303" s="76" t="s">
@@ -53632,7 +53534,7 @@
       <c r="C362" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D362" s="221" t="s">
+      <c r="D362" s="220" t="s">
         <v>1275</v>
       </c>
       <c r="E362" s="7" t="s">
@@ -53806,7 +53708,7 @@
       <c r="C371" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D371" s="221" t="s">
+      <c r="D371" s="220" t="s">
         <v>1415</v>
       </c>
       <c r="E371" s="152" t="s">
@@ -54383,7 +54285,7 @@
       <c r="C401" t="s">
         <v>844</v>
       </c>
-      <c r="D401" s="221" t="s">
+      <c r="D401" s="220" t="s">
         <v>1315</v>
       </c>
       <c r="E401" s="152" t="s">
@@ -56014,7 +55916,7 @@
       <c r="N502" s="97"/>
     </row>
     <row r="504" spans="2:14">
-      <c r="B504" s="263"/>
+      <c r="B504" s="262"/>
       <c r="C504" s="49" t="s">
         <v>1722</v>
       </c>
@@ -56432,7 +56334,7 @@
       <c r="C529" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D529" s="221" t="s">
+      <c r="D529" s="220" t="s">
         <v>1417</v>
       </c>
       <c r="E529" s="76" t="s">
@@ -56542,7 +56444,7 @@
       <c r="C535" s="1" t="s">
         <v>3047</v>
       </c>
-      <c r="D535" s="221" t="s">
+      <c r="D535" s="220" t="s">
         <v>3049</v>
       </c>
       <c r="E535" t="s">

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59760" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5743907A-E47A-402D-A065-504F99A5FAF4}"/>
+  <xr:revisionPtr revIDLastSave="59774" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10FF87CB-CADF-4AA9-B208-736FC9D3A38B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1302,7 +1302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6263" uniqueCount="3661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6263" uniqueCount="3662">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -10208,12 +10208,6 @@
     <t>TV 68947134 (Maritza)</t>
   </si>
   <si>
-    <t>65509692 1 pantalla hasta el 25 de agosto wrallan</t>
-  </si>
-  <si>
-    <t>65208339 1 pantalla hasta el 24 de agosto</t>
-  </si>
-  <si>
     <t>67507440 1 pantalla hasta el 25 de agosto (Jorge Carrera)</t>
   </si>
   <si>
@@ -10415,15 +10409,9 @@
     <t>Tbx280726</t>
   </si>
   <si>
-    <t>67377137 1 pantalla hasta el 28 de agosto (Irina)</t>
-  </si>
-  <si>
     <t>Ytrr280726</t>
   </si>
   <si>
-    <t>67377137 1 pantalla hasta el 28 de agosto (irianys)</t>
-  </si>
-  <si>
     <t>62813047 2 pantalla hasta el 27 de agosto (Miguel y Dorelis)</t>
   </si>
   <si>
@@ -12285,6 +12273,21 @@
   </si>
   <si>
     <t>64966680-dany 1 pantalla hasta el 25 de septiembre</t>
+  </si>
+  <si>
+    <t>65208339 1 pantalla hasta el 24 de septiembre</t>
+  </si>
+  <si>
+    <t>67377137 1 pantalla hasta el 28 de septiembre (Irina)</t>
+  </si>
+  <si>
+    <t>67377137 1 pantalla hasta el 28 de septiembre (irianys)</t>
+  </si>
+  <si>
+    <t>65509692 1 pantalla hasta el 25 de septiembre wrallan</t>
+  </si>
+  <si>
+    <t>63465332-hilary 1 pantalla hasta el 13 de septiembre</t>
   </si>
 </sst>
 </file>
@@ -13603,7 +13606,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="449">
+  <cellXfs count="445">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -14090,13 +14093,9 @@
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="55" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -30398,7 +30397,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30410,7 +30409,7 @@
         <v>2085</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3390</v>
+        <v>3386</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2159</v>
@@ -30430,12 +30429,12 @@
         <v>2208</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3586</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2872</v>
@@ -30449,7 +30448,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30461,7 +30460,7 @@
         <v>2083</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3492</v>
+        <v>3488</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2159</v>
@@ -30481,12 +30480,12 @@
         <v>2222</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
       <c r="A6" s="226" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B6" s="148">
         <v>68241069</v>
@@ -30509,10 +30508,10 @@
         <v>2086</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>3229</v>
+        <v>3225</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3568</v>
+        <v>3564</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2164</v>
@@ -30554,7 +30553,7 @@
     </row>
     <row r="10" spans="1:11" s="439" customFormat="1">
       <c r="A10" s="439" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B10" s="439">
         <v>60389752</v>
@@ -30566,10 +30565,10 @@
         <v>2177</v>
       </c>
       <c r="E10" s="439" t="s">
-        <v>3116</v>
+        <v>3112</v>
       </c>
       <c r="F10" s="439" t="s">
-        <v>3115</v>
+        <v>3111</v>
       </c>
       <c r="G10" s="439" t="s">
         <v>59</v>
@@ -30591,7 +30590,7 @@
         <v>2228</v>
       </c>
       <c r="E13" s="403" t="s">
-        <v>3277</v>
+        <v>3273</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2227</v>
@@ -30603,7 +30602,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="226" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="B14" s="226" t="s">
         <v>1735</v>
@@ -30617,7 +30616,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="226" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="B15" s="432">
         <v>62439069</v>
@@ -30640,7 +30639,7 @@
         <v>1580</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3570</v>
+        <v>3566</v>
       </c>
       <c r="E16" s="32" t="s">
         <v>2963</v>
@@ -30652,21 +30651,21 @@
         <v>201</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3571</v>
+        <v>3567</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3139</v>
+        <v>3135</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3588</v>
+        <v>3584</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3109</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="253" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="B17" s="253" t="s">
         <v>1435</v>
@@ -30700,7 +30699,7 @@
     </row>
     <row r="19" spans="1:11" s="30" customFormat="1">
       <c r="A19" s="32" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B19" s="30">
         <v>62360487</v>
@@ -30712,7 +30711,7 @@
         <v>2116</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>3547</v>
+        <v>3543</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>1401</v>
@@ -30723,7 +30722,7 @@
     </row>
     <row r="20" spans="1:11" s="298" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>3373</v>
+        <v>3369</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30732,7 +30731,7 @@
         <v>1742</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>3459</v>
+        <v>3455</v>
       </c>
       <c r="E20" s="253" t="s">
         <v>1743</v>
@@ -30740,7 +30739,7 @@
     </row>
     <row r="21" spans="1:11" s="298" customFormat="1">
       <c r="A21" s="253" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B21" s="253">
         <v>60432412</v>
@@ -30769,7 +30768,7 @@
         <v>2205</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3390</v>
+        <v>3386</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2158</v>
@@ -30780,7 +30779,7 @@
     </row>
     <row r="23" spans="1:11" s="148" customFormat="1">
       <c r="A23" s="226" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B23" s="148">
         <v>64858241</v>
@@ -30794,7 +30793,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="148" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B24" s="148">
         <v>62279384</v>
@@ -30808,7 +30807,7 @@
     </row>
     <row r="25" spans="1:11" s="30" customFormat="1">
       <c r="A25" s="30" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B25" s="30">
         <v>63166786</v>
@@ -30820,7 +30819,7 @@
         <v>1576</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1401</v>
@@ -30851,7 +30850,7 @@
     </row>
     <row r="27" spans="1:11" s="226" customFormat="1">
       <c r="A27" s="226" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B27" s="226">
         <v>64476521</v>
@@ -30880,7 +30879,7 @@
         <v>2080</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3091</v>
+        <v>3087</v>
       </c>
       <c r="F28" s="306" t="s">
         <v>2240</v>
@@ -30914,24 +30913,24 @@
         <v>2485</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>3269</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3532</v>
+        <v>3528</v>
       </c>
       <c r="C31" s="252" t="s">
         <v>1968</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3423</v>
+        <v>3419</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2104</v>
@@ -30940,16 +30939,16 @@
         <v>201</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3534</v>
+        <v>3530</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="J31" s="437" t="s">
-        <v>3557</v>
+        <v>3553</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3238</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30969,7 +30968,7 @@
     </row>
     <row r="33" spans="1:11" s="164" customFormat="1">
       <c r="A33" s="164" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B33" s="164">
         <v>68845841</v>
@@ -30983,7 +30982,7 @@
     </row>
     <row r="34" spans="1:11" s="30" customFormat="1">
       <c r="A34" s="30" t="s">
-        <v>3135</v>
+        <v>3131</v>
       </c>
       <c r="B34" s="30">
         <v>60389752</v>
@@ -30995,7 +30994,7 @@
         <v>2171</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3319</v>
+        <v>3315</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2162</v>
@@ -31006,7 +31005,7 @@
     </row>
     <row r="35" spans="1:11" s="148" customFormat="1">
       <c r="A35" s="148" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B35" s="148">
         <v>69561522</v>
@@ -31023,7 +31022,7 @@
     </row>
     <row r="36" spans="1:11" s="148" customFormat="1">
       <c r="A36" s="226" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B36" s="148">
         <v>61381388</v>
@@ -31037,7 +31036,7 @@
     </row>
     <row r="37" spans="1:11" s="30" customFormat="1">
       <c r="A37" s="30" t="s">
-        <v>2835</v>
+        <v>2612</v>
       </c>
       <c r="B37" s="30" t="s">
         <v>2967</v>
@@ -31049,7 +31048,7 @@
         <v>2742</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3391</v>
+        <v>3387</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2152</v>
@@ -31058,21 +31057,21 @@
         <v>201</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>3254</v>
+        <v>3250</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="J37" s="217" t="s">
         <v>2818</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3239</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2870</v>
@@ -31108,10 +31107,10 @@
         <v>1722</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3319</v>
+        <v>3315</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2167</v>
@@ -31120,21 +31119,21 @@
         <v>201</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3627</v>
+        <v>3623</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3037</v>
+        <v>3658</v>
       </c>
       <c r="J40" s="303" t="s">
-        <v>3654</v>
+        <v>3650</v>
       </c>
       <c r="K40" s="30" t="s">
-        <v>3232</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31166,7 +31165,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31178,7 +31177,7 @@
         <v>2108</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3495</v>
+        <v>3491</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2202</v>
@@ -31189,7 +31188,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31206,7 +31205,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31232,10 +31231,10 @@
         <v>997</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>3213</v>
+        <v>3209</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3170</v>
+        <v>3166</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2184</v>
@@ -31247,7 +31246,7 @@
     </row>
     <row r="47" spans="1:11" s="164" customFormat="1">
       <c r="A47" s="164" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B47" s="164">
         <v>63183787</v>
@@ -31256,7 +31255,7 @@
         <v>2204</v>
       </c>
       <c r="D47" s="164" t="s">
-        <v>3169</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="164" customFormat="1">
@@ -31278,7 +31277,7 @@
     </row>
     <row r="49" spans="1:11" s="30" customFormat="1">
       <c r="A49" s="30" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B49" s="30" t="s">
         <v>2319</v>
@@ -31287,10 +31286,10 @@
         <v>2069</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3659</v>
+        <v>3655</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3321</v>
+        <v>3317</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2170</v>
@@ -31298,14 +31297,14 @@
       <c r="G49" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="H49" s="446" t="s">
-        <v>3660</v>
+      <c r="H49" s="30" t="s">
+        <v>3656</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3108</v>
+        <v>3104</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3161</v>
+        <v>3157</v>
       </c>
       <c r="K49" s="303" t="s">
         <v>2246</v>
@@ -31313,7 +31312,7 @@
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
       <c r="A50" s="164" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B50" s="164">
         <v>60450256</v>
@@ -31336,12 +31335,12 @@
         <v>2077</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3611</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
       <c r="A52" s="140" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B52" s="429" t="s">
         <v>1485</v>
@@ -31350,10 +31349,10 @@
         <v>1404</v>
       </c>
       <c r="D52" s="139" t="s">
-        <v>3244</v>
+        <v>3240</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3319</v>
+        <v>3315</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2168</v>
@@ -31362,21 +31361,21 @@
         <v>201</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3383</v>
+        <v>3661</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3245</v>
+        <v>3241</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3125</v>
+        <v>3121</v>
       </c>
       <c r="K52" s="270" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
       <c r="A53" s="164" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B53" s="164" t="s">
         <v>1174</v>
@@ -31393,7 +31392,7 @@
     </row>
     <row r="54" spans="1:11" s="164" customFormat="1">
       <c r="A54" s="419" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B54" s="163" t="s">
         <v>1790</v>
@@ -31412,7 +31411,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31423,8 +31422,8 @@
       <c r="D55" s="30" t="s">
         <v>2073</v>
       </c>
-      <c r="E55" s="446" t="s">
-        <v>3653</v>
+      <c r="E55" s="30" t="s">
+        <v>3649</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2185</v>
@@ -31443,7 +31442,7 @@
     </row>
     <row r="58" spans="1:11" s="30" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B58" s="428" t="s">
         <v>2150</v>
@@ -31452,7 +31451,7 @@
         <v>2105</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>3087</v>
+        <v>3083</v>
       </c>
       <c r="E58" s="30" t="s">
         <v>2668</v>
@@ -31464,16 +31463,16 @@
         <v>201</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3110</v>
+        <v>3106</v>
       </c>
       <c r="I58" s="217" t="s">
         <v>2916</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3123</v>
+        <v>3119</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3392</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="397" customFormat="1">
@@ -31488,16 +31487,16 @@
         <v>2518</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3061</v>
+        <v>3057</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2151</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3569</v>
+        <v>3565</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2152</v>
@@ -31506,16 +31505,16 @@
         <v>201</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3278</v>
+        <v>3274</v>
       </c>
       <c r="I61" s="217" t="s">
         <v>2831</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3266</v>
+        <v>3262</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3165</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
@@ -31537,7 +31536,7 @@
     </row>
     <row r="63" spans="1:11" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31546,13 +31545,13 @@
         <v>2136</v>
       </c>
       <c r="D63" s="379" t="s">
-        <v>3628</v>
+        <v>3624</v>
       </c>
       <c r="E63" s="164"/>
     </row>
     <row r="64" spans="1:11" s="30" customFormat="1">
       <c r="A64" s="32" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B64" s="32" t="s">
         <v>2206</v>
@@ -31561,10 +31560,10 @@
         <v>1721</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3086</v>
+        <v>3082</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3320</v>
+        <v>3316</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2169</v>
@@ -31573,21 +31572,21 @@
         <v>201</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3124</v>
+        <v>3120</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3221</v>
+        <v>3217</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3220</v>
+        <v>3216</v>
       </c>
       <c r="K64" s="145" t="s">
-        <v>3544</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
       <c r="A65" s="253" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B65" s="253">
         <v>62535724</v>
@@ -31621,7 +31620,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="254" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="B67" s="285" t="s">
         <v>1976</v>
@@ -31630,10 +31629,10 @@
         <v>1725</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>3479</v>
+        <v>3475</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3363</v>
+        <v>3359</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2173</v>
@@ -31642,16 +31641,16 @@
         <v>201</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3480</v>
+        <v>3476</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3261</v>
+        <v>3257</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3491</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
@@ -31662,13 +31661,13 @@
         <v>1944</v>
       </c>
       <c r="D68" s="380" t="s">
-        <v>3655</v>
+        <v>3651</v>
       </c>
       <c r="E68" s="148"/>
     </row>
     <row r="69" spans="1:11" s="148" customFormat="1">
       <c r="A69" s="226" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B69" s="148">
         <v>66850767</v>
@@ -31677,12 +31676,12 @@
         <v>2172</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3342</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
       <c r="A70" s="30" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B70" s="285" t="s">
         <v>2672</v>
@@ -31703,13 +31702,13 @@
         <v>201</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3527</v>
+        <v>3523</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>3044</v>
+        <v>3040</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>3455</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31723,12 +31722,12 @@
         <v>2031</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>3302</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="269" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
       <c r="B72" s="269" t="s">
         <v>1497</v>
@@ -31737,13 +31736,13 @@
         <v>1778</v>
       </c>
       <c r="D72" s="379" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
       <c r="E72" s="164"/>
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3113</v>
+        <v>3109</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31752,10 +31751,10 @@
         <v>1381</v>
       </c>
       <c r="D73" s="252" t="s">
-        <v>3112</v>
+        <v>3108</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3577</v>
+        <v>3573</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2103</v>
@@ -31766,7 +31765,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31805,10 +31804,10 @@
         <v>1943</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>3414</v>
+        <v>3410</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2184</v>
@@ -31817,16 +31816,16 @@
         <v>201</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3416</v>
+        <v>3412</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3418</v>
+        <v>3414</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3415</v>
+        <v>3411</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31842,16 +31841,16 @@
         <v>144</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>3355</v>
+        <v>3351</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2076</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3451</v>
+        <v>3447</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3390</v>
+        <v>3386</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2163</v>
@@ -31860,16 +31859,16 @@
         <v>201</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>3476</v>
+        <v>3472</v>
       </c>
       <c r="I79" s="404" t="s">
-        <v>3629</v>
+        <v>3625</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3452</v>
+        <v>3448</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3356</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31889,7 +31888,7 @@
     </row>
     <row r="81" spans="1:11" s="147" customFormat="1">
       <c r="A81" s="149" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B81" s="147">
         <v>64720128</v>
@@ -31912,10 +31911,10 @@
         <v>1969</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>3176</v>
+        <v>3172</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>3252</v>
+        <v>3248</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1970</v>
@@ -31924,21 +31923,21 @@
         <v>201</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3657</v>
+        <v>3653</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3095</v>
+        <v>3091</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3658</v>
+        <v>3654</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3265</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
       <c r="A83" s="148" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B83" s="148">
         <v>63145336</v>
@@ -31952,7 +31951,7 @@
     </row>
     <row r="84" spans="1:11" s="281" customFormat="1">
       <c r="A84" s="148" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B84" s="148">
         <v>68971798</v>
@@ -31987,21 +31986,21 @@
         <v>498</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3057</v>
+        <v>3053</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3281</v>
+        <v>3277</v>
       </c>
       <c r="J85" s="217" t="s">
         <v>2661</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3559</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
       <c r="A86" s="147" t="s">
-        <v>2835</v>
+        <v>2612</v>
       </c>
       <c r="B86" s="147">
         <v>65509692</v>
@@ -32019,7 +32018,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>923</v>
@@ -32037,7 +32036,7 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B88" s="30">
         <v>68496217</v>
@@ -32046,7 +32045,7 @@
         <v>701</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3393</v>
+        <v>3389</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1104</v>
@@ -32058,16 +32057,16 @@
         <v>1578</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3394</v>
+        <v>3390</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3433</v>
+        <v>3429</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3536</v>
+        <v>3532</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3535</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32090,16 +32089,16 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="226" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
       </c>
       <c r="C90" s="412" t="s">
-        <v>3117</v>
+        <v>3113</v>
       </c>
       <c r="D90" s="148" t="s">
-        <v>3080</v>
+        <v>3076</v>
       </c>
       <c r="E90" s="148" t="s">
         <v>879</v>
@@ -32108,7 +32107,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="250" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1441</v>
@@ -32132,13 +32131,13 @@
         <v>2836</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3357</v>
+        <v>3353</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3515</v>
+        <v>3511</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="420" customFormat="1">
@@ -32186,7 +32185,7 @@
         <v>1402</v>
       </c>
       <c r="E94" s="254" t="s">
-        <v>3225</v>
+        <v>3221</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1403</v>
@@ -32215,7 +32214,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B96" s="148">
         <v>62928817</v>
@@ -32235,16 +32234,16 @@
         <v>1462</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>3353</v>
+        <v>3349</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>2066</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>3352</v>
+        <v>3348</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1970</v>
@@ -32253,16 +32252,16 @@
         <v>201</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3275</v>
+        <v>3271</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3468</v>
+        <v>3464</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3567</v>
+        <v>3563</v>
       </c>
       <c r="K97" s="139" t="s">
-        <v>3434</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="397" customFormat="1">
@@ -32275,19 +32274,19 @@
     </row>
     <row r="100" spans="1:11" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="C100" s="252" t="s">
-        <v>3174</v>
+        <v>3170</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3173</v>
+        <v>3169</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3622</v>
+        <v>3618</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1970</v>
@@ -32296,16 +32295,16 @@
         <v>201</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3119</v>
+        <v>3115</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="K100" s="32" t="s">
-        <v>3179</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="397" customFormat="1">
@@ -32318,22 +32317,22 @@
     </row>
     <row r="103" spans="1:11" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B103" s="30">
         <v>62724019</v>
       </c>
       <c r="C103" s="252" t="s">
-        <v>3273</v>
+        <v>3269</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>3540</v>
+        <v>3536</v>
       </c>
       <c r="E103" s="30" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>3541</v>
+        <v>3537</v>
       </c>
       <c r="G103" s="30" t="s">
         <v>59</v>
@@ -32352,7 +32351,7 @@
         <v>158</v>
       </c>
       <c r="B106" s="285" t="s">
-        <v>3560</v>
+        <v>3556</v>
       </c>
       <c r="C106" s="134" t="s">
         <v>2063</v>
@@ -32372,16 +32371,16 @@
         <v>60756926</v>
       </c>
       <c r="C108" s="30" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
       <c r="D108" s="30" t="s">
-        <v>3217</v>
+        <v>3213</v>
       </c>
       <c r="E108" s="30" t="s">
-        <v>3218</v>
+        <v>3214</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>3175</v>
+        <v>3171</v>
       </c>
       <c r="G108" s="30" t="s">
         <v>59</v>
@@ -32392,20 +32391,20 @@
         <v>79</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>3364</v>
+        <v>3360</v>
       </c>
       <c r="E124" s="32" t="s">
-        <v>3218</v>
+        <v>3214</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>3175</v>
+        <v>3171</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>3272</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="30" customFormat="1"/>
-    <row r="126" spans="1:8" s="447" customFormat="1" ht="28" customHeight="1">
+    <row r="126" spans="1:8" s="444" customFormat="1" ht="28" customHeight="1">
       <c r="A126" s="146"/>
       <c r="B126" s="146"/>
       <c r="C126" s="146" t="s">
@@ -32419,7 +32418,7 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B127">
         <v>69581554</v>
@@ -32431,7 +32430,7 @@
         <v>2053</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
       <c r="F127" t="s">
         <v>2051</v>
@@ -32451,7 +32450,7 @@
         <v>2021</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32465,15 +32464,15 @@
         <v>2941</v>
       </c>
       <c r="D129" s="382" t="s">
-        <v>2988</v>
+        <v>2986</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="4" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B130">
         <v>67046608</v>
@@ -32485,12 +32484,12 @@
         <v>2790</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="282" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B131" s="282" t="s">
         <v>1215</v>
@@ -32502,7 +32501,7 @@
         <v>2027</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32564,7 +32563,7 @@
         <v>2942</v>
       </c>
       <c r="E136" s="30" t="s">
-        <v>3195</v>
+        <v>3191</v>
       </c>
       <c r="F136" t="s">
         <v>1350</v>
@@ -32608,7 +32607,7 @@
         <v>2467</v>
       </c>
       <c r="E139" s="30" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="F139" t="s">
         <v>1378</v>
@@ -32624,7 +32623,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="B150">
         <v>64720128</v>
@@ -32695,7 +32694,7 @@
         <v>2750</v>
       </c>
       <c r="D156" s="382" t="s">
-        <v>3270</v>
+        <v>3266</v>
       </c>
       <c r="E156" s="403" t="s">
         <v>2780</v>
@@ -32745,18 +32744,18 @@
     </row>
     <row r="162" spans="1:6">
       <c r="C162" t="s">
+        <v>3025</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>3027</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>3029</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="C163" s="1" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D163" s="382" t="s">
         <v>3028</v>
-      </c>
-      <c r="D163" s="382" t="s">
-        <v>3030</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -32770,10 +32769,10 @@
         <v>2320</v>
       </c>
       <c r="D165" s="382" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
       <c r="F165" t="s">
         <v>2039</v>
@@ -32793,7 +32792,7 @@
         <v>2472</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -32807,15 +32806,15 @@
         <v>2322</v>
       </c>
       <c r="D167" s="382" t="s">
-        <v>3059</v>
+        <v>3055</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B168">
         <v>60183566</v>
@@ -32827,12 +32826,12 @@
         <v>2791</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B169">
         <v>62491046</v>
@@ -32841,10 +32840,10 @@
         <v>2332</v>
       </c>
       <c r="D169" s="382" t="s">
-        <v>3426</v>
+        <v>3422</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -32861,7 +32860,7 @@
         <v>2643</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -32878,7 +32877,7 @@
         <v>2841</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -32895,7 +32894,7 @@
         <v>2764</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -32912,12 +32911,12 @@
         <v>2675</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="4" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B174" s="4" t="s">
         <v>1165</v>
@@ -32926,10 +32925,10 @@
         <v>2793</v>
       </c>
       <c r="D174" s="382" t="s">
-        <v>3579</v>
+        <v>3575</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -32943,10 +32942,10 @@
         <v>2677</v>
       </c>
       <c r="D175" s="382" t="s">
-        <v>3208</v>
+        <v>3204</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -32957,35 +32956,35 @@
         <v>12369714760</v>
       </c>
       <c r="C176" t="s">
-        <v>3341</v>
+        <v>3337</v>
       </c>
       <c r="D176" s="382" t="s">
-        <v>3358</v>
+        <v>3354</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="4" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>2257</v>
       </c>
       <c r="C177" t="s">
-        <v>3189</v>
+        <v>3185</v>
       </c>
       <c r="D177" s="382" t="s">
         <v>2644</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3287</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="B178">
         <v>66315726</v>
@@ -32997,12 +32996,12 @@
         <v>2375</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3287</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B179">
         <v>64568369</v>
@@ -33014,12 +33013,12 @@
         <v>2375</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3287</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B180">
         <v>66935922</v>
@@ -33031,7 +33030,7 @@
         <v>2794</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3287</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -33048,7 +33047,7 @@
         <v>2945</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -33062,10 +33061,10 @@
         <v>2421</v>
       </c>
       <c r="D182" s="382" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33082,7 +33081,7 @@
         <v>2641</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -33099,7 +33098,7 @@
         <v>2423</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -33116,7 +33115,7 @@
         <v>2645</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3578</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -33133,7 +33132,7 @@
         <v>2439</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3578</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33147,10 +33146,10 @@
         <v>2438</v>
       </c>
       <c r="D187" s="382" t="s">
-        <v>3048</v>
+        <v>3044</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3578</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33161,13 +33160,13 @@
         <v>62640383</v>
       </c>
       <c r="C188" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="D188" s="382" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33178,30 +33177,30 @@
         <v>68918211</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="D189" s="220" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>2518</v>
+        <v>159</v>
       </c>
       <c r="B190">
         <v>68017742</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="D190" s="220" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -33212,13 +33211,13 @@
         <v>63000428</v>
       </c>
       <c r="C191" s="3" t="s">
+        <v>3022</v>
+      </c>
+      <c r="D191" s="220" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E191" s="30" t="s">
         <v>3024</v>
-      </c>
-      <c r="D191" s="220" t="s">
-        <v>3060</v>
-      </c>
-      <c r="E191" s="30" t="s">
-        <v>3026</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -33229,13 +33228,13 @@
         <v>68501487</v>
       </c>
       <c r="C192" s="22" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="D192" s="220" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -33246,98 +33245,98 @@
         <v>63195211</v>
       </c>
       <c r="C193" t="s">
-        <v>3068</v>
+        <v>3064</v>
       </c>
       <c r="D193" s="382" t="s">
+        <v>3065</v>
+      </c>
+      <c r="E193" s="30" t="s">
         <v>3069</v>
-      </c>
-      <c r="E193" s="30" t="s">
-        <v>3073</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B194">
         <v>63950696</v>
       </c>
       <c r="C194" t="s">
-        <v>3070</v>
+        <v>3066</v>
       </c>
       <c r="D194" s="382" t="s">
+        <v>3065</v>
+      </c>
+      <c r="E194" s="30" t="s">
         <v>3069</v>
-      </c>
-      <c r="E194" s="30" t="s">
-        <v>3073</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="4" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B195" t="s">
-        <v>3121</v>
+        <v>3117</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>3071</v>
+        <v>3067</v>
       </c>
       <c r="D195" s="220" t="s">
+        <v>3065</v>
+      </c>
+      <c r="E195" s="30" t="s">
         <v>3069</v>
-      </c>
-      <c r="E195" s="30" t="s">
-        <v>3073</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B196">
         <v>66805512</v>
       </c>
       <c r="C196" t="s">
-        <v>3072</v>
+        <v>3068</v>
       </c>
       <c r="D196" s="382" t="s">
-        <v>3230</v>
+        <v>3226</v>
       </c>
       <c r="E196" s="30" t="s">
-        <v>3073</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B197" t="s">
-        <v>3253</v>
+        <v>3249</v>
       </c>
       <c r="C197" t="s">
-        <v>3200</v>
+        <v>3196</v>
       </c>
       <c r="D197" s="382" t="s">
-        <v>3233</v>
+        <v>3229</v>
       </c>
       <c r="E197" s="30" t="s">
-        <v>3073</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="B198">
         <v>68201775</v>
       </c>
       <c r="C198" t="s">
-        <v>3141</v>
+        <v>3137</v>
       </c>
       <c r="D198" s="382" t="s">
-        <v>3236</v>
+        <v>3232</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -33345,16 +33344,16 @@
         <v>2683</v>
       </c>
       <c r="B199" t="s">
-        <v>3153</v>
+        <v>3149</v>
       </c>
       <c r="C199" t="s">
-        <v>3142</v>
+        <v>3138</v>
       </c>
       <c r="D199" s="382" t="s">
-        <v>3150</v>
+        <v>3146</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -33365,30 +33364,30 @@
         <v>62724019</v>
       </c>
       <c r="C200" t="s">
-        <v>3143</v>
+        <v>3139</v>
       </c>
       <c r="D200" s="382" t="s">
-        <v>3150</v>
+        <v>3146</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="30" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B201" s="32" t="s">
         <v>2197</v>
       </c>
       <c r="C201" t="s">
-        <v>3144</v>
+        <v>3140</v>
       </c>
       <c r="D201" s="382" t="s">
-        <v>3150</v>
+        <v>3146</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -33399,13 +33398,13 @@
         <v>65080956</v>
       </c>
       <c r="C202" t="s">
-        <v>3145</v>
+        <v>3141</v>
       </c>
       <c r="D202" s="382" t="s">
-        <v>3150</v>
+        <v>3146</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33416,47 +33415,47 @@
         <v>68726473</v>
       </c>
       <c r="C203" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D203" s="382" t="s">
         <v>3146</v>
       </c>
-      <c r="D203" s="382" t="s">
-        <v>3150</v>
-      </c>
       <c r="E203" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="4" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B204" s="4" t="s">
         <v>1922</v>
       </c>
       <c r="C204" t="s">
+        <v>3143</v>
+      </c>
+      <c r="D204" s="382" t="s">
+        <v>3146</v>
+      </c>
+      <c r="E204" s="30" t="s">
         <v>3147</v>
-      </c>
-      <c r="D204" s="382" t="s">
-        <v>3150</v>
-      </c>
-      <c r="E204" s="30" t="s">
-        <v>3151</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>3625</v>
+        <v>3621</v>
       </c>
       <c r="B205">
         <v>64046277</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>3234</v>
+        <v>3230</v>
       </c>
       <c r="D205" s="382" t="s">
-        <v>3235</v>
+        <v>3231</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33467,13 +33466,13 @@
         <v>66520892</v>
       </c>
       <c r="C206" t="s">
-        <v>3148</v>
+        <v>3144</v>
       </c>
       <c r="D206" s="382" t="s">
-        <v>3150</v>
+        <v>3146</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33484,18 +33483,18 @@
         <v>62031509</v>
       </c>
       <c r="C207" t="s">
-        <v>3149</v>
+        <v>3145</v>
       </c>
       <c r="D207" s="382" t="s">
-        <v>3150</v>
+        <v>3146</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3151</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="210" spans="1:5" s="401" customFormat="1" ht="23.5">
       <c r="C210" s="401" t="s">
-        <v>3182</v>
+        <v>3178</v>
       </c>
       <c r="D210" s="401">
         <v>51957149094</v>
@@ -33503,87 +33502,87 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B211">
         <v>60240509</v>
       </c>
       <c r="C211" t="s">
-        <v>3201</v>
+        <v>3197</v>
       </c>
       <c r="D211" s="382" t="s">
-        <v>3202</v>
+        <v>3198</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B212">
         <v>66003234</v>
       </c>
       <c r="C212" t="s">
-        <v>3183</v>
+        <v>3179</v>
       </c>
       <c r="D212" s="382" t="s">
-        <v>3564</v>
+        <v>3560</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B213">
         <v>65344753</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>3203</v>
+        <v>3199</v>
       </c>
       <c r="D213" s="382" t="s">
-        <v>3314</v>
+        <v>3310</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>3504</v>
+        <v>3500</v>
       </c>
       <c r="B214">
         <v>65633205</v>
       </c>
       <c r="C214" t="s">
+        <v>3180</v>
+      </c>
+      <c r="D214" s="382" t="s">
+        <v>3499</v>
+      </c>
+      <c r="E214" s="30" t="s">
         <v>3184</v>
-      </c>
-      <c r="D214" s="382" t="s">
-        <v>3503</v>
-      </c>
-      <c r="E214" s="30" t="s">
-        <v>3188</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="B215">
         <v>61248427</v>
       </c>
       <c r="C215" t="s">
-        <v>3185</v>
+        <v>3181</v>
       </c>
       <c r="D215" s="382" t="s">
-        <v>3303</v>
+        <v>3299</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33594,64 +33593,64 @@
         <v>69329372</v>
       </c>
       <c r="C216" t="s">
-        <v>3313</v>
+        <v>3309</v>
       </c>
       <c r="D216" s="382" t="s">
-        <v>3327</v>
+        <v>3323</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="30" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="B217">
         <v>68168617</v>
       </c>
       <c r="C217" t="s">
-        <v>3186</v>
+        <v>3182</v>
       </c>
       <c r="D217" s="382" t="s">
-        <v>3309</v>
+        <v>3305</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="4" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B218" s="4">
         <v>68934853</v>
       </c>
       <c r="C218" t="s">
-        <v>3187</v>
+        <v>3183</v>
       </c>
       <c r="D218" s="382" t="s">
-        <v>3326</v>
+        <v>3322</v>
       </c>
       <c r="E218" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B219" t="s">
-        <v>3346</v>
+        <v>3342</v>
       </c>
       <c r="C219" t="s">
-        <v>3340</v>
+        <v>3336</v>
       </c>
       <c r="D219" s="382" t="s">
-        <v>3343</v>
+        <v>3339</v>
       </c>
       <c r="E219" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -33662,30 +33661,30 @@
         <v>61430885</v>
       </c>
       <c r="C220" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="D220" s="382" t="s">
-        <v>3345</v>
+        <v>3341</v>
       </c>
       <c r="E220" s="30" t="s">
-        <v>3188</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>3373</v>
+        <v>3369</v>
       </c>
       <c r="B221">
         <v>66496809</v>
       </c>
       <c r="C221" t="s">
-        <v>3369</v>
+        <v>3365</v>
       </c>
       <c r="D221" t="s">
-        <v>3371</v>
+        <v>3367</v>
       </c>
       <c r="E221" s="30" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -33696,13 +33695,13 @@
         <v>65583706</v>
       </c>
       <c r="C222" t="s">
-        <v>3427</v>
+        <v>3423</v>
       </c>
       <c r="D222" s="382" t="s">
-        <v>3429</v>
+        <v>3425</v>
       </c>
       <c r="E222" s="30" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -33713,44 +33712,44 @@
         <v>65574051</v>
       </c>
       <c r="C223" t="s">
-        <v>3370</v>
+        <v>3366</v>
       </c>
       <c r="D223" t="s">
-        <v>3375</v>
+        <v>3371</v>
       </c>
       <c r="E223" s="30" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B224" t="s">
-        <v>3457</v>
+        <v>3453</v>
       </c>
       <c r="C224" t="s">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="D224" s="382" t="s">
-        <v>3430</v>
+        <v>3426</v>
       </c>
       <c r="E224" s="30" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="B225" t="s">
-        <v>3484</v>
+        <v>3480</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>3483</v>
+        <v>3479</v>
       </c>
       <c r="D225" t="s">
-        <v>3458</v>
+        <v>3454</v>
       </c>
       <c r="E225" s="30" t="s">
-        <v>3372</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -33761,30 +33760,30 @@
         <v>62863306</v>
       </c>
       <c r="C226" s="22" t="s">
-        <v>3485</v>
+        <v>3481</v>
       </c>
       <c r="D226" s="382" t="s">
-        <v>3487</v>
+        <v>3483</v>
       </c>
       <c r="E226" s="30" t="s">
-        <v>3488</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
       <c r="B227">
         <v>63258169</v>
       </c>
       <c r="C227" s="22" t="s">
-        <v>3508</v>
+        <v>3504</v>
       </c>
       <c r="D227" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
       <c r="E227" s="30" t="s">
-        <v>3488</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -33795,30 +33794,30 @@
         <v>69243886</v>
       </c>
       <c r="C228" s="22" t="s">
-        <v>3509</v>
+        <v>3505</v>
       </c>
       <c r="D228" t="s">
-        <v>3501</v>
+        <v>3497</v>
       </c>
       <c r="E228" s="30" t="s">
-        <v>3488</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B229">
         <v>67752170</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="D229" t="s">
-        <v>3502</v>
+        <v>3498</v>
       </c>
       <c r="E229" s="30" t="s">
-        <v>3488</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -33829,13 +33828,13 @@
         <v>64457890</v>
       </c>
       <c r="C230" t="s">
-        <v>3510</v>
+        <v>3506</v>
       </c>
       <c r="D230" s="382" t="s">
-        <v>3511</v>
+        <v>3507</v>
       </c>
       <c r="E230" s="30" t="s">
-        <v>3488</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -33921,7 +33920,7 @@
         <v>234</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>3172</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -33945,7 +33944,7 @@
         <v>1381</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>3111</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -33953,23 +33952,23 @@
         <v>1299</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>3174</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="C258" s="1" t="s">
-        <v>3215</v>
+        <v>3211</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>3216</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
-        <v>3271</v>
+        <v>3267</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>3273</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -33977,10 +33976,10 @@
         <v>1723</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>3276</v>
+        <v>3272</v>
       </c>
       <c r="E260" s="30" t="s">
-        <v>3274</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36614,8 +36613,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" s="76" customFormat="1">
-      <c r="A6" s="49" t="s">
-        <v>2852</v>
+      <c r="A6" s="76" t="s">
+        <v>3477</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36630,7 +36629,7 @@
         <v>684</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3133</v>
+        <v>3129</v>
       </c>
       <c r="G6" s="222" t="s">
         <v>1487</v>
@@ -36650,13 +36649,13 @@
         <v>1910</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3362</v>
+        <v>3358</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3133</v>
+        <v>3129</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1487</v>
@@ -36682,7 +36681,7 @@
         <v>365</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3133</v>
+        <v>3129</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1487</v>
@@ -36708,7 +36707,7 @@
         <v>365</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3133</v>
+        <v>3129</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1487</v>
@@ -36734,7 +36733,7 @@
         <v>365</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3133</v>
+        <v>3129</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1487</v>
@@ -36760,7 +36759,7 @@
         <v>365</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3133</v>
+        <v>3129</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1487</v>
@@ -36783,7 +36782,7 @@
         <v>2685</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1472</v>
@@ -36810,7 +36809,7 @@
         <v>1911</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1472</v>
@@ -36825,19 +36824,19 @@
     </row>
     <row r="15" spans="1:9" s="183" customFormat="1">
       <c r="A15" s="193" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B15" s="193">
         <v>60389752</v>
       </c>
       <c r="C15" s="191" t="s">
-        <v>3078</v>
+        <v>3074</v>
       </c>
       <c r="D15" s="193" t="s">
-        <v>3079</v>
+        <v>3075</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1472</v>
@@ -36852,7 +36851,7 @@
     </row>
     <row r="16" spans="1:9" s="183" customFormat="1">
       <c r="A16" s="183" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36864,7 +36863,7 @@
         <v>2426</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1472</v>
@@ -36891,7 +36890,7 @@
         <v>1555</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1472</v>
@@ -36906,7 +36905,7 @@
     </row>
     <row r="18" spans="1:9" s="183" customFormat="1">
       <c r="A18" s="193" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B18" s="193">
         <v>60389752</v>
@@ -36918,7 +36917,7 @@
         <v>2245</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1472</v>
@@ -36933,7 +36932,7 @@
     </row>
     <row r="20" spans="1:9" s="76" customFormat="1">
       <c r="A20" s="195" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36948,7 +36947,7 @@
         <v>365</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>427</v>
@@ -36962,7 +36961,7 @@
     </row>
     <row r="21" spans="1:9" s="183" customFormat="1">
       <c r="A21" s="183" t="s">
-        <v>3250</v>
+        <v>3246</v>
       </c>
       <c r="B21" s="183">
         <v>62723048</v>
@@ -36977,7 +36976,7 @@
         <v>365</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>427</v>
@@ -36991,7 +36990,7 @@
     </row>
     <row r="22" spans="1:9" s="183" customFormat="1">
       <c r="A22" s="183" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B22" s="183">
         <v>66439962</v>
@@ -37006,7 +37005,7 @@
         <v>365</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>427</v>
@@ -37020,7 +37019,7 @@
     </row>
     <row r="23" spans="1:9" s="183" customFormat="1">
       <c r="A23" s="183" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -37035,7 +37034,7 @@
         <v>365</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>427</v>
@@ -37064,7 +37063,7 @@
         <v>365</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>427</v>
@@ -37078,7 +37077,7 @@
     </row>
     <row r="25" spans="1:9" s="183" customFormat="1">
       <c r="A25" s="183" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B25" s="183">
         <v>69757885</v>
@@ -37093,7 +37092,7 @@
         <v>365</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>427</v>
@@ -37107,7 +37106,7 @@
     </row>
     <row r="27" spans="1:9" s="76" customFormat="1">
       <c r="A27" s="195" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B27" s="195">
         <v>62747874</v>
@@ -37122,7 +37121,7 @@
         <v>365</v>
       </c>
       <c r="F27" s="195" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>427</v>
@@ -37151,7 +37150,7 @@
         <v>365</v>
       </c>
       <c r="F28" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>427</v>
@@ -37180,7 +37179,7 @@
         <v>365</v>
       </c>
       <c r="F29" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>427</v>
@@ -37194,22 +37193,22 @@
     </row>
     <row r="30" spans="1:9" s="183" customFormat="1">
       <c r="A30" s="183" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B30" s="183">
         <v>63950696</v>
       </c>
       <c r="C30" s="193" t="s">
-        <v>3104</v>
+        <v>3100</v>
       </c>
       <c r="D30" s="193" t="s">
-        <v>3105</v>
+        <v>3101</v>
       </c>
       <c r="E30" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F30" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>427</v>
@@ -37238,7 +37237,7 @@
         <v>365</v>
       </c>
       <c r="F31" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>427</v>
@@ -37252,7 +37251,7 @@
     </row>
     <row r="32" spans="1:9" s="183" customFormat="1">
       <c r="A32" s="193" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B32" s="193">
         <v>64967407</v>
@@ -37267,7 +37266,7 @@
         <v>365</v>
       </c>
       <c r="F32" s="193" t="s">
-        <v>3136</v>
+        <v>3132</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>427</v>
@@ -37281,7 +37280,7 @@
     </row>
     <row r="34" spans="1:9" s="76" customFormat="1">
       <c r="A34" s="76" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B34" s="76">
         <v>60389752</v>
@@ -37296,7 +37295,7 @@
         <v>365</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1488</v>
@@ -37323,7 +37322,7 @@
         <v>365</v>
       </c>
       <c r="F35" s="183" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>381</v>
@@ -37352,7 +37351,7 @@
         <v>365</v>
       </c>
       <c r="F36" s="183" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>381</v>
@@ -37381,7 +37380,7 @@
         <v>365</v>
       </c>
       <c r="F37" s="183" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>381</v>
@@ -37410,7 +37409,7 @@
         <v>365</v>
       </c>
       <c r="F38" s="183" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>381</v>
@@ -37424,7 +37423,7 @@
     </row>
     <row r="39" spans="1:9" s="183" customFormat="1">
       <c r="A39" s="183" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B39" s="183">
         <v>68241069</v>
@@ -37439,7 +37438,7 @@
         <v>365</v>
       </c>
       <c r="F39" s="183" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>381</v>
@@ -37468,7 +37467,7 @@
         <v>2639</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>1487</v>
@@ -37480,7 +37479,7 @@
     </row>
     <row r="42" spans="1:9" s="183" customFormat="1">
       <c r="A42" s="193" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B42" s="193">
         <v>63465332</v>
@@ -37495,7 +37494,7 @@
         <v>2639</v>
       </c>
       <c r="F42" s="193" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="G42" s="183" t="s">
         <v>1487</v>
@@ -37522,7 +37521,7 @@
         <v>2639</v>
       </c>
       <c r="F43" s="193" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="G43" s="183" t="s">
         <v>1487</v>
@@ -37549,7 +37548,7 @@
         <v>2639</v>
       </c>
       <c r="F44" s="193" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="G44" s="183" t="s">
         <v>1487</v>
@@ -37576,7 +37575,7 @@
         <v>2639</v>
       </c>
       <c r="F45" s="193" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="G45" s="183" t="s">
         <v>1487</v>
@@ -37603,7 +37602,7 @@
         <v>2639</v>
       </c>
       <c r="F46" s="193" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="G46" s="183" t="s">
         <v>1487</v>
@@ -37624,13 +37623,13 @@
         <v>1724</v>
       </c>
       <c r="D48" s="195" t="s">
-        <v>3531</v>
+        <v>3527</v>
       </c>
       <c r="E48" s="76" t="s">
         <v>2639</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1487</v>
@@ -37657,7 +37656,7 @@
         <v>2639</v>
       </c>
       <c r="F49" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G49" s="183" t="s">
         <v>1487</v>
@@ -37684,7 +37683,7 @@
         <v>2639</v>
       </c>
       <c r="F50" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G50" s="183" t="s">
         <v>1487</v>
@@ -37711,7 +37710,7 @@
         <v>2639</v>
       </c>
       <c r="F51" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G51" s="183" t="s">
         <v>1487</v>
@@ -37729,7 +37728,7 @@
         <v>65174343</v>
       </c>
       <c r="C52" s="193" t="s">
-        <v>3192</v>
+        <v>3188</v>
       </c>
       <c r="D52" s="193" t="s">
         <v>2074</v>
@@ -37738,7 +37737,7 @@
         <v>2639</v>
       </c>
       <c r="F52" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G52" s="183" t="s">
         <v>1487</v>
@@ -37757,7 +37756,7 @@
         <v>2639</v>
       </c>
       <c r="F53" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G53" s="183" t="s">
         <v>1487</v>
@@ -37783,7 +37782,7 @@
         <v>2639</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1487</v>
@@ -37810,7 +37809,7 @@
         <v>2639</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1487</v>
@@ -37822,7 +37821,7 @@
     </row>
     <row r="57" spans="1:9" s="183" customFormat="1">
       <c r="A57" s="183" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="B57" s="183">
         <v>64403333</v>
@@ -37837,7 +37836,7 @@
         <v>2639</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1487</v>
@@ -37864,7 +37863,7 @@
         <v>2639</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1487</v>
@@ -37876,7 +37875,7 @@
     </row>
     <row r="59" spans="1:9" s="183" customFormat="1">
       <c r="A59" s="183" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="B59" s="183">
         <v>65003516</v>
@@ -37891,7 +37890,7 @@
         <v>2639</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1487</v>
@@ -37903,7 +37902,7 @@
     </row>
     <row r="60" spans="1:9" s="183" customFormat="1">
       <c r="A60" s="183" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B60" s="183">
         <v>61326385</v>
@@ -37918,7 +37917,7 @@
         <v>2639</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1487</v>
@@ -37930,7 +37929,7 @@
     </row>
     <row r="62" spans="1:9" s="76" customFormat="1">
       <c r="A62" s="76" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B62" s="76">
         <v>64147946</v>
@@ -37942,7 +37941,7 @@
         <v>2591</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F62" s="195" t="s">
         <v>2592</v>
@@ -37957,7 +37956,7 @@
     </row>
     <row r="63" spans="1:9" s="183" customFormat="1">
       <c r="A63" s="193" t="s">
-        <v>3312</v>
+        <v>3308</v>
       </c>
       <c r="B63" s="193">
         <v>62646186</v>
@@ -37969,7 +37968,7 @@
         <v>2596</v>
       </c>
       <c r="E63" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F63" s="193" t="s">
         <v>2592</v>
@@ -37996,7 +37995,7 @@
         <v>2395</v>
       </c>
       <c r="E64" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F64" s="193" t="s">
         <v>2592</v>
@@ -38011,19 +38010,19 @@
     </row>
     <row r="65" spans="1:9" s="183" customFormat="1">
       <c r="A65" s="183" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B65" s="183">
         <v>68632558</v>
       </c>
       <c r="C65" s="194" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="E65" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F65" s="183" t="s">
         <v>2592</v>
@@ -38049,7 +38048,7 @@
         <v>2135</v>
       </c>
       <c r="E66" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F66" s="183" t="s">
         <v>2592</v>
@@ -38075,7 +38074,7 @@
         <v>2586</v>
       </c>
       <c r="E67" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F67" s="183" t="s">
         <v>2592</v>
@@ -38101,7 +38100,7 @@
         <v>1786</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2590</v>
@@ -38113,7 +38112,7 @@
     </row>
     <row r="70" spans="1:9" s="183" customFormat="1">
       <c r="A70" s="193" t="s">
-        <v>3250</v>
+        <v>3246</v>
       </c>
       <c r="B70" s="193">
         <v>66082581</v>
@@ -38125,7 +38124,7 @@
         <v>2443</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2590</v>
@@ -38149,7 +38148,7 @@
         <v>1273</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2590</v>
@@ -38173,7 +38172,7 @@
         <v>2481</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F72" s="193" t="s">
         <v>2590</v>
@@ -38185,7 +38184,7 @@
     </row>
     <row r="73" spans="1:9" s="183" customFormat="1">
       <c r="A73" s="423" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B73" s="193">
         <v>60196388</v>
@@ -38197,7 +38196,7 @@
         <v>2392</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F73" s="193" t="s">
         <v>2590</v>
@@ -38209,7 +38208,7 @@
     </row>
     <row r="74" spans="1:9" s="183" customFormat="1">
       <c r="A74" s="183" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="B74" s="183" t="s">
         <v>1483</v>
@@ -38221,7 +38220,7 @@
         <v>2651</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="F74" s="193" t="s">
         <v>2590</v>
@@ -38239,16 +38238,16 @@
         <v>63574980</v>
       </c>
       <c r="C76" s="76" t="s">
-        <v>3181</v>
+        <v>3177</v>
       </c>
       <c r="D76" s="76" t="s">
-        <v>3180</v>
+        <v>3176</v>
       </c>
       <c r="E76" s="76" t="s">
         <v>1383</v>
       </c>
       <c r="F76" s="195" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="G76" s="76" t="s">
         <v>1487</v>
@@ -38274,7 +38273,7 @@
         <v>1383</v>
       </c>
       <c r="F77" s="183" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="G77" s="183" t="s">
         <v>1487</v>
@@ -38285,13 +38284,13 @@
     </row>
     <row r="78" spans="1:9" s="183" customFormat="1">
       <c r="A78" s="183" t="s">
-        <v>3324</v>
+        <v>3320</v>
       </c>
       <c r="B78" s="183">
         <v>68483411</v>
       </c>
       <c r="C78" s="183" t="s">
-        <v>3323</v>
+        <v>3319</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>2243</v>
@@ -38300,7 +38299,7 @@
         <v>1383</v>
       </c>
       <c r="F78" s="183" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="G78" s="183" t="s">
         <v>1487</v>
@@ -38326,7 +38325,7 @@
         <v>1383</v>
       </c>
       <c r="F79" s="183" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="G79" s="183" t="s">
         <v>1487</v>
@@ -38352,7 +38351,7 @@
         <v>1383</v>
       </c>
       <c r="F80" s="183" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="G80" s="183" t="s">
         <v>1487</v>
@@ -38378,7 +38377,7 @@
         <v>1383</v>
       </c>
       <c r="F81" s="183" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="G81" s="183" t="s">
         <v>1487</v>
@@ -38404,7 +38403,7 @@
         <v>1714</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1487</v>
@@ -38428,7 +38427,7 @@
         <v>1714</v>
       </c>
       <c r="F84" s="193" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1487</v>
@@ -38452,7 +38451,7 @@
         <v>1714</v>
       </c>
       <c r="F85" s="193" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1487</v>
@@ -38476,7 +38475,7 @@
         <v>1714</v>
       </c>
       <c r="F86" s="193" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1487</v>
@@ -38500,7 +38499,7 @@
         <v>1714</v>
       </c>
       <c r="F87" s="193" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1487</v>
@@ -38524,7 +38523,7 @@
         <v>1714</v>
       </c>
       <c r="F88" s="193" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1487</v>
@@ -38533,7 +38532,7 @@
     </row>
     <row r="90" spans="1:9" s="76" customFormat="1">
       <c r="A90" s="195" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="B90" s="195">
         <v>64476521</v>
@@ -38548,7 +38547,7 @@
         <v>2639</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1487</v>
@@ -38575,7 +38574,7 @@
         <v>2639</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1487</v>
@@ -38602,7 +38601,7 @@
         <v>2639</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1487</v>
@@ -38629,7 +38628,7 @@
         <v>2639</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1487</v>
@@ -38656,7 +38655,7 @@
         <v>2639</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1487</v>
@@ -38683,7 +38682,7 @@
         <v>2639</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1487</v>
@@ -38695,7 +38694,7 @@
     </row>
     <row r="97" spans="1:9" s="76" customFormat="1">
       <c r="A97" s="195" t="s">
-        <v>3514</v>
+        <v>3510</v>
       </c>
       <c r="B97" s="195">
         <v>66082581</v>
@@ -38707,7 +38706,7 @@
         <v>2405</v>
       </c>
       <c r="E97" s="76" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="F97" s="195" t="s">
         <v>427</v>
@@ -38722,7 +38721,7 @@
     </row>
     <row r="98" spans="1:9" s="183" customFormat="1">
       <c r="A98" s="193" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B98" s="193" t="s">
         <v>2930</v>
@@ -38734,7 +38733,7 @@
         <v>2410</v>
       </c>
       <c r="E98" s="183" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="F98" s="193" t="s">
         <v>427</v>
@@ -38761,7 +38760,7 @@
         <v>2412</v>
       </c>
       <c r="E99" s="183" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="F99" s="193" t="s">
         <v>427</v>
@@ -38782,13 +38781,13 @@
         <v>69017426</v>
       </c>
       <c r="C100" s="194" t="s">
-        <v>3365</v>
+        <v>3361</v>
       </c>
       <c r="D100" s="193" t="s">
         <v>2603</v>
       </c>
       <c r="E100" s="183" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="F100" s="193" t="s">
         <v>427</v>
@@ -38815,7 +38814,7 @@
         <v>2416</v>
       </c>
       <c r="E101" s="183" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="F101" s="193" t="s">
         <v>427</v>
@@ -38836,13 +38835,13 @@
         <v>62723048</v>
       </c>
       <c r="C102" s="194" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3385</v>
+        <v>3381</v>
       </c>
       <c r="E102" s="183" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="F102" s="193" t="s">
         <v>427</v>
@@ -38863,16 +38862,16 @@
         <v>68310153</v>
       </c>
       <c r="C104" s="195" t="s">
-        <v>3506</v>
+        <v>3502</v>
       </c>
       <c r="D104" s="195" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
       <c r="E104" s="76" t="s">
         <v>365</v>
       </c>
       <c r="F104" s="195" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G104" s="76" t="s">
         <v>1383</v>
@@ -38886,7 +38885,7 @@
     </row>
     <row r="105" spans="1:9" s="183" customFormat="1">
       <c r="A105" s="193" t="s">
-        <v>3513</v>
+        <v>3509</v>
       </c>
       <c r="B105" s="193">
         <v>63910392</v>
@@ -38899,7 +38898,7 @@
         <v>365</v>
       </c>
       <c r="F105" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G105" s="183" t="s">
         <v>1383</v>
@@ -38913,22 +38912,22 @@
     </row>
     <row r="106" spans="1:9" s="183" customFormat="1">
       <c r="A106" s="193" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B106" s="193">
         <v>68853797</v>
       </c>
       <c r="C106" s="193" t="s">
-        <v>3581</v>
+        <v>3577</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3432</v>
+        <v>3428</v>
       </c>
       <c r="E106" s="183" t="s">
         <v>2639</v>
       </c>
       <c r="F106" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G106" s="183" t="s">
         <v>1383</v>
@@ -38947,7 +38946,7 @@
         <v>365</v>
       </c>
       <c r="F107" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G107" s="183" t="s">
         <v>1383</v>
@@ -38968,7 +38967,7 @@
         <v>365</v>
       </c>
       <c r="F108" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G108" s="183" t="s">
         <v>1383</v>
@@ -38989,7 +38988,7 @@
         <v>365</v>
       </c>
       <c r="F109" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G109" s="183" t="s">
         <v>1383</v>
@@ -39003,7 +39002,7 @@
     </row>
     <row r="111" spans="1:9" s="76" customFormat="1">
       <c r="A111" s="76" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B111" s="76">
         <v>62751201</v>
@@ -39018,7 +39017,7 @@
         <v>1383</v>
       </c>
       <c r="F111" s="76" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G111" s="222" t="s">
         <v>1487</v>
@@ -39030,7 +39029,7 @@
     </row>
     <row r="112" spans="1:9" s="183" customFormat="1">
       <c r="A112" s="183" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B112" s="183">
         <v>68361109</v>
@@ -39045,7 +39044,7 @@
         <v>1383</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1487</v>
@@ -39063,16 +39062,16 @@
         <v>64543204</v>
       </c>
       <c r="C113" s="194" t="s">
-        <v>3445</v>
+        <v>3441</v>
       </c>
       <c r="D113" s="183" t="s">
-        <v>3444</v>
+        <v>3440</v>
       </c>
       <c r="E113" s="183" t="s">
         <v>1383</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1487</v>
@@ -39099,7 +39098,7 @@
         <v>1383</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1487</v>
@@ -39126,7 +39125,7 @@
         <v>1383</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1487</v>
@@ -39153,7 +39152,7 @@
         <v>1383</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1487</v>
@@ -39177,7 +39176,7 @@
         <v>1738</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>1569</v>
@@ -39203,7 +39202,7 @@
         <v>895</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F119" s="183" t="s">
         <v>1569</v>
@@ -39217,7 +39216,7 @@
     </row>
     <row r="120" spans="1:9" s="183" customFormat="1">
       <c r="A120" s="183" t="s">
-        <v>3545</v>
+        <v>3541</v>
       </c>
       <c r="B120" s="183">
         <v>69563253</v>
@@ -39229,7 +39228,7 @@
         <v>1021</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F120" s="183" t="s">
         <v>1569</v>
@@ -39243,19 +39242,19 @@
     </row>
     <row r="121" spans="1:9" s="183" customFormat="1">
       <c r="A121" s="183" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="B121" s="183">
         <v>63062167</v>
       </c>
       <c r="C121" s="194" t="s">
-        <v>3279</v>
+        <v>3275</v>
       </c>
       <c r="D121" s="183" t="s">
         <v>1285</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F121" s="183" t="s">
         <v>1569</v>
@@ -39281,7 +39280,7 @@
         <v>950</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F122" s="183" t="s">
         <v>1569</v>
@@ -39307,7 +39306,7 @@
         <v>1997</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F123" s="183" t="s">
         <v>1569</v>
@@ -39333,7 +39332,7 @@
         <v>2431</v>
       </c>
       <c r="E125" s="76" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>427</v>
@@ -39359,7 +39358,7 @@
         <v>2433</v>
       </c>
       <c r="E126" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F126" s="193" t="s">
         <v>427</v>
@@ -39386,7 +39385,7 @@
         <v>2435</v>
       </c>
       <c r="E127" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F127" s="193" t="s">
         <v>427</v>
@@ -39401,7 +39400,7 @@
     </row>
     <row r="128" spans="1:9" s="183" customFormat="1">
       <c r="A128" s="49" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
       <c r="B128" s="183">
         <v>67836337</v>
@@ -39410,7 +39409,7 @@
         <v>2508</v>
       </c>
       <c r="E128" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F128" s="193" t="s">
         <v>427</v>
@@ -39437,7 +39436,7 @@
         <v>380</v>
       </c>
       <c r="E129" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F129" s="193" t="s">
         <v>427</v>
@@ -39464,7 +39463,7 @@
         <v>1710</v>
       </c>
       <c r="E130" s="183" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
       <c r="F130" s="193" t="s">
         <v>427</v>
@@ -39494,7 +39493,7 @@
         <v>684</v>
       </c>
       <c r="F132" s="76" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>427</v>
@@ -39508,7 +39507,7 @@
     </row>
     <row r="133" spans="1:9" s="183" customFormat="1">
       <c r="A133" s="183" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B133" s="183">
         <v>64403333</v>
@@ -39523,7 +39522,7 @@
         <v>365</v>
       </c>
       <c r="F133" s="183" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>427</v>
@@ -39552,7 +39551,7 @@
         <v>365</v>
       </c>
       <c r="F134" s="183" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>427</v>
@@ -39578,7 +39577,7 @@
         <v>365</v>
       </c>
       <c r="F135" s="183" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>427</v>
@@ -39592,7 +39591,7 @@
     </row>
     <row r="136" spans="1:9" s="183" customFormat="1">
       <c r="A136" s="183" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B136" s="183">
         <v>66230961</v>
@@ -39607,7 +39606,7 @@
         <v>365</v>
       </c>
       <c r="F136" s="183" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>427</v>
@@ -39621,7 +39620,7 @@
     </row>
     <row r="137" spans="1:9" s="183" customFormat="1">
       <c r="A137" s="183" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B137" s="183">
         <v>69888391</v>
@@ -39636,7 +39635,7 @@
         <v>365</v>
       </c>
       <c r="F137" s="183" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>427</v>
@@ -39665,7 +39664,7 @@
         <v>2494</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1487</v>
@@ -39692,7 +39691,7 @@
         <v>2494</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1487</v>
@@ -39719,7 +39718,7 @@
         <v>2494</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1487</v>
@@ -39746,7 +39745,7 @@
         <v>2494</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1487</v>
@@ -39758,7 +39757,7 @@
     </row>
     <row r="143" spans="1:9" s="183" customFormat="1">
       <c r="A143" s="183" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B143" s="183">
         <v>62385671</v>
@@ -39773,7 +39772,7 @@
         <v>2494</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1487</v>
@@ -39800,7 +39799,7 @@
         <v>2494</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1487</v>
@@ -39812,7 +39811,7 @@
     </row>
     <row r="146" spans="1:9" s="76" customFormat="1">
       <c r="A146" s="195" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B146" s="195" t="s">
         <v>2251</v>
@@ -39827,7 +39826,7 @@
         <v>2494</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1487</v>
@@ -39854,7 +39853,7 @@
         <v>2494</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1487</v>
@@ -39866,7 +39865,7 @@
     </row>
     <row r="148" spans="1:9" s="183" customFormat="1">
       <c r="A148" s="183" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B148" s="183">
         <v>60389752</v>
@@ -39881,7 +39880,7 @@
         <v>2494</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1487</v>
@@ -39908,7 +39907,7 @@
         <v>2494</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1487</v>
@@ -39920,22 +39919,22 @@
     </row>
     <row r="150" spans="1:9" s="183" customFormat="1">
       <c r="A150" s="183" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B150" s="183">
         <v>67433224</v>
       </c>
       <c r="C150" s="183" t="s">
-        <v>3053</v>
+        <v>3049</v>
       </c>
       <c r="D150" s="183" t="s">
-        <v>3055</v>
+        <v>3051</v>
       </c>
       <c r="E150" s="183" t="s">
         <v>2494</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1487</v>
@@ -39962,7 +39961,7 @@
         <v>2494</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1487</v>
@@ -39989,7 +39988,7 @@
         <v>2639</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>1487</v>
@@ -40016,7 +40015,7 @@
         <v>2639</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>1487</v>
@@ -40028,7 +40027,7 @@
     </row>
     <row r="155" spans="1:9" s="183" customFormat="1">
       <c r="A155" s="183" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B155" s="183">
         <v>62560788</v>
@@ -40043,7 +40042,7 @@
         <v>2639</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>1487</v>
@@ -40055,7 +40054,7 @@
     </row>
     <row r="156" spans="1:9" s="183" customFormat="1">
       <c r="A156" s="193" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B156" s="193">
         <v>64403333</v>
@@ -40070,7 +40069,7 @@
         <v>2639</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>1487</v>
@@ -40082,22 +40081,22 @@
     </row>
     <row r="157" spans="1:9" s="183" customFormat="1">
       <c r="A157" s="193" t="s">
-        <v>3447</v>
+        <v>3443</v>
       </c>
       <c r="B157" s="193">
         <v>60125401</v>
       </c>
       <c r="C157" s="194" t="s">
-        <v>3446</v>
+        <v>3442</v>
       </c>
       <c r="D157" s="193" t="s">
-        <v>3448</v>
+        <v>3444</v>
       </c>
       <c r="E157" s="183" t="s">
         <v>2639</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>1487</v>
@@ -40109,7 +40108,7 @@
     </row>
     <row r="158" spans="1:9" s="183" customFormat="1">
       <c r="A158" s="193" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B158" s="193">
         <v>64720128</v>
@@ -40124,7 +40123,7 @@
         <v>2639</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>1487</v>
@@ -40136,7 +40135,7 @@
     </row>
     <row r="160" spans="1:9" s="76" customFormat="1">
       <c r="A160" s="76" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B160" s="76">
         <v>69661499</v>
@@ -40151,7 +40150,7 @@
         <v>365</v>
       </c>
       <c r="F160" s="195" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="G160" s="76" t="s">
         <v>2501</v>
@@ -40180,7 +40179,7 @@
         <v>365</v>
       </c>
       <c r="F161" s="193" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="G161" s="183" t="s">
         <v>2501</v>
@@ -40209,7 +40208,7 @@
         <v>365</v>
       </c>
       <c r="F162" s="193" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="G162" s="183" t="s">
         <v>2501</v>
@@ -40223,7 +40222,7 @@
     </row>
     <row r="163" spans="1:9" s="183" customFormat="1">
       <c r="A163" s="235" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B163" s="183">
         <v>62747874</v>
@@ -40238,7 +40237,7 @@
         <v>365</v>
       </c>
       <c r="F163" s="193" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="G163" s="183" t="s">
         <v>2501</v>
@@ -40267,7 +40266,7 @@
         <v>365</v>
       </c>
       <c r="F164" s="193" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="G164" s="183" t="s">
         <v>2501</v>
@@ -40287,16 +40286,16 @@
         <v>64403333</v>
       </c>
       <c r="C165" s="194" t="s">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="D165" s="426" t="s">
-        <v>3448</v>
+        <v>3444</v>
       </c>
       <c r="E165" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F165" s="193" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="G165" s="183" t="s">
         <v>2501</v>
@@ -40331,7 +40330,7 @@
     </row>
     <row r="192" spans="1:9" s="389" customFormat="1" ht="23.5">
       <c r="B192" s="389" t="s">
-        <v>3054</v>
+        <v>3050</v>
       </c>
       <c r="C192" s="390"/>
       <c r="D192" s="391"/>
@@ -40357,7 +40356,7 @@
         <v>319</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>3053</v>
+        <v>3049</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40370,7 +40369,7 @@
         <v>316</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>3078</v>
+        <v>3074</v>
       </c>
       <c r="E195" s="30"/>
       <c r="F195"/>
@@ -40383,7 +40382,7 @@
         <v>444</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>3104</v>
+        <v>3100</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40394,7 +40393,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>3181</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40402,7 +40401,7 @@
         <v>1366</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>3192</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40410,7 +40409,7 @@
         <v>1721</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>3279</v>
+        <v>3275</v>
       </c>
       <c r="F199" s="408"/>
     </row>
@@ -40419,7 +40418,7 @@
         <v>1344</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>3323</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40427,7 +40426,7 @@
         <v>411</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>3365</v>
+        <v>3361</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40435,7 +40434,7 @@
         <v>716</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40443,7 +40442,7 @@
         <v>284</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>3445</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40451,7 +40450,7 @@
         <v>2505</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>3446</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40461,7 +40460,7 @@
         <v>470</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>3506</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40469,7 +40468,7 @@
         <v>222</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>3581</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41786,7 +41785,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B3">
         <v>62349088</v>
@@ -41807,16 +41806,16 @@
         <v>712</v>
       </c>
       <c r="H3" t="s">
-        <v>3328</v>
+        <v>3324</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3549</v>
+        <v>3545</v>
       </c>
       <c r="J3"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="220" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B4" t="s">
         <v>2769</v>
@@ -41840,16 +41839,16 @@
         <v>2875</v>
       </c>
       <c r="I4" t="s">
-        <v>3437</v>
+        <v>3433</v>
       </c>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B5" t="s">
-        <v>3280</v>
+        <v>3276</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>485</v>
@@ -41858,7 +41857,7 @@
         <v>1575</v>
       </c>
       <c r="E5" t="s">
-        <v>3587</v>
+        <v>3583</v>
       </c>
       <c r="F5" t="s">
         <v>2260</v>
@@ -41867,10 +41866,10 @@
         <v>520</v>
       </c>
       <c r="H5" s="440" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3199</v>
+        <v>3195</v>
       </c>
       <c r="J5" t="s">
         <v>1438</v>
@@ -41898,7 +41897,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B7" s="180">
         <v>64403333</v>
@@ -41924,13 +41923,13 @@
         <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>3412</v>
+        <v>3408</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2146</v>
       </c>
       <c r="D8" t="s">
-        <v>3411</v>
+        <v>3407</v>
       </c>
       <c r="E8" t="s">
         <v>2445</v>
@@ -41942,10 +41941,10 @@
         <v>253</v>
       </c>
       <c r="H8" s="105" t="s">
-        <v>3413</v>
+        <v>3409</v>
       </c>
       <c r="I8" t="s">
-        <v>3139</v>
+        <v>3135</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41963,7 +41962,7 @@
         <v>2951</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3138</v>
+        <v>3134</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2147</v>
@@ -41972,10 +41971,10 @@
         <v>253</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3242</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -42009,7 +42008,7 @@
         <v>441</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>2968</v>
+        <v>3660</v>
       </c>
       <c r="I12" s="49" t="s">
         <v>2781</v>
@@ -42054,34 +42053,34 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="10" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="B16" s="10">
         <v>67663098</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>3247</v>
+        <v>3243</v>
       </c>
       <c r="D16" t="s">
-        <v>3246</v>
+        <v>3242</v>
       </c>
       <c r="E16" t="s">
-        <v>3307</v>
+        <v>3303</v>
       </c>
       <c r="F16" t="s">
-        <v>3308</v>
+        <v>3304</v>
       </c>
       <c r="G16" t="s">
         <v>122</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>3322</v>
+        <v>3318</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>3325</v>
+        <v>3321</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>3409</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="19" customFormat="1"/>
@@ -42207,15 +42206,15 @@
         <v>522</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3553</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2546</v>
@@ -42236,7 +42235,7 @@
         <v>522</v>
       </c>
       <c r="H7" t="s">
-        <v>3130</v>
+        <v>3126</v>
       </c>
       <c r="I7" s="276" t="s">
         <v>2785</v>
@@ -42318,7 +42317,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -42327,7 +42326,7 @@
         <v>2303</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3591</v>
+        <v>3587</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>976</v>
@@ -42339,10 +42338,10 @@
         <v>522</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42415,12 +42414,12 @@
         <v>2702</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3222</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="10" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B19" s="10">
         <v>65188271</v>
@@ -42441,7 +42440,7 @@
         <v>522</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>3520</v>
+        <v>3516</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2765</v>
@@ -42478,10 +42477,10 @@
         <v>522</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -42507,10 +42506,10 @@
         <v>522</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3333</v>
+        <v>3329</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3334</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42524,7 +42523,7 @@
         <v>2578</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3563</v>
+        <v>3559</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>976</v>
@@ -42536,10 +42535,10 @@
         <v>522</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3289</v>
+        <v>3285</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3529</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42549,7 +42548,7 @@
         <v>2593</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3590</v>
+        <v>3586</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>976</v>
@@ -42802,10 +42801,10 @@
         <v>980</v>
       </c>
       <c r="H6" t="s">
-        <v>3197</v>
+        <v>3193</v>
       </c>
       <c r="I6" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2329</v>
@@ -42813,16 +42812,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="10" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>3089</v>
+        <v>3085</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>2402</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3088</v>
+        <v>3084</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2403</v>
@@ -42834,13 +42833,13 @@
         <v>980</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>3090</v>
+        <v>3086</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3103</v>
+        <v>3099</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3580</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42848,58 +42847,58 @@
         <v>2587</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>3351</v>
+        <v>3347</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>3348</v>
+        <v>3344</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>3347</v>
+        <v>3343</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>3349</v>
+        <v>3345</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>3350</v>
+        <v>3346</v>
       </c>
       <c r="G8" t="s">
         <v>980</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3589</v>
+        <v>3585</v>
       </c>
       <c r="I8" s="279"/>
       <c r="J8" s="10" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>3602</v>
+        <v>3598</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>3347</v>
+        <v>3343</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>3350</v>
+        <v>3346</v>
       </c>
       <c r="G9" t="s">
         <v>980</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3607</v>
+        <v>3603</v>
       </c>
       <c r="J9" s="97"/>
     </row>
@@ -42958,18 +42957,18 @@
         <v>361</v>
       </c>
       <c r="D2" s="367" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>3064</v>
+        <v>3060</v>
       </c>
       <c r="B5">
         <v>68658411</v>
       </c>
       <c r="C5" t="s">
-        <v>3063</v>
+        <v>3059</v>
       </c>
       <c r="D5" t="s">
         <v>2849</v>
@@ -42980,13 +42979,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="B6" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="C6" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="D6" t="s">
         <v>1342</v>
@@ -43064,7 +43063,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -43073,7 +43072,7 @@
         <v>1854</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2817</v>
@@ -43114,7 +43113,7 @@
         <v>65124748</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3419</v>
+        <v>3415</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2849</v>
@@ -43135,7 +43134,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3450</v>
+        <v>3446</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2849</v>
@@ -43311,7 +43310,7 @@
     <row r="1" spans="1:8" s="425" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="424"/>
       <c r="B1" s="424" t="s">
-        <v>3438</v>
+        <v>3434</v>
       </c>
       <c r="C1" s="424"/>
     </row>
@@ -43320,25 +43319,25 @@
         <v>148</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3505</v>
+        <v>3501</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>3525</v>
+        <v>3521</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3526</v>
+        <v>3522</v>
       </c>
       <c r="E4" t="s">
-        <v>3439</v>
+        <v>3435</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3453</v>
+        <v>3449</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>3454</v>
+        <v>3450</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3651</v>
+        <v>3647</v>
       </c>
     </row>
   </sheetData>
@@ -43556,7 +43555,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="B27" t="s">
         <v>297</v>
@@ -43573,7 +43572,7 @@
         <v>2884</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2883</v>
@@ -43584,7 +43583,7 @@
         <v>2884</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -43700,7 +43699,7 @@
         <v>2740</v>
       </c>
       <c r="C5" s="329" t="s">
-        <v>3286</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="329" customFormat="1">
@@ -43708,10 +43707,10 @@
         <v>2719</v>
       </c>
       <c r="B6" s="329" t="s">
-        <v>3285</v>
+        <v>3281</v>
       </c>
       <c r="C6" s="329" t="s">
-        <v>3285</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="329" customFormat="1">
@@ -43786,10 +43785,10 @@
         <v>2751</v>
       </c>
       <c r="H14" s="335" t="s">
-        <v>3293</v>
+        <v>3289</v>
       </c>
       <c r="I14" s="335" t="s">
-        <v>3296</v>
+        <v>3292</v>
       </c>
       <c r="L14" s="335"/>
       <c r="M14" s="335"/>
@@ -43817,10 +43816,10 @@
         <v>2752</v>
       </c>
       <c r="H15" s="336" t="s">
-        <v>3294</v>
+        <v>3290</v>
       </c>
       <c r="I15" s="336" t="s">
-        <v>3297</v>
+        <v>3293</v>
       </c>
       <c r="L15" s="336"/>
       <c r="M15" s="336"/>
@@ -43848,7 +43847,7 @@
         <v>2753</v>
       </c>
       <c r="H16" s="336" t="s">
-        <v>3295</v>
+        <v>3291</v>
       </c>
       <c r="I16" s="336" t="s">
         <v>1383</v>
@@ -43861,7 +43860,7 @@
         <v>2724</v>
       </c>
       <c r="B17" s="410" t="s">
-        <v>3282</v>
+        <v>3278</v>
       </c>
       <c r="C17" s="410"/>
       <c r="D17" s="410"/>
@@ -43878,7 +43877,7 @@
         <v>2719</v>
       </c>
       <c r="B18" s="410" t="s">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="C18" s="410"/>
       <c r="D18" s="410"/>
@@ -43895,7 +43894,7 @@
         <v>2720</v>
       </c>
       <c r="B19" s="410" t="s">
-        <v>3284</v>
+        <v>3280</v>
       </c>
       <c r="C19" s="410"/>
       <c r="D19" s="410"/>
@@ -44024,7 +44023,7 @@
         <v>2730</v>
       </c>
       <c r="C29" s="348" t="s">
-        <v>3041</v>
+        <v>3037</v>
       </c>
       <c r="D29" s="348"/>
       <c r="E29" s="348"/>
@@ -44043,7 +44042,7 @@
         <v>2731</v>
       </c>
       <c r="C30" s="349" t="s">
-        <v>3042</v>
+        <v>3038</v>
       </c>
       <c r="D30" s="349"/>
       <c r="E30" s="349"/>
@@ -44797,7 +44796,7 @@
         <v>2372</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3082</v>
+        <v>3078</v>
       </c>
       <c r="L7" s="3"/>
     </row>
@@ -44824,7 +44823,7 @@
         <v>901</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="I8" s="309" t="s">
         <v>2955</v>
@@ -44832,7 +44831,7 @@
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
       <c r="A9" t="s">
-        <v>2835</v>
+        <v>2612</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>1149</v>
@@ -44853,10 +44852,10 @@
         <v>160</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3220</v>
+        <v>3216</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>828</v>
@@ -44864,7 +44863,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44885,10 +44884,10 @@
         <v>247</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3328</v>
+        <v>3324</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3127</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44914,10 +44913,10 @@
         <v>247</v>
       </c>
       <c r="H11" t="s">
-        <v>3401</v>
+        <v>3397</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3407</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44943,10 +44942,10 @@
         <v>247</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3435</v>
+        <v>3431</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3496</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44972,10 +44971,10 @@
         <v>247</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3167</v>
+        <v>3163</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3421</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -45001,25 +45000,25 @@
         <v>247</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3366</v>
+        <v>3362</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3383</v>
+        <v>3379</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="105" t="s">
-        <v>3263</v>
+        <v>3259</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>343</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>3262</v>
+        <v>3258</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>1587</v>
@@ -45031,10 +45030,10 @@
         <v>901</v>
       </c>
       <c r="H15" t="s">
-        <v>3120</v>
+        <v>3116</v>
       </c>
       <c r="I15" t="s">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>503</v>
@@ -45042,16 +45041,16 @@
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1">
       <c r="A16" s="4" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>2799</v>
       </c>
       <c r="D16" t="s">
-        <v>3240</v>
+        <v>3236</v>
       </c>
       <c r="E16" t="s">
         <v>2801</v>
@@ -45063,10 +45062,10 @@
         <v>160</v>
       </c>
       <c r="H16" t="s">
-        <v>3315</v>
+        <v>3311</v>
       </c>
       <c r="I16" t="s">
-        <v>3241</v>
+        <v>3237</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>817</v>
@@ -45074,7 +45073,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -45109,19 +45108,19 @@
         <v>2316</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3396</v>
+        <v>3392</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3397</v>
+        <v>3393</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>247</v>
       </c>
       <c r="H18" t="s">
-        <v>3620</v>
+        <v>3616</v>
       </c>
       <c r="I18" t="s">
-        <v>3389</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -45132,13 +45131,13 @@
         <v>64403333</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3160</v>
+        <v>3156</v>
       </c>
       <c r="D19" t="s">
         <v>2800</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3159</v>
+        <v>3155</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>2628</v>
@@ -45151,7 +45150,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45244,7 +45243,7 @@
         <v>160</v>
       </c>
       <c r="H23" t="s">
-        <v>3154</v>
+        <v>3150</v>
       </c>
       <c r="I23" s="309" t="s">
         <v>2759</v>
@@ -45262,10 +45261,10 @@
         <v>1693</v>
       </c>
       <c r="D24" t="s">
-        <v>3650</v>
+        <v>3646</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3652</v>
+        <v>3648</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2628</v>
@@ -45276,7 +45275,7 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2631</v>
@@ -45288,7 +45287,7 @@
         <v>2109</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3539</v>
+        <v>3535</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2634</v>
@@ -45297,7 +45296,7 @@
         <v>247</v>
       </c>
       <c r="H25" s="220" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="I25" s="309" t="s">
         <v>2908</v>
@@ -45326,10 +45325,10 @@
         <v>247</v>
       </c>
       <c r="H26" t="s">
-        <v>3193</v>
+        <v>3189</v>
       </c>
       <c r="I26" t="s">
-        <v>3045</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -45337,7 +45336,7 @@
         <v>2650</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>3178</v>
+        <v>3174</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>370</v>
@@ -45355,10 +45354,10 @@
         <v>160</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3403</v>
+        <v>3399</v>
       </c>
       <c r="I27" t="s">
-        <v>3126</v>
+        <v>3122</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>825</v>
@@ -45366,7 +45365,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2621</v>
@@ -45390,13 +45389,13 @@
         <v>2873</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="K28"/>
     </row>
     <row r="29" spans="1:12" s="75" customFormat="1">
       <c r="A29" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B29" t="s">
         <v>1246</v>
@@ -45405,10 +45404,10 @@
         <v>353</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>3310</v>
+        <v>3306</v>
       </c>
       <c r="E29" t="s">
-        <v>3248</v>
+        <v>3244</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2634</v>
@@ -45417,26 +45416,26 @@
         <v>253</v>
       </c>
       <c r="H29" t="s">
-        <v>3311</v>
+        <v>3307</v>
       </c>
       <c r="I29" t="s">
-        <v>3223</v>
+        <v>3219</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3613</v>
+        <v>3609</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>407</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
       <c r="E30" t="s">
         <v>2509</v>
@@ -45448,15 +45447,15 @@
         <v>160</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3617</v>
+        <v>3613</v>
       </c>
       <c r="I30" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3263</v>
+        <v>3259</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45477,10 +45476,10 @@
         <v>160</v>
       </c>
       <c r="H31" t="s">
-        <v>3131</v>
+        <v>3127</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3196</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45506,10 +45505,10 @@
         <v>160</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3517</v>
+        <v>3513</v>
       </c>
       <c r="I32" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45517,7 +45516,7 @@
         <v>2664</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2798</v>
@@ -45535,10 +45534,10 @@
         <v>160</v>
       </c>
       <c r="H33" t="s">
-        <v>3177</v>
+        <v>3173</v>
       </c>
       <c r="I33" t="s">
-        <v>3550</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45567,7 +45566,7 @@
         <v>2803</v>
       </c>
       <c r="I34" t="s">
-        <v>3211</v>
+        <v>3207</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45576,13 +45575,13 @@
         <v>148</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3475</v>
+        <v>3471</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2796</v>
       </c>
       <c r="D35" t="s">
-        <v>3474</v>
+        <v>3470</v>
       </c>
       <c r="E35" t="s">
         <v>2801</v>
@@ -45594,10 +45593,10 @@
         <v>2804</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3522</v>
+        <v>3518</v>
       </c>
       <c r="I35" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -45623,10 +45622,10 @@
         <v>160</v>
       </c>
       <c r="H36" s="378" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="I36" t="s">
-        <v>3096</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45634,13 +45633,13 @@
         <v>2650</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3206</v>
+        <v>3202</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2811</v>
       </c>
       <c r="D37" t="s">
-        <v>3380</v>
+        <v>3376</v>
       </c>
       <c r="E37" t="s">
         <v>2813</v>
@@ -45652,10 +45651,10 @@
         <v>160</v>
       </c>
       <c r="H37" t="s">
-        <v>3381</v>
+        <v>3377</v>
       </c>
       <c r="I37" t="s">
-        <v>3462</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45663,7 +45662,7 @@
         <v>158</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3633</v>
+        <v>3629</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2812</v>
@@ -45717,10 +45716,10 @@
         <v>2697</v>
       </c>
       <c r="J45" s="49" t="s">
-        <v>3152</v>
+        <v>3148</v>
       </c>
       <c r="K45" t="s">
-        <v>3456</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -46126,13 +46125,13 @@
         <v>158</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3636</v>
+        <v>3632</v>
       </c>
       <c r="C2" s="277" t="s">
         <v>257</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1335</v>
@@ -46144,16 +46143,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="301" t="s">
-        <v>2991</v>
-      </c>
-      <c r="I2" s="448" t="s">
-        <v>3649</v>
+        <v>2989</v>
+      </c>
+      <c r="I2" s="106" t="s">
+        <v>3645</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3424</v>
+        <v>3420</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3388</v>
+        <v>3384</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -46180,16 +46179,16 @@
         <v>273</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3081</v>
+        <v>3077</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3122</v>
+        <v>3118</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3402</v>
+        <v>3398</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3190</v>
+        <v>3186</v>
       </c>
       <c r="M4" s="39"/>
     </row>
@@ -46216,56 +46215,56 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3288</v>
+        <v>3284</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>3482</v>
+        <v>3478</v>
       </c>
       <c r="J5" s="145"/>
       <c r="K5" s="217" t="s">
-        <v>3062</v>
+        <v>3058</v>
       </c>
       <c r="M5" s="36"/>
     </row>
     <row r="6" spans="1:13" s="30" customFormat="1">
       <c r="A6" s="107" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>2278</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>3043</v>
+        <v>3039</v>
       </c>
       <c r="D6" s="30" t="s">
         <v>2545</v>
       </c>
       <c r="E6" s="140" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="F6" s="140" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="G6" s="106" t="s">
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3521</v>
-      </c>
-      <c r="I6" s="442" t="s">
-        <v>3641</v>
+        <v>3517</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>3637</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3207</v>
+        <v>3203</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3094</v>
+        <v>3090</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1246</v>
@@ -46286,16 +46285,16 @@
         <v>731</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3132</v>
+        <v>3128</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>2891</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3523</v>
+        <v>3519</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46322,22 +46321,22 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3406</v>
+        <v>3402</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3598</v>
+        <v>3594</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3420</v>
+        <v>3416</v>
       </c>
       <c r="K8" s="139" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="305" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1736</v>
@@ -46358,22 +46357,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3584</v>
+        <v>3580</v>
       </c>
       <c r="J9" s="217" t="s">
         <v>2932</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3551</v>
+        <v>3547</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>2054</v>
@@ -46394,22 +46393,22 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3155</v>
+        <v>3151</v>
       </c>
       <c r="I10" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3329</v>
+        <v>3325</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3585</v>
+        <v>3581</v>
       </c>
       <c r="M10" s="34"/>
     </row>
     <row r="11" spans="1:13" s="30" customFormat="1">
       <c r="A11" s="107" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B11" s="107">
         <v>62657225</v>
@@ -46430,16 +46429,16 @@
         <v>610</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3197</v>
+        <v>3193</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3518</v>
+        <v>3514</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3139</v>
+        <v>3135</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -46454,7 +46453,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3268</v>
+        <v>3264</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>922</v>
@@ -46466,25 +46465,25 @@
         <v>248</v>
       </c>
       <c r="H12" s="106" t="s">
-        <v>3395</v>
+        <v>3391</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3382</v>
+        <v>3378</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3317</v>
+        <v>3313</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3267</v>
+        <v>3263</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3074</v>
+        <v>3070</v>
       </c>
       <c r="B13" s="107" t="s">
-        <v>3101</v>
+        <v>3097</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>933</v>
@@ -46493,25 +46492,25 @@
         <v>1105</v>
       </c>
       <c r="E13" s="140" t="s">
-        <v>3049</v>
+        <v>3045</v>
       </c>
       <c r="F13" s="140" t="s">
-        <v>3050</v>
+        <v>3046</v>
       </c>
       <c r="G13" s="106" t="s">
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="I13" s="217" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3191</v>
+        <v>3187</v>
       </c>
       <c r="K13" t="s">
-        <v>3046</v>
+        <v>3042</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46538,7 +46537,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3442</v>
+        <v>3438</v>
       </c>
       <c r="I14" s="427" t="s">
         <v>2373</v>
@@ -46571,21 +46570,21 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3367</v>
+        <v>3363</v>
       </c>
       <c r="I15" t="s">
-        <v>3645</v>
+        <v>3641</v>
       </c>
       <c r="J15" t="s">
-        <v>3140</v>
+        <v>3136</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="M15" s="36"/>
     </row>
     <row r="16" spans="1:13" s="30" customFormat="1">
-      <c r="A16" s="446" t="s">
+      <c r="A16" s="30" t="s">
         <v>158</v>
       </c>
       <c r="B16" s="30">
@@ -46632,16 +46631,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3129</v>
-      </c>
-      <c r="I17" s="446" t="s">
-        <v>3656</v>
+        <v>3125</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>3652</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3493</v>
+        <v>3489</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3306</v>
+        <v>3302</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46668,16 +46667,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
       <c r="I18" t="s">
-        <v>3102</v>
+        <v>3098</v>
       </c>
       <c r="J18" t="s">
-        <v>3120</v>
+        <v>3116</v>
       </c>
       <c r="K18" t="s">
-        <v>3443</v>
+        <v>3439</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46692,7 +46691,7 @@
         <v>1754</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3038</v>
+        <v>3035</v>
       </c>
       <c r="E19" t="s">
         <v>1757</v>
@@ -46704,22 +46703,22 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3039</v>
+        <v>3659</v>
       </c>
       <c r="I19" t="s">
-        <v>3431</v>
+        <v>3427</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3052</v>
+        <v>3048</v>
       </c>
       <c r="K19" t="s">
-        <v>3597</v>
+        <v>3593</v>
       </c>
       <c r="M19" s="36"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="305" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B20" t="s">
         <v>2665</v>
@@ -46728,7 +46727,7 @@
         <v>2655</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2559</v>
@@ -46740,16 +46739,16 @@
         <v>65</v>
       </c>
       <c r="H20" s="319" t="s">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="I20" t="s">
-        <v>3573</v>
+        <v>3569</v>
       </c>
       <c r="J20" t="s">
-        <v>3575</v>
+        <v>3571</v>
       </c>
       <c r="K20" t="s">
-        <v>3616</v>
+        <v>3612</v>
       </c>
       <c r="M20" s="36"/>
     </row>
@@ -46814,7 +46813,7 @@
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B31" s="107">
         <v>64403333</v>
@@ -46909,7 +46908,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46921,10 +46920,10 @@
         <v>2221</v>
       </c>
       <c r="E35" s="140" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="F35" s="140" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="G35" s="106" t="s">
         <v>731</v>
@@ -46933,7 +46932,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B36">
         <v>60389752</v>
@@ -46957,7 +46956,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -47019,10 +47018,10 @@
         <v>2234</v>
       </c>
       <c r="E39" s="140" t="s">
-        <v>3376</v>
+        <v>3372</v>
       </c>
       <c r="F39" s="140" t="s">
-        <v>3377</v>
+        <v>3373</v>
       </c>
       <c r="G39" s="106" t="s">
         <v>731</v>
@@ -47060,7 +47059,7 @@
         <v>372</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>3082</v>
+        <v>3078</v>
       </c>
       <c r="I43" s="139"/>
       <c r="K43" s="240"/>
@@ -47075,10 +47074,10 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="180" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B45" t="s">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="C45" t="s">
         <v>2693</v>
@@ -47087,7 +47086,7 @@
         <v>2694</v>
       </c>
       <c r="E45" t="s">
-        <v>3163</v>
+        <v>3159</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2695</v>
@@ -47096,13 +47095,13 @@
         <v>372</v>
       </c>
       <c r="H45" t="s">
-        <v>3040</v>
+        <v>3036</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3212</v>
+        <v>3208</v>
       </c>
       <c r="J45" t="s">
-        <v>3478</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47132,16 +47131,16 @@
     </row>
     <row r="54" spans="1:13" s="30" customFormat="1">
       <c r="C54" s="138" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="D54" t="s">
+        <v>2972</v>
+      </c>
+      <c r="E54" s="140" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F54" s="140" t="s">
         <v>2974</v>
-      </c>
-      <c r="E54" s="140" t="s">
-        <v>2975</v>
-      </c>
-      <c r="F54" s="140" t="s">
-        <v>2976</v>
       </c>
       <c r="G54" s="32" t="s">
         <v>273</v>
@@ -47205,7 +47204,7 @@
     </row>
     <row r="71" spans="1:38">
       <c r="C71" s="7" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="D71" s="107" t="s">
         <v>2232</v>
@@ -47636,12 +47635,12 @@
         <v>361</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="105" spans="2:5">
       <c r="D105" s="1" t="s">
-        <v>3043</v>
+        <v>3039</v>
       </c>
     </row>
   </sheetData>
@@ -47857,7 +47856,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="45" t="s">
-        <v>3166</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -47993,7 +47992,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>3339</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -48002,7 +48001,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48254,7 +48253,7 @@
         <v>144</v>
       </c>
       <c r="B6" s="248" t="s">
-        <v>3387</v>
+        <v>3383</v>
       </c>
       <c r="C6" s="247" t="s">
         <v>1327</v>
@@ -48272,13 +48271,13 @@
         <v>360</v>
       </c>
       <c r="H6" s="248" t="s">
-        <v>3219</v>
+        <v>3215</v>
       </c>
       <c r="I6" s="245" t="s">
-        <v>3400</v>
+        <v>3396</v>
       </c>
       <c r="J6" s="296" t="s">
-        <v>3467</v>
+        <v>3463</v>
       </c>
       <c r="K6" s="248" t="s">
         <v>480</v>
@@ -48291,7 +48290,7 @@
     </row>
     <row r="8" spans="1:11" s="266" customFormat="1">
       <c r="A8" s="299" t="s">
-        <v>2835</v>
+        <v>2612</v>
       </c>
       <c r="B8" s="265">
         <v>65509692</v>
@@ -48306,19 +48305,19 @@
         <v>1055</v>
       </c>
       <c r="F8" s="266" t="s">
-        <v>3204</v>
+        <v>3200</v>
       </c>
       <c r="G8" s="266" t="s">
         <v>696</v>
       </c>
       <c r="H8" s="296" t="s">
-        <v>3168</v>
+        <v>3164</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>3593</v>
+        <v>3589</v>
       </c>
       <c r="J8" s="266" t="s">
-        <v>3330</v>
+        <v>3326</v>
       </c>
       <c r="K8" s="266" t="s">
         <v>717</v>
@@ -48347,17 +48346,17 @@
         <v>253</v>
       </c>
       <c r="H9" s="106" t="s">
-        <v>3194</v>
+        <v>3190</v>
       </c>
       <c r="I9" s="106" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="J9" s="106" t="s">
         <v>2315</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="260" customFormat="1">
-      <c r="A10" s="444" t="s">
+      <c r="A10" s="443" t="s">
         <v>2716</v>
       </c>
       <c r="B10" s="265">
@@ -48373,7 +48372,7 @@
         <v>1456</v>
       </c>
       <c r="F10" s="264" t="s">
-        <v>3231</v>
+        <v>3227</v>
       </c>
       <c r="G10" s="264" t="s">
         <v>962</v>
@@ -48405,13 +48404,13 @@
         <v>696</v>
       </c>
       <c r="H11" s="265" t="s">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="I11" s="296" t="s">
-        <v>3543</v>
+        <v>3539</v>
       </c>
       <c r="J11" s="265" t="s">
-        <v>3436</v>
+        <v>3432</v>
       </c>
       <c r="K11" s="246" t="s">
         <v>1240</v>
@@ -48440,20 +48439,20 @@
         <v>696</v>
       </c>
       <c r="H12" s="215" t="s">
-        <v>3574</v>
+        <v>3570</v>
       </c>
       <c r="I12" s="215" t="s">
-        <v>3232</v>
+        <v>3228</v>
       </c>
       <c r="J12" s="270" t="s">
-        <v>3473</v>
+        <v>3469</v>
       </c>
       <c r="K12" s="183" t="s">
         <v>1241</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="183" customFormat="1">
-      <c r="A13" s="443" t="s">
+      <c r="A13" s="442" t="s">
         <v>2828</v>
       </c>
       <c r="B13" s="215">
@@ -48480,10 +48479,10 @@
     </row>
     <row r="14" spans="1:11" s="224" customFormat="1">
       <c r="A14" s="224" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B14" s="224" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
       <c r="C14" s="441" t="s">
         <v>338</v>
@@ -48492,22 +48491,22 @@
         <v>2535</v>
       </c>
       <c r="E14" s="224" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
       <c r="F14" s="224" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
       <c r="G14" s="224" t="s">
         <v>696</v>
       </c>
       <c r="H14" s="224" t="s">
-        <v>3637</v>
+        <v>3633</v>
       </c>
       <c r="I14" s="224" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
       <c r="J14" s="224" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
       <c r="K14" s="224" t="s">
         <v>1359</v>
@@ -48527,7 +48526,7 @@
         <v>2047</v>
       </c>
       <c r="E15" s="216" t="s">
-        <v>3204</v>
+        <v>3200</v>
       </c>
       <c r="F15" s="216" t="s">
         <v>1480</v>
@@ -48536,13 +48535,13 @@
         <v>696</v>
       </c>
       <c r="H15" s="273" t="s">
-        <v>3565</v>
+        <v>3561</v>
       </c>
       <c r="I15" s="215" t="s">
-        <v>3519</v>
+        <v>3515</v>
       </c>
       <c r="J15" s="263" t="s">
-        <v>3198</v>
+        <v>3194</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1242</v>
@@ -48553,31 +48552,31 @@
         <v>1462</v>
       </c>
       <c r="B16" s="265" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
       <c r="C16" s="271" t="s">
         <v>1344</v>
       </c>
       <c r="D16" s="260" t="s">
-        <v>3489</v>
+        <v>3485</v>
       </c>
       <c r="E16" s="260" t="s">
-        <v>3065</v>
+        <v>3061</v>
       </c>
       <c r="F16" s="260" t="s">
-        <v>3066</v>
+        <v>3062</v>
       </c>
       <c r="G16" s="260" t="s">
         <v>696</v>
       </c>
       <c r="H16" s="265" t="s">
-        <v>3524</v>
+        <v>3520</v>
       </c>
       <c r="I16" s="272" t="s">
-        <v>3354</v>
+        <v>3350</v>
       </c>
       <c r="J16" s="265" t="s">
-        <v>3490</v>
+        <v>3486</v>
       </c>
       <c r="K16" s="260" t="s">
         <v>1486</v>
@@ -48608,7 +48607,7 @@
     </row>
     <row r="18" spans="1:11" s="265" customFormat="1">
       <c r="A18" s="266" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B18" s="266">
         <v>65325884</v>
@@ -48650,7 +48649,7 @@
         <v>696</v>
       </c>
       <c r="J19" s="265" t="s">
-        <v>3298</v>
+        <v>3294</v>
       </c>
       <c r="K19" s="265" t="s">
         <v>1705</v>
@@ -48679,7 +48678,7 @@
         <v>696</v>
       </c>
       <c r="I20" s="260" t="s">
-        <v>3425</v>
+        <v>3421</v>
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="265" t="s">
@@ -48688,7 +48687,7 @@
     </row>
     <row r="21" spans="1:11" s="260" customFormat="1">
       <c r="A21" s="272" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B21" s="260" t="s">
         <v>2465</v>
@@ -48709,13 +48708,13 @@
         <v>696</v>
       </c>
       <c r="H21" s="260" t="s">
-        <v>3494</v>
+        <v>3490</v>
       </c>
       <c r="I21" s="265" t="s">
-        <v>3051</v>
+        <v>3047</v>
       </c>
       <c r="J21" s="260" t="s">
-        <v>3378</v>
+        <v>3374</v>
       </c>
       <c r="K21" s="265" t="s">
         <v>1833</v>
@@ -48723,7 +48722,7 @@
     </row>
     <row r="22" spans="1:11" s="260" customFormat="1">
       <c r="A22" s="246" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="B22" s="260" t="s">
         <v>2522</v>
@@ -48744,13 +48743,13 @@
         <v>696</v>
       </c>
       <c r="H22" s="260" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="I22" s="260" t="s">
-        <v>3011</v>
-      </c>
-      <c r="J22" s="49" t="s">
-        <v>2969</v>
+        <v>3009</v>
+      </c>
+      <c r="J22" s="260" t="s">
+        <v>3657</v>
       </c>
       <c r="K22" s="260" t="s">
         <v>1878</v>
@@ -48779,13 +48778,13 @@
         <v>696</v>
       </c>
       <c r="H24" s="265" t="s">
-        <v>3077</v>
+        <v>3073</v>
       </c>
       <c r="I24" s="265" t="s">
-        <v>3405</v>
+        <v>3401</v>
       </c>
       <c r="J24" s="265" t="s">
-        <v>3374</v>
+        <v>3370</v>
       </c>
       <c r="K24" s="260" t="s">
         <v>1880</v>
@@ -48826,7 +48825,7 @@
         <v>642</v>
       </c>
       <c r="D27" s="256" t="s">
-        <v>3621</v>
+        <v>3617</v>
       </c>
       <c r="E27" s="272" t="s">
         <v>2539</v>
@@ -48838,7 +48837,7 @@
         <v>714</v>
       </c>
       <c r="H27" s="260" t="s">
-        <v>3620</v>
+        <v>3616</v>
       </c>
       <c r="I27" s="145"/>
       <c r="J27" s="145"/>
@@ -48848,7 +48847,7 @@
         <v>853</v>
       </c>
       <c r="D29" s="265" t="s">
-        <v>3566</v>
+        <v>3562</v>
       </c>
       <c r="E29" s="260" t="s">
         <v>1856</v>
@@ -49226,16 +49225,16 @@
         <v>575</v>
       </c>
       <c r="G2" t="s">
-        <v>3097</v>
+        <v>3093</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3228</v>
+        <v>3224</v>
       </c>
       <c r="I2" t="s">
-        <v>3335</v>
+        <v>3331</v>
       </c>
       <c r="J2" t="s">
-        <v>3469</v>
+        <v>3465</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1208</v>
@@ -49261,7 +49260,7 @@
         <v>301</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3209</v>
+        <v>3205</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>715</v>
@@ -49287,25 +49286,25 @@
         <v>316</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3558</v>
+        <v>3554</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>326</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3404</v>
+        <v>3400</v>
       </c>
       <c r="H4" t="s">
-        <v>3626</v>
+        <v>3622</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3468</v>
+        <v>3464</v>
       </c>
       <c r="J4" t="s">
-        <v>3461</v>
+        <v>3457</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>325</v>
@@ -49313,7 +49312,7 @@
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1">
       <c r="A5" s="4" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="B5" s="4">
         <v>64720128</v>
@@ -49331,13 +49330,13 @@
         <v>429</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3632</v>
+        <v>3628</v>
       </c>
       <c r="H5" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="I5" s="75" t="s">
-        <v>3226</v>
+        <v>3222</v>
       </c>
       <c r="J5" s="220" t="s">
         <v>2821</v>
@@ -49355,25 +49354,25 @@
         <v>330</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>3360</v>
+        <v>3356</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>3359</v>
+        <v>3355</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>167</v>
       </c>
       <c r="G6" t="s">
-        <v>3164</v>
+        <v>3160</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3498</v>
+        <v>3494</v>
       </c>
       <c r="I6" t="s">
-        <v>3256</v>
+        <v>3252</v>
       </c>
       <c r="J6" t="s">
-        <v>3361</v>
+        <v>3357</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>428</v>
@@ -49399,16 +49398,16 @@
         <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>3424</v>
+        <v>3420</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3332</v>
+        <v>3328</v>
       </c>
       <c r="I7" s="309" t="s">
         <v>2430</v>
       </c>
       <c r="J7" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>440</v>
@@ -49416,10 +49415,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3500</v>
+        <v>3496</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>664</v>
@@ -49437,13 +49436,13 @@
         <v>2877</v>
       </c>
       <c r="H8" t="s">
-        <v>3422</v>
+        <v>3418</v>
       </c>
       <c r="I8" t="s">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="J8" t="s">
-        <v>3093</v>
+        <v>3089</v>
       </c>
       <c r="L8" s="36"/>
     </row>
@@ -49467,16 +49466,16 @@
         <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>3197</v>
+        <v>3193</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3499</v>
+        <v>3495</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49490,7 +49489,7 @@
         <v>2295</v>
       </c>
       <c r="D10" t="s">
-        <v>3576</v>
+        <v>3572</v>
       </c>
       <c r="E10" t="s">
         <v>2265</v>
@@ -49499,16 +49498,16 @@
         <v>1886</v>
       </c>
       <c r="G10" t="s">
-        <v>3210</v>
+        <v>3206</v>
       </c>
       <c r="H10" t="s">
-        <v>3417</v>
+        <v>3413</v>
       </c>
       <c r="I10" t="s">
-        <v>3243</v>
+        <v>3239</v>
       </c>
       <c r="J10" t="s">
-        <v>3237</v>
+        <v>3233</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>2296</v>
@@ -49522,7 +49521,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B12" s="4">
         <v>64403333</v>
@@ -49541,7 +49540,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="445" t="s">
+      <c r="A13" t="s">
         <v>2716</v>
       </c>
       <c r="B13">
@@ -49585,7 +49584,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="49" t="s">
-        <v>3615</v>
+        <v>3611</v>
       </c>
       <c r="B15">
         <v>69184177</v>
@@ -49605,10 +49604,10 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B16" t="s">
-        <v>3100</v>
+        <v>3096</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>716</v>
@@ -49617,22 +49616,22 @@
         <v>1200</v>
       </c>
       <c r="E16" t="s">
-        <v>3099</v>
+        <v>3095</v>
       </c>
       <c r="F16" t="s">
         <v>152</v>
       </c>
       <c r="G16" t="s">
-        <v>3128</v>
+        <v>3124</v>
       </c>
       <c r="H16" t="s">
-        <v>3134</v>
+        <v>3130</v>
       </c>
       <c r="I16" t="s">
-        <v>3137</v>
+        <v>3133</v>
       </c>
       <c r="J16" t="s">
-        <v>3162</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -49640,7 +49639,7 @@
     </row>
     <row r="20" spans="2:12" s="393" customFormat="1" ht="23.5">
       <c r="B20" s="393" t="s">
-        <v>3098</v>
+        <v>3094</v>
       </c>
       <c r="C20" s="394"/>
       <c r="D20" s="395"/>
@@ -49868,7 +49867,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3594</v>
+        <v>3590</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49880,30 +49879,30 @@
     </row>
     <row r="7" spans="1:14">
       <c r="C7" t="s">
-        <v>3156</v>
+        <v>3152</v>
       </c>
       <c r="D7" t="s">
-        <v>3157</v>
+        <v>3153</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="30" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B8" s="30">
         <v>67129610</v>
       </c>
       <c r="C8" t="s">
-        <v>3158</v>
+        <v>3154</v>
       </c>
       <c r="D8" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49920,7 +49919,7 @@
         <v>1609</v>
       </c>
       <c r="E9" t="s">
-        <v>3379</v>
+        <v>3375</v>
       </c>
       <c r="F9" t="s">
         <v>1798</v>
@@ -49928,7 +49927,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B10">
         <v>63000545</v>
@@ -49940,7 +49939,7 @@
         <v>2313</v>
       </c>
       <c r="E10" t="s">
-        <v>3368</v>
+        <v>3364</v>
       </c>
       <c r="F10" t="s">
         <v>1746</v>
@@ -49960,7 +49959,7 @@
         <v>2140</v>
       </c>
       <c r="E11" t="s">
-        <v>3614</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49977,7 +49976,7 @@
         <v>2923</v>
       </c>
       <c r="E12" t="s">
-        <v>3299</v>
+        <v>3295</v>
       </c>
       <c r="F12" t="s">
         <v>1746</v>
@@ -49985,7 +49984,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3249</v>
+        <v>3245</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49997,10 +49996,10 @@
         <v>2528</v>
       </c>
       <c r="E13" t="s">
-        <v>3440</v>
+        <v>3436</v>
       </c>
       <c r="F13" t="s">
-        <v>3441</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -50014,7 +50013,7 @@
         <v>2010</v>
       </c>
       <c r="D14" t="s">
-        <v>3582</v>
+        <v>3578</v>
       </c>
       <c r="E14" t="s">
         <v>2878</v>
@@ -50025,7 +50024,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -50037,7 +50036,7 @@
         <v>1801</v>
       </c>
       <c r="E15" t="s">
-        <v>3251</v>
+        <v>3247</v>
       </c>
       <c r="F15" t="s">
         <v>2927</v>
@@ -50051,13 +50050,13 @@
         <v>65790414</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>3623</v>
+        <v>3619</v>
       </c>
       <c r="E16" t="s">
-        <v>3624</v>
+        <v>3620</v>
       </c>
       <c r="F16" t="s">
         <v>2927</v>
@@ -50065,19 +50064,19 @@
     </row>
     <row r="17" spans="1:7" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>3477</v>
+        <v>3473</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>3643</v>
+        <v>3639</v>
       </c>
       <c r="E17" t="s">
-        <v>3644</v>
+        <v>3640</v>
       </c>
       <c r="F17" t="s">
         <v>2927</v>
@@ -50094,13 +50093,13 @@
         <v>64276131</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="E18" t="s">
-        <v>3644</v>
+        <v>3640</v>
       </c>
       <c r="F18" t="s">
         <v>2927</v>
@@ -50128,7 +50127,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>3171</v>
+        <v>3167</v>
       </c>
       <c r="B21">
         <v>64245493</v>
@@ -50148,7 +50147,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="B22">
         <v>65324947</v>
@@ -50157,7 +50156,7 @@
         <v>1873</v>
       </c>
       <c r="D22" t="s">
-        <v>3085</v>
+        <v>3081</v>
       </c>
       <c r="E22" t="s">
         <v>2614</v>
@@ -50177,7 +50176,7 @@
         <v>2640</v>
       </c>
       <c r="D23" t="s">
-        <v>3107</v>
+        <v>3103</v>
       </c>
       <c r="E23" t="s">
         <v>2648</v>
@@ -50199,7 +50198,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -50211,13 +50210,13 @@
         <v>2895</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3595</v>
+        <v>3591</v>
       </c>
       <c r="F26" t="s">
-        <v>3596</v>
+        <v>3592</v>
       </c>
       <c r="G26" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -50233,7 +50232,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>3481</v>
+        <v>3477</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50245,10 +50244,10 @@
         <v>2926</v>
       </c>
       <c r="E30" t="s">
-        <v>3609</v>
+        <v>3605</v>
       </c>
       <c r="F30" t="s">
-        <v>3610</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="308" customFormat="1" ht="15.5">
@@ -50343,7 +50342,7 @@
         <v>364</v>
       </c>
       <c r="D46" t="s">
-        <v>3106</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="30" customFormat="1">
@@ -50354,10 +50353,10 @@
         <v>2680</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>3300</v>
+        <v>3296</v>
       </c>
       <c r="F47" s="411" t="s">
-        <v>3301</v>
+        <v>3297</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>412</v>
@@ -50387,13 +50386,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="97" t="s">
-        <v>3084</v>
+        <v>3080</v>
       </c>
       <c r="C51" t="s">
         <v>1413</v>
       </c>
       <c r="D51" t="s">
-        <v>3083</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -50453,12 +50452,12 @@
     </row>
     <row r="60" spans="1:5" s="406" customFormat="1" ht="18">
       <c r="C60" s="406" t="s">
-        <v>3257</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="30" t="s">
-        <v>3205</v>
+        <v>3201</v>
       </c>
       <c r="B61" s="30">
         <v>65036571</v>
@@ -50470,7 +50469,7 @@
         <v>2688</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3258</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="76" customFormat="1">
@@ -52312,12 +52311,12 @@
     </row>
     <row r="252" spans="1:6" s="436" customFormat="1" ht="21">
       <c r="C252" s="436" t="s">
-        <v>3556</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B253">
         <v>64476521</v>
@@ -52329,30 +52328,30 @@
         <v>2349</v>
       </c>
       <c r="E253" t="s">
-        <v>3554</v>
+        <v>3550</v>
       </c>
       <c r="F253" t="s">
-        <v>3555</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>3464</v>
+        <v>3460</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>3466</v>
+        <v>3462</v>
       </c>
       <c r="D254" t="s">
-        <v>3463</v>
+        <v>3459</v>
       </c>
       <c r="E254" t="s">
-        <v>3554</v>
+        <v>3550</v>
       </c>
       <c r="F254" t="s">
-        <v>3555</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52363,21 +52362,21 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="D255" s="252" t="s">
         <v>2857</v>
       </c>
       <c r="E255" t="s">
-        <v>3554</v>
+        <v>3550</v>
       </c>
       <c r="F255" t="s">
-        <v>3555</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>3075</v>
+        <v>3071</v>
       </c>
       <c r="B256">
         <v>61915064</v>
@@ -55763,7 +55762,7 @@
         <v>1381</v>
       </c>
       <c r="D456" t="s">
-        <v>3114</v>
+        <v>3110</v>
       </c>
       <c r="E456" s="76" t="s">
         <v>1458</v>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59972" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87BCA14B-8E5F-41F5-843D-8C6D40E08AE1}"/>
+  <xr:revisionPtr revIDLastSave="59977" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{764F2FCC-ADD7-4F8F-B5B9-7F0528CFE122}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1302,7 +1302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6262" uniqueCount="3664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6263" uniqueCount="3665">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -12294,6 +12294,9 @@
   </si>
   <si>
     <t xml:space="preserve">64625560-vivian 1 pantalla hasta el 27 de septiembre </t>
+  </si>
+  <si>
+    <t>62806425-cecilio</t>
   </si>
 </sst>
 </file>
@@ -19415,6 +19418,57 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2736850</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2930526</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>147638</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="449" name="Imagen 448">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6888D285-2EFE-41FB-A65A-1F733B3DB433}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="15217" t="25162" r="18477" b="23947"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25819100" y="8851900"/>
+          <a:ext cx="193676" cy="134938"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -30817,10 +30871,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="30" customFormat="1">
-      <c r="A40" s="145" t="s">
-        <v>2239</v>
-      </c>
-      <c r="B40" s="32"/>
+      <c r="A40" s="442" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>3664</v>
+      </c>
       <c r="C40" s="252" t="s">
         <v>1718</v>
       </c>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59984" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DA7F1F4-6B8F-4F21-AC07-66E02A0E4BD7}"/>
+  <xr:revisionPtr revIDLastSave="59991" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9ACB45E-6C6C-4DFB-BA9B-6BBAF351E889}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,6 +71,7 @@
     <author>tc={2DA6ACCC-7F6B-4F63-9F66-2022723D557F}</author>
     <author>tc={2C80CEB1-D520-47E4-8891-F2B7A2059B85}</author>
     <author>tc={A1BAE17A-7373-4E96-9A79-0A588580086C}</author>
+    <author>tc={6CB69787-04DC-427D-92C4-EA68685283A6}</author>
     <author>tc={D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}</author>
     <author>tc={A3554D91-2D1C-4186-8090-CCD5996EDC8F}</author>
   </authors>
@@ -171,7 +172,15 @@
     https://netflix-server-a9i0.onrender.com/cliente/69645877-yimara</t>
       </text>
     </comment>
-    <comment ref="J97" authorId="12" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
+    <comment ref="H91" authorId="12" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    https://netflix-server-a9i0.onrender.com/cliente/68131498-melanie</t>
+      </text>
+    </comment>
+    <comment ref="J97" authorId="13" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -179,7 +188,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/67208668-n005</t>
       </text>
     </comment>
-    <comment ref="K97" authorId="13" shapeId="0" xr:uid="{A3554D91-2D1C-4186-8090-CCD5996EDC8F}">
+    <comment ref="K97" authorId="14" shapeId="0" xr:uid="{A3554D91-2D1C-4186-8090-CCD5996EDC8F}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1302,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6263" uniqueCount="3665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6264" uniqueCount="3667">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -10475,9 +10484,6 @@
     <t>62884444 1 pantalla hasta el 29 de agosto</t>
   </si>
   <si>
-    <t>69105664 1 pantalla hasta el 30 de agosto</t>
-  </si>
-  <si>
     <t>69105664 1 pantalla hasta el 29 de agosto (Andres)</t>
   </si>
   <si>
@@ -12297,6 +12303,15 @@
   </si>
   <si>
     <t>68131498-melanie 1 pantalla hasta el 27 de septiembre</t>
+  </si>
+  <si>
+    <t>60128573-deibys</t>
+  </si>
+  <si>
+    <t>QUINCENAL 13 de septiembre</t>
+  </si>
+  <si>
+    <t>69105664 1 pantalla hasta el 30 de agosto (Andres)</t>
   </si>
 </sst>
 </file>
@@ -30079,6 +30094,15 @@
       </x:ext>
     </extLst>
   </threadedComment>
+  <threadedComment ref="H91" dT="2026-08-28T04:21:40.05" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{6CB69787-04DC-427D-92C4-EA68685283A6}">
+    <text>https://netflix-server-a9i0.onrender.com/cliente/68131498-melanie</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1578031737</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="49" url="https://netflix-server-a9i0.onrender.com/cliente/"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
   <threadedComment ref="J97" dT="2026-08-22T16:02:34.68" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
     <text>https://netflix-server-a9i0.onrender.com/cliente/67208668-n005</text>
     <extLst>
@@ -30180,7 +30204,7 @@
         <v>2079</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2152</v>
@@ -30200,12 +30224,12 @@
         <v>2201</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2852</v>
@@ -30231,7 +30255,7 @@
         <v>2077</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2152</v>
@@ -30279,10 +30303,10 @@
         <v>2080</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2157</v>
@@ -30336,10 +30360,10 @@
         <v>2170</v>
       </c>
       <c r="E10" s="436" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="F10" s="436" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="G10" s="436" t="s">
         <v>59</v>
@@ -30361,7 +30385,7 @@
         <v>2221</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2220</v>
@@ -30373,7 +30397,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="226" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="B14" s="226" t="s">
         <v>1731</v>
@@ -30410,10 +30434,10 @@
         <v>1578</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1579</v>
@@ -30422,21 +30446,21 @@
         <v>201</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="253" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B17" s="253" t="s">
         <v>1433</v>
@@ -30482,7 +30506,7 @@
         <v>2109</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>1399</v>
@@ -30493,7 +30517,7 @@
     </row>
     <row r="20" spans="1:11" s="298" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30502,7 +30526,7 @@
         <v>1738</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="E20" s="253" t="s">
         <v>1739</v>
@@ -30510,7 +30534,7 @@
     </row>
     <row r="21" spans="1:11" s="298" customFormat="1">
       <c r="A21" s="253" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B21" s="253">
         <v>60432412</v>
@@ -30539,7 +30563,7 @@
         <v>2198</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2151</v>
@@ -30564,7 +30588,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="148" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B24" s="148">
         <v>62279384</v>
@@ -30590,7 +30614,7 @@
         <v>1574</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1399</v>
@@ -30621,7 +30645,7 @@
     </row>
     <row r="27" spans="1:11" s="226" customFormat="1">
       <c r="A27" s="226" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B27" s="226">
         <v>64476521</v>
@@ -30684,24 +30708,24 @@
         <v>2476</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="C31" s="252" t="s">
         <v>1962</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2097</v>
@@ -30710,16 +30734,16 @@
         <v>201</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="J31" s="434" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30753,7 +30777,7 @@
     </row>
     <row r="34" spans="1:11" s="30" customFormat="1">
       <c r="A34" s="30" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="B34" s="30">
         <v>60389752</v>
@@ -30765,7 +30789,7 @@
         <v>2164</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2155</v>
@@ -30793,7 +30817,7 @@
     </row>
     <row r="36" spans="1:11" s="148" customFormat="1">
       <c r="A36" s="226" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B36" s="148">
         <v>61381388</v>
@@ -30816,10 +30840,10 @@
         <v>2072</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2145</v>
@@ -30828,21 +30852,21 @@
         <v>201</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="I37" s="30" t="s">
         <v>2998</v>
       </c>
       <c r="J37" s="442" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2850</v>
@@ -30874,7 +30898,7 @@
         <v>2630</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="C40" s="252" t="s">
         <v>1718</v>
@@ -30883,7 +30907,7 @@
         <v>3002</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2160</v>
@@ -30892,21 +30916,21 @@
         <v>201</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="J40" s="444" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="K40" s="30" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -30950,7 +30974,7 @@
         <v>2101</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2195</v>
@@ -30961,7 +30985,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -30978,7 +31002,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31004,10 +31028,10 @@
         <v>997</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2177</v>
@@ -31028,7 +31052,7 @@
         <v>2197</v>
       </c>
       <c r="D47" s="164" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="164" customFormat="1">
@@ -31059,10 +31083,10 @@
         <v>2063</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2163</v>
@@ -31071,16 +31095,16 @@
         <v>201</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="I49" s="217" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="K49" s="444" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31108,12 +31132,12 @@
         <v>2071</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
       <c r="A52" s="140" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B52" s="426" t="s">
         <v>1483</v>
@@ -31122,10 +31146,10 @@
         <v>1402</v>
       </c>
       <c r="D52" s="139" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2161</v>
@@ -31134,16 +31158,16 @@
         <v>201</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="K52" s="270" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31165,7 +31189,7 @@
     </row>
     <row r="54" spans="1:11" s="164" customFormat="1">
       <c r="A54" s="416" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B54" s="163" t="s">
         <v>1785</v>
@@ -31184,7 +31208,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31196,7 +31220,7 @@
         <v>2067</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2178</v>
@@ -31213,10 +31237,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="411" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="D56" s="377" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31225,13 +31249,13 @@
         <v>2630</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="C57" s="411" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="D57" s="377" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="E57" s="164"/>
     </row>
@@ -31258,16 +31282,16 @@
         <v>201</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="I58" s="442" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="395" customFormat="1">
@@ -31282,16 +31306,16 @@
         <v>2508</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2144</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2145</v>
@@ -31300,21 +31324,21 @@
         <v>201</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="I61" s="442" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31323,7 +31347,7 @@
         <v>1514</v>
       </c>
       <c r="D62" s="378" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1419</v>
@@ -31340,7 +31364,7 @@
         <v>2129</v>
       </c>
       <c r="D63" s="377" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="E63" s="164"/>
     </row>
@@ -31358,7 +31382,7 @@
         <v>3048</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2162</v>
@@ -31367,16 +31391,16 @@
         <v>201</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="K64" s="442" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31424,10 +31448,10 @@
         <v>1721</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2166</v>
@@ -31436,21 +31460,21 @@
         <v>201</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31459,7 +31483,7 @@
         <v>1938</v>
       </c>
       <c r="D68" s="378" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="E68" s="148"/>
     </row>
@@ -31474,7 +31498,7 @@
         <v>2165</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31500,13 +31524,13 @@
         <v>201</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="I70" s="30" t="s">
         <v>3008</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31520,12 +31544,12 @@
         <v>2025</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="269" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B72" s="269" t="s">
         <v>1495</v>
@@ -31540,7 +31564,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31549,10 +31573,10 @@
         <v>1379</v>
       </c>
       <c r="D73" s="252" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2096</v>
@@ -31563,7 +31587,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31602,10 +31626,10 @@
         <v>1937</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2177</v>
@@ -31614,16 +31638,16 @@
         <v>201</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="J76" s="30" t="s">
         <v>2944</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31639,16 +31663,16 @@
         <v>144</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2070</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2156</v>
@@ -31657,16 +31681,16 @@
         <v>201</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="I79" s="444" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31702,17 +31726,20 @@
       </c>
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
-      <c r="A82" s="145" t="s">
-        <v>2239</v>
+      <c r="A82" s="442" t="s">
+        <v>3665</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>3664</v>
       </c>
       <c r="C82" s="134" t="s">
         <v>1963</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1964</v>
@@ -31721,21 +31748,21 @@
         <v>201</v>
       </c>
       <c r="H82" s="30" t="s">
+        <v>3601</v>
+      </c>
+      <c r="I82" s="30" t="s">
+        <v>3666</v>
+      </c>
+      <c r="J82" s="30" t="s">
         <v>3602</v>
       </c>
-      <c r="I82" s="30" t="s">
-        <v>3057</v>
-      </c>
-      <c r="J82" s="30" t="s">
-        <v>3603</v>
-      </c>
       <c r="K82" s="30" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
       <c r="A83" s="148" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B83" s="148">
         <v>63145336</v>
@@ -31749,7 +31776,7 @@
     </row>
     <row r="84" spans="1:11" s="281" customFormat="1">
       <c r="A84" s="148" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B84" s="148">
         <v>68971798</v>
@@ -31784,16 +31811,16 @@
         <v>498</v>
       </c>
       <c r="H85" s="442" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="J85" s="217" t="s">
         <v>2649</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31834,7 +31861,7 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B88" s="30">
         <v>68496217</v>
@@ -31843,7 +31870,7 @@
         <v>701</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1104</v>
@@ -31855,16 +31882,16 @@
         <v>1576</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -31893,7 +31920,7 @@
         <v>67381873</v>
       </c>
       <c r="C90" s="409" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="D90" s="148" t="s">
         <v>3042</v>
@@ -31905,7 +31932,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="250" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1439</v>
@@ -31914,7 +31941,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1150</v>
@@ -31926,16 +31953,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="442" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="417" customFormat="1">
@@ -31983,7 +32010,7 @@
         <v>1400</v>
       </c>
       <c r="E94" s="254" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1401</v>
@@ -32012,7 +32039,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B96" s="148">
         <v>62928817</v>
@@ -32032,16 +32059,16 @@
         <v>1460</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>2060</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1964</v>
@@ -32050,16 +32077,16 @@
         <v>201</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="K97" s="139" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="395" customFormat="1">
@@ -32072,19 +32099,19 @@
     </row>
     <row r="100" spans="1:11" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
+        <v>3217</v>
+      </c>
+      <c r="B100" s="30" t="s">
         <v>3218</v>
       </c>
-      <c r="B100" s="30" t="s">
-        <v>3219</v>
-      </c>
       <c r="C100" s="252" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1964</v>
@@ -32093,7 +32120,7 @@
         <v>201</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="I100" s="30" t="s">
         <v>2999</v>
@@ -32102,7 +32129,7 @@
         <v>2983</v>
       </c>
       <c r="K100" s="32" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="395" customFormat="1">
@@ -32115,22 +32142,22 @@
     </row>
     <row r="103" spans="1:11" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B103" s="30">
         <v>62724019</v>
       </c>
       <c r="C103" s="252" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>3489</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>3491</v>
+      </c>
+      <c r="F103" s="30" t="s">
         <v>3490</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3492</v>
-      </c>
-      <c r="F103" s="30" t="s">
-        <v>3491</v>
       </c>
       <c r="G103" s="30" t="s">
         <v>59</v>
@@ -32149,7 +32176,7 @@
         <v>158</v>
       </c>
       <c r="B106" s="285" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="C106" s="134" t="s">
         <v>2057</v>
@@ -32169,16 +32196,16 @@
         <v>60756926</v>
       </c>
       <c r="C108" s="30" t="s">
+        <v>3174</v>
+      </c>
+      <c r="D108" s="30" t="s">
         <v>3175</v>
       </c>
-      <c r="D108" s="30" t="s">
+      <c r="E108" s="30" t="s">
         <v>3176</v>
       </c>
-      <c r="E108" s="30" t="s">
-        <v>3177</v>
-      </c>
       <c r="F108" s="30" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="G108" s="30" t="s">
         <v>59</v>
@@ -32189,16 +32216,16 @@
         <v>79</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="E124" s="32" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="30" customFormat="1"/>
@@ -32228,7 +32255,7 @@
         <v>2047</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="F127" t="s">
         <v>2045</v>
@@ -32248,7 +32275,7 @@
         <v>2015</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32265,7 +32292,7 @@
         <v>2958</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -32282,7 +32309,7 @@
         <v>2775</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32299,7 +32326,7 @@
         <v>2021</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32341,7 +32368,7 @@
         <v>2919</v>
       </c>
       <c r="E135" s="30" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="F135" t="s">
         <v>1348</v>
@@ -32378,7 +32405,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32407,7 +32434,7 @@
         <v>2032</v>
       </c>
       <c r="D140" s="380" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>2031</v>
@@ -32493,7 +32520,7 @@
         <v>2975</v>
       </c>
       <c r="E152" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="F152" t="s">
         <v>2033</v>
@@ -32513,7 +32540,7 @@
         <v>2463</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -32530,7 +32557,7 @@
         <v>3022</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -32561,7 +32588,7 @@
         <v>2325</v>
       </c>
       <c r="D156" s="380" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="E156" s="30" t="s">
         <v>3011</v>
@@ -32646,7 +32673,7 @@
         <v>2778</v>
       </c>
       <c r="D161" s="380" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="E161" s="30" t="s">
         <v>3011</v>
@@ -32663,7 +32690,7 @@
         <v>2665</v>
       </c>
       <c r="D162" s="380" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="E162" s="30" t="s">
         <v>3011</v>
@@ -32677,10 +32704,10 @@
         <v>12369714760</v>
       </c>
       <c r="C163" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="D163" s="380" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="E163" s="30" t="s">
         <v>3011</v>
@@ -32694,18 +32721,18 @@
         <v>2250</v>
       </c>
       <c r="C164" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="D164" s="380" t="s">
         <v>2632</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32717,7 +32744,7 @@
         <v>2367</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -32734,12 +32761,12 @@
         <v>2367</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B167">
         <v>66935922</v>
@@ -32751,7 +32778,7 @@
         <v>2779</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32768,7 +32795,7 @@
         <v>2922</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32785,7 +32812,7 @@
         <v>2982</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32802,7 +32829,7 @@
         <v>2629</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32819,7 +32846,7 @@
         <v>2415</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32836,7 +32863,7 @@
         <v>2633</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32853,7 +32880,7 @@
         <v>2430</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32870,7 +32897,7 @@
         <v>3012</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -32887,7 +32914,7 @@
         <v>2988</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -32904,7 +32931,7 @@
         <v>2988</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -32921,7 +32948,7 @@
         <v>2988</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -32938,7 +32965,7 @@
         <v>3023</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -32955,7 +32982,7 @@
         <v>2988</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -32997,7 +33024,7 @@
         <v>2959</v>
       </c>
       <c r="B182" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>3033</v>
@@ -33020,7 +33047,7 @@
         <v>3034</v>
       </c>
       <c r="D183" s="380" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="E183" s="30" t="s">
         <v>3035</v>
@@ -33028,16 +33055,16 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B184" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="C184" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="D184" s="380" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="E184" s="30" t="s">
         <v>3035</v>
@@ -33045,19 +33072,19 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B185">
         <v>68201775</v>
       </c>
       <c r="C185" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D185" s="380" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -33065,16 +33092,16 @@
         <v>2671</v>
       </c>
       <c r="B186" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="C186" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="D186" s="380" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33085,30 +33112,30 @@
         <v>62724019</v>
       </c>
       <c r="C187" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="D187" s="380" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E187" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E187" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="30" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B188" s="32" t="s">
         <v>2190</v>
       </c>
       <c r="C188" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="D188" s="380" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E188" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E188" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33119,13 +33146,13 @@
         <v>65080956</v>
       </c>
       <c r="C189" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="D189" s="380" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E189" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E189" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33136,47 +33163,47 @@
         <v>68726473</v>
       </c>
       <c r="C190" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="D190" s="380" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E190" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E190" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1917</v>
       </c>
       <c r="C191" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D191" s="380" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E191" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E191" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="B192">
         <v>64046277</v>
       </c>
       <c r="C192" s="1" t="s">
+        <v>3192</v>
+      </c>
+      <c r="D192" s="380" t="s">
         <v>3193</v>
       </c>
-      <c r="D192" s="380" t="s">
-        <v>3194</v>
-      </c>
       <c r="E192" s="30" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -33187,13 +33214,13 @@
         <v>66520892</v>
       </c>
       <c r="C193" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="D193" s="380" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E193" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E193" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33204,18 +33231,18 @@
         <v>62031509</v>
       </c>
       <c r="C194" t="s">
+        <v>3109</v>
+      </c>
+      <c r="D194" s="380" t="s">
         <v>3110</v>
       </c>
-      <c r="D194" s="380" t="s">
+      <c r="E194" s="30" t="s">
         <v>3111</v>
-      </c>
-      <c r="E194" s="30" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="399" customFormat="1" ht="23.5">
       <c r="C197" s="399" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="D197" s="399">
         <v>51957149094</v>
@@ -33229,13 +33256,13 @@
         <v>60240509</v>
       </c>
       <c r="C198" t="s">
+        <v>3159</v>
+      </c>
+      <c r="D198" s="380" t="s">
         <v>3160</v>
       </c>
-      <c r="D198" s="380" t="s">
-        <v>3161</v>
-      </c>
       <c r="E198" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -33246,13 +33273,13 @@
         <v>66003234</v>
       </c>
       <c r="C199" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="D199" s="380" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -33263,30 +33290,30 @@
         <v>65344753</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="D200" s="380" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="B201">
         <v>65633205</v>
       </c>
       <c r="C201" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D201" s="380" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -33297,13 +33324,13 @@
         <v>61248427</v>
       </c>
       <c r="C202" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D202" s="380" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33314,13 +33341,13 @@
         <v>69329372</v>
       </c>
       <c r="C203" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="D203" s="380" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -33331,13 +33358,13 @@
         <v>68168617</v>
       </c>
       <c r="C204" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="D204" s="380" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33348,13 +33375,13 @@
         <v>68934853</v>
       </c>
       <c r="C205" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D205" s="380" t="s">
+        <v>3282</v>
+      </c>
+      <c r="E205" s="30" t="s">
         <v>3146</v>
-      </c>
-      <c r="D205" s="380" t="s">
-        <v>3283</v>
-      </c>
-      <c r="E205" s="30" t="s">
-        <v>3147</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33362,16 +33389,16 @@
         <v>2957</v>
       </c>
       <c r="B206" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="C206" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="D206" s="380" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33382,30 +33409,30 @@
         <v>61430885</v>
       </c>
       <c r="C207" t="s">
+        <v>3300</v>
+      </c>
+      <c r="D207" s="380" t="s">
         <v>3301</v>
       </c>
-      <c r="D207" s="380" t="s">
-        <v>3302</v>
-      </c>
       <c r="E207" s="30" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="D208" t="s">
+        <v>3327</v>
+      </c>
+      <c r="E208" s="30" t="s">
         <v>3328</v>
-      </c>
-      <c r="E208" s="30" t="s">
-        <v>3329</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33416,13 +33443,13 @@
         <v>65583706</v>
       </c>
       <c r="C209" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="D209" s="380" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -33433,13 +33460,13 @@
         <v>65574051</v>
       </c>
       <c r="C210" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="D210" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -33447,27 +33474,27 @@
         <v>3037</v>
       </c>
       <c r="B211" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="C211" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="D211" s="380" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="C212" s="7" t="s">
+        <v>3630</v>
+      </c>
+      <c r="D212" t="s">
         <v>3631</v>
       </c>
-      <c r="D212" t="s">
-        <v>3632</v>
-      </c>
       <c r="E212" s="30" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33478,30 +33505,30 @@
         <v>62863306</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="D213" s="380" t="s">
+        <v>3438</v>
+      </c>
+      <c r="E213" s="30" t="s">
         <v>3439</v>
-      </c>
-      <c r="E213" s="30" t="s">
-        <v>3440</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="D214" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33512,30 +33539,30 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="D215" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B216">
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
       <c r="D216" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33546,13 +33573,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
+        <v>3461</v>
+      </c>
+      <c r="D217" s="380" t="s">
         <v>3462</v>
       </c>
-      <c r="D217" s="380" t="s">
-        <v>3463</v>
-      </c>
       <c r="E217" s="30" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -33638,7 +33665,7 @@
         <v>234</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -33662,7 +33689,7 @@
         <v>1379</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -33670,23 +33697,23 @@
         <v>1298</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="C258" s="1" t="s">
+        <v>3173</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>3174</v>
-      </c>
-      <c r="D258" s="1" t="s">
-        <v>3175</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -33694,10 +33721,10 @@
         <v>1719</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="E260" s="30" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36323,7 +36350,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36367,7 +36394,7 @@
     </row>
     <row r="6" spans="1:9" s="76" customFormat="1">
       <c r="A6" s="76" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36382,7 +36409,7 @@
         <v>684</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="G6" s="222" t="s">
         <v>1485</v>
@@ -36402,13 +36429,13 @@
         <v>1905</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1485</v>
@@ -36434,7 +36461,7 @@
         <v>365</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1485</v>
@@ -36460,7 +36487,7 @@
         <v>365</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1485</v>
@@ -36486,7 +36513,7 @@
         <v>365</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1485</v>
@@ -36512,7 +36539,7 @@
         <v>365</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1485</v>
@@ -36535,7 +36562,7 @@
         <v>2673</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1470</v>
@@ -36562,7 +36589,7 @@
         <v>1906</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1470</v>
@@ -36589,7 +36616,7 @@
         <v>3041</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1470</v>
@@ -36604,7 +36631,7 @@
     </row>
     <row r="16" spans="1:9" s="183" customFormat="1">
       <c r="A16" s="183" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36616,7 +36643,7 @@
         <v>2418</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1470</v>
@@ -36643,7 +36670,7 @@
         <v>1553</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1470</v>
@@ -36670,7 +36697,7 @@
         <v>2238</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1470</v>
@@ -36685,7 +36712,7 @@
     </row>
     <row r="20" spans="1:9" s="76" customFormat="1">
       <c r="A20" s="195" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36700,7 +36727,7 @@
         <v>365</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>427</v>
@@ -36714,7 +36741,7 @@
     </row>
     <row r="21" spans="1:9" s="183" customFormat="1">
       <c r="A21" s="183" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B21" s="183">
         <v>62723048</v>
@@ -36729,7 +36756,7 @@
         <v>365</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>427</v>
@@ -36758,7 +36785,7 @@
         <v>365</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>427</v>
@@ -36772,7 +36799,7 @@
     </row>
     <row r="23" spans="1:9" s="183" customFormat="1">
       <c r="A23" s="183" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36787,7 +36814,7 @@
         <v>365</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>427</v>
@@ -36816,7 +36843,7 @@
         <v>365</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>427</v>
@@ -36845,7 +36872,7 @@
         <v>365</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>427</v>
@@ -36874,7 +36901,7 @@
         <v>365</v>
       </c>
       <c r="F27" s="195" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>427</v>
@@ -36903,7 +36930,7 @@
         <v>365</v>
       </c>
       <c r="F28" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>427</v>
@@ -36932,7 +36959,7 @@
         <v>365</v>
       </c>
       <c r="F29" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>427</v>
@@ -36952,16 +36979,16 @@
         <v>63950696</v>
       </c>
       <c r="C30" s="193" t="s">
+        <v>3065</v>
+      </c>
+      <c r="D30" s="193" t="s">
         <v>3066</v>
-      </c>
-      <c r="D30" s="193" t="s">
-        <v>3067</v>
       </c>
       <c r="E30" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F30" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>427</v>
@@ -36990,7 +37017,7 @@
         <v>365</v>
       </c>
       <c r="F31" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>427</v>
@@ -37004,7 +37031,7 @@
     </row>
     <row r="32" spans="1:9" s="183" customFormat="1">
       <c r="A32" s="193" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B32" s="193">
         <v>64967407</v>
@@ -37019,7 +37046,7 @@
         <v>365</v>
       </c>
       <c r="F32" s="193" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>427</v>
@@ -37048,7 +37075,7 @@
         <v>365</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1486</v>
@@ -37075,7 +37102,7 @@
         <v>365</v>
       </c>
       <c r="F35" s="183" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>381</v>
@@ -37104,7 +37131,7 @@
         <v>365</v>
       </c>
       <c r="F36" s="183" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>381</v>
@@ -37133,7 +37160,7 @@
         <v>365</v>
       </c>
       <c r="F37" s="183" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>381</v>
@@ -37162,7 +37189,7 @@
         <v>365</v>
       </c>
       <c r="F38" s="183" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>381</v>
@@ -37191,7 +37218,7 @@
         <v>365</v>
       </c>
       <c r="F39" s="183" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>381</v>
@@ -37220,7 +37247,7 @@
         <v>2627</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>1485</v>
@@ -37247,7 +37274,7 @@
         <v>2627</v>
       </c>
       <c r="F42" s="193" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G42" s="183" t="s">
         <v>1485</v>
@@ -37259,7 +37286,7 @@
     </row>
     <row r="43" spans="1:9" s="183" customFormat="1">
       <c r="A43" s="193" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B43" s="193">
         <v>63226030</v>
@@ -37274,7 +37301,7 @@
         <v>2627</v>
       </c>
       <c r="F43" s="193" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G43" s="183" t="s">
         <v>1485</v>
@@ -37301,7 +37328,7 @@
         <v>2627</v>
       </c>
       <c r="F44" s="193" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G44" s="183" t="s">
         <v>1485</v>
@@ -37328,7 +37355,7 @@
         <v>2627</v>
       </c>
       <c r="F45" s="193" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G45" s="183" t="s">
         <v>1485</v>
@@ -37355,7 +37382,7 @@
         <v>2627</v>
       </c>
       <c r="F46" s="193" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G46" s="183" t="s">
         <v>1485</v>
@@ -37376,13 +37403,13 @@
         <v>1720</v>
       </c>
       <c r="D48" s="195" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="E48" s="76" t="s">
         <v>2627</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1485</v>
@@ -37409,7 +37436,7 @@
         <v>2627</v>
       </c>
       <c r="F49" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G49" s="183" t="s">
         <v>1485</v>
@@ -37436,7 +37463,7 @@
         <v>2627</v>
       </c>
       <c r="F50" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G50" s="183" t="s">
         <v>1485</v>
@@ -37463,7 +37490,7 @@
         <v>2627</v>
       </c>
       <c r="F51" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G51" s="183" t="s">
         <v>1485</v>
@@ -37481,7 +37508,7 @@
         <v>65174343</v>
       </c>
       <c r="C52" s="193" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="D52" s="193" t="s">
         <v>2068</v>
@@ -37490,7 +37517,7 @@
         <v>2627</v>
       </c>
       <c r="F52" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G52" s="183" t="s">
         <v>1485</v>
@@ -37509,7 +37536,7 @@
         <v>2627</v>
       </c>
       <c r="F53" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G53" s="183" t="s">
         <v>1485</v>
@@ -37535,7 +37562,7 @@
         <v>2627</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1485</v>
@@ -37562,7 +37589,7 @@
         <v>2627</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1485</v>
@@ -37574,7 +37601,7 @@
     </row>
     <row r="57" spans="1:9" s="183" customFormat="1">
       <c r="A57" s="183" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B57" s="183">
         <v>64403333</v>
@@ -37589,7 +37616,7 @@
         <v>2627</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1485</v>
@@ -37616,7 +37643,7 @@
         <v>2627</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1485</v>
@@ -37628,7 +37655,7 @@
     </row>
     <row r="59" spans="1:9" s="183" customFormat="1">
       <c r="A59" s="183" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B59" s="183">
         <v>65003516</v>
@@ -37643,7 +37670,7 @@
         <v>2627</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1485</v>
@@ -37670,7 +37697,7 @@
         <v>2627</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1485</v>
@@ -37682,7 +37709,7 @@
     </row>
     <row r="62" spans="1:9" s="76" customFormat="1">
       <c r="A62" s="76" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B62" s="76">
         <v>64147946</v>
@@ -37694,7 +37721,7 @@
         <v>2580</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F62" s="195" t="s">
         <v>2581</v>
@@ -37709,7 +37736,7 @@
     </row>
     <row r="63" spans="1:9" s="183" customFormat="1">
       <c r="A63" s="193" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B63" s="193">
         <v>62646186</v>
@@ -37721,7 +37748,7 @@
         <v>2585</v>
       </c>
       <c r="E63" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F63" s="193" t="s">
         <v>2581</v>
@@ -37748,7 +37775,7 @@
         <v>2387</v>
       </c>
       <c r="E64" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F64" s="193" t="s">
         <v>2581</v>
@@ -37775,7 +37802,7 @@
         <v>2960</v>
       </c>
       <c r="E65" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F65" s="183" t="s">
         <v>2581</v>
@@ -37801,7 +37828,7 @@
         <v>2128</v>
       </c>
       <c r="E66" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F66" s="183" t="s">
         <v>2581</v>
@@ -37827,7 +37854,7 @@
         <v>2575</v>
       </c>
       <c r="E67" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F67" s="183" t="s">
         <v>2581</v>
@@ -37853,7 +37880,7 @@
         <v>1781</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2579</v>
@@ -37865,7 +37892,7 @@
     </row>
     <row r="70" spans="1:9" s="183" customFormat="1">
       <c r="A70" s="193" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B70" s="193">
         <v>66082581</v>
@@ -37877,7 +37904,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2579</v>
@@ -37901,7 +37928,7 @@
         <v>1272</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2579</v>
@@ -37925,7 +37952,7 @@
         <v>2472</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F72" s="193" t="s">
         <v>2579</v>
@@ -37937,7 +37964,7 @@
     </row>
     <row r="73" spans="1:9" s="183" customFormat="1">
       <c r="A73" s="420" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B73" s="193">
         <v>60196388</v>
@@ -37949,7 +37976,7 @@
         <v>2384</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F73" s="193" t="s">
         <v>2579</v>
@@ -37961,7 +37988,7 @@
     </row>
     <row r="74" spans="1:9" s="183" customFormat="1">
       <c r="A74" s="183" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B74" s="183" t="s">
         <v>1481</v>
@@ -37973,7 +38000,7 @@
         <v>2639</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="F74" s="193" t="s">
         <v>2579</v>
@@ -37991,16 +38018,16 @@
         <v>63574980</v>
       </c>
       <c r="C76" s="76" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="D76" s="76" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="E76" s="76" t="s">
         <v>1381</v>
       </c>
       <c r="F76" s="195" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="G76" s="76" t="s">
         <v>1485</v>
@@ -38026,7 +38053,7 @@
         <v>1381</v>
       </c>
       <c r="F77" s="183" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="G77" s="183" t="s">
         <v>1485</v>
@@ -38037,13 +38064,13 @@
     </row>
     <row r="78" spans="1:9" s="183" customFormat="1">
       <c r="A78" s="183" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B78" s="183">
         <v>68483411</v>
       </c>
       <c r="C78" s="183" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>2236</v>
@@ -38052,7 +38079,7 @@
         <v>1381</v>
       </c>
       <c r="F78" s="183" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="G78" s="183" t="s">
         <v>1485</v>
@@ -38066,19 +38093,19 @@
         <v>2648</v>
       </c>
       <c r="B79" s="183" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="C79" s="194" t="s">
         <v>2865</v>
       </c>
       <c r="D79" s="183" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="E79" s="183" t="s">
         <v>1381</v>
       </c>
       <c r="F79" s="183" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="G79" s="183" t="s">
         <v>1485</v>
@@ -38104,7 +38131,7 @@
         <v>1381</v>
       </c>
       <c r="F80" s="183" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="G80" s="183" t="s">
         <v>1485</v>
@@ -38130,7 +38157,7 @@
         <v>1381</v>
       </c>
       <c r="F81" s="183" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="G81" s="183" t="s">
         <v>1485</v>
@@ -38156,7 +38183,7 @@
         <v>1710</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1485</v>
@@ -38180,7 +38207,7 @@
         <v>1710</v>
       </c>
       <c r="F84" s="193" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1485</v>
@@ -38204,7 +38231,7 @@
         <v>1710</v>
       </c>
       <c r="F85" s="193" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1485</v>
@@ -38228,7 +38255,7 @@
         <v>1710</v>
       </c>
       <c r="F86" s="193" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1485</v>
@@ -38252,7 +38279,7 @@
         <v>1710</v>
       </c>
       <c r="F87" s="193" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1485</v>
@@ -38276,7 +38303,7 @@
         <v>1710</v>
       </c>
       <c r="F88" s="193" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1485</v>
@@ -38285,7 +38312,7 @@
     </row>
     <row r="90" spans="1:9" s="76" customFormat="1">
       <c r="A90" s="195" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="B90" s="195">
         <v>64476521</v>
@@ -38300,7 +38327,7 @@
         <v>2627</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1485</v>
@@ -38327,7 +38354,7 @@
         <v>2627</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1485</v>
@@ -38354,7 +38381,7 @@
         <v>2627</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1485</v>
@@ -38381,7 +38408,7 @@
         <v>2627</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1485</v>
@@ -38408,7 +38435,7 @@
         <v>2627</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1485</v>
@@ -38435,7 +38462,7 @@
         <v>2627</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1485</v>
@@ -38447,7 +38474,7 @@
     </row>
     <row r="97" spans="1:9" s="76" customFormat="1">
       <c r="A97" s="195" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="B97" s="195">
         <v>66082581</v>
@@ -38459,7 +38486,7 @@
         <v>2397</v>
       </c>
       <c r="E97" s="76" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="F97" s="195" t="s">
         <v>427</v>
@@ -38474,7 +38501,7 @@
     </row>
     <row r="98" spans="1:9" s="183" customFormat="1">
       <c r="A98" s="193" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B98" s="193" t="s">
         <v>2907</v>
@@ -38486,7 +38513,7 @@
         <v>2402</v>
       </c>
       <c r="E98" s="183" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="F98" s="193" t="s">
         <v>427</v>
@@ -38513,7 +38540,7 @@
         <v>2404</v>
       </c>
       <c r="E99" s="183" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="F99" s="193" t="s">
         <v>427</v>
@@ -38534,13 +38561,13 @@
         <v>69017426</v>
       </c>
       <c r="C100" s="194" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="D100" s="193" t="s">
         <v>2592</v>
       </c>
       <c r="E100" s="183" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="F100" s="193" t="s">
         <v>427</v>
@@ -38567,7 +38594,7 @@
         <v>2408</v>
       </c>
       <c r="E101" s="183" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="F101" s="193" t="s">
         <v>427</v>
@@ -38588,13 +38615,13 @@
         <v>62723048</v>
       </c>
       <c r="C102" s="194" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="E102" s="183" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="F102" s="193" t="s">
         <v>427</v>
@@ -38615,16 +38642,16 @@
         <v>68310153</v>
       </c>
       <c r="C104" s="195" t="s">
+        <v>3457</v>
+      </c>
+      <c r="D104" s="195" t="s">
         <v>3458</v>
-      </c>
-      <c r="D104" s="195" t="s">
-        <v>3459</v>
       </c>
       <c r="E104" s="76" t="s">
         <v>365</v>
       </c>
       <c r="F104" s="195" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G104" s="76" t="s">
         <v>1381</v>
@@ -38638,7 +38665,7 @@
     </row>
     <row r="105" spans="1:9" s="183" customFormat="1">
       <c r="A105" s="193" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="B105" s="193">
         <v>63910392</v>
@@ -38651,7 +38678,7 @@
         <v>365</v>
       </c>
       <c r="F105" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G105" s="183" t="s">
         <v>1381</v>
@@ -38665,22 +38692,22 @@
     </row>
     <row r="106" spans="1:9" s="183" customFormat="1">
       <c r="A106" s="193" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B106" s="193">
         <v>68853797</v>
       </c>
       <c r="C106" s="193" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="E106" s="183" t="s">
         <v>2627</v>
       </c>
       <c r="F106" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G106" s="183" t="s">
         <v>1381</v>
@@ -38699,7 +38726,7 @@
         <v>365</v>
       </c>
       <c r="F107" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G107" s="183" t="s">
         <v>1381</v>
@@ -38720,7 +38747,7 @@
         <v>365</v>
       </c>
       <c r="F108" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G108" s="183" t="s">
         <v>1381</v>
@@ -38741,7 +38768,7 @@
         <v>365</v>
       </c>
       <c r="F109" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G109" s="183" t="s">
         <v>1381</v>
@@ -38755,7 +38782,7 @@
     </row>
     <row r="111" spans="1:9" s="76" customFormat="1">
       <c r="A111" s="76" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B111" s="76">
         <v>62751201</v>
@@ -38770,7 +38797,7 @@
         <v>1381</v>
       </c>
       <c r="F111" s="76" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G111" s="222" t="s">
         <v>1485</v>
@@ -38797,7 +38824,7 @@
         <v>1381</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1485</v>
@@ -38815,16 +38842,16 @@
         <v>64543204</v>
       </c>
       <c r="C113" s="194" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="D113" s="183" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="E113" s="183" t="s">
         <v>1381</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1485</v>
@@ -38851,7 +38878,7 @@
         <v>1381</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1485</v>
@@ -38878,7 +38905,7 @@
         <v>1381</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1485</v>
@@ -38905,7 +38932,7 @@
         <v>1381</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1485</v>
@@ -38929,7 +38956,7 @@
         <v>1734</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>1567</v>
@@ -38955,7 +38982,7 @@
         <v>895</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F119" s="183" t="s">
         <v>1567</v>
@@ -38969,7 +38996,7 @@
     </row>
     <row r="120" spans="1:9" s="183" customFormat="1">
       <c r="A120" s="183" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="B120" s="183">
         <v>69563253</v>
@@ -38981,7 +39008,7 @@
         <v>1021</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F120" s="183" t="s">
         <v>1567</v>
@@ -39001,13 +39028,13 @@
         <v>63062167</v>
       </c>
       <c r="C121" s="194" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D121" s="183" t="s">
         <v>1284</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F121" s="183" t="s">
         <v>1567</v>
@@ -39033,7 +39060,7 @@
         <v>950</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F122" s="183" t="s">
         <v>1567</v>
@@ -39059,7 +39086,7 @@
         <v>1991</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F123" s="183" t="s">
         <v>1567</v>
@@ -39085,7 +39112,7 @@
         <v>2422</v>
       </c>
       <c r="E125" s="76" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>427</v>
@@ -39111,7 +39138,7 @@
         <v>2424</v>
       </c>
       <c r="E126" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F126" s="193" t="s">
         <v>427</v>
@@ -39138,7 +39165,7 @@
         <v>2426</v>
       </c>
       <c r="E127" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F127" s="193" t="s">
         <v>427</v>
@@ -39153,7 +39180,7 @@
     </row>
     <row r="128" spans="1:9" s="183" customFormat="1">
       <c r="A128" s="49" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="B128" s="183">
         <v>67836337</v>
@@ -39162,7 +39189,7 @@
         <v>2498</v>
       </c>
       <c r="E128" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F128" s="193" t="s">
         <v>427</v>
@@ -39189,7 +39216,7 @@
         <v>380</v>
       </c>
       <c r="E129" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F129" s="193" t="s">
         <v>427</v>
@@ -39216,7 +39243,7 @@
         <v>1706</v>
       </c>
       <c r="E130" s="183" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="F130" s="193" t="s">
         <v>427</v>
@@ -39344,7 +39371,7 @@
     </row>
     <row r="136" spans="1:9" s="183" customFormat="1">
       <c r="A136" s="183" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="B136" s="183">
         <v>66230961</v>
@@ -39373,7 +39400,7 @@
     </row>
     <row r="137" spans="1:9" s="183" customFormat="1">
       <c r="A137" s="183" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B137" s="183">
         <v>69888391</v>
@@ -39510,7 +39537,7 @@
     </row>
     <row r="143" spans="1:9" s="183" customFormat="1">
       <c r="A143" s="183" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B143" s="183">
         <v>62385671</v>
@@ -39780,7 +39807,7 @@
     </row>
     <row r="155" spans="1:9" s="183" customFormat="1">
       <c r="A155" s="183" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B155" s="183">
         <v>62560788</v>
@@ -39834,16 +39861,16 @@
     </row>
     <row r="157" spans="1:9" s="183" customFormat="1">
       <c r="A157" s="193" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="B157" s="193">
         <v>60125401</v>
       </c>
       <c r="C157" s="194" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
       <c r="D157" s="193" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="E157" s="183" t="s">
         <v>2627</v>
@@ -39861,7 +39888,7 @@
     </row>
     <row r="158" spans="1:9" s="183" customFormat="1">
       <c r="A158" s="193" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B158" s="193">
         <v>64720128</v>
@@ -39903,7 +39930,7 @@
         <v>365</v>
       </c>
       <c r="F160" s="195" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G160" s="76" t="s">
         <v>2491</v>
@@ -39932,7 +39959,7 @@
         <v>365</v>
       </c>
       <c r="F161" s="193" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G161" s="183" t="s">
         <v>2491</v>
@@ -39961,7 +39988,7 @@
         <v>365</v>
       </c>
       <c r="F162" s="193" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G162" s="183" t="s">
         <v>2491</v>
@@ -39990,7 +40017,7 @@
         <v>365</v>
       </c>
       <c r="F163" s="193" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G163" s="183" t="s">
         <v>2491</v>
@@ -40019,7 +40046,7 @@
         <v>365</v>
       </c>
       <c r="F164" s="193" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G164" s="183" t="s">
         <v>2491</v>
@@ -40039,16 +40066,16 @@
         <v>64403333</v>
       </c>
       <c r="C165" s="194" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="D165" s="423" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="E165" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F165" s="193" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G165" s="183" t="s">
         <v>2491</v>
@@ -40135,7 +40162,7 @@
         <v>444</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40146,7 +40173,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40154,7 +40181,7 @@
         <v>1364</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40162,7 +40189,7 @@
         <v>1717</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="F199" s="405"/>
     </row>
@@ -40171,7 +40198,7 @@
         <v>1343</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40179,7 +40206,7 @@
         <v>411</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40187,7 +40214,7 @@
         <v>716</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40195,7 +40222,7 @@
         <v>284</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40203,7 +40230,7 @@
         <v>2495</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40213,7 +40240,7 @@
         <v>470</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40221,7 +40248,7 @@
         <v>222</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41559,10 +41586,10 @@
         <v>712</v>
       </c>
       <c r="H3" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41592,16 +41619,16 @@
         <v>2855</v>
       </c>
       <c r="I4" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B5" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>485</v>
@@ -41610,7 +41637,7 @@
         <v>1573</v>
       </c>
       <c r="E5" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="F5" t="s">
         <v>2253</v>
@@ -41622,7 +41649,7 @@
         <v>2980</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="J5" t="s">
         <v>1436</v>
@@ -41650,7 +41677,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B7" s="180">
         <v>64403333</v>
@@ -41676,13 +41703,13 @@
         <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2139</v>
       </c>
       <c r="D8" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="E8" t="s">
         <v>2436</v>
@@ -41694,10 +41721,10 @@
         <v>253</v>
       </c>
       <c r="H8" s="445" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="I8" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41715,7 +41742,7 @@
         <v>2927</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2140</v>
@@ -41727,7 +41754,7 @@
         <v>2985</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41761,7 +41788,7 @@
         <v>441</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="I12" s="49" t="s">
         <v>2766</v>
@@ -41806,34 +41833,34 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="10" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B16" s="10">
         <v>67663098</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="D16" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="E16" t="s">
+        <v>3263</v>
+      </c>
+      <c r="F16" t="s">
         <v>3264</v>
-      </c>
-      <c r="F16" t="s">
-        <v>3265</v>
       </c>
       <c r="G16" t="s">
         <v>122</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="19" customFormat="1"/>
@@ -41962,7 +41989,7 @@
         <v>3000</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -41988,7 +42015,7 @@
         <v>522</v>
       </c>
       <c r="H7" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="I7" s="276" t="s">
         <v>2770</v>
@@ -42070,7 +42097,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -42079,7 +42106,7 @@
         <v>2296</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>976</v>
@@ -42091,10 +42118,10 @@
         <v>522</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42167,7 +42194,7 @@
         <v>2689</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42193,7 +42220,7 @@
         <v>522</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2750</v>
@@ -42230,7 +42257,7 @@
         <v>522</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="I22" s="276" t="s">
         <v>2974</v>
@@ -42259,10 +42286,10 @@
         <v>522</v>
       </c>
       <c r="H23" s="10" t="s">
+        <v>3289</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>3290</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>3291</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42276,7 +42303,7 @@
         <v>2567</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>976</v>
@@ -42288,10 +42315,10 @@
         <v>522</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42301,7 +42328,7 @@
         <v>2582</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>976</v>
@@ -42489,13 +42516,13 @@
         <v>2600</v>
       </c>
       <c r="B4" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1929</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="E4" t="s">
         <v>1930</v>
@@ -42507,10 +42534,10 @@
         <v>980</v>
       </c>
       <c r="H4" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="I4" s="446" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="J4" s="97"/>
     </row>
@@ -42560,10 +42587,10 @@
         <v>980</v>
       </c>
       <c r="H6" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="I6" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2322</v>
@@ -42595,10 +42622,10 @@
         <v>3052</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42606,73 +42633,73 @@
         <v>2576</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>3304</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>3305</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3304</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>3306</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>3307</v>
       </c>
       <c r="G8" t="s">
         <v>980</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="I8" s="279"/>
       <c r="J8" s="10" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
+        <v>3551</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>3552</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>3553</v>
-      </c>
       <c r="C9" s="22" t="s">
+        <v>3549</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>3550</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>3304</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>3551</v>
-      </c>
       <c r="F9" s="10" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="G9" t="s">
         <v>980</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>3553</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>3554</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>3555</v>
-      </c>
       <c r="J9" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="279"/>
       <c r="C10" s="3" t="s">
+        <v>3632</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3633</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>3634</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>3635</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2396</v>
@@ -42843,7 +42870,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -42852,7 +42879,7 @@
         <v>1849</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2802</v>
@@ -42893,7 +42920,7 @@
         <v>65124748</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2829</v>
@@ -42914,7 +42941,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2829</v>
@@ -43090,7 +43117,7 @@
     <row r="1" spans="1:9" s="422" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="421"/>
       <c r="B1" s="421" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="C1" s="421"/>
     </row>
@@ -43099,25 +43126,25 @@
         <v>148</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>3620</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>3621</v>
       </c>
-      <c r="E4" t="s">
-        <v>3395</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>3622</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
     </row>
   </sheetData>
@@ -43463,7 +43490,7 @@
         <v>2727</v>
       </c>
       <c r="C5" s="328" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="328" customFormat="1">
@@ -43471,10 +43498,10 @@
         <v>2706</v>
       </c>
       <c r="B6" s="328" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="C6" s="328" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="328" customFormat="1">
@@ -43549,10 +43576,10 @@
         <v>2736</v>
       </c>
       <c r="H14" s="334" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I14" s="334" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="L14" s="334"/>
       <c r="M14" s="334"/>
@@ -43580,10 +43607,10 @@
         <v>2737</v>
       </c>
       <c r="H15" s="335" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I15" s="335" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="L15" s="335"/>
       <c r="M15" s="335"/>
@@ -43611,7 +43638,7 @@
         <v>2738</v>
       </c>
       <c r="H16" s="335" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I16" s="335" t="s">
         <v>1381</v>
@@ -43624,7 +43651,7 @@
         <v>2711</v>
       </c>
       <c r="B17" s="407" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C17" s="407"/>
       <c r="D17" s="407"/>
@@ -43641,7 +43668,7 @@
         <v>2706</v>
       </c>
       <c r="B18" s="407" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="C18" s="407"/>
       <c r="D18" s="407"/>
@@ -43658,7 +43685,7 @@
         <v>2707</v>
       </c>
       <c r="B19" s="407" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="C19" s="407"/>
       <c r="D19" s="407"/>
@@ -44616,10 +44643,10 @@
         <v>160</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>828</v>
@@ -44627,7 +44654,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44648,10 +44675,10 @@
         <v>247</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44677,10 +44704,10 @@
         <v>247</v>
       </c>
       <c r="H11" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3364</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44706,10 +44733,10 @@
         <v>247</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44735,10 +44762,10 @@
         <v>247</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44764,25 +44791,25 @@
         <v>247</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="105" t="s">
+        <v>3221</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>3222</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>3223</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>343</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>1584</v>
@@ -44794,10 +44821,10 @@
         <v>901</v>
       </c>
       <c r="H15" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="I15" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>503</v>
@@ -44814,7 +44841,7 @@
         <v>2784</v>
       </c>
       <c r="D16" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="E16" t="s">
         <v>2786</v>
@@ -44826,10 +44853,10 @@
         <v>160</v>
       </c>
       <c r="H16" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="I16" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>817</v>
@@ -44872,19 +44899,19 @@
         <v>2309</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>3352</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>3353</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>3354</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>247</v>
       </c>
       <c r="H18" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="I18" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44895,13 +44922,13 @@
         <v>64403333</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="D19" t="s">
         <v>2785</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>2616</v>
@@ -44914,7 +44941,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45007,7 +45034,7 @@
         <v>160</v>
       </c>
       <c r="H23" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="I23" s="308" t="s">
         <v>2744</v>
@@ -45025,10 +45052,10 @@
         <v>1689</v>
       </c>
       <c r="D24" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2616</v>
@@ -45051,7 +45078,7 @@
         <v>2102</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2622</v>
@@ -45089,7 +45116,7 @@
         <v>247</v>
       </c>
       <c r="H26" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="I26" t="s">
         <v>3009</v>
@@ -45100,7 +45127,7 @@
         <v>2638</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>370</v>
@@ -45118,10 +45145,10 @@
         <v>160</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="I27" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>825</v>
@@ -45129,7 +45156,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2609</v>
@@ -45141,7 +45168,7 @@
         <v>2103</v>
       </c>
       <c r="E28" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2622</v>
@@ -45153,7 +45180,7 @@
         <v>2853</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45168,10 +45195,10 @@
         <v>353</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="E29" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2622</v>
@@ -45180,26 +45207,26 @@
         <v>253</v>
       </c>
       <c r="H29" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="I29" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>407</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="E30" t="s">
         <v>2499</v>
@@ -45211,7 +45238,7 @@
         <v>160</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="I30" t="s">
         <v>2999</v>
@@ -45219,7 +45246,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45240,10 +45267,10 @@
         <v>160</v>
       </c>
       <c r="H31" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45269,7 +45296,7 @@
         <v>160</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2977</v>
@@ -45298,10 +45325,10 @@
         <v>160</v>
       </c>
       <c r="H33" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="I33" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45330,7 +45357,7 @@
         <v>2788</v>
       </c>
       <c r="I34" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45339,13 +45366,13 @@
         <v>148</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2781</v>
       </c>
       <c r="D35" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="E35" t="s">
         <v>2786</v>
@@ -45357,10 +45384,10 @@
         <v>2789</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="I35" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -45389,7 +45416,7 @@
         <v>2972</v>
       </c>
       <c r="I36" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45397,13 +45424,13 @@
         <v>2638</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2796</v>
       </c>
       <c r="D37" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="E37" t="s">
         <v>2798</v>
@@ -45415,10 +45442,10 @@
         <v>160</v>
       </c>
       <c r="H37" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="I37" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45426,7 +45453,7 @@
         <v>158</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2797</v>
@@ -45480,10 +45507,10 @@
         <v>2684</v>
       </c>
       <c r="J45" s="49" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="K45" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45889,13 +45916,13 @@
         <v>158</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="C2" s="277" t="s">
         <v>257</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1334</v>
@@ -45907,16 +45934,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="301" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45946,13 +45973,13 @@
         <v>3043</v>
       </c>
       <c r="I4" s="217" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="M4" s="39"/>
     </row>
@@ -45979,10 +46006,10 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="J5" s="145"/>
       <c r="K5" s="217" t="s">
@@ -46013,13 +46040,13 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="K6" s="30" t="s">
         <v>3056</v>
@@ -46049,16 +46076,16 @@
         <v>731</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>2871</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46085,13 +46112,13 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="K8" s="278" t="s">
         <v>2943</v>
@@ -46121,16 +46148,16 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="J9" s="217" t="s">
         <v>2909</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -46157,22 +46184,22 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="I10" s="49" t="s">
         <v>2946</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="M10" s="34"/>
     </row>
     <row r="11" spans="1:13" s="30" customFormat="1">
       <c r="A11" s="107" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B11" s="107">
         <v>62657225</v>
@@ -46193,16 +46220,16 @@
         <v>610</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -46217,7 +46244,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>922</v>
@@ -46229,16 +46256,16 @@
         <v>248</v>
       </c>
       <c r="H12" s="106" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="M12" s="151"/>
     </row>
@@ -46247,13 +46274,13 @@
         <v>3036</v>
       </c>
       <c r="B13" s="107" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>933</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>3013</v>
@@ -46265,13 +46292,13 @@
         <v>65</v>
       </c>
       <c r="H13" s="442" t="s">
+        <v>3648</v>
+      </c>
+      <c r="I13" s="145" t="s">
         <v>3649</v>
       </c>
-      <c r="I13" s="145" t="s">
-        <v>3650</v>
-      </c>
       <c r="J13" s="107" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="K13" t="s">
         <v>3010</v>
@@ -46301,7 +46328,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="I14" s="424" t="s">
         <v>2365</v>
@@ -46334,16 +46361,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="I15" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="J15" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46395,16 +46422,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46431,16 +46458,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="I18" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="J18" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="K18" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46467,16 +46494,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="I19" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="J19" s="220" t="s">
         <v>3016</v>
       </c>
       <c r="K19" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46491,7 +46518,7 @@
         <v>2643</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2548</v>
@@ -46503,16 +46530,16 @@
         <v>65</v>
       </c>
       <c r="H20" s="318" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="I20" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="J20" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="K20" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="M20" s="36"/>
     </row>
@@ -46672,7 +46699,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46720,7 +46747,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46782,10 +46809,10 @@
         <v>2227</v>
       </c>
       <c r="E39" s="140" t="s">
+        <v>3332</v>
+      </c>
+      <c r="F39" s="140" t="s">
         <v>3333</v>
-      </c>
-      <c r="F39" s="140" t="s">
-        <v>3334</v>
       </c>
       <c r="G39" s="106" t="s">
         <v>731</v>
@@ -46841,7 +46868,7 @@
         <v>2945</v>
       </c>
       <c r="B45" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="C45" t="s">
         <v>2680</v>
@@ -46850,7 +46877,7 @@
         <v>2681</v>
       </c>
       <c r="E45" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2682</v>
@@ -46862,10 +46889,10 @@
         <v>3004</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="J45" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47621,7 +47648,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="45" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -47757,7 +47784,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -47766,7 +47793,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48018,7 +48045,7 @@
         <v>144</v>
       </c>
       <c r="B6" s="248" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="C6" s="247" t="s">
         <v>1326</v>
@@ -48036,13 +48063,13 @@
         <v>360</v>
       </c>
       <c r="H6" s="248" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="I6" s="245" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="J6" s="296" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="K6" s="248" t="s">
         <v>480</v>
@@ -48070,19 +48097,19 @@
         <v>1055</v>
       </c>
       <c r="F8" s="266" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="G8" s="266" t="s">
         <v>696</v>
       </c>
       <c r="H8" s="296" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="J8" s="266" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="K8" s="266" t="s">
         <v>717</v>
@@ -48111,10 +48138,10 @@
         <v>253</v>
       </c>
       <c r="H9" s="106" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="I9" s="106" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="J9" s="106" t="s">
         <v>2308</v>
@@ -48137,7 +48164,7 @@
         <v>1454</v>
       </c>
       <c r="F10" s="264" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="G10" s="264" t="s">
         <v>962</v>
@@ -48169,13 +48196,13 @@
         <v>696</v>
       </c>
       <c r="H11" s="265" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="I11" s="296" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="J11" s="265" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="K11" s="246" t="s">
         <v>1239</v>
@@ -48204,13 +48231,13 @@
         <v>696</v>
       </c>
       <c r="H12" s="215" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="I12" s="215" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="J12" s="270" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="K12" s="183" t="s">
         <v>1240</v>
@@ -48247,7 +48274,7 @@
         <v>2959</v>
       </c>
       <c r="B14" s="224" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="C14" s="438" t="s">
         <v>338</v>
@@ -48256,22 +48283,22 @@
         <v>2525</v>
       </c>
       <c r="E14" s="224" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="F14" s="224" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="G14" s="224" t="s">
         <v>696</v>
       </c>
       <c r="H14" s="224" t="s">
+        <v>3583</v>
+      </c>
+      <c r="I14" s="224" t="s">
         <v>3584</v>
       </c>
-      <c r="I14" s="224" t="s">
-        <v>3585</v>
-      </c>
       <c r="J14" s="224" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="K14" s="224" t="s">
         <v>1357</v>
@@ -48291,7 +48318,7 @@
         <v>2041</v>
       </c>
       <c r="E15" s="216" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="F15" s="216" t="s">
         <v>1478</v>
@@ -48300,13 +48327,13 @@
         <v>696</v>
       </c>
       <c r="H15" s="273" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="I15" s="215" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="J15" s="263" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1241</v>
@@ -48317,13 +48344,13 @@
         <v>1460</v>
       </c>
       <c r="B16" s="265" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="C16" s="271" t="s">
         <v>1343</v>
       </c>
       <c r="D16" s="260" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="E16" s="260" t="s">
         <v>3027</v>
@@ -48335,13 +48362,13 @@
         <v>696</v>
       </c>
       <c r="H16" s="265" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="I16" s="272" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="J16" s="265" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="K16" s="260" t="s">
         <v>1484</v>
@@ -48414,7 +48441,7 @@
         <v>696</v>
       </c>
       <c r="J19" s="265" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="K19" s="265" t="s">
         <v>1701</v>
@@ -48443,7 +48470,7 @@
         <v>696</v>
       </c>
       <c r="I20" s="260" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="265" t="s">
@@ -48473,13 +48500,13 @@
         <v>696</v>
       </c>
       <c r="H21" s="260" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="I21" s="265" t="s">
         <v>3015</v>
       </c>
       <c r="J21" s="260" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="K21" s="265" t="s">
         <v>1828</v>
@@ -48487,7 +48514,7 @@
     </row>
     <row r="22" spans="1:11" s="260" customFormat="1">
       <c r="A22" s="246" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B22" s="260" t="s">
         <v>2512</v>
@@ -48514,7 +48541,7 @@
         <v>2978</v>
       </c>
       <c r="J22" s="260" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="K22" s="260" t="s">
         <v>1873</v>
@@ -48546,10 +48573,10 @@
         <v>3039</v>
       </c>
       <c r="I24" s="265" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="J24" s="265" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="K24" s="260" t="s">
         <v>1875</v>
@@ -48590,7 +48617,7 @@
         <v>642</v>
       </c>
       <c r="D27" s="256" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
       <c r="E27" s="272" t="s">
         <v>2529</v>
@@ -48602,7 +48629,7 @@
         <v>714</v>
       </c>
       <c r="H27" s="260" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="I27" s="145"/>
       <c r="J27" s="145"/>
@@ -48612,7 +48639,7 @@
         <v>853</v>
       </c>
       <c r="D29" s="265" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="E29" s="260" t="s">
         <v>1851</v>
@@ -48990,16 +49017,16 @@
         <v>575</v>
       </c>
       <c r="G2" s="49" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="I2" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="J2" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1207</v>
@@ -49025,7 +49052,7 @@
         <v>301</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>715</v>
@@ -49051,25 +49078,25 @@
         <v>316</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>326</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="H4" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="J4" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>325</v>
@@ -49077,7 +49104,7 @@
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1">
       <c r="A5" s="4" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="B5" s="4">
         <v>64720128</v>
@@ -49095,13 +49122,13 @@
         <v>429</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="H5" t="s">
         <v>2997</v>
       </c>
       <c r="I5" s="75" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="J5" s="220" t="s">
         <v>2805</v>
@@ -49119,25 +49146,25 @@
         <v>330</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>167</v>
       </c>
       <c r="G6" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="I6" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="J6" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>428</v>
@@ -49163,13 +49190,13 @@
         <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="J7" s="49" t="s">
         <v>2979</v>
@@ -49180,10 +49207,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>664</v>
@@ -49201,10 +49228,10 @@
         <v>2857</v>
       </c>
       <c r="H8" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="I8" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="J8" t="s">
         <v>3055</v>
@@ -49231,16 +49258,16 @@
         <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="H9" s="443" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="J9" s="443" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49254,7 +49281,7 @@
         <v>2288</v>
       </c>
       <c r="D10" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="E10" t="s">
         <v>2258</v>
@@ -49263,16 +49290,16 @@
         <v>1881</v>
       </c>
       <c r="G10" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="H10" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="I10" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="J10" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>2289</v>
@@ -49349,7 +49376,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="49" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="B15">
         <v>69184177</v>
@@ -49372,7 +49399,7 @@
         <v>3020</v>
       </c>
       <c r="B16" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>716</v>
@@ -49381,22 +49408,22 @@
         <v>1199</v>
       </c>
       <c r="E16" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="F16" t="s">
         <v>152</v>
       </c>
       <c r="G16" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="H16" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="I16" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="J16" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -49404,7 +49431,7 @@
     </row>
     <row r="20" spans="2:12" s="391" customFormat="1" ht="23.5">
       <c r="B20" s="391" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C20" s="392"/>
       <c r="D20" s="393"/>
@@ -49632,7 +49659,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49653,7 +49680,7 @@
         <v>67129610</v>
       </c>
       <c r="C8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="D8" t="s">
         <v>2967</v>
@@ -49676,7 +49703,7 @@
         <v>1606</v>
       </c>
       <c r="E9" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="F9" t="s">
         <v>1793</v>
@@ -49696,7 +49723,7 @@
         <v>2306</v>
       </c>
       <c r="E10" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="F10" t="s">
         <v>1742</v>
@@ -49716,7 +49743,7 @@
         <v>2133</v>
       </c>
       <c r="E11" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49733,7 +49760,7 @@
         <v>2900</v>
       </c>
       <c r="E12" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="F12" t="s">
         <v>1742</v>
@@ -49741,7 +49768,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49753,10 +49780,10 @@
         <v>2518</v>
       </c>
       <c r="E13" t="s">
+        <v>3395</v>
+      </c>
+      <c r="F13" t="s">
         <v>3396</v>
-      </c>
-      <c r="F13" t="s">
-        <v>3397</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -49770,7 +49797,7 @@
         <v>2004</v>
       </c>
       <c r="D14" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="E14" t="s">
         <v>2858</v>
@@ -49793,7 +49820,7 @@
         <v>1796</v>
       </c>
       <c r="E15" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="F15" t="s">
         <v>2904</v>
@@ -49810,10 +49837,10 @@
         <v>2966</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>3570</v>
+      </c>
+      <c r="E16" t="s">
         <v>3571</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3572</v>
       </c>
       <c r="F16" t="s">
         <v>2904</v>
@@ -49821,19 +49848,19 @@
     </row>
     <row r="17" spans="1:7" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>3589</v>
+      </c>
+      <c r="E17" t="s">
         <v>3590</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3591</v>
       </c>
       <c r="F17" t="s">
         <v>2904</v>
@@ -49856,7 +49883,7 @@
         <v>2970</v>
       </c>
       <c r="E18" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="F18" t="s">
         <v>2904</v>
@@ -49864,7 +49891,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="B21">
         <v>64245493</v>
@@ -49913,7 +49940,7 @@
         <v>2628</v>
       </c>
       <c r="D23" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="E23" t="s">
         <v>2636</v>
@@ -49935,7 +49962,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -49947,13 +49974,13 @@
         <v>2875</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>3542</v>
+      </c>
+      <c r="F26" t="s">
         <v>3543</v>
       </c>
-      <c r="F26" t="s">
-        <v>3544</v>
-      </c>
       <c r="G26" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -49970,13 +49997,13 @@
         <v>426</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="F27" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="G27" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -49992,7 +50019,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50004,10 +50031,10 @@
         <v>2903</v>
       </c>
       <c r="E30" t="s">
+        <v>3556</v>
+      </c>
+      <c r="F30" t="s">
         <v>3557</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3558</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="307" customFormat="1" ht="15.5">
@@ -50102,7 +50129,7 @@
         <v>364</v>
       </c>
       <c r="D46" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="30" customFormat="1">
@@ -50113,10 +50140,10 @@
         <v>2668</v>
       </c>
       <c r="D47" s="30" t="s">
+        <v>3256</v>
+      </c>
+      <c r="F47" s="408" t="s">
         <v>3257</v>
-      </c>
-      <c r="F47" s="408" t="s">
-        <v>3258</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>412</v>
@@ -50212,12 +50239,12 @@
     </row>
     <row r="60" spans="1:5" s="403" customFormat="1" ht="18">
       <c r="C60" s="403" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="30" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B61" s="30">
         <v>65036571</v>
@@ -50229,7 +50256,7 @@
         <v>2676</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="76" customFormat="1">
@@ -52071,7 +52098,7 @@
     </row>
     <row r="252" spans="1:6" s="433" customFormat="1" ht="21">
       <c r="C252" s="433" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -52088,30 +52115,30 @@
         <v>2342</v>
       </c>
       <c r="E253" t="s">
+        <v>3502</v>
+      </c>
+      <c r="F253" t="s">
         <v>3503</v>
-      </c>
-      <c r="F253" t="s">
-        <v>3504</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="D254" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="E254" t="s">
+        <v>3502</v>
+      </c>
+      <c r="F254" t="s">
         <v>3503</v>
-      </c>
-      <c r="F254" t="s">
-        <v>3504</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52122,16 +52149,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="D255" s="252" t="s">
         <v>2837</v>
       </c>
       <c r="E255" t="s">
+        <v>3502</v>
+      </c>
+      <c r="F255" t="s">
         <v>3503</v>
-      </c>
-      <c r="F255" t="s">
-        <v>3504</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -55522,7 +55549,7 @@
         <v>1379</v>
       </c>
       <c r="D456" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="E456" s="76" t="s">
         <v>1456</v>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59991" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9ACB45E-6C6C-4DFB-BA9B-6BBAF351E889}"/>
+  <xr:revisionPtr revIDLastSave="60008" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBD3AE93-3199-49E7-873F-DEDA2EC0AE37}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1311,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6264" uniqueCount="3667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6264" uniqueCount="3668">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -10520,9 +10520,6 @@
     <t>Traa010826</t>
   </si>
   <si>
-    <t>62942108 1 pantalla hasta el 26 de agosto</t>
-  </si>
-  <si>
     <t>67399212 1 pantalla hasta el 02 de septiembre (Abdalis)</t>
   </si>
   <si>
@@ -10775,18 +10772,6 @@
     <t>M.E hasta el `02 de septiembre</t>
   </si>
   <si>
-    <t>63813581 1 pantalla hasta el 02 de septiembre (Erick)</t>
-  </si>
-  <si>
-    <t>63813581 1 pantalla hasta el 03 de septiembre (Erick)</t>
-  </si>
-  <si>
-    <t>63813581 1 pantalla hasta el 03 de septiembre</t>
-  </si>
-  <si>
-    <t>63813581 1 pantalla hasta el 10 de septiembre (Erick)</t>
-  </si>
-  <si>
     <t>bishopmeredith9785+rj_cat.au@outlook.com</t>
   </si>
   <si>
@@ -12284,9 +12269,6 @@
     <t>62122994 1 pantalla hasta el 27 de septiembre Bonnie 270826-0426f</t>
   </si>
   <si>
-    <t>63971854 1 pantalla hasta el 27 de septiembre (Gustavo) 270826-0510w</t>
-  </si>
-  <si>
     <t>573188177287 1 pantalla hasta el 27 de septiembre (Mariana) 200826-2350</t>
   </si>
   <si>
@@ -12312,6 +12294,27 @@
   </si>
   <si>
     <t>69105664 1 pantalla hasta el 30 de agosto (Andres)</t>
+  </si>
+  <si>
+    <t>04 de octubre</t>
+  </si>
+  <si>
+    <t>63813581 1 pantalla hasta el 02 de octubre (Erick)</t>
+  </si>
+  <si>
+    <t>63813581 1 pantalla hasta el 03 de octubre (Erick)</t>
+  </si>
+  <si>
+    <t>63813581 1 pantalla hasta el 03 de octubre</t>
+  </si>
+  <si>
+    <t>63813581 1 pantalla hasta el 10 de octubre (Erick)</t>
+  </si>
+  <si>
+    <t>62942108 1 pantalla hasta el 26 de septiembre</t>
+  </si>
+  <si>
+    <t>crear 280826-1051g</t>
   </si>
 </sst>
 </file>
@@ -13630,7 +13633,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="447">
+  <cellXfs count="443">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -14118,10 +14121,6 @@
     <xf numFmtId="0" fontId="55" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -30204,7 +30203,7 @@
         <v>2079</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3346</v>
+        <v>3341</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2152</v>
@@ -30224,12 +30223,12 @@
         <v>2201</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3533</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2852</v>
@@ -30255,7 +30254,7 @@
         <v>2077</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3443</v>
+        <v>3438</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2152</v>
@@ -30303,10 +30302,10 @@
         <v>2080</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>3187</v>
+        <v>3182</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3515</v>
+        <v>3510</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2157</v>
@@ -30360,10 +30359,10 @@
         <v>2170</v>
       </c>
       <c r="E10" s="436" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="F10" s="436" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="G10" s="436" t="s">
         <v>59</v>
@@ -30385,7 +30384,7 @@
         <v>2221</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3622</v>
+        <v>3617</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2220</v>
@@ -30397,7 +30396,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="226" t="s">
-        <v>3354</v>
+        <v>3349</v>
       </c>
       <c r="B14" s="226" t="s">
         <v>1731</v>
@@ -30434,10 +30433,10 @@
         <v>1578</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3517</v>
+        <v>3512</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3623</v>
+        <v>3618</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1579</v>
@@ -30446,21 +30445,21 @@
         <v>201</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3518</v>
+        <v>3513</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3535</v>
+        <v>3530</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3611</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="253" t="s">
-        <v>3217</v>
+        <v>3212</v>
       </c>
       <c r="B17" s="253" t="s">
         <v>1433</v>
@@ -30506,7 +30505,7 @@
         <v>2109</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>3495</v>
+        <v>3490</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>1399</v>
@@ -30517,7 +30516,7 @@
     </row>
     <row r="20" spans="1:11" s="298" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>3329</v>
+        <v>3324</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30526,7 +30525,7 @@
         <v>1738</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>3412</v>
+        <v>3407</v>
       </c>
       <c r="E20" s="253" t="s">
         <v>1739</v>
@@ -30534,7 +30533,7 @@
     </row>
     <row r="21" spans="1:11" s="298" customFormat="1">
       <c r="A21" s="253" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B21" s="253">
         <v>60432412</v>
@@ -30563,7 +30562,7 @@
         <v>2198</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3346</v>
+        <v>3341</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2151</v>
@@ -30588,7 +30587,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="148" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B24" s="148">
         <v>62279384</v>
@@ -30614,7 +30613,7 @@
         <v>1574</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3494</v>
+        <v>3489</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1399</v>
@@ -30645,7 +30644,7 @@
     </row>
     <row r="27" spans="1:11" s="226" customFormat="1">
       <c r="A27" s="226" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B27" s="226">
         <v>64476521</v>
@@ -30708,24 +30707,24 @@
         <v>2476</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>3227</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3481</v>
+        <v>3476</v>
       </c>
       <c r="C31" s="252" t="s">
         <v>1962</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3482</v>
+        <v>3477</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3378</v>
+        <v>3373</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2097</v>
@@ -30734,16 +30733,16 @@
         <v>201</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3483</v>
+        <v>3478</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3618</v>
+        <v>3613</v>
       </c>
       <c r="J31" s="434" t="s">
-        <v>3505</v>
+        <v>3500</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3196</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30777,7 +30776,7 @@
     </row>
     <row r="34" spans="1:11" s="30" customFormat="1">
       <c r="A34" s="30" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="B34" s="30">
         <v>60389752</v>
@@ -30789,7 +30788,7 @@
         <v>2164</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3275</v>
+        <v>3270</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2155</v>
@@ -30817,7 +30816,7 @@
     </row>
     <row r="36" spans="1:11" s="148" customFormat="1">
       <c r="A36" s="226" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B36" s="148">
         <v>61381388</v>
@@ -30840,10 +30839,10 @@
         <v>2072</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3646</v>
+        <v>3641</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3347</v>
+        <v>3342</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2145</v>
@@ -30852,21 +30851,21 @@
         <v>201</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>3212</v>
+        <v>3207</v>
       </c>
       <c r="I37" s="30" t="s">
         <v>2998</v>
       </c>
-      <c r="J37" s="442" t="s">
-        <v>3653</v>
+      <c r="J37" s="30" t="s">
+        <v>3648</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3197</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2850</v>
@@ -30894,11 +30893,11 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="30" customFormat="1">
-      <c r="A40" s="442" t="s">
+      <c r="A40" s="30" t="s">
         <v>2630</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3660</v>
+        <v>3654</v>
       </c>
       <c r="C40" s="252" t="s">
         <v>1718</v>
@@ -30907,7 +30906,7 @@
         <v>3002</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3275</v>
+        <v>3270</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2160</v>
@@ -30916,21 +30915,21 @@
         <v>201</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3574</v>
+        <v>3569</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3606</v>
-      </c>
-      <c r="J40" s="444" t="s">
-        <v>3642</v>
+        <v>3601</v>
+      </c>
+      <c r="J40" s="32" t="s">
+        <v>3637</v>
       </c>
       <c r="K40" s="30" t="s">
-        <v>3190</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -30974,7 +30973,7 @@
         <v>2101</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3446</v>
+        <v>3441</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2195</v>
@@ -30985,7 +30984,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31002,7 +31001,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31028,10 +31027,10 @@
         <v>997</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>3171</v>
+        <v>3166</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2177</v>
@@ -31052,7 +31051,7 @@
         <v>2197</v>
       </c>
       <c r="D47" s="164" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="164" customFormat="1">
@@ -31083,10 +31082,10 @@
         <v>2063</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3603</v>
+        <v>3598</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3277</v>
+        <v>3272</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2163</v>
@@ -31095,16 +31094,16 @@
         <v>201</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3604</v>
-      </c>
-      <c r="I49" s="217" t="s">
-        <v>3069</v>
+        <v>3599</v>
+      </c>
+      <c r="I49" s="442" t="s">
+        <v>3666</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3119</v>
-      </c>
-      <c r="K49" s="444" t="s">
-        <v>3659</v>
+        <v>3118</v>
+      </c>
+      <c r="K49" s="32" t="s">
+        <v>3653</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31132,12 +31131,12 @@
         <v>2071</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3558</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
       <c r="A52" s="140" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B52" s="426" t="s">
         <v>1483</v>
@@ -31146,10 +31145,10 @@
         <v>1402</v>
       </c>
       <c r="D52" s="139" t="s">
-        <v>3202</v>
+        <v>3197</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3275</v>
+        <v>3270</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2161</v>
@@ -31158,16 +31157,16 @@
         <v>201</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3609</v>
+        <v>3604</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3203</v>
+        <v>3198</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="K52" s="270" t="s">
-        <v>3467</v>
+        <v>3462</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31189,7 +31188,7 @@
     </row>
     <row r="54" spans="1:11" s="164" customFormat="1">
       <c r="A54" s="416" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B54" s="163" t="s">
         <v>1785</v>
@@ -31208,7 +31207,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3272</v>
+        <v>3267</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31220,7 +31219,7 @@
         <v>2067</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3622</v>
+        <v>3617</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2178</v>
@@ -31237,10 +31236,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="411" t="s">
-        <v>3637</v>
+        <v>3632</v>
       </c>
       <c r="D56" s="377" t="s">
-        <v>3639</v>
+        <v>3634</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31249,13 +31248,13 @@
         <v>2630</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3643</v>
+        <v>3638</v>
       </c>
       <c r="C57" s="411" t="s">
-        <v>3638</v>
+        <v>3633</v>
       </c>
       <c r="D57" s="377" t="s">
-        <v>3640</v>
+        <v>3635</v>
       </c>
       <c r="E57" s="164"/>
     </row>
@@ -31282,16 +31281,16 @@
         <v>201</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3070</v>
-      </c>
-      <c r="I58" s="442" t="s">
-        <v>3656</v>
+        <v>3069</v>
+      </c>
+      <c r="I58" s="30" t="s">
+        <v>3651</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3348</v>
+        <v>3343</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="395" customFormat="1">
@@ -31306,16 +31305,16 @@
         <v>2508</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3626</v>
+        <v>3621</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2144</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>3182</v>
+        <v>3177</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3516</v>
+        <v>3511</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2145</v>
@@ -31324,21 +31323,21 @@
         <v>201</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3234</v>
-      </c>
-      <c r="I61" s="442" t="s">
-        <v>3657</v>
+        <v>3229</v>
+      </c>
+      <c r="I61" s="145" t="s">
+        <v>3667</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3224</v>
+        <v>3219</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3624</v>
+        <v>3619</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31347,7 +31346,7 @@
         <v>1514</v>
       </c>
       <c r="D62" s="378" t="s">
-        <v>3627</v>
+        <v>3622</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1419</v>
@@ -31364,7 +31363,7 @@
         <v>2129</v>
       </c>
       <c r="D63" s="377" t="s">
-        <v>3575</v>
+        <v>3570</v>
       </c>
       <c r="E63" s="164"/>
     </row>
@@ -31382,7 +31381,7 @@
         <v>3048</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3276</v>
+        <v>3271</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2162</v>
@@ -31391,16 +31390,16 @@
         <v>201</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3179</v>
+        <v>3174</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3178</v>
-      </c>
-      <c r="K64" s="442" t="s">
-        <v>3658</v>
+        <v>3173</v>
+      </c>
+      <c r="K64" s="30" t="s">
+        <v>3652</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31448,10 +31447,10 @@
         <v>1721</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>3432</v>
+        <v>3427</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3319</v>
+        <v>3314</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2166</v>
@@ -31460,21 +31459,21 @@
         <v>201</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3433</v>
+        <v>3428</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3219</v>
+        <v>3214</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3293</v>
+        <v>3288</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3442</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3624</v>
+        <v>3619</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31483,7 +31482,7 @@
         <v>1938</v>
       </c>
       <c r="D68" s="378" t="s">
-        <v>3599</v>
+        <v>3594</v>
       </c>
       <c r="E68" s="148"/>
     </row>
@@ -31498,7 +31497,7 @@
         <v>2165</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3298</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
@@ -31524,13 +31523,13 @@
         <v>201</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3476</v>
+        <v>3471</v>
       </c>
       <c r="I70" s="30" t="s">
         <v>3008</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>3409</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31544,12 +31543,12 @@
         <v>2025</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>3258</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="269" t="s">
-        <v>3364</v>
+        <v>3359</v>
       </c>
       <c r="B72" s="269" t="s">
         <v>1495</v>
@@ -31564,7 +31563,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31573,10 +31572,10 @@
         <v>1379</v>
       </c>
       <c r="D73" s="252" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3524</v>
+        <v>3519</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2096</v>
@@ -31587,7 +31586,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3354</v>
+        <v>3349</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31626,10 +31625,10 @@
         <v>1937</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>3369</v>
+        <v>3364</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3565</v>
+        <v>3560</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2177</v>
@@ -31638,16 +31637,16 @@
         <v>201</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3371</v>
+        <v>3366</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3373</v>
+        <v>3368</v>
       </c>
       <c r="J76" s="30" t="s">
         <v>2944</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3370</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31663,16 +31662,16 @@
         <v>144</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>3311</v>
+        <v>3306</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2070</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3406</v>
+        <v>3401</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3346</v>
+        <v>3341</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2156</v>
@@ -31681,16 +31680,16 @@
         <v>201</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>3429</v>
-      </c>
-      <c r="I79" s="444" t="s">
-        <v>3652</v>
+        <v>3424</v>
+      </c>
+      <c r="I79" s="32" t="s">
+        <v>3647</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3407</v>
+        <v>3402</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3312</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31726,20 +31725,20 @@
       </c>
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
-      <c r="A82" s="442" t="s">
-        <v>3665</v>
+      <c r="A82" s="30" t="s">
+        <v>3659</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3664</v>
+        <v>3658</v>
       </c>
       <c r="C82" s="134" t="s">
         <v>1963</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>3210</v>
+        <v>3205</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1964</v>
@@ -31748,21 +31747,21 @@
         <v>201</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3601</v>
+        <v>3596</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3666</v>
+        <v>3660</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3602</v>
+        <v>3597</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3223</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
       <c r="A83" s="148" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B83" s="148">
         <v>63145336</v>
@@ -31776,7 +31775,7 @@
     </row>
     <row r="84" spans="1:11" s="281" customFormat="1">
       <c r="A84" s="148" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B84" s="148">
         <v>68971798</v>
@@ -31810,17 +31809,17 @@
       <c r="G85" s="30" t="s">
         <v>498</v>
       </c>
-      <c r="H85" s="442" t="s">
-        <v>3636</v>
+      <c r="H85" s="30" t="s">
+        <v>3631</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3237</v>
+        <v>3232</v>
       </c>
       <c r="J85" s="217" t="s">
         <v>2649</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3507</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31861,7 +31860,7 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B88" s="30">
         <v>68496217</v>
@@ -31870,7 +31869,7 @@
         <v>701</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3349</v>
+        <v>3344</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1104</v>
@@ -31882,16 +31881,16 @@
         <v>1576</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3350</v>
+        <v>3345</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3388</v>
+        <v>3383</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3485</v>
+        <v>3480</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3484</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -31920,7 +31919,7 @@
         <v>67381873</v>
       </c>
       <c r="C90" s="409" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="D90" s="148" t="s">
         <v>3042</v>
@@ -31932,7 +31931,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="250" t="s">
-        <v>3364</v>
+        <v>3359</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1439</v>
@@ -31941,7 +31940,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3662</v>
+        <v>3656</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1150</v>
@@ -31952,17 +31951,17 @@
       <c r="G91" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="H91" s="442" t="s">
-        <v>3663</v>
+      <c r="H91" s="30" t="s">
+        <v>3657</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3313</v>
+        <v>3308</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3466</v>
+        <v>3461</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3566</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="417" customFormat="1">
@@ -32010,7 +32009,7 @@
         <v>1400</v>
       </c>
       <c r="E94" s="254" t="s">
-        <v>3183</v>
+        <v>3178</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1401</v>
@@ -32039,7 +32038,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B96" s="148">
         <v>62928817</v>
@@ -32059,16 +32058,16 @@
         <v>1460</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>3309</v>
+        <v>3304</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>2060</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>3308</v>
+        <v>3303</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>3366</v>
+        <v>3361</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1964</v>
@@ -32077,16 +32076,16 @@
         <v>201</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3232</v>
+        <v>3227</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3421</v>
+        <v>3416</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3514</v>
+        <v>3509</v>
       </c>
       <c r="K97" s="139" t="s">
-        <v>3389</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="98" spans="1:11" s="395" customFormat="1">
@@ -32099,19 +32098,19 @@
     </row>
     <row r="100" spans="1:11" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3217</v>
+        <v>3212</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3218</v>
+        <v>3213</v>
       </c>
       <c r="C100" s="252" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3569</v>
+        <v>3564</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1964</v>
@@ -32120,7 +32119,7 @@
         <v>201</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="I100" s="30" t="s">
         <v>2999</v>
@@ -32129,7 +32128,7 @@
         <v>2983</v>
       </c>
       <c r="K100" s="32" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="101" spans="1:11" s="395" customFormat="1">
@@ -32142,22 +32141,22 @@
     </row>
     <row r="103" spans="1:11" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B103" s="30">
         <v>62724019</v>
       </c>
       <c r="C103" s="252" t="s">
-        <v>3230</v>
+        <v>3225</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>3489</v>
+        <v>3484</v>
       </c>
       <c r="E103" s="30" t="s">
-        <v>3491</v>
+        <v>3486</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>3490</v>
+        <v>3485</v>
       </c>
       <c r="G103" s="30" t="s">
         <v>59</v>
@@ -32176,7 +32175,7 @@
         <v>158</v>
       </c>
       <c r="B106" s="285" t="s">
-        <v>3508</v>
+        <v>3503</v>
       </c>
       <c r="C106" s="134" t="s">
         <v>2057</v>
@@ -32196,16 +32195,16 @@
         <v>60756926</v>
       </c>
       <c r="C108" s="30" t="s">
-        <v>3174</v>
+        <v>3169</v>
       </c>
       <c r="D108" s="30" t="s">
-        <v>3175</v>
+        <v>3170</v>
       </c>
       <c r="E108" s="30" t="s">
-        <v>3176</v>
+        <v>3171</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G108" s="30" t="s">
         <v>59</v>
@@ -32216,16 +32215,16 @@
         <v>79</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>3320</v>
+        <v>3315</v>
       </c>
       <c r="E124" s="32" t="s">
-        <v>3176</v>
+        <v>3171</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>3229</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="30" customFormat="1"/>
@@ -32255,7 +32254,7 @@
         <v>2047</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3593</v>
+        <v>3588</v>
       </c>
       <c r="F127" t="s">
         <v>2045</v>
@@ -32275,7 +32274,7 @@
         <v>2015</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3593</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32292,7 +32291,7 @@
         <v>2958</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3593</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -32309,7 +32308,7 @@
         <v>2775</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3593</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32326,7 +32325,7 @@
         <v>2021</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3593</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32368,7 +32367,7 @@
         <v>2919</v>
       </c>
       <c r="E135" s="30" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="F135" t="s">
         <v>1348</v>
@@ -32405,7 +32404,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3272</v>
+        <v>3267</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32434,7 +32433,7 @@
         <v>2032</v>
       </c>
       <c r="D140" s="380" t="s">
-        <v>3644</v>
+        <v>3639</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>2031</v>
@@ -32520,7 +32519,7 @@
         <v>2975</v>
       </c>
       <c r="E152" s="30" t="s">
-        <v>3594</v>
+        <v>3589</v>
       </c>
       <c r="F152" t="s">
         <v>2033</v>
@@ -32540,7 +32539,7 @@
         <v>2463</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3594</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -32557,7 +32556,7 @@
         <v>3022</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3594</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -32588,7 +32587,7 @@
         <v>2325</v>
       </c>
       <c r="D156" s="380" t="s">
-        <v>3381</v>
+        <v>3376</v>
       </c>
       <c r="E156" s="30" t="s">
         <v>3011</v>
@@ -32664,7 +32663,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3054</v>
+        <v>3661</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1164</v>
@@ -32673,7 +32672,7 @@
         <v>2778</v>
       </c>
       <c r="D161" s="380" t="s">
-        <v>3526</v>
+        <v>3521</v>
       </c>
       <c r="E161" s="30" t="s">
         <v>3011</v>
@@ -32690,7 +32689,7 @@
         <v>2665</v>
       </c>
       <c r="D162" s="380" t="s">
-        <v>3166</v>
+        <v>3161</v>
       </c>
       <c r="E162" s="30" t="s">
         <v>3011</v>
@@ -32704,10 +32703,10 @@
         <v>12369714760</v>
       </c>
       <c r="C163" t="s">
-        <v>3297</v>
+        <v>3292</v>
       </c>
       <c r="D163" s="380" t="s">
-        <v>3314</v>
+        <v>3309</v>
       </c>
       <c r="E163" s="30" t="s">
         <v>3011</v>
@@ -32721,18 +32720,18 @@
         <v>2250</v>
       </c>
       <c r="C164" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="D164" s="380" t="s">
         <v>2632</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3243</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3217</v>
+        <v>3212</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32744,7 +32743,7 @@
         <v>2367</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3243</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -32761,12 +32760,12 @@
         <v>2367</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3243</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B167">
         <v>66935922</v>
@@ -32778,7 +32777,7 @@
         <v>2779</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3243</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32795,7 +32794,7 @@
         <v>2922</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3479</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -32812,7 +32811,7 @@
         <v>2982</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3479</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32829,7 +32828,7 @@
         <v>2629</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3479</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32846,7 +32845,7 @@
         <v>2415</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3479</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32863,7 +32862,7 @@
         <v>2633</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3525</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32880,7 +32879,7 @@
         <v>2430</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3525</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32897,7 +32896,7 @@
         <v>3012</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3525</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -32914,7 +32913,7 @@
         <v>2988</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3615</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -32931,7 +32930,7 @@
         <v>2988</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3615</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -32948,7 +32947,7 @@
         <v>2988</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3615</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -32965,7 +32964,7 @@
         <v>3023</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3615</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -32982,7 +32981,7 @@
         <v>2988</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3615</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -33024,7 +33023,7 @@
         <v>2959</v>
       </c>
       <c r="B182" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>3033</v>
@@ -33047,7 +33046,7 @@
         <v>3034</v>
       </c>
       <c r="D183" s="380" t="s">
-        <v>3188</v>
+        <v>3183</v>
       </c>
       <c r="E183" s="30" t="s">
         <v>3035</v>
@@ -33055,16 +33054,16 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B184" t="s">
-        <v>3211</v>
+        <v>3206</v>
       </c>
       <c r="C184" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="D184" s="380" t="s">
-        <v>3191</v>
+        <v>3186</v>
       </c>
       <c r="E184" s="30" t="s">
         <v>3035</v>
@@ -33072,19 +33071,19 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3217</v>
+        <v>3212</v>
       </c>
       <c r="B185">
         <v>68201775</v>
       </c>
       <c r="C185" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="D185" s="380" t="s">
-        <v>3194</v>
+        <v>3189</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -33092,16 +33091,16 @@
         <v>2671</v>
       </c>
       <c r="B186" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="C186" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="D186" s="380" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E186" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E186" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33112,30 +33111,30 @@
         <v>62724019</v>
       </c>
       <c r="C187" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="D187" s="380" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E187" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E187" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="30" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B188" s="32" t="s">
         <v>2190</v>
       </c>
       <c r="C188" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="D188" s="380" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E188" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E188" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33146,13 +33145,13 @@
         <v>65080956</v>
       </c>
       <c r="C189" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="D189" s="380" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E189" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E189" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33163,47 +33162,47 @@
         <v>68726473</v>
       </c>
       <c r="C190" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="D190" s="380" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E190" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E190" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3629</v>
+        <v>3624</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1917</v>
       </c>
       <c r="C191" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="D191" s="380" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E191" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E191" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>3572</v>
+        <v>3567</v>
       </c>
       <c r="B192">
         <v>64046277</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>3192</v>
+        <v>3187</v>
       </c>
       <c r="D192" s="380" t="s">
-        <v>3193</v>
+        <v>3188</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -33214,13 +33213,13 @@
         <v>66520892</v>
       </c>
       <c r="C193" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D193" s="380" t="s">
+        <v>3109</v>
+      </c>
+      <c r="E193" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E193" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33231,18 +33230,18 @@
         <v>62031509</v>
       </c>
       <c r="C194" t="s">
+        <v>3108</v>
+      </c>
+      <c r="D194" s="380" t="s">
         <v>3109</v>
       </c>
-      <c r="D194" s="380" t="s">
+      <c r="E194" s="30" t="s">
         <v>3110</v>
-      </c>
-      <c r="E194" s="30" t="s">
-        <v>3111</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="399" customFormat="1" ht="23.5">
       <c r="C197" s="399" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="D197" s="399">
         <v>51957149094</v>
@@ -33256,13 +33255,13 @@
         <v>60240509</v>
       </c>
       <c r="C198" t="s">
-        <v>3159</v>
+        <v>3154</v>
       </c>
       <c r="D198" s="380" t="s">
-        <v>3160</v>
+        <v>3155</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -33273,13 +33272,13 @@
         <v>66003234</v>
       </c>
       <c r="C199" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="D199" s="380" t="s">
-        <v>3511</v>
+        <v>3506</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -33290,30 +33289,30 @@
         <v>65344753</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>3161</v>
+        <v>3156</v>
       </c>
       <c r="D200" s="380" t="s">
-        <v>3270</v>
+        <v>3265</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3455</v>
+        <v>3450</v>
       </c>
       <c r="B201">
         <v>65633205</v>
       </c>
       <c r="C201" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="D201" s="380" t="s">
-        <v>3454</v>
+        <v>3449</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -33324,13 +33323,13 @@
         <v>61248427</v>
       </c>
       <c r="C202" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D202" s="380" t="s">
-        <v>3259</v>
+        <v>3254</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33341,13 +33340,13 @@
         <v>69329372</v>
       </c>
       <c r="C203" t="s">
-        <v>3269</v>
+        <v>3264</v>
       </c>
       <c r="D203" s="380" t="s">
-        <v>3283</v>
+        <v>3278</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -33358,13 +33357,13 @@
         <v>68168617</v>
       </c>
       <c r="C204" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D204" s="380" t="s">
-        <v>3265</v>
+        <v>3260</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33375,13 +33374,13 @@
         <v>68934853</v>
       </c>
       <c r="C205" t="s">
+        <v>3144</v>
+      </c>
+      <c r="D205" s="380" t="s">
+        <v>3277</v>
+      </c>
+      <c r="E205" s="30" t="s">
         <v>3145</v>
-      </c>
-      <c r="D205" s="380" t="s">
-        <v>3282</v>
-      </c>
-      <c r="E205" s="30" t="s">
-        <v>3146</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33389,16 +33388,16 @@
         <v>2957</v>
       </c>
       <c r="B206" t="s">
-        <v>3302</v>
+        <v>3297</v>
       </c>
       <c r="C206" t="s">
-        <v>3296</v>
+        <v>3291</v>
       </c>
       <c r="D206" s="380" t="s">
-        <v>3299</v>
+        <v>3294</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33409,30 +33408,30 @@
         <v>61430885</v>
       </c>
       <c r="C207" t="s">
-        <v>3300</v>
+        <v>3295</v>
       </c>
       <c r="D207" s="380" t="s">
-        <v>3301</v>
+        <v>3296</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>3329</v>
+        <v>3324</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" t="s">
-        <v>3325</v>
+        <v>3320</v>
       </c>
       <c r="D208" t="s">
-        <v>3327</v>
+        <v>3322</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3328</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33443,13 +33442,13 @@
         <v>65583706</v>
       </c>
       <c r="C209" t="s">
-        <v>3382</v>
+        <v>3377</v>
       </c>
       <c r="D209" s="380" t="s">
-        <v>3384</v>
+        <v>3379</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3328</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -33460,13 +33459,13 @@
         <v>65574051</v>
       </c>
       <c r="C210" t="s">
+        <v>3321</v>
+      </c>
+      <c r="D210" t="s">
         <v>3326</v>
       </c>
-      <c r="D210" t="s">
-        <v>3331</v>
-      </c>
       <c r="E210" s="30" t="s">
-        <v>3328</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -33474,27 +33473,27 @@
         <v>3037</v>
       </c>
       <c r="B211" t="s">
-        <v>3411</v>
+        <v>3406</v>
       </c>
       <c r="C211" t="s">
-        <v>3383</v>
+        <v>3378</v>
       </c>
       <c r="D211" s="380" t="s">
-        <v>3385</v>
+        <v>3380</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3328</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="C212" s="7" t="s">
-        <v>3630</v>
+        <v>3625</v>
       </c>
       <c r="D212" t="s">
-        <v>3631</v>
+        <v>3626</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3328</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33505,30 +33504,30 @@
         <v>62863306</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>3436</v>
+        <v>3431</v>
       </c>
       <c r="D213" s="380" t="s">
-        <v>3438</v>
+        <v>3433</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3439</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>3364</v>
+        <v>3359</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3459</v>
+        <v>3454</v>
       </c>
       <c r="D214" t="s">
-        <v>3510</v>
+        <v>3505</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3439</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33539,30 +33538,30 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3460</v>
+        <v>3455</v>
       </c>
       <c r="D215" t="s">
-        <v>3452</v>
+        <v>3447</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3439</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B216">
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>3437</v>
+        <v>3432</v>
       </c>
       <c r="D216" t="s">
-        <v>3453</v>
+        <v>3448</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3439</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33573,13 +33572,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
-        <v>3461</v>
+        <v>3456</v>
       </c>
       <c r="D217" s="380" t="s">
-        <v>3462</v>
+        <v>3457</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3439</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -33665,7 +33664,7 @@
         <v>234</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -33689,7 +33688,7 @@
         <v>1379</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -33697,23 +33696,23 @@
         <v>1298</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="C258" s="1" t="s">
-        <v>3173</v>
+        <v>3168</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>3174</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
-        <v>3228</v>
+        <v>3223</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>3230</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -33721,10 +33720,10 @@
         <v>1719</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>3233</v>
+        <v>3228</v>
       </c>
       <c r="E260" s="30" t="s">
-        <v>3231</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36350,7 +36349,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>3430</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36394,7 +36393,7 @@
     </row>
     <row r="6" spans="1:9" s="76" customFormat="1">
       <c r="A6" s="76" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36409,7 +36408,7 @@
         <v>684</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="G6" s="222" t="s">
         <v>1485</v>
@@ -36429,13 +36428,13 @@
         <v>1905</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3318</v>
+        <v>3313</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1485</v>
@@ -36461,7 +36460,7 @@
         <v>365</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1485</v>
@@ -36487,7 +36486,7 @@
         <v>365</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1485</v>
@@ -36497,8 +36496,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" s="183" customFormat="1">
-      <c r="A10" s="276" t="s">
-        <v>2809</v>
+      <c r="A10" s="193" t="s">
+        <v>2648</v>
       </c>
       <c r="B10" s="193">
         <v>64403333</v>
@@ -36513,7 +36512,7 @@
         <v>365</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1485</v>
@@ -36539,7 +36538,7 @@
         <v>365</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1485</v>
@@ -36562,7 +36561,7 @@
         <v>2673</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1470</v>
@@ -36589,7 +36588,7 @@
         <v>1906</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1470</v>
@@ -36616,7 +36615,7 @@
         <v>3041</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1470</v>
@@ -36631,7 +36630,7 @@
     </row>
     <row r="16" spans="1:9" s="183" customFormat="1">
       <c r="A16" s="183" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36643,7 +36642,7 @@
         <v>2418</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1470</v>
@@ -36670,7 +36669,7 @@
         <v>1553</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1470</v>
@@ -36697,7 +36696,7 @@
         <v>2238</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1470</v>
@@ -36712,7 +36711,7 @@
     </row>
     <row r="20" spans="1:9" s="76" customFormat="1">
       <c r="A20" s="195" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36727,7 +36726,7 @@
         <v>365</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>427</v>
@@ -36741,7 +36740,7 @@
     </row>
     <row r="21" spans="1:9" s="183" customFormat="1">
       <c r="A21" s="183" t="s">
-        <v>3208</v>
+        <v>3203</v>
       </c>
       <c r="B21" s="183">
         <v>62723048</v>
@@ -36756,7 +36755,7 @@
         <v>365</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>427</v>
@@ -36785,7 +36784,7 @@
         <v>365</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>427</v>
@@ -36799,7 +36798,7 @@
     </row>
     <row r="23" spans="1:9" s="183" customFormat="1">
       <c r="A23" s="183" t="s">
-        <v>3625</v>
+        <v>3620</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36814,7 +36813,7 @@
         <v>365</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>427</v>
@@ -36843,7 +36842,7 @@
         <v>365</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>427</v>
@@ -36872,7 +36871,7 @@
         <v>365</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>427</v>
@@ -36901,7 +36900,7 @@
         <v>365</v>
       </c>
       <c r="F27" s="195" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>427</v>
@@ -36930,7 +36929,7 @@
         <v>365</v>
       </c>
       <c r="F28" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>427</v>
@@ -36959,7 +36958,7 @@
         <v>365</v>
       </c>
       <c r="F29" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>427</v>
@@ -36988,7 +36987,7 @@
         <v>365</v>
       </c>
       <c r="F30" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>427</v>
@@ -37017,7 +37016,7 @@
         <v>365</v>
       </c>
       <c r="F31" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>427</v>
@@ -37031,7 +37030,7 @@
     </row>
     <row r="32" spans="1:9" s="183" customFormat="1">
       <c r="A32" s="193" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B32" s="193">
         <v>64967407</v>
@@ -37046,7 +37045,7 @@
         <v>365</v>
       </c>
       <c r="F32" s="193" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>427</v>
@@ -37075,7 +37074,7 @@
         <v>365</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>3172</v>
+        <v>3167</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1486</v>
@@ -37102,7 +37101,7 @@
         <v>365</v>
       </c>
       <c r="F35" s="183" t="s">
-        <v>3172</v>
+        <v>3167</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>381</v>
@@ -37131,7 +37130,7 @@
         <v>365</v>
       </c>
       <c r="F36" s="183" t="s">
-        <v>3172</v>
+        <v>3167</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>381</v>
@@ -37160,7 +37159,7 @@
         <v>365</v>
       </c>
       <c r="F37" s="183" t="s">
-        <v>3172</v>
+        <v>3167</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>381</v>
@@ -37189,7 +37188,7 @@
         <v>365</v>
       </c>
       <c r="F38" s="183" t="s">
-        <v>3172</v>
+        <v>3167</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>381</v>
@@ -37218,7 +37217,7 @@
         <v>365</v>
       </c>
       <c r="F39" s="183" t="s">
-        <v>3172</v>
+        <v>3167</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>381</v>
@@ -37247,7 +37246,7 @@
         <v>2627</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3213</v>
+        <v>3208</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>1485</v>
@@ -37274,7 +37273,7 @@
         <v>2627</v>
       </c>
       <c r="F42" s="193" t="s">
-        <v>3213</v>
+        <v>3208</v>
       </c>
       <c r="G42" s="183" t="s">
         <v>1485</v>
@@ -37286,7 +37285,7 @@
     </row>
     <row r="43" spans="1:9" s="183" customFormat="1">
       <c r="A43" s="193" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B43" s="193">
         <v>63226030</v>
@@ -37301,7 +37300,7 @@
         <v>2627</v>
       </c>
       <c r="F43" s="193" t="s">
-        <v>3213</v>
+        <v>3208</v>
       </c>
       <c r="G43" s="183" t="s">
         <v>1485</v>
@@ -37328,7 +37327,7 @@
         <v>2627</v>
       </c>
       <c r="F44" s="193" t="s">
-        <v>3213</v>
+        <v>3208</v>
       </c>
       <c r="G44" s="183" t="s">
         <v>1485</v>
@@ -37355,7 +37354,7 @@
         <v>2627</v>
       </c>
       <c r="F45" s="193" t="s">
-        <v>3213</v>
+        <v>3208</v>
       </c>
       <c r="G45" s="183" t="s">
         <v>1485</v>
@@ -37382,7 +37381,7 @@
         <v>2627</v>
       </c>
       <c r="F46" s="193" t="s">
-        <v>3213</v>
+        <v>3208</v>
       </c>
       <c r="G46" s="183" t="s">
         <v>1485</v>
@@ -37403,13 +37402,13 @@
         <v>1720</v>
       </c>
       <c r="D48" s="195" t="s">
-        <v>3480</v>
+        <v>3475</v>
       </c>
       <c r="E48" s="76" t="s">
         <v>2627</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1485</v>
@@ -37436,7 +37435,7 @@
         <v>2627</v>
       </c>
       <c r="F49" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G49" s="183" t="s">
         <v>1485</v>
@@ -37463,7 +37462,7 @@
         <v>2627</v>
       </c>
       <c r="F50" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G50" s="183" t="s">
         <v>1485</v>
@@ -37490,7 +37489,7 @@
         <v>2627</v>
       </c>
       <c r="F51" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G51" s="183" t="s">
         <v>1485</v>
@@ -37508,7 +37507,7 @@
         <v>65174343</v>
       </c>
       <c r="C52" s="193" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="D52" s="193" t="s">
         <v>2068</v>
@@ -37517,7 +37516,7 @@
         <v>2627</v>
       </c>
       <c r="F52" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G52" s="183" t="s">
         <v>1485</v>
@@ -37536,7 +37535,7 @@
         <v>2627</v>
       </c>
       <c r="F53" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G53" s="183" t="s">
         <v>1485</v>
@@ -37562,7 +37561,7 @@
         <v>2627</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1485</v>
@@ -37589,7 +37588,7 @@
         <v>2627</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1485</v>
@@ -37601,7 +37600,7 @@
     </row>
     <row r="57" spans="1:9" s="183" customFormat="1">
       <c r="A57" s="183" t="s">
-        <v>3217</v>
+        <v>3212</v>
       </c>
       <c r="B57" s="183">
         <v>64403333</v>
@@ -37616,7 +37615,7 @@
         <v>2627</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1485</v>
@@ -37643,7 +37642,7 @@
         <v>2627</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1485</v>
@@ -37655,7 +37654,7 @@
     </row>
     <row r="59" spans="1:9" s="183" customFormat="1">
       <c r="A59" s="183" t="s">
-        <v>3272</v>
+        <v>3267</v>
       </c>
       <c r="B59" s="183">
         <v>65003516</v>
@@ -37670,7 +37669,7 @@
         <v>2627</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1485</v>
@@ -37697,7 +37696,7 @@
         <v>2627</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3292</v>
+        <v>3287</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1485</v>
@@ -37709,7 +37708,7 @@
     </row>
     <row r="62" spans="1:9" s="76" customFormat="1">
       <c r="A62" s="76" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B62" s="76">
         <v>64147946</v>
@@ -37721,7 +37720,7 @@
         <v>2580</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F62" s="195" t="s">
         <v>2581</v>
@@ -37736,7 +37735,7 @@
     </row>
     <row r="63" spans="1:9" s="183" customFormat="1">
       <c r="A63" s="193" t="s">
-        <v>3268</v>
+        <v>3263</v>
       </c>
       <c r="B63" s="193">
         <v>62646186</v>
@@ -37748,7 +37747,7 @@
         <v>2585</v>
       </c>
       <c r="E63" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F63" s="193" t="s">
         <v>2581</v>
@@ -37775,7 +37774,7 @@
         <v>2387</v>
       </c>
       <c r="E64" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F64" s="193" t="s">
         <v>2581</v>
@@ -37802,7 +37801,7 @@
         <v>2960</v>
       </c>
       <c r="E65" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F65" s="183" t="s">
         <v>2581</v>
@@ -37828,7 +37827,7 @@
         <v>2128</v>
       </c>
       <c r="E66" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F66" s="183" t="s">
         <v>2581</v>
@@ -37854,7 +37853,7 @@
         <v>2575</v>
       </c>
       <c r="E67" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F67" s="183" t="s">
         <v>2581</v>
@@ -37880,7 +37879,7 @@
         <v>1781</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2579</v>
@@ -37892,7 +37891,7 @@
     </row>
     <row r="70" spans="1:9" s="183" customFormat="1">
       <c r="A70" s="193" t="s">
-        <v>3208</v>
+        <v>3203</v>
       </c>
       <c r="B70" s="193">
         <v>66082581</v>
@@ -37904,7 +37903,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2579</v>
@@ -37928,7 +37927,7 @@
         <v>1272</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2579</v>
@@ -37952,7 +37951,7 @@
         <v>2472</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F72" s="193" t="s">
         <v>2579</v>
@@ -37964,7 +37963,7 @@
     </row>
     <row r="73" spans="1:9" s="183" customFormat="1">
       <c r="A73" s="420" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B73" s="193">
         <v>60196388</v>
@@ -37976,7 +37975,7 @@
         <v>2384</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F73" s="193" t="s">
         <v>2579</v>
@@ -37988,7 +37987,7 @@
     </row>
     <row r="74" spans="1:9" s="183" customFormat="1">
       <c r="A74" s="183" t="s">
-        <v>3217</v>
+        <v>3212</v>
       </c>
       <c r="B74" s="183" t="s">
         <v>1481</v>
@@ -38000,7 +37999,7 @@
         <v>2639</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3340</v>
+        <v>3335</v>
       </c>
       <c r="F74" s="193" t="s">
         <v>2579</v>
@@ -38018,16 +38017,16 @@
         <v>63574980</v>
       </c>
       <c r="C76" s="76" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="D76" s="76" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="E76" s="76" t="s">
         <v>1381</v>
       </c>
       <c r="F76" s="195" t="s">
-        <v>3423</v>
+        <v>3418</v>
       </c>
       <c r="G76" s="76" t="s">
         <v>1485</v>
@@ -38053,7 +38052,7 @@
         <v>1381</v>
       </c>
       <c r="F77" s="183" t="s">
-        <v>3423</v>
+        <v>3418</v>
       </c>
       <c r="G77" s="183" t="s">
         <v>1485</v>
@@ -38064,13 +38063,13 @@
     </row>
     <row r="78" spans="1:9" s="183" customFormat="1">
       <c r="A78" s="183" t="s">
-        <v>3280</v>
+        <v>3275</v>
       </c>
       <c r="B78" s="183">
         <v>68483411</v>
       </c>
       <c r="C78" s="183" t="s">
-        <v>3279</v>
+        <v>3274</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>2236</v>
@@ -38079,7 +38078,7 @@
         <v>1381</v>
       </c>
       <c r="F78" s="183" t="s">
-        <v>3423</v>
+        <v>3418</v>
       </c>
       <c r="G78" s="183" t="s">
         <v>1485</v>
@@ -38093,19 +38092,19 @@
         <v>2648</v>
       </c>
       <c r="B79" s="183" t="s">
-        <v>3651</v>
+        <v>3646</v>
       </c>
       <c r="C79" s="194" t="s">
         <v>2865</v>
       </c>
       <c r="D79" s="183" t="s">
-        <v>3650</v>
+        <v>3645</v>
       </c>
       <c r="E79" s="183" t="s">
         <v>1381</v>
       </c>
       <c r="F79" s="183" t="s">
-        <v>3423</v>
+        <v>3418</v>
       </c>
       <c r="G79" s="183" t="s">
         <v>1485</v>
@@ -38131,7 +38130,7 @@
         <v>1381</v>
       </c>
       <c r="F80" s="183" t="s">
-        <v>3423</v>
+        <v>3418</v>
       </c>
       <c r="G80" s="183" t="s">
         <v>1485</v>
@@ -38157,7 +38156,7 @@
         <v>1381</v>
       </c>
       <c r="F81" s="183" t="s">
-        <v>3423</v>
+        <v>3418</v>
       </c>
       <c r="G81" s="183" t="s">
         <v>1485</v>
@@ -38183,7 +38182,7 @@
         <v>1710</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3424</v>
+        <v>3419</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1485</v>
@@ -38207,7 +38206,7 @@
         <v>1710</v>
       </c>
       <c r="F84" s="193" t="s">
-        <v>3424</v>
+        <v>3419</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1485</v>
@@ -38231,7 +38230,7 @@
         <v>1710</v>
       </c>
       <c r="F85" s="193" t="s">
-        <v>3424</v>
+        <v>3419</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1485</v>
@@ -38255,7 +38254,7 @@
         <v>1710</v>
       </c>
       <c r="F86" s="193" t="s">
-        <v>3424</v>
+        <v>3419</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1485</v>
@@ -38279,7 +38278,7 @@
         <v>1710</v>
       </c>
       <c r="F87" s="193" t="s">
-        <v>3424</v>
+        <v>3419</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1485</v>
@@ -38287,8 +38286,8 @@
       <c r="I87" s="193"/>
     </row>
     <row r="88" spans="1:9" s="183" customFormat="1">
-      <c r="A88" s="49" t="s">
-        <v>2809</v>
+      <c r="A88" s="183" t="s">
+        <v>2648</v>
       </c>
       <c r="B88" s="183">
         <v>64403333</v>
@@ -38303,7 +38302,7 @@
         <v>1710</v>
       </c>
       <c r="F88" s="193" t="s">
-        <v>3424</v>
+        <v>3419</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1485</v>
@@ -38312,7 +38311,7 @@
     </row>
     <row r="90" spans="1:9" s="76" customFormat="1">
       <c r="A90" s="195" t="s">
-        <v>3248</v>
+        <v>3243</v>
       </c>
       <c r="B90" s="195">
         <v>64476521</v>
@@ -38327,7 +38326,7 @@
         <v>2627</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1485</v>
@@ -38354,7 +38353,7 @@
         <v>2627</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1485</v>
@@ -38381,7 +38380,7 @@
         <v>2627</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1485</v>
@@ -38408,7 +38407,7 @@
         <v>2627</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1485</v>
@@ -38435,7 +38434,7 @@
         <v>2627</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1485</v>
@@ -38462,7 +38461,7 @@
         <v>2627</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1485</v>
@@ -38474,7 +38473,7 @@
     </row>
     <row r="97" spans="1:9" s="76" customFormat="1">
       <c r="A97" s="195" t="s">
-        <v>3465</v>
+        <v>3460</v>
       </c>
       <c r="B97" s="195">
         <v>66082581</v>
@@ -38486,7 +38485,7 @@
         <v>2397</v>
       </c>
       <c r="E97" s="76" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="F97" s="195" t="s">
         <v>427</v>
@@ -38501,7 +38500,7 @@
     </row>
     <row r="98" spans="1:9" s="183" customFormat="1">
       <c r="A98" s="193" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B98" s="193" t="s">
         <v>2907</v>
@@ -38513,7 +38512,7 @@
         <v>2402</v>
       </c>
       <c r="E98" s="183" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="F98" s="193" t="s">
         <v>427</v>
@@ -38540,7 +38539,7 @@
         <v>2404</v>
       </c>
       <c r="E99" s="183" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="F99" s="193" t="s">
         <v>427</v>
@@ -38561,13 +38560,13 @@
         <v>69017426</v>
       </c>
       <c r="C100" s="194" t="s">
-        <v>3321</v>
+        <v>3316</v>
       </c>
       <c r="D100" s="193" t="s">
         <v>2592</v>
       </c>
       <c r="E100" s="183" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="F100" s="193" t="s">
         <v>427</v>
@@ -38594,7 +38593,7 @@
         <v>2408</v>
       </c>
       <c r="E101" s="183" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="F101" s="193" t="s">
         <v>427</v>
@@ -38615,13 +38614,13 @@
         <v>62723048</v>
       </c>
       <c r="C102" s="194" t="s">
-        <v>3342</v>
+        <v>3337</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3341</v>
+        <v>3336</v>
       </c>
       <c r="E102" s="183" t="s">
-        <v>3425</v>
+        <v>3420</v>
       </c>
       <c r="F102" s="193" t="s">
         <v>427</v>
@@ -38642,16 +38641,16 @@
         <v>68310153</v>
       </c>
       <c r="C104" s="195" t="s">
-        <v>3457</v>
+        <v>3452</v>
       </c>
       <c r="D104" s="195" t="s">
-        <v>3458</v>
+        <v>3453</v>
       </c>
       <c r="E104" s="76" t="s">
         <v>365</v>
       </c>
       <c r="F104" s="195" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G104" s="76" t="s">
         <v>1381</v>
@@ -38665,7 +38664,7 @@
     </row>
     <row r="105" spans="1:9" s="183" customFormat="1">
       <c r="A105" s="193" t="s">
-        <v>3464</v>
+        <v>3459</v>
       </c>
       <c r="B105" s="193">
         <v>63910392</v>
@@ -38678,7 +38677,7 @@
         <v>365</v>
       </c>
       <c r="F105" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G105" s="183" t="s">
         <v>1381</v>
@@ -38692,22 +38691,22 @@
     </row>
     <row r="106" spans="1:9" s="183" customFormat="1">
       <c r="A106" s="193" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B106" s="193">
         <v>68853797</v>
       </c>
       <c r="C106" s="193" t="s">
-        <v>3528</v>
+        <v>3523</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3387</v>
+        <v>3382</v>
       </c>
       <c r="E106" s="183" t="s">
         <v>2627</v>
       </c>
       <c r="F106" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G106" s="183" t="s">
         <v>1381</v>
@@ -38726,7 +38725,7 @@
         <v>365</v>
       </c>
       <c r="F107" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G107" s="183" t="s">
         <v>1381</v>
@@ -38747,7 +38746,7 @@
         <v>365</v>
       </c>
       <c r="F108" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G108" s="183" t="s">
         <v>1381</v>
@@ -38768,7 +38767,7 @@
         <v>365</v>
       </c>
       <c r="F109" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G109" s="183" t="s">
         <v>1381</v>
@@ -38782,7 +38781,7 @@
     </row>
     <row r="111" spans="1:9" s="76" customFormat="1">
       <c r="A111" s="76" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B111" s="76">
         <v>62751201</v>
@@ -38797,7 +38796,7 @@
         <v>1381</v>
       </c>
       <c r="F111" s="76" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G111" s="222" t="s">
         <v>1485</v>
@@ -38824,7 +38823,7 @@
         <v>1381</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1485</v>
@@ -38842,16 +38841,16 @@
         <v>64543204</v>
       </c>
       <c r="C113" s="194" t="s">
-        <v>3400</v>
+        <v>3395</v>
       </c>
       <c r="D113" s="183" t="s">
-        <v>3399</v>
+        <v>3394</v>
       </c>
       <c r="E113" s="183" t="s">
         <v>1381</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1485</v>
@@ -38878,7 +38877,7 @@
         <v>1381</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1485</v>
@@ -38905,7 +38904,7 @@
         <v>1381</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1485</v>
@@ -38932,7 +38931,7 @@
         <v>1381</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3463</v>
+        <v>3458</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1485</v>
@@ -38956,7 +38955,7 @@
         <v>1734</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>1567</v>
@@ -38982,7 +38981,7 @@
         <v>895</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F119" s="183" t="s">
         <v>1567</v>
@@ -38996,7 +38995,7 @@
     </row>
     <row r="120" spans="1:9" s="183" customFormat="1">
       <c r="A120" s="183" t="s">
-        <v>3493</v>
+        <v>3488</v>
       </c>
       <c r="B120" s="183">
         <v>69563253</v>
@@ -39008,7 +39007,7 @@
         <v>1021</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F120" s="183" t="s">
         <v>1567</v>
@@ -39028,13 +39027,13 @@
         <v>63062167</v>
       </c>
       <c r="C121" s="194" t="s">
-        <v>3235</v>
+        <v>3230</v>
       </c>
       <c r="D121" s="183" t="s">
         <v>1284</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F121" s="183" t="s">
         <v>1567</v>
@@ -39060,7 +39059,7 @@
         <v>950</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F122" s="183" t="s">
         <v>1567</v>
@@ -39086,7 +39085,7 @@
         <v>1991</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F123" s="183" t="s">
         <v>1567</v>
@@ -39112,7 +39111,7 @@
         <v>2422</v>
       </c>
       <c r="E125" s="76" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>427</v>
@@ -39138,7 +39137,7 @@
         <v>2424</v>
       </c>
       <c r="E126" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F126" s="193" t="s">
         <v>427</v>
@@ -39165,7 +39164,7 @@
         <v>2426</v>
       </c>
       <c r="E127" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F127" s="193" t="s">
         <v>427</v>
@@ -39180,7 +39179,7 @@
     </row>
     <row r="128" spans="1:9" s="183" customFormat="1">
       <c r="A128" s="49" t="s">
-        <v>3588</v>
+        <v>3583</v>
       </c>
       <c r="B128" s="183">
         <v>67836337</v>
@@ -39189,7 +39188,7 @@
         <v>2498</v>
       </c>
       <c r="E128" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F128" s="193" t="s">
         <v>427</v>
@@ -39216,7 +39215,7 @@
         <v>380</v>
       </c>
       <c r="E129" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F129" s="193" t="s">
         <v>427</v>
@@ -39243,7 +39242,7 @@
         <v>1706</v>
       </c>
       <c r="E130" s="183" t="s">
-        <v>3546</v>
+        <v>3541</v>
       </c>
       <c r="F130" s="193" t="s">
         <v>427</v>
@@ -39371,7 +39370,7 @@
     </row>
     <row r="136" spans="1:9" s="183" customFormat="1">
       <c r="A136" s="183" t="s">
-        <v>3246</v>
+        <v>3241</v>
       </c>
       <c r="B136" s="183">
         <v>66230961</v>
@@ -39400,7 +39399,7 @@
     </row>
     <row r="137" spans="1:9" s="183" customFormat="1">
       <c r="A137" s="183" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B137" s="183">
         <v>69888391</v>
@@ -39537,7 +39536,7 @@
     </row>
     <row r="143" spans="1:9" s="183" customFormat="1">
       <c r="A143" s="183" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B143" s="183">
         <v>62385671</v>
@@ -39807,7 +39806,7 @@
     </row>
     <row r="155" spans="1:9" s="183" customFormat="1">
       <c r="A155" s="183" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B155" s="183">
         <v>62560788</v>
@@ -39861,16 +39860,16 @@
     </row>
     <row r="157" spans="1:9" s="183" customFormat="1">
       <c r="A157" s="193" t="s">
-        <v>3402</v>
+        <v>3397</v>
       </c>
       <c r="B157" s="193">
         <v>60125401</v>
       </c>
       <c r="C157" s="194" t="s">
-        <v>3401</v>
+        <v>3396</v>
       </c>
       <c r="D157" s="193" t="s">
-        <v>3403</v>
+        <v>3398</v>
       </c>
       <c r="E157" s="183" t="s">
         <v>2627</v>
@@ -39888,7 +39887,7 @@
     </row>
     <row r="158" spans="1:9" s="183" customFormat="1">
       <c r="A158" s="193" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B158" s="193">
         <v>64720128</v>
@@ -39930,7 +39929,7 @@
         <v>365</v>
       </c>
       <c r="F160" s="195" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G160" s="76" t="s">
         <v>2491</v>
@@ -39959,7 +39958,7 @@
         <v>365</v>
       </c>
       <c r="F161" s="193" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G161" s="183" t="s">
         <v>2491</v>
@@ -39988,7 +39987,7 @@
         <v>365</v>
       </c>
       <c r="F162" s="193" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G162" s="183" t="s">
         <v>2491</v>
@@ -40017,7 +40016,7 @@
         <v>365</v>
       </c>
       <c r="F163" s="193" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G163" s="183" t="s">
         <v>2491</v>
@@ -40046,7 +40045,7 @@
         <v>365</v>
       </c>
       <c r="F164" s="193" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G164" s="183" t="s">
         <v>2491</v>
@@ -40066,16 +40065,16 @@
         <v>64403333</v>
       </c>
       <c r="C165" s="194" t="s">
-        <v>3404</v>
+        <v>3399</v>
       </c>
       <c r="D165" s="423" t="s">
-        <v>3403</v>
+        <v>3398</v>
       </c>
       <c r="E165" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F165" s="193" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G165" s="183" t="s">
         <v>2491</v>
@@ -40173,7 +40172,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40181,7 +40180,7 @@
         <v>1364</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40189,7 +40188,7 @@
         <v>1717</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>3235</v>
+        <v>3230</v>
       </c>
       <c r="F199" s="405"/>
     </row>
@@ -40198,7 +40197,7 @@
         <v>1343</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>3279</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40206,7 +40205,7 @@
         <v>411</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>3321</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40214,7 +40213,7 @@
         <v>716</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>3342</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40222,7 +40221,7 @@
         <v>284</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>3400</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40230,7 +40229,7 @@
         <v>2495</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>3401</v>
+        <v>3396</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40240,7 +40239,7 @@
         <v>470</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>3457</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40248,7 +40247,7 @@
         <v>222</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>3528</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41586,10 +41585,10 @@
         <v>712</v>
       </c>
       <c r="H3" t="s">
-        <v>3284</v>
+        <v>3279</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3497</v>
+        <v>3492</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41619,16 +41618,16 @@
         <v>2855</v>
       </c>
       <c r="I4" t="s">
-        <v>3392</v>
+        <v>3387</v>
       </c>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B5" t="s">
-        <v>3236</v>
+        <v>3231</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>485</v>
@@ -41637,7 +41636,7 @@
         <v>1573</v>
       </c>
       <c r="E5" t="s">
-        <v>3534</v>
+        <v>3529</v>
       </c>
       <c r="F5" t="s">
         <v>2253</v>
@@ -41649,7 +41648,7 @@
         <v>2980</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3157</v>
+        <v>3665</v>
       </c>
       <c r="J5" t="s">
         <v>1436</v>
@@ -41677,7 +41676,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B7" s="180">
         <v>64403333</v>
@@ -41703,13 +41702,13 @@
         <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>3368</v>
+        <v>3363</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2139</v>
       </c>
       <c r="D8" t="s">
-        <v>3367</v>
+        <v>3362</v>
       </c>
       <c r="E8" t="s">
         <v>2436</v>
@@ -41720,11 +41719,11 @@
       <c r="G8" t="s">
         <v>253</v>
       </c>
-      <c r="H8" s="445" t="s">
-        <v>3661</v>
+      <c r="H8" s="4" t="s">
+        <v>3655</v>
       </c>
       <c r="I8" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41742,7 +41741,7 @@
         <v>2927</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2140</v>
@@ -41754,7 +41753,7 @@
         <v>2985</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3200</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41788,7 +41787,7 @@
         <v>441</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3608</v>
+        <v>3603</v>
       </c>
       <c r="I12" s="49" t="s">
         <v>2766</v>
@@ -41833,34 +41832,34 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="10" t="s">
-        <v>3247</v>
+        <v>3242</v>
       </c>
       <c r="B16" s="10">
         <v>67663098</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>3205</v>
+        <v>3200</v>
       </c>
       <c r="D16" t="s">
-        <v>3204</v>
+        <v>3199</v>
       </c>
       <c r="E16" t="s">
-        <v>3263</v>
+        <v>3258</v>
       </c>
       <c r="F16" t="s">
-        <v>3264</v>
+        <v>3259</v>
       </c>
       <c r="G16" t="s">
         <v>122</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>3278</v>
+        <v>3273</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>3281</v>
+        <v>3276</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>3365</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="19" customFormat="1"/>
@@ -41989,7 +41988,7 @@
         <v>3000</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3501</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -42015,7 +42014,7 @@
         <v>522</v>
       </c>
       <c r="H7" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="I7" s="276" t="s">
         <v>2770</v>
@@ -42097,7 +42096,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>3246</v>
+        <v>3241</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -42106,7 +42105,7 @@
         <v>2296</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3538</v>
+        <v>3533</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>976</v>
@@ -42118,10 +42117,10 @@
         <v>522</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3539</v>
+        <v>3534</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3548</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42194,7 +42193,7 @@
         <v>2689</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3180</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -42220,7 +42219,7 @@
         <v>522</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>3471</v>
+        <v>3466</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2750</v>
@@ -42257,7 +42256,7 @@
         <v>522</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3294</v>
+        <v>3289</v>
       </c>
       <c r="I22" s="276" t="s">
         <v>2974</v>
@@ -42286,10 +42285,10 @@
         <v>522</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3289</v>
+        <v>3284</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3290</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42303,7 +42302,7 @@
         <v>2567</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3654</v>
+        <v>3649</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>976</v>
@@ -42315,10 +42314,10 @@
         <v>522</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3245</v>
+        <v>3240</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3478</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42328,7 +42327,7 @@
         <v>2582</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3537</v>
+        <v>3532</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>976</v>
@@ -42516,13 +42515,13 @@
         <v>2600</v>
       </c>
       <c r="B4" t="s">
-        <v>3617</v>
+        <v>3612</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1929</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3616</v>
+        <v>3611</v>
       </c>
       <c r="E4" t="s">
         <v>1930</v>
@@ -42534,10 +42533,10 @@
         <v>980</v>
       </c>
       <c r="H4" t="s">
-        <v>3635</v>
-      </c>
-      <c r="I4" s="446" t="s">
-        <v>3645</v>
+        <v>3630</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>3640</v>
       </c>
       <c r="J4" s="97"/>
     </row>
@@ -42587,10 +42586,10 @@
         <v>980</v>
       </c>
       <c r="H6" t="s">
-        <v>3155</v>
+        <v>3663</v>
       </c>
       <c r="I6" t="s">
-        <v>3592</v>
+        <v>3587</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2322</v>
@@ -42625,7 +42624,7 @@
         <v>3064</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3527</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42633,73 +42632,73 @@
         <v>2576</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>3307</v>
+        <v>3302</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>3304</v>
+        <v>3299</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>3303</v>
+        <v>3298</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>3305</v>
+        <v>3300</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>3306</v>
+        <v>3301</v>
       </c>
       <c r="G8" t="s">
         <v>980</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3536</v>
+        <v>3531</v>
       </c>
       <c r="I8" s="279"/>
       <c r="J8" s="10" t="s">
-        <v>3547</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>3551</v>
+        <v>3546</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>3552</v>
+        <v>3547</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>3549</v>
+        <v>3544</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>3303</v>
+        <v>3298</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3550</v>
+        <v>3545</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>3306</v>
+        <v>3301</v>
       </c>
       <c r="G9" t="s">
         <v>980</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>3553</v>
+        <v>3548</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3554</v>
+        <v>3549</v>
       </c>
       <c r="J9" t="s">
-        <v>3612</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="279"/>
       <c r="C10" s="3" t="s">
-        <v>3632</v>
+        <v>3627</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3633</v>
+        <v>3628</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3634</v>
+        <v>3629</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2396</v>
@@ -42870,7 +42869,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -42879,7 +42878,7 @@
         <v>1849</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3509</v>
+        <v>3504</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2802</v>
@@ -42920,7 +42919,7 @@
         <v>65124748</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3374</v>
+        <v>3369</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2829</v>
@@ -42941,7 +42940,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3405</v>
+        <v>3400</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2829</v>
@@ -43117,7 +43116,7 @@
     <row r="1" spans="1:9" s="422" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="421"/>
       <c r="B1" s="421" t="s">
-        <v>3393</v>
+        <v>3388</v>
       </c>
       <c r="C1" s="421"/>
     </row>
@@ -43126,25 +43125,25 @@
         <v>148</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3456</v>
+        <v>3451</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3620</v>
+        <v>3615</v>
       </c>
       <c r="E4" t="s">
-        <v>3394</v>
+        <v>3389</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3621</v>
+        <v>3616</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>3408</v>
+        <v>3403</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3597</v>
+        <v>3592</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3614</v>
+        <v>3609</v>
       </c>
     </row>
   </sheetData>
@@ -43490,7 +43489,7 @@
         <v>2727</v>
       </c>
       <c r="C5" s="328" t="s">
-        <v>3242</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="328" customFormat="1">
@@ -43498,10 +43497,10 @@
         <v>2706</v>
       </c>
       <c r="B6" s="328" t="s">
-        <v>3241</v>
+        <v>3236</v>
       </c>
       <c r="C6" s="328" t="s">
-        <v>3241</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="328" customFormat="1">
@@ -43576,10 +43575,10 @@
         <v>2736</v>
       </c>
       <c r="H14" s="334" t="s">
-        <v>3249</v>
+        <v>3244</v>
       </c>
       <c r="I14" s="334" t="s">
-        <v>3252</v>
+        <v>3247</v>
       </c>
       <c r="L14" s="334"/>
       <c r="M14" s="334"/>
@@ -43607,10 +43606,10 @@
         <v>2737</v>
       </c>
       <c r="H15" s="335" t="s">
-        <v>3250</v>
+        <v>3245</v>
       </c>
       <c r="I15" s="335" t="s">
-        <v>3253</v>
+        <v>3248</v>
       </c>
       <c r="L15" s="335"/>
       <c r="M15" s="335"/>
@@ -43638,7 +43637,7 @@
         <v>2738</v>
       </c>
       <c r="H16" s="335" t="s">
-        <v>3251</v>
+        <v>3246</v>
       </c>
       <c r="I16" s="335" t="s">
         <v>1381</v>
@@ -43651,7 +43650,7 @@
         <v>2711</v>
       </c>
       <c r="B17" s="407" t="s">
-        <v>3238</v>
+        <v>3233</v>
       </c>
       <c r="C17" s="407"/>
       <c r="D17" s="407"/>
@@ -43668,7 +43667,7 @@
         <v>2706</v>
       </c>
       <c r="B18" s="407" t="s">
-        <v>3239</v>
+        <v>3234</v>
       </c>
       <c r="C18" s="407"/>
       <c r="D18" s="407"/>
@@ -43685,7 +43684,7 @@
         <v>2707</v>
       </c>
       <c r="B19" s="407" t="s">
-        <v>3240</v>
+        <v>3235</v>
       </c>
       <c r="C19" s="407"/>
       <c r="D19" s="407"/>
@@ -44643,10 +44642,10 @@
         <v>160</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3260</v>
+        <v>3255</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3178</v>
+        <v>3173</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>828</v>
@@ -44654,7 +44653,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3354</v>
+        <v>3349</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44675,10 +44674,10 @@
         <v>247</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3284</v>
+        <v>3279</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44704,10 +44703,10 @@
         <v>247</v>
       </c>
       <c r="H11" t="s">
-        <v>3357</v>
+        <v>3352</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3363</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44733,10 +44732,10 @@
         <v>247</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3390</v>
+        <v>3385</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3447</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44762,10 +44761,10 @@
         <v>247</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3376</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44791,25 +44790,25 @@
         <v>247</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3322</v>
+        <v>3317</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3339</v>
+        <v>3334</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="105" t="s">
-        <v>3221</v>
+        <v>3216</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3222</v>
+        <v>3217</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>343</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>3220</v>
+        <v>3215</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>1584</v>
@@ -44821,10 +44820,10 @@
         <v>901</v>
       </c>
       <c r="H15" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="I15" t="s">
-        <v>3496</v>
+        <v>3491</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>503</v>
@@ -44841,7 +44840,7 @@
         <v>2784</v>
       </c>
       <c r="D16" t="s">
-        <v>3198</v>
+        <v>3193</v>
       </c>
       <c r="E16" t="s">
         <v>2786</v>
@@ -44853,10 +44852,10 @@
         <v>160</v>
       </c>
       <c r="H16" t="s">
-        <v>3271</v>
+        <v>3266</v>
       </c>
       <c r="I16" t="s">
-        <v>3199</v>
+        <v>3194</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>817</v>
@@ -44899,19 +44898,19 @@
         <v>2309</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3352</v>
+        <v>3347</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3353</v>
+        <v>3348</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>247</v>
       </c>
       <c r="H18" t="s">
-        <v>3567</v>
+        <v>3562</v>
       </c>
       <c r="I18" t="s">
-        <v>3345</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44922,13 +44921,13 @@
         <v>64403333</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="D19" t="s">
         <v>2785</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>2616</v>
@@ -44941,7 +44940,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3217</v>
+        <v>3212</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45034,7 +45033,7 @@
         <v>160</v>
       </c>
       <c r="H23" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="I23" s="308" t="s">
         <v>2744</v>
@@ -45052,10 +45051,10 @@
         <v>1689</v>
       </c>
       <c r="D24" t="s">
-        <v>3596</v>
+        <v>3591</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3598</v>
+        <v>3593</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2616</v>
@@ -45078,7 +45077,7 @@
         <v>2102</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3488</v>
+        <v>3483</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2622</v>
@@ -45116,7 +45115,7 @@
         <v>247</v>
       </c>
       <c r="H26" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="I26" t="s">
         <v>3009</v>
@@ -45124,10 +45123,10 @@
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
       <c r="A27" t="s">
-        <v>2638</v>
+        <v>2678</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>370</v>
@@ -45145,10 +45144,10 @@
         <v>160</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3359</v>
+        <v>3354</v>
       </c>
       <c r="I27" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>825</v>
@@ -45156,7 +45155,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3364</v>
+        <v>3359</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2609</v>
@@ -45168,7 +45167,7 @@
         <v>2103</v>
       </c>
       <c r="E28" t="s">
-        <v>3613</v>
+        <v>3608</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2622</v>
@@ -45180,7 +45179,7 @@
         <v>2853</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3261</v>
+        <v>3256</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45195,10 +45194,10 @@
         <v>353</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>3266</v>
+        <v>3261</v>
       </c>
       <c r="E29" t="s">
-        <v>3206</v>
+        <v>3201</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2622</v>
@@ -45207,26 +45206,26 @@
         <v>253</v>
       </c>
       <c r="H29" t="s">
-        <v>3267</v>
+        <v>3262</v>
       </c>
       <c r="I29" t="s">
-        <v>3181</v>
+        <v>3176</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3560</v>
+        <v>3555</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>407</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3559</v>
+        <v>3554</v>
       </c>
       <c r="E30" t="s">
         <v>2499</v>
@@ -45238,7 +45237,7 @@
         <v>160</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3564</v>
+        <v>3559</v>
       </c>
       <c r="I30" t="s">
         <v>2999</v>
@@ -45246,7 +45245,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3221</v>
+        <v>3216</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45267,10 +45266,10 @@
         <v>160</v>
       </c>
       <c r="H31" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3154</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45296,7 +45295,7 @@
         <v>160</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3468</v>
+        <v>3463</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2977</v>
@@ -45325,10 +45324,10 @@
         <v>160</v>
       </c>
       <c r="H33" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="I33" t="s">
-        <v>3498</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45357,7 +45356,7 @@
         <v>2788</v>
       </c>
       <c r="I34" t="s">
-        <v>3169</v>
+        <v>3164</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45366,13 +45365,13 @@
         <v>148</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3428</v>
+        <v>3423</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2781</v>
       </c>
       <c r="D35" t="s">
-        <v>3427</v>
+        <v>3422</v>
       </c>
       <c r="E35" t="s">
         <v>2786</v>
@@ -45384,10 +45383,10 @@
         <v>2789</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3473</v>
+        <v>3468</v>
       </c>
       <c r="I35" t="s">
-        <v>3486</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -45424,13 +45423,13 @@
         <v>2638</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3164</v>
+        <v>3159</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2796</v>
       </c>
       <c r="D37" t="s">
-        <v>3336</v>
+        <v>3331</v>
       </c>
       <c r="E37" t="s">
         <v>2798</v>
@@ -45442,10 +45441,10 @@
         <v>160</v>
       </c>
       <c r="H37" t="s">
-        <v>3337</v>
+        <v>3332</v>
       </c>
       <c r="I37" t="s">
-        <v>3415</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45453,7 +45452,7 @@
         <v>158</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3579</v>
+        <v>3574</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2797</v>
@@ -45507,10 +45506,10 @@
         <v>2684</v>
       </c>
       <c r="J45" s="49" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="K45" t="s">
-        <v>3410</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45916,13 +45915,13 @@
         <v>158</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3582</v>
+        <v>3577</v>
       </c>
       <c r="C2" s="277" t="s">
         <v>257</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3581</v>
+        <v>3576</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1334</v>
@@ -45934,16 +45933,16 @@
         <v>62</v>
       </c>
       <c r="H2" s="301" t="s">
-        <v>3628</v>
+        <v>3623</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3595</v>
+        <v>3590</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3379</v>
+        <v>3374</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3344</v>
+        <v>3339</v>
       </c>
       <c r="M2" s="159"/>
     </row>
@@ -45973,13 +45972,13 @@
         <v>3043</v>
       </c>
       <c r="I4" s="217" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3358</v>
+        <v>3353</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="M4" s="39"/>
     </row>
@@ -46006,10 +46005,10 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3244</v>
+        <v>3239</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>3435</v>
+        <v>3430</v>
       </c>
       <c r="J5" s="145"/>
       <c r="K5" s="217" t="s">
@@ -46040,13 +46039,13 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3472</v>
+        <v>3467</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3587</v>
+        <v>3582</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3165</v>
+        <v>3160</v>
       </c>
       <c r="K6" s="30" t="s">
         <v>3056</v>
@@ -46076,16 +46075,16 @@
         <v>731</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3448</v>
+        <v>3443</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>2871</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3474</v>
+        <v>3469</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46112,13 +46111,13 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3362</v>
+        <v>3357</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3545</v>
+        <v>3540</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3375</v>
+        <v>3370</v>
       </c>
       <c r="K8" s="278" t="s">
         <v>2943</v>
@@ -46148,16 +46147,16 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3496</v>
+        <v>3491</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3531</v>
+        <v>3526</v>
       </c>
       <c r="J9" s="217" t="s">
         <v>2909</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3499</v>
+        <v>3494</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -46184,22 +46183,22 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="I10" s="49" t="s">
         <v>2946</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3285</v>
+        <v>3280</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3532</v>
+        <v>3527</v>
       </c>
       <c r="M10" s="34"/>
     </row>
     <row r="11" spans="1:13" s="30" customFormat="1">
       <c r="A11" s="107" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B11" s="107">
         <v>62657225</v>
@@ -46220,16 +46219,16 @@
         <v>610</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3155</v>
+        <v>3663</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3355</v>
+        <v>3350</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3469</v>
+        <v>3464</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -46244,7 +46243,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3226</v>
+        <v>3221</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>922</v>
@@ -46256,16 +46255,16 @@
         <v>248</v>
       </c>
       <c r="H12" s="106" t="s">
-        <v>3351</v>
+        <v>3346</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3338</v>
+        <v>3333</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3273</v>
+        <v>3268</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3225</v>
+        <v>3220</v>
       </c>
       <c r="M12" s="151"/>
     </row>
@@ -46280,7 +46279,7 @@
         <v>933</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3647</v>
+        <v>3642</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>3013</v>
@@ -46291,14 +46290,14 @@
       <c r="G13" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="442" t="s">
-        <v>3648</v>
+      <c r="H13" s="30" t="s">
+        <v>3643</v>
       </c>
       <c r="I13" s="145" t="s">
-        <v>3649</v>
+        <v>3644</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="K13" t="s">
         <v>3010</v>
@@ -46328,7 +46327,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3397</v>
+        <v>3392</v>
       </c>
       <c r="I14" s="424" t="s">
         <v>2365</v>
@@ -46361,16 +46360,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3323</v>
+        <v>3318</v>
       </c>
       <c r="I15" t="s">
-        <v>3591</v>
+        <v>3586</v>
       </c>
       <c r="J15" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3487</v>
+        <v>3482</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46422,16 +46421,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3600</v>
+        <v>3595</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3444</v>
+        <v>3439</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3262</v>
+        <v>3257</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46458,16 +46457,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3580</v>
+        <v>3575</v>
       </c>
       <c r="I18" t="s">
         <v>3063</v>
       </c>
       <c r="J18" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="K18" t="s">
-        <v>3398</v>
+        <v>3393</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46494,16 +46493,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3607</v>
+        <v>3602</v>
       </c>
       <c r="I19" t="s">
-        <v>3386</v>
+        <v>3381</v>
       </c>
       <c r="J19" s="220" t="s">
         <v>3016</v>
       </c>
       <c r="K19" t="s">
-        <v>3544</v>
+        <v>3539</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46518,7 +46517,7 @@
         <v>2643</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3519</v>
+        <v>3514</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2548</v>
@@ -46530,16 +46529,16 @@
         <v>65</v>
       </c>
       <c r="H20" s="318" t="s">
-        <v>3274</v>
+        <v>3269</v>
       </c>
       <c r="I20" t="s">
-        <v>3520</v>
+        <v>3515</v>
       </c>
       <c r="J20" t="s">
-        <v>3522</v>
+        <v>3517</v>
       </c>
       <c r="K20" t="s">
-        <v>3563</v>
+        <v>3558</v>
       </c>
       <c r="M20" s="36"/>
     </row>
@@ -46699,7 +46698,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46747,7 +46746,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46809,10 +46808,10 @@
         <v>2227</v>
       </c>
       <c r="E39" s="140" t="s">
-        <v>3332</v>
+        <v>3327</v>
       </c>
       <c r="F39" s="140" t="s">
-        <v>3333</v>
+        <v>3328</v>
       </c>
       <c r="G39" s="106" t="s">
         <v>731</v>
@@ -46868,7 +46867,7 @@
         <v>2945</v>
       </c>
       <c r="B45" t="s">
-        <v>3185</v>
+        <v>3180</v>
       </c>
       <c r="C45" t="s">
         <v>2680</v>
@@ -46877,7 +46876,7 @@
         <v>2681</v>
       </c>
       <c r="E45" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2682</v>
@@ -46889,10 +46888,10 @@
         <v>3004</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3170</v>
+        <v>3165</v>
       </c>
       <c r="J45" t="s">
-        <v>3431</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47648,7 +47647,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="45" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -47784,7 +47783,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>3295</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -47793,7 +47792,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3530</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48045,7 +48044,7 @@
         <v>144</v>
       </c>
       <c r="B6" s="248" t="s">
-        <v>3343</v>
+        <v>3338</v>
       </c>
       <c r="C6" s="247" t="s">
         <v>1326</v>
@@ -48063,13 +48062,13 @@
         <v>360</v>
       </c>
       <c r="H6" s="248" t="s">
-        <v>3177</v>
+        <v>3172</v>
       </c>
       <c r="I6" s="245" t="s">
-        <v>3356</v>
+        <v>3351</v>
       </c>
       <c r="J6" s="296" t="s">
-        <v>3420</v>
+        <v>3415</v>
       </c>
       <c r="K6" s="248" t="s">
         <v>480</v>
@@ -48097,19 +48096,19 @@
         <v>1055</v>
       </c>
       <c r="F8" s="266" t="s">
-        <v>3162</v>
+        <v>3157</v>
       </c>
       <c r="G8" s="266" t="s">
         <v>696</v>
       </c>
       <c r="H8" s="296" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>3540</v>
+        <v>3535</v>
       </c>
       <c r="J8" s="266" t="s">
-        <v>3286</v>
+        <v>3281</v>
       </c>
       <c r="K8" s="266" t="s">
         <v>717</v>
@@ -48138,10 +48137,10 @@
         <v>253</v>
       </c>
       <c r="H9" s="106" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="I9" s="106" t="s">
-        <v>3261</v>
+        <v>3256</v>
       </c>
       <c r="J9" s="106" t="s">
         <v>2308</v>
@@ -48164,7 +48163,7 @@
         <v>1454</v>
       </c>
       <c r="F10" s="264" t="s">
-        <v>3189</v>
+        <v>3184</v>
       </c>
       <c r="G10" s="264" t="s">
         <v>962</v>
@@ -48196,13 +48195,13 @@
         <v>696</v>
       </c>
       <c r="H11" s="265" t="s">
-        <v>3500</v>
+        <v>3495</v>
       </c>
       <c r="I11" s="296" t="s">
-        <v>3492</v>
+        <v>3487</v>
       </c>
       <c r="J11" s="265" t="s">
-        <v>3391</v>
+        <v>3386</v>
       </c>
       <c r="K11" s="246" t="s">
         <v>1239</v>
@@ -48231,13 +48230,13 @@
         <v>696</v>
       </c>
       <c r="H12" s="215" t="s">
-        <v>3521</v>
+        <v>3516</v>
       </c>
       <c r="I12" s="215" t="s">
-        <v>3190</v>
+        <v>3185</v>
       </c>
       <c r="J12" s="270" t="s">
-        <v>3426</v>
+        <v>3421</v>
       </c>
       <c r="K12" s="183" t="s">
         <v>1240</v>
@@ -48274,7 +48273,7 @@
         <v>2959</v>
       </c>
       <c r="B14" s="224" t="s">
-        <v>3585</v>
+        <v>3580</v>
       </c>
       <c r="C14" s="438" t="s">
         <v>338</v>
@@ -48283,22 +48282,22 @@
         <v>2525</v>
       </c>
       <c r="E14" s="224" t="s">
-        <v>3577</v>
+        <v>3572</v>
       </c>
       <c r="F14" s="224" t="s">
-        <v>3576</v>
+        <v>3571</v>
       </c>
       <c r="G14" s="224" t="s">
         <v>696</v>
       </c>
       <c r="H14" s="224" t="s">
-        <v>3583</v>
+        <v>3578</v>
       </c>
       <c r="I14" s="224" t="s">
-        <v>3584</v>
+        <v>3579</v>
       </c>
       <c r="J14" s="224" t="s">
-        <v>3586</v>
+        <v>3581</v>
       </c>
       <c r="K14" s="224" t="s">
         <v>1357</v>
@@ -48318,7 +48317,7 @@
         <v>2041</v>
       </c>
       <c r="E15" s="216" t="s">
-        <v>3162</v>
+        <v>3157</v>
       </c>
       <c r="F15" s="216" t="s">
         <v>1478</v>
@@ -48327,13 +48326,13 @@
         <v>696</v>
       </c>
       <c r="H15" s="273" t="s">
-        <v>3512</v>
+        <v>3507</v>
       </c>
       <c r="I15" s="215" t="s">
-        <v>3470</v>
+        <v>3465</v>
       </c>
       <c r="J15" s="263" t="s">
-        <v>3156</v>
+        <v>3664</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1241</v>
@@ -48344,13 +48343,13 @@
         <v>1460</v>
       </c>
       <c r="B16" s="265" t="s">
-        <v>3477</v>
+        <v>3472</v>
       </c>
       <c r="C16" s="271" t="s">
         <v>1343</v>
       </c>
       <c r="D16" s="260" t="s">
-        <v>3440</v>
+        <v>3435</v>
       </c>
       <c r="E16" s="260" t="s">
         <v>3027</v>
@@ -48362,13 +48361,13 @@
         <v>696</v>
       </c>
       <c r="H16" s="265" t="s">
-        <v>3475</v>
+        <v>3470</v>
       </c>
       <c r="I16" s="272" t="s">
-        <v>3310</v>
+        <v>3305</v>
       </c>
       <c r="J16" s="265" t="s">
-        <v>3441</v>
+        <v>3436</v>
       </c>
       <c r="K16" s="260" t="s">
         <v>1484</v>
@@ -48441,7 +48440,7 @@
         <v>696</v>
       </c>
       <c r="J19" s="265" t="s">
-        <v>3254</v>
+        <v>3249</v>
       </c>
       <c r="K19" s="265" t="s">
         <v>1701</v>
@@ -48470,7 +48469,7 @@
         <v>696</v>
       </c>
       <c r="I20" s="260" t="s">
-        <v>3380</v>
+        <v>3375</v>
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="265" t="s">
@@ -48500,13 +48499,13 @@
         <v>696</v>
       </c>
       <c r="H21" s="260" t="s">
-        <v>3445</v>
+        <v>3440</v>
       </c>
       <c r="I21" s="265" t="s">
         <v>3015</v>
       </c>
       <c r="J21" s="260" t="s">
-        <v>3334</v>
+        <v>3329</v>
       </c>
       <c r="K21" s="265" t="s">
         <v>1828</v>
@@ -48514,7 +48513,7 @@
     </row>
     <row r="22" spans="1:11" s="260" customFormat="1">
       <c r="A22" s="246" t="s">
-        <v>3272</v>
+        <v>3267</v>
       </c>
       <c r="B22" s="260" t="s">
         <v>2512</v>
@@ -48541,7 +48540,7 @@
         <v>2978</v>
       </c>
       <c r="J22" s="260" t="s">
-        <v>3605</v>
+        <v>3600</v>
       </c>
       <c r="K22" s="260" t="s">
         <v>1873</v>
@@ -48573,10 +48572,10 @@
         <v>3039</v>
       </c>
       <c r="I24" s="265" t="s">
-        <v>3361</v>
+        <v>3356</v>
       </c>
       <c r="J24" s="265" t="s">
-        <v>3330</v>
+        <v>3325</v>
       </c>
       <c r="K24" s="260" t="s">
         <v>1875</v>
@@ -48617,7 +48616,7 @@
         <v>642</v>
       </c>
       <c r="D27" s="256" t="s">
-        <v>3568</v>
+        <v>3563</v>
       </c>
       <c r="E27" s="272" t="s">
         <v>2529</v>
@@ -48629,7 +48628,7 @@
         <v>714</v>
       </c>
       <c r="H27" s="260" t="s">
-        <v>3567</v>
+        <v>3562</v>
       </c>
       <c r="I27" s="145"/>
       <c r="J27" s="145"/>
@@ -48639,7 +48638,7 @@
         <v>853</v>
       </c>
       <c r="D29" s="265" t="s">
-        <v>3513</v>
+        <v>3508</v>
       </c>
       <c r="E29" s="260" t="s">
         <v>1851</v>
@@ -49020,13 +49019,13 @@
         <v>3058</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3186</v>
+        <v>3181</v>
       </c>
       <c r="I2" t="s">
-        <v>3291</v>
+        <v>3286</v>
       </c>
       <c r="J2" t="s">
-        <v>3422</v>
+        <v>3417</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1207</v>
@@ -49052,7 +49051,7 @@
         <v>301</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3167</v>
+        <v>3162</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>715</v>
@@ -49078,25 +49077,25 @@
         <v>316</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3413</v>
+        <v>3408</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3506</v>
+        <v>3501</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>326</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3360</v>
+        <v>3355</v>
       </c>
       <c r="H4" t="s">
-        <v>3573</v>
+        <v>3568</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3421</v>
+        <v>3416</v>
       </c>
       <c r="J4" t="s">
-        <v>3414</v>
+        <v>3409</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>325</v>
@@ -49104,7 +49103,7 @@
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1">
       <c r="A5" s="4" t="s">
-        <v>3287</v>
+        <v>3282</v>
       </c>
       <c r="B5" s="4">
         <v>64720128</v>
@@ -49122,13 +49121,13 @@
         <v>429</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3578</v>
+        <v>3573</v>
       </c>
       <c r="H5" t="s">
         <v>2997</v>
       </c>
       <c r="I5" s="75" t="s">
-        <v>3184</v>
+        <v>3179</v>
       </c>
       <c r="J5" s="220" t="s">
         <v>2805</v>
@@ -49146,25 +49145,25 @@
         <v>330</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>3316</v>
+        <v>3311</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>3315</v>
+        <v>3310</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>167</v>
       </c>
       <c r="G6" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3449</v>
+        <v>3444</v>
       </c>
       <c r="I6" t="s">
-        <v>3214</v>
+        <v>3209</v>
       </c>
       <c r="J6" t="s">
-        <v>3317</v>
+        <v>3312</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>428</v>
@@ -49190,13 +49189,13 @@
         <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>3379</v>
+        <v>3374</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3288</v>
+        <v>3283</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3610</v>
+        <v>3605</v>
       </c>
       <c r="J7" s="49" t="s">
         <v>2979</v>
@@ -49207,10 +49206,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3354</v>
+        <v>3349</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3451</v>
+        <v>3446</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>664</v>
@@ -49228,10 +49227,10 @@
         <v>2857</v>
       </c>
       <c r="H8" t="s">
-        <v>3377</v>
+        <v>3372</v>
       </c>
       <c r="I8" t="s">
-        <v>3487</v>
+        <v>3482</v>
       </c>
       <c r="J8" t="s">
         <v>3055</v>
@@ -49258,16 +49257,16 @@
         <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>3155</v>
-      </c>
-      <c r="H9" s="443" t="s">
-        <v>3655</v>
+        <v>3663</v>
+      </c>
+      <c r="H9" s="220" t="s">
+        <v>3650</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3450</v>
-      </c>
-      <c r="J9" s="443" t="s">
-        <v>3641</v>
+        <v>3445</v>
+      </c>
+      <c r="J9" s="220" t="s">
+        <v>3636</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49281,7 +49280,7 @@
         <v>2288</v>
       </c>
       <c r="D10" t="s">
-        <v>3523</v>
+        <v>3518</v>
       </c>
       <c r="E10" t="s">
         <v>2258</v>
@@ -49290,16 +49289,16 @@
         <v>1881</v>
       </c>
       <c r="G10" t="s">
-        <v>3168</v>
+        <v>3163</v>
       </c>
       <c r="H10" t="s">
-        <v>3372</v>
+        <v>3367</v>
       </c>
       <c r="I10" t="s">
-        <v>3201</v>
+        <v>3196</v>
       </c>
       <c r="J10" t="s">
-        <v>3195</v>
+        <v>3190</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>2289</v>
@@ -49376,7 +49375,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="49" t="s">
-        <v>3562</v>
+        <v>3557</v>
       </c>
       <c r="B15">
         <v>69184177</v>
@@ -49414,16 +49413,16 @@
         <v>152</v>
       </c>
       <c r="G16" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="H16" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="I16" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="J16" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -49659,7 +49658,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3541</v>
+        <v>3536</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49680,7 +49679,7 @@
         <v>67129610</v>
       </c>
       <c r="C8" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="D8" t="s">
         <v>2967</v>
@@ -49703,7 +49702,7 @@
         <v>1606</v>
       </c>
       <c r="E9" t="s">
-        <v>3335</v>
+        <v>3330</v>
       </c>
       <c r="F9" t="s">
         <v>1793</v>
@@ -49723,7 +49722,7 @@
         <v>2306</v>
       </c>
       <c r="E10" t="s">
-        <v>3324</v>
+        <v>3319</v>
       </c>
       <c r="F10" t="s">
         <v>1742</v>
@@ -49743,7 +49742,7 @@
         <v>2133</v>
       </c>
       <c r="E11" t="s">
-        <v>3561</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49760,7 +49759,7 @@
         <v>2900</v>
       </c>
       <c r="E12" t="s">
-        <v>3255</v>
+        <v>3250</v>
       </c>
       <c r="F12" t="s">
         <v>1742</v>
@@ -49768,7 +49767,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3207</v>
+        <v>3202</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49780,10 +49779,10 @@
         <v>2518</v>
       </c>
       <c r="E13" t="s">
-        <v>3395</v>
+        <v>3390</v>
       </c>
       <c r="F13" t="s">
-        <v>3396</v>
+        <v>3391</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -49797,7 +49796,7 @@
         <v>2004</v>
       </c>
       <c r="D14" t="s">
-        <v>3529</v>
+        <v>3524</v>
       </c>
       <c r="E14" t="s">
         <v>2858</v>
@@ -49820,7 +49819,7 @@
         <v>1796</v>
       </c>
       <c r="E15" t="s">
-        <v>3209</v>
+        <v>3204</v>
       </c>
       <c r="F15" t="s">
         <v>2904</v>
@@ -49837,10 +49836,10 @@
         <v>2966</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>3570</v>
+        <v>3565</v>
       </c>
       <c r="E16" t="s">
-        <v>3571</v>
+        <v>3566</v>
       </c>
       <c r="F16" t="s">
         <v>2904</v>
@@ -49848,19 +49847,19 @@
     </row>
     <row r="17" spans="1:7" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3354</v>
+        <v>3349</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>3430</v>
+        <v>3425</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>3589</v>
+        <v>3584</v>
       </c>
       <c r="E17" t="s">
-        <v>3590</v>
+        <v>3585</v>
       </c>
       <c r="F17" t="s">
         <v>2904</v>
@@ -49870,7 +49869,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" s="30" customFormat="1">
-      <c r="A18" s="442" t="s">
+      <c r="A18" s="30" t="s">
         <v>2648</v>
       </c>
       <c r="B18" s="30">
@@ -49883,7 +49882,7 @@
         <v>2970</v>
       </c>
       <c r="E18" t="s">
-        <v>3590</v>
+        <v>3585</v>
       </c>
       <c r="F18" t="s">
         <v>2904</v>
@@ -49891,7 +49890,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="B21">
         <v>64245493</v>
@@ -49962,7 +49961,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -49974,13 +49973,13 @@
         <v>2875</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3542</v>
+        <v>3537</v>
       </c>
       <c r="F26" t="s">
-        <v>3543</v>
+        <v>3538</v>
       </c>
       <c r="G26" t="s">
-        <v>3555</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -49997,13 +49996,13 @@
         <v>426</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3542</v>
+        <v>3537</v>
       </c>
       <c r="F27" t="s">
-        <v>3577</v>
+        <v>3572</v>
       </c>
       <c r="G27" t="s">
-        <v>3619</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -50019,7 +50018,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>3434</v>
+        <v>3429</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50031,10 +50030,10 @@
         <v>2903</v>
       </c>
       <c r="E30" t="s">
-        <v>3556</v>
+        <v>3551</v>
       </c>
       <c r="F30" t="s">
-        <v>3557</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="307" customFormat="1" ht="15.5">
@@ -50140,10 +50139,10 @@
         <v>2668</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>3256</v>
+        <v>3251</v>
       </c>
       <c r="F47" s="408" t="s">
-        <v>3257</v>
+        <v>3252</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>412</v>
@@ -50239,12 +50238,12 @@
     </row>
     <row r="60" spans="1:5" s="403" customFormat="1" ht="18">
       <c r="C60" s="403" t="s">
-        <v>3215</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="30" t="s">
-        <v>3163</v>
+        <v>3158</v>
       </c>
       <c r="B61" s="30">
         <v>65036571</v>
@@ -50256,7 +50255,7 @@
         <v>2676</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3216</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="76" customFormat="1">
@@ -52098,7 +52097,7 @@
     </row>
     <row r="252" spans="1:6" s="433" customFormat="1" ht="21">
       <c r="C252" s="433" t="s">
-        <v>3504</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -52115,30 +52114,30 @@
         <v>2342</v>
       </c>
       <c r="E253" t="s">
-        <v>3502</v>
+        <v>3497</v>
       </c>
       <c r="F253" t="s">
-        <v>3503</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>3417</v>
+        <v>3412</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>3419</v>
+        <v>3414</v>
       </c>
       <c r="D254" t="s">
-        <v>3416</v>
+        <v>3411</v>
       </c>
       <c r="E254" t="s">
-        <v>3502</v>
+        <v>3497</v>
       </c>
       <c r="F254" t="s">
-        <v>3503</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52149,16 +52148,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>3418</v>
+        <v>3413</v>
       </c>
       <c r="D255" s="252" t="s">
         <v>2837</v>
       </c>
       <c r="E255" t="s">
-        <v>3502</v>
+        <v>3497</v>
       </c>
       <c r="F255" t="s">
-        <v>3503</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -55549,7 +55548,7 @@
         <v>1379</v>
       </c>
       <c r="D456" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="E456" s="76" t="s">
         <v>1456</v>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60008" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBD3AE93-3199-49E7-873F-DEDA2EC0AE37}"/>
+  <xr:revisionPtr revIDLastSave="60084" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB12F33-2D1D-4EF6-863A-BE3F67FE767C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,6 +63,7 @@
     <author>tc={40F52014-4F67-4B56-99C7-26BB3092ADF1}</author>
     <author>tc={E742BF3C-66AD-4EAB-B9A3-3B5BDA53496E}</author>
     <author>tc={42704FC5-7F73-4867-BAB8-0CBC858CB363}</author>
+    <author>tc={DA8DAF0D-B0F6-41A4-BEF1-65B0D0110B01}</author>
     <author>tc={63325648-98C5-43A5-B0A0-BE3F1931179F}</author>
     <author>tc={D74A6BC7-C936-4D18-B207-7662524F2FF1}</author>
     <author>tc={A3C653E5-B008-4D78-A9B3-C292CBCE6481}</author>
@@ -108,7 +109,15 @@
     https://netflix-server-a9i0.onrender.com/cliente/250826-0420x</t>
       </text>
     </comment>
-    <comment ref="K64" authorId="4" shapeId="0" xr:uid="{63325648-98C5-43A5-B0A0-BE3F1931179F}">
+    <comment ref="I61" authorId="4" shapeId="0" xr:uid="{DA8DAF0D-B0F6-41A4-BEF1-65B0D0110B01}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    https://netflix-server-a9i0.onrender.com/cliente/280826-1051g</t>
+      </text>
+    </comment>
+    <comment ref="K64" authorId="5" shapeId="0" xr:uid="{63325648-98C5-43A5-B0A0-BE3F1931179F}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,7 +125,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/200826-1844</t>
       </text>
     </comment>
-    <comment ref="H67" authorId="5" shapeId="0" xr:uid="{D74A6BC7-C936-4D18-B207-7662524F2FF1}">
+    <comment ref="H67" authorId="6" shapeId="0" xr:uid="{D74A6BC7-C936-4D18-B207-7662524F2FF1}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -124,7 +133,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/64242340-marisol</t>
       </text>
     </comment>
-    <comment ref="K67" authorId="6" shapeId="0" xr:uid="{A3C653E5-B008-4D78-A9B3-C292CBCE6481}">
+    <comment ref="K67" authorId="7" shapeId="0" xr:uid="{A3C653E5-B008-4D78-A9B3-C292CBCE6481}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -132,7 +141,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/180826-2044</t>
       </text>
     </comment>
-    <comment ref="J70" authorId="7" shapeId="0" xr:uid="{76A385E1-B49D-4CB9-9F2C-60615C4FA65C}">
+    <comment ref="J70" authorId="8" shapeId="0" xr:uid="{76A385E1-B49D-4CB9-9F2C-60615C4FA65C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -140,7 +149,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/60957473-jose</t>
       </text>
     </comment>
-    <comment ref="I76" authorId="8" shapeId="0" xr:uid="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
+    <comment ref="I76" authorId="9" shapeId="0" xr:uid="{263CFA38-6940-48E3-8C6D-4FD90BA5C72C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +157,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/150826-2208</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="9" shapeId="0" xr:uid="{2DA6ACCC-7F6B-4F63-9F66-2022723D557F}">
+    <comment ref="J79" authorId="10" shapeId="0" xr:uid="{2DA6ACCC-7F6B-4F63-9F66-2022723D557F}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -156,7 +165,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68582631-melanie</t>
       </text>
     </comment>
-    <comment ref="J88" authorId="10" shapeId="0" xr:uid="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
+    <comment ref="J88" authorId="11" shapeId="0" xr:uid="{2C80CEB1-D520-47E4-8891-F2B7A2059B85}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -164,7 +173,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/200826-2043</t>
       </text>
     </comment>
-    <comment ref="K88" authorId="11" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
+    <comment ref="K88" authorId="12" shapeId="0" xr:uid="{A1BAE17A-7373-4E96-9A79-0A588580086C}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -172,7 +181,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/69645877-yimara</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="12" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
+    <comment ref="H91" authorId="13" shapeId="0" xr:uid="{6CB69787-04DC-427D-92C4-EA68685283A6}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -180,7 +189,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68131498-melanie</t>
       </text>
     </comment>
-    <comment ref="J97" authorId="13" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
+    <comment ref="J97" authorId="14" shapeId="0" xr:uid="{D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -188,7 +197,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/67208668-n005</t>
       </text>
     </comment>
-    <comment ref="K97" authorId="14" shapeId="0" xr:uid="{A3554D91-2D1C-4186-8090-CCD5996EDC8F}">
+    <comment ref="K97" authorId="15" shapeId="0" xr:uid="{A3554D91-2D1C-4186-8090-CCD5996EDC8F}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1311,7 +1320,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6264" uniqueCount="3668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6273" uniqueCount="3674">
   <si>
     <t>shopfreefire.1.21.2@gmail.com</t>
   </si>
@@ -10187,9 +10196,6 @@
     <t>13 de septiembre</t>
   </si>
   <si>
-    <t>Yts270726</t>
-  </si>
-  <si>
     <t>01 de septiembre</t>
   </si>
   <si>
@@ -10226,9 +10232,6 @@
     <t>Premium2911</t>
   </si>
   <si>
-    <t>Tsd270726</t>
-  </si>
-  <si>
     <t>gratis 68853797 1 pantalla hasta el 26 de agosto (Max005)</t>
   </si>
   <si>
@@ -10238,9 +10241,6 @@
     <t>68153085 1 pantalla hasta el 26 de agosto</t>
   </si>
   <si>
-    <t>Tea270726</t>
-  </si>
-  <si>
     <t>67521865 1 pantalla hasta el 26 de agosto (Antonio)</t>
   </si>
   <si>
@@ -10283,9 +10283,6 @@
     <t>tokalgdl.us@botranox.com</t>
   </si>
   <si>
-    <t>mcdanieltamara3483+nottmichaell.au@outlook.com</t>
-  </si>
-  <si>
     <t>carla_csr_.br@botranox.com</t>
   </si>
   <si>
@@ -10418,9 +10415,6 @@
     <t>freemanwendy2878+connierasmussen45.us@outlook.com</t>
   </si>
   <si>
-    <t>M.E hasta el 28 de agosto</t>
-  </si>
-  <si>
     <t>10 de septiembre</t>
   </si>
   <si>
@@ -10796,9 +10790,6 @@
     <t>68488348 1 pantalla hasta el 03 de septiembre (Ashley)</t>
   </si>
   <si>
-    <t>Yta050826</t>
-  </si>
-  <si>
     <t>62884444 1 pantalla hasta el 04 de septiembre</t>
   </si>
   <si>
@@ -10991,9 +10982,6 @@
     <t>neetflixpma+net01@gmail.com</t>
   </si>
   <si>
-    <t>disponible para usar</t>
-  </si>
-  <si>
     <t>68515631 1 pantalla hasta el 10 de septiembre (Yamileth)</t>
   </si>
   <si>
@@ -12188,9 +12176,6 @@
     <t>01 de octubre</t>
   </si>
   <si>
-    <t>perkinschristina7980+emgbep.br@outlook.com</t>
-  </si>
-  <si>
     <t>Rea260826</t>
   </si>
   <si>
@@ -12314,7 +12299,49 @@
     <t>62942108 1 pantalla hasta el 26 de septiembre</t>
   </si>
   <si>
-    <t>crear 280826-1051g</t>
+    <t>Gdd280826</t>
+  </si>
+  <si>
+    <t>Yrd280826</t>
+  </si>
+  <si>
+    <t>Gda280826</t>
+  </si>
+  <si>
+    <t>howellchristopher9117+andreseresz.br@outlook.com</t>
+  </si>
+  <si>
+    <t>maxwelltimothy5952+juaniriso.ar@outlook.com</t>
+  </si>
+  <si>
+    <t>Yrs280826</t>
+  </si>
+  <si>
+    <t>M.E hasta el 28 de septiembre</t>
+  </si>
+  <si>
+    <t>67237055 1 pantalla hasta el 28 de septiembre (Jorge) 280826-1051g</t>
+  </si>
+  <si>
+    <t>Prf280826</t>
+  </si>
+  <si>
+    <t>14.60 USD BELICE hasta 23 de octubre</t>
+  </si>
+  <si>
+    <t>280826-0400d</t>
+  </si>
+  <si>
+    <t>280826-0425s</t>
+  </si>
+  <si>
+    <t>280826-0427c</t>
+  </si>
+  <si>
+    <t>280826-0430z</t>
+  </si>
+  <si>
+    <t>280826-0431l</t>
   </si>
 </sst>
 </file>
@@ -13633,7 +13660,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="443">
+  <cellXfs count="444">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -14121,6 +14148,7 @@
     <xf numFmtId="0" fontId="55" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -30021,6 +30049,15 @@
       </x:ext>
     </extLst>
   </threadedComment>
+  <threadedComment ref="I61" dT="2026-08-28T19:54:38.67" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{DA8DAF0D-B0F6-41A4-BEF1-65B0D0110B01}">
+    <text>https://netflix-server-a9i0.onrender.com/cliente/280826-1051g</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>480236659</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="49" url="https://netflix-server-a9i0.onrender.com/cliente/"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
   <threadedComment ref="K64" dT="2026-08-20T23:49:38.31" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{63325648-98C5-43A5-B0A0-BE3F1931179F}">
     <text>https://netflix-server-a9i0.onrender.com/cliente/200826-1844</text>
     <extLst>
@@ -30191,7 +30228,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3054</v>
+        <v>3049</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30203,7 +30240,7 @@
         <v>2079</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>3341</v>
+        <v>3334</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>2152</v>
@@ -30223,12 +30260,12 @@
         <v>2201</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3528</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
       <c r="A3" s="148" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B3" s="148" t="s">
         <v>2852</v>
@@ -30242,7 +30279,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3054</v>
+        <v>3049</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30254,7 +30291,7 @@
         <v>2077</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3438</v>
+        <v>3431</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2152</v>
@@ -30265,21 +30302,21 @@
     </row>
     <row r="5" spans="1:11" s="148" customFormat="1">
       <c r="A5" s="148" t="s">
-        <v>2846</v>
+        <v>1475</v>
       </c>
       <c r="B5" s="148">
-        <v>68853797</v>
+        <v>63971854</v>
       </c>
       <c r="C5" s="409" t="s">
         <v>2215</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>2971</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
       <c r="A6" s="226" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B6" s="148">
         <v>68241069</v>
@@ -30302,10 +30339,10 @@
         <v>2080</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>3182</v>
+        <v>3176</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3510</v>
+        <v>3503</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2157</v>
@@ -30347,7 +30384,7 @@
     </row>
     <row r="10" spans="1:11" s="436" customFormat="1">
       <c r="A10" s="436" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B10" s="436">
         <v>60389752</v>
@@ -30359,10 +30396,10 @@
         <v>2170</v>
       </c>
       <c r="E10" s="436" t="s">
-        <v>3075</v>
+        <v>3070</v>
       </c>
       <c r="F10" s="436" t="s">
-        <v>3074</v>
+        <v>3069</v>
       </c>
       <c r="G10" s="436" t="s">
         <v>59</v>
@@ -30384,7 +30421,7 @@
         <v>2221</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3617</v>
+        <v>3610</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2220</v>
@@ -30396,7 +30433,7 @@
     </row>
     <row r="14" spans="1:11" s="148" customFormat="1">
       <c r="A14" s="226" t="s">
-        <v>3349</v>
+        <v>3342</v>
       </c>
       <c r="B14" s="226" t="s">
         <v>1731</v>
@@ -30410,7 +30447,7 @@
     </row>
     <row r="15" spans="1:11" s="148" customFormat="1">
       <c r="A15" s="226" t="s">
-        <v>3036</v>
+        <v>3031</v>
       </c>
       <c r="B15" s="429">
         <v>62439069</v>
@@ -30433,10 +30470,10 @@
         <v>1578</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3512</v>
+        <v>3505</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3618</v>
+        <v>3611</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1579</v>
@@ -30445,21 +30482,21 @@
         <v>201</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3513</v>
+        <v>3506</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3098</v>
+        <v>3093</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>3530</v>
+        <v>3523</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>3606</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
       <c r="A17" s="253" t="s">
-        <v>3212</v>
+        <v>3206</v>
       </c>
       <c r="B17" s="253" t="s">
         <v>1433</v>
@@ -30493,7 +30530,7 @@
     </row>
     <row r="19" spans="1:11" s="30" customFormat="1">
       <c r="A19" s="32" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B19" s="30">
         <v>62360487</v>
@@ -30505,7 +30542,7 @@
         <v>2109</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>3490</v>
+        <v>3483</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>1399</v>
@@ -30516,7 +30553,7 @@
     </row>
     <row r="20" spans="1:11" s="298" customFormat="1">
       <c r="A20" s="164" t="s">
-        <v>3324</v>
+        <v>3317</v>
       </c>
       <c r="B20" s="164">
         <v>68444421</v>
@@ -30525,7 +30562,7 @@
         <v>1738</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>3407</v>
+        <v>3400</v>
       </c>
       <c r="E20" s="253" t="s">
         <v>1739</v>
@@ -30533,7 +30570,7 @@
     </row>
     <row r="21" spans="1:11" s="298" customFormat="1">
       <c r="A21" s="253" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B21" s="253">
         <v>60432412</v>
@@ -30562,7 +30599,7 @@
         <v>2198</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>3341</v>
+        <v>3334</v>
       </c>
       <c r="F22" s="30" t="s">
         <v>2151</v>
@@ -30587,7 +30624,7 @@
     </row>
     <row r="24" spans="1:11" s="148" customFormat="1">
       <c r="A24" s="148" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B24" s="148">
         <v>62279384</v>
@@ -30613,7 +30650,7 @@
         <v>1574</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3489</v>
+        <v>3482</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1399</v>
@@ -30644,7 +30681,7 @@
     </row>
     <row r="27" spans="1:11" s="226" customFormat="1">
       <c r="A27" s="226" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B27" s="226">
         <v>64476521</v>
@@ -30673,7 +30710,7 @@
         <v>2074</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3053</v>
+        <v>3048</v>
       </c>
       <c r="F28" s="305" t="s">
         <v>2233</v>
@@ -30707,24 +30744,24 @@
         <v>2476</v>
       </c>
       <c r="D30" s="164" t="s">
-        <v>3222</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="30" customFormat="1">
       <c r="A31" s="30" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3476</v>
+        <v>3469</v>
       </c>
       <c r="C31" s="252" t="s">
         <v>1962</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3477</v>
+        <v>3470</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>3373</v>
+        <v>3366</v>
       </c>
       <c r="F31" s="30" t="s">
         <v>2097</v>
@@ -30733,16 +30770,16 @@
         <v>201</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3478</v>
+        <v>3471</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3613</v>
+        <v>3606</v>
       </c>
       <c r="J31" s="434" t="s">
-        <v>3500</v>
+        <v>3493</v>
       </c>
       <c r="K31" s="30" t="s">
-        <v>3191</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="163" customFormat="1">
@@ -30776,7 +30813,7 @@
     </row>
     <row r="34" spans="1:11" s="30" customFormat="1">
       <c r="A34" s="30" t="s">
-        <v>3094</v>
+        <v>3089</v>
       </c>
       <c r="B34" s="30">
         <v>60389752</v>
@@ -30788,7 +30825,7 @@
         <v>2164</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>3270</v>
+        <v>3263</v>
       </c>
       <c r="F34" s="30" t="s">
         <v>2155</v>
@@ -30816,7 +30853,7 @@
     </row>
     <row r="36" spans="1:11" s="148" customFormat="1">
       <c r="A36" s="226" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B36" s="148">
         <v>61381388</v>
@@ -30839,10 +30876,10 @@
         <v>2072</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3641</v>
+        <v>3633</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>3342</v>
+        <v>3335</v>
       </c>
       <c r="F37" s="30" t="s">
         <v>2145</v>
@@ -30851,21 +30888,21 @@
         <v>201</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>3207</v>
-      </c>
-      <c r="I37" s="30" t="s">
-        <v>2998</v>
+        <v>3201</v>
+      </c>
+      <c r="I37" s="217" t="s">
+        <v>2994</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3648</v>
+        <v>3640</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3192</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
       <c r="A38" s="147" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B38" s="147" t="s">
         <v>2850</v>
@@ -30897,16 +30934,16 @@
         <v>2630</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3654</v>
+        <v>3646</v>
       </c>
       <c r="C40" s="252" t="s">
         <v>1718</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>3002</v>
+        <v>2998</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>3270</v>
+        <v>3263</v>
       </c>
       <c r="F40" s="30" t="s">
         <v>2160</v>
@@ -30915,21 +30952,21 @@
         <v>201</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3569</v>
+        <v>3562</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3601</v>
+        <v>3594</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3637</v>
+        <v>3629</v>
       </c>
       <c r="K40" s="30" t="s">
-        <v>3185</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -30961,7 +30998,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -30973,7 +31010,7 @@
         <v>2101</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3441</v>
+        <v>3434</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2195</v>
@@ -30984,7 +31021,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31001,7 +31038,7 @@
     </row>
     <row r="45" spans="1:11" s="163" customFormat="1">
       <c r="A45" s="163" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B45" s="163">
         <v>64079861</v>
@@ -31027,10 +31064,10 @@
         <v>997</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>3166</v>
+        <v>3160</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>3127</v>
+        <v>3122</v>
       </c>
       <c r="F46" s="30" t="s">
         <v>2177</v>
@@ -31051,7 +31088,7 @@
         <v>2197</v>
       </c>
       <c r="D47" s="164" t="s">
-        <v>3126</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="164" customFormat="1">
@@ -31082,10 +31119,10 @@
         <v>2063</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3598</v>
+        <v>3591</v>
       </c>
       <c r="E49" s="30" t="s">
-        <v>3272</v>
+        <v>3265</v>
       </c>
       <c r="F49" s="30" t="s">
         <v>2163</v>
@@ -31094,16 +31131,16 @@
         <v>201</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3599</v>
+        <v>3592</v>
       </c>
       <c r="I49" s="442" t="s">
-        <v>3666</v>
+        <v>3658</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>3118</v>
+        <v>3113</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3653</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31131,12 +31168,12 @@
         <v>2071</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3553</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
       <c r="A52" s="140" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B52" s="426" t="s">
         <v>1483</v>
@@ -31145,10 +31182,10 @@
         <v>1402</v>
       </c>
       <c r="D52" s="139" t="s">
-        <v>3197</v>
+        <v>3191</v>
       </c>
       <c r="E52" s="139" t="s">
-        <v>3270</v>
+        <v>3263</v>
       </c>
       <c r="F52" s="139" t="s">
         <v>2161</v>
@@ -31157,16 +31194,16 @@
         <v>201</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3604</v>
+        <v>3597</v>
       </c>
       <c r="I52" s="140" t="s">
-        <v>3198</v>
+        <v>3192</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3084</v>
+        <v>3079</v>
       </c>
       <c r="K52" s="270" t="s">
-        <v>3462</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31188,7 +31225,7 @@
     </row>
     <row r="54" spans="1:11" s="164" customFormat="1">
       <c r="A54" s="416" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B54" s="163" t="s">
         <v>1785</v>
@@ -31207,7 +31244,7 @@
     </row>
     <row r="55" spans="1:11" s="30" customFormat="1">
       <c r="A55" s="30" t="s">
-        <v>3267</v>
+        <v>3260</v>
       </c>
       <c r="B55" s="30">
         <v>61130088</v>
@@ -31219,7 +31256,7 @@
         <v>2067</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3617</v>
+        <v>3610</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2178</v>
@@ -31236,10 +31273,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="411" t="s">
-        <v>3632</v>
+        <v>3624</v>
       </c>
       <c r="D56" s="377" t="s">
-        <v>3634</v>
+        <v>3626</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31248,13 +31285,13 @@
         <v>2630</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3638</v>
+        <v>3630</v>
       </c>
       <c r="C57" s="411" t="s">
-        <v>3633</v>
+        <v>3625</v>
       </c>
       <c r="D57" s="377" t="s">
-        <v>3635</v>
+        <v>3627</v>
       </c>
       <c r="E57" s="164"/>
     </row>
@@ -31269,9 +31306,9 @@
         <v>2098</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>3049</v>
-      </c>
-      <c r="E58" s="30" t="s">
+        <v>3044</v>
+      </c>
+      <c r="E58" s="401" t="s">
         <v>2656</v>
       </c>
       <c r="F58" s="30" t="s">
@@ -31281,16 +31318,16 @@
         <v>201</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3069</v>
+        <v>3064</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3651</v>
+        <v>3643</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3082</v>
+        <v>3077</v>
       </c>
       <c r="K58" s="30" t="s">
-        <v>3343</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="395" customFormat="1">
@@ -31305,16 +31342,16 @@
         <v>2508</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3621</v>
+        <v>3614</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2144</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>3177</v>
+        <v>3171</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3511</v>
+        <v>3504</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2145</v>
@@ -31323,21 +31360,21 @@
         <v>201</v>
       </c>
       <c r="H61" s="30" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I61" s="145" t="s">
-        <v>3667</v>
+        <v>3222</v>
+      </c>
+      <c r="I61" s="442" t="s">
+        <v>3666</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3219</v>
+        <v>3213</v>
       </c>
       <c r="K61" s="30" t="s">
-        <v>3122</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3619</v>
+        <v>3612</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31346,7 +31383,7 @@
         <v>1514</v>
       </c>
       <c r="D62" s="378" t="s">
-        <v>3622</v>
+        <v>3615</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1419</v>
@@ -31354,7 +31391,7 @@
     </row>
     <row r="63" spans="1:11" s="163" customFormat="1">
       <c r="A63" s="163" t="s">
-        <v>3054</v>
+        <v>3049</v>
       </c>
       <c r="B63" s="163">
         <v>62960567</v>
@@ -31363,7 +31400,7 @@
         <v>2129</v>
       </c>
       <c r="D63" s="377" t="s">
-        <v>3570</v>
+        <v>3563</v>
       </c>
       <c r="E63" s="164"/>
     </row>
@@ -31378,10 +31415,10 @@
         <v>1717</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3048</v>
+        <v>3043</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>3271</v>
+        <v>3264</v>
       </c>
       <c r="F64" s="30" t="s">
         <v>2162</v>
@@ -31390,21 +31427,21 @@
         <v>201</v>
       </c>
       <c r="H64" s="32" t="s">
-        <v>3083</v>
+        <v>3078</v>
       </c>
       <c r="I64" s="32" t="s">
-        <v>3174</v>
+        <v>3168</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>3173</v>
+        <v>3167</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3652</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
       <c r="A65" s="253" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B65" s="253">
         <v>62535724</v>
@@ -31438,7 +31475,7 @@
     </row>
     <row r="67" spans="1:11" s="30" customFormat="1">
       <c r="A67" s="254" t="s">
-        <v>3036</v>
+        <v>3031</v>
       </c>
       <c r="B67" s="285" t="s">
         <v>1970</v>
@@ -31447,10 +31484,10 @@
         <v>1721</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>3427</v>
+        <v>3420</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>3314</v>
+        <v>3307</v>
       </c>
       <c r="F67" s="30" t="s">
         <v>2166</v>
@@ -31459,21 +31496,21 @@
         <v>201</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3428</v>
+        <v>3421</v>
       </c>
       <c r="I67" s="30" t="s">
-        <v>3214</v>
+        <v>3208</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>3288</v>
+        <v>3281</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3437</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3619</v>
+        <v>3612</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31482,7 +31519,7 @@
         <v>1938</v>
       </c>
       <c r="D68" s="378" t="s">
-        <v>3594</v>
+        <v>3587</v>
       </c>
       <c r="E68" s="148"/>
     </row>
@@ -31497,12 +31534,12 @@
         <v>2165</v>
       </c>
       <c r="D69" s="148" t="s">
-        <v>3293</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="30" customFormat="1">
       <c r="A70" s="30" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B70" s="285" t="s">
         <v>2660</v>
@@ -31513,7 +31550,7 @@
       <c r="D70" s="30" t="s">
         <v>2759</v>
       </c>
-      <c r="E70" s="30" t="s">
+      <c r="E70" s="401" t="s">
         <v>2656</v>
       </c>
       <c r="F70" s="30" t="s">
@@ -31523,13 +31560,13 @@
         <v>201</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3471</v>
+        <v>3464</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>3404</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31543,12 +31580,12 @@
         <v>2025</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>3253</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="72" spans="1:11" s="163" customFormat="1">
       <c r="A72" s="269" t="s">
-        <v>3359</v>
+        <v>3352</v>
       </c>
       <c r="B72" s="269" t="s">
         <v>1495</v>
@@ -31557,13 +31594,13 @@
         <v>1774</v>
       </c>
       <c r="D72" s="377" t="s">
-        <v>3001</v>
+        <v>2997</v>
       </c>
       <c r="E72" s="164"/>
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3072</v>
+        <v>3067</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31572,10 +31609,10 @@
         <v>1379</v>
       </c>
       <c r="D73" s="252" t="s">
-        <v>3071</v>
+        <v>3066</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3519</v>
+        <v>3512</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2096</v>
@@ -31586,7 +31623,7 @@
     </row>
     <row r="74" spans="1:11" s="147" customFormat="1">
       <c r="A74" s="147" t="s">
-        <v>3349</v>
+        <v>3342</v>
       </c>
       <c r="B74" s="147">
         <v>64226974</v>
@@ -31625,10 +31662,10 @@
         <v>1937</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>3364</v>
+        <v>3357</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3560</v>
+        <v>3553</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2177</v>
@@ -31637,16 +31674,16 @@
         <v>201</v>
       </c>
       <c r="H76" s="30" t="s">
-        <v>3366</v>
+        <v>3359</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>3368</v>
+        <v>3361</v>
       </c>
       <c r="J76" s="30" t="s">
         <v>2944</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3365</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31662,16 +31699,16 @@
         <v>144</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>3306</v>
+        <v>3299</v>
       </c>
       <c r="C79" s="134" t="s">
         <v>2070</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3401</v>
+        <v>3394</v>
       </c>
       <c r="E79" s="30" t="s">
-        <v>3341</v>
+        <v>3334</v>
       </c>
       <c r="F79" s="30" t="s">
         <v>2156</v>
@@ -31680,16 +31717,16 @@
         <v>201</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>3424</v>
+        <v>3417</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3647</v>
+        <v>3639</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3402</v>
+        <v>3395</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3307</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31726,19 +31763,19 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="30" t="s">
-        <v>3659</v>
+        <v>3651</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3658</v>
+        <v>3650</v>
       </c>
       <c r="C82" s="134" t="s">
         <v>1963</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>3133</v>
+        <v>3128</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>3205</v>
+        <v>3199</v>
       </c>
       <c r="F82" s="30" t="s">
         <v>1964</v>
@@ -31747,21 +31784,21 @@
         <v>201</v>
       </c>
       <c r="H82" s="30" t="s">
-        <v>3596</v>
+        <v>3589</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>3660</v>
+        <v>3652</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>3597</v>
+        <v>3590</v>
       </c>
       <c r="K82" s="30" t="s">
-        <v>3218</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="148" customFormat="1">
       <c r="A83" s="148" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B83" s="148">
         <v>63145336</v>
@@ -31775,7 +31812,7 @@
     </row>
     <row r="84" spans="1:11" s="281" customFormat="1">
       <c r="A84" s="148" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B84" s="148">
         <v>68971798</v>
@@ -31810,16 +31847,16 @@
         <v>498</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3631</v>
+        <v>3623</v>
       </c>
       <c r="I85" s="32" t="s">
-        <v>3232</v>
+        <v>3225</v>
       </c>
       <c r="J85" s="217" t="s">
         <v>2649</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3502</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -31842,7 +31879,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>923</v>
@@ -31860,7 +31897,7 @@
     </row>
     <row r="88" spans="1:11" s="30" customFormat="1">
       <c r="A88" s="30" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B88" s="30">
         <v>68496217</v>
@@ -31869,7 +31906,7 @@
         <v>701</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>3344</v>
+        <v>3337</v>
       </c>
       <c r="E88" s="30" t="s">
         <v>1104</v>
@@ -31881,16 +31918,16 @@
         <v>1576</v>
       </c>
       <c r="H88" s="30" t="s">
-        <v>3345</v>
+        <v>3338</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>3383</v>
+        <v>3376</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3480</v>
+        <v>3473</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3479</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -31913,16 +31950,16 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="226" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
       </c>
       <c r="C90" s="409" t="s">
-        <v>3076</v>
+        <v>3071</v>
       </c>
       <c r="D90" s="148" t="s">
-        <v>3042</v>
+        <v>3037</v>
       </c>
       <c r="E90" s="148" t="s">
         <v>879</v>
@@ -31931,7 +31968,7 @@
     </row>
     <row r="91" spans="1:11" s="106" customFormat="1">
       <c r="A91" s="250" t="s">
-        <v>3359</v>
+        <v>3352</v>
       </c>
       <c r="B91" s="32" t="s">
         <v>1439</v>
@@ -31940,7 +31977,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3656</v>
+        <v>3648</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1150</v>
@@ -31952,16 +31989,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3657</v>
+        <v>3649</v>
       </c>
       <c r="I91" s="31" t="s">
-        <v>3308</v>
+        <v>3301</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3461</v>
+        <v>3454</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3561</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="417" customFormat="1">
@@ -32009,7 +32046,7 @@
         <v>1400</v>
       </c>
       <c r="E94" s="254" t="s">
-        <v>3178</v>
+        <v>3172</v>
       </c>
       <c r="F94" s="32" t="s">
         <v>1401</v>
@@ -32038,7 +32075,7 @@
     </row>
     <row r="96" spans="1:11" s="148" customFormat="1">
       <c r="A96" s="148" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B96" s="148">
         <v>62928817</v>
@@ -32053,21 +32090,21 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="30" customFormat="1">
+    <row r="97" spans="1:13" s="30" customFormat="1">
       <c r="A97" s="32" t="s">
         <v>1460</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>3304</v>
+        <v>3297</v>
       </c>
       <c r="C97" s="153" t="s">
         <v>2060</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>3303</v>
+        <v>3296</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>3361</v>
+        <v>3354</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>1964</v>
@@ -32076,41 +32113,41 @@
         <v>201</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>3227</v>
+        <v>3220</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3416</v>
+        <v>3409</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>3509</v>
+        <v>3502</v>
       </c>
       <c r="K97" s="139" t="s">
-        <v>3384</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" s="395" customFormat="1">
+        <v>3377</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" s="395" customFormat="1">
       <c r="D98" s="396"/>
       <c r="E98" s="375"/>
     </row>
-    <row r="99" spans="1:11" s="395" customFormat="1">
+    <row r="99" spans="1:13" s="395" customFormat="1">
       <c r="D99" s="396"/>
       <c r="E99" s="375"/>
     </row>
-    <row r="100" spans="1:11" s="30" customFormat="1">
+    <row r="100" spans="1:13" s="30" customFormat="1">
       <c r="A100" s="30" t="s">
-        <v>3212</v>
+        <v>3206</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>3213</v>
+        <v>3207</v>
       </c>
       <c r="C100" s="252" t="s">
-        <v>3131</v>
+        <v>3126</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>3130</v>
+        <v>3125</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3564</v>
+        <v>3557</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1964</v>
@@ -32119,94 +32156,156 @@
         <v>201</v>
       </c>
       <c r="H100" s="30" t="s">
-        <v>3078</v>
+        <v>3073</v>
       </c>
       <c r="I100" s="30" t="s">
-        <v>2999</v>
+        <v>2995</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>2983</v>
+        <v>2980</v>
       </c>
       <c r="K100" s="32" t="s">
-        <v>3136</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" s="395" customFormat="1">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" s="395" customFormat="1">
       <c r="D101" s="396"/>
       <c r="E101" s="375"/>
     </row>
-    <row r="102" spans="1:11" s="395" customFormat="1">
+    <row r="102" spans="1:13" s="395" customFormat="1">
       <c r="D102" s="396"/>
       <c r="E102" s="375"/>
     </row>
-    <row r="103" spans="1:11" s="30" customFormat="1">
-      <c r="A103" s="30" t="s">
-        <v>3282</v>
-      </c>
-      <c r="B103" s="30">
+    <row r="103" spans="1:13" s="30" customFormat="1">
+      <c r="B103" s="145" t="s">
+        <v>3669</v>
+      </c>
+      <c r="C103" s="252" t="s">
+        <v>3221</v>
+      </c>
+      <c r="D103" s="30" t="s">
+        <v>3667</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>3668</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G103" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="H103" s="145" t="s">
+        <v>3670</v>
+      </c>
+      <c r="I103" s="145" t="s">
+        <v>3671</v>
+      </c>
+      <c r="J103" s="145" t="s">
+        <v>3672</v>
+      </c>
+      <c r="K103" s="145" t="s">
+        <v>3673</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" s="395"/>
+      <c r="B104" s="395"/>
+      <c r="C104" s="395"/>
+      <c r="D104" s="396"/>
+      <c r="E104" s="375"/>
+      <c r="F104" s="395"/>
+      <c r="G104" s="395"/>
+      <c r="H104" s="395"/>
+      <c r="I104" s="395"/>
+      <c r="J104" s="395"/>
+      <c r="K104" s="395"/>
+      <c r="L104" s="395"/>
+      <c r="M104" s="395"/>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="395"/>
+      <c r="B105" s="395"/>
+      <c r="C105" s="395"/>
+      <c r="D105" s="396"/>
+      <c r="E105" s="375"/>
+      <c r="F105" s="395"/>
+      <c r="G105" s="395"/>
+      <c r="H105" s="395"/>
+      <c r="I105" s="395"/>
+      <c r="J105" s="395"/>
+      <c r="K105" s="395"/>
+      <c r="L105" s="395"/>
+      <c r="M105" s="395"/>
+    </row>
+    <row r="106" spans="1:13" s="30" customFormat="1">
+      <c r="A106" s="30" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B106" s="30">
         <v>62724019</v>
       </c>
-      <c r="C103" s="252" t="s">
-        <v>3225</v>
-      </c>
-      <c r="D103" s="30" t="s">
-        <v>3484</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3486</v>
-      </c>
-      <c r="F103" s="30" t="s">
-        <v>3485</v>
-      </c>
-      <c r="G103" s="30" t="s">
+      <c r="C106" s="252" t="s">
+        <v>3219</v>
+      </c>
+      <c r="D106" s="30" t="s">
+        <v>3477</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>3479</v>
+      </c>
+      <c r="F106" s="30" t="s">
+        <v>3478</v>
+      </c>
+      <c r="G106" s="30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:11" s="430" customFormat="1">
-      <c r="D104" s="431"/>
-      <c r="E104" s="432"/>
-    </row>
-    <row r="105" spans="1:11" s="430" customFormat="1">
-      <c r="D105" s="431"/>
-      <c r="E105" s="432"/>
-    </row>
-    <row r="106" spans="1:11">
-      <c r="A106" s="30" t="s">
+    <row r="107" spans="1:13" s="430" customFormat="1">
+      <c r="D107" s="431"/>
+      <c r="E107" s="432"/>
+    </row>
+    <row r="108" spans="1:13" s="430" customFormat="1">
+      <c r="D108" s="431"/>
+      <c r="E108" s="432"/>
+    </row>
+    <row r="112" spans="1:13">
+      <c r="A112" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B106" s="285" t="s">
-        <v>3503</v>
-      </c>
-      <c r="C106" s="134" t="s">
+      <c r="B112" s="285" t="s">
+        <v>3496</v>
+      </c>
+      <c r="C112" s="134" t="s">
         <v>2057</v>
       </c>
-      <c r="D106" s="30" t="s">
+      <c r="D112" s="30" t="s">
         <v>2764</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
-      <c r="E107"/>
-    </row>
-    <row r="108" spans="1:11" s="30" customFormat="1">
-      <c r="A108" s="30" t="s">
+    <row r="113" spans="1:8">
+      <c r="E113"/>
+    </row>
+    <row r="114" spans="1:8" s="30" customFormat="1">
+      <c r="A114" s="217" t="s">
         <v>2846</v>
       </c>
-      <c r="B108" s="30">
+      <c r="B114" s="30">
         <v>60756926</v>
       </c>
-      <c r="C108" s="30" t="s">
-        <v>3169</v>
-      </c>
-      <c r="D108" s="30" t="s">
-        <v>3170</v>
-      </c>
-      <c r="E108" s="30" t="s">
-        <v>3171</v>
-      </c>
-      <c r="F108" s="30" t="s">
-        <v>3132</v>
-      </c>
-      <c r="G108" s="30" t="s">
+      <c r="C114" s="30" t="s">
+        <v>3163</v>
+      </c>
+      <c r="D114" s="30" t="s">
+        <v>3164</v>
+      </c>
+      <c r="E114" s="30" t="s">
+        <v>3165</v>
+      </c>
+      <c r="F114" s="30" t="s">
+        <v>3127</v>
+      </c>
+      <c r="G114" s="30" t="s">
         <v>59</v>
       </c>
     </row>
@@ -32215,16 +32314,16 @@
         <v>79</v>
       </c>
       <c r="D124" s="32" t="s">
-        <v>3315</v>
+        <v>3308</v>
       </c>
       <c r="E124" s="32" t="s">
-        <v>3171</v>
+        <v>3165</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>3132</v>
+        <v>3127</v>
       </c>
       <c r="G124" s="32" t="s">
-        <v>3224</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="125" spans="1:8" s="30" customFormat="1"/>
@@ -32254,7 +32353,7 @@
         <v>2047</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3588</v>
+        <v>3581</v>
       </c>
       <c r="F127" t="s">
         <v>2045</v>
@@ -32274,24 +32373,21 @@
         <v>2015</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3588</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" t="s">
-        <v>2846</v>
-      </c>
-      <c r="B129">
-        <v>67845784</v>
+      <c r="A129" s="97" t="s">
+        <v>1194</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>2918</v>
       </c>
       <c r="D129" s="380" t="s">
-        <v>2958</v>
+        <v>3664</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3588</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -32308,7 +32404,7 @@
         <v>2775</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3588</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32325,7 +32421,7 @@
         <v>2021</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3588</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32367,7 +32463,7 @@
         <v>2919</v>
       </c>
       <c r="E135" s="30" t="s">
-        <v>3152</v>
+        <v>3147</v>
       </c>
       <c r="F135" t="s">
         <v>1348</v>
@@ -32387,7 +32483,7 @@
         <v>2458</v>
       </c>
       <c r="E136" s="401" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="F136" t="s">
         <v>1376</v>
@@ -32404,7 +32500,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>3267</v>
+        <v>3260</v>
       </c>
       <c r="B139">
         <v>64720128</v>
@@ -32433,7 +32529,7 @@
         <v>2032</v>
       </c>
       <c r="D140" s="380" t="s">
-        <v>3639</v>
+        <v>3631</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>2031</v>
@@ -32491,22 +32587,22 @@
     </row>
     <row r="149" spans="1:6">
       <c r="C149" t="s">
-        <v>2993</v>
+        <v>2989</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>2995</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="C150" s="1" t="s">
-        <v>2994</v>
+        <v>2990</v>
       </c>
       <c r="D150" s="380" t="s">
-        <v>2996</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" t="s">
+      <c r="A152" s="49" t="s">
         <v>2846</v>
       </c>
       <c r="B152">
@@ -32516,10 +32612,10 @@
         <v>2313</v>
       </c>
       <c r="D152" s="380" t="s">
-        <v>2975</v>
+        <v>3660</v>
       </c>
       <c r="E152" s="30" t="s">
-        <v>3589</v>
+        <v>3582</v>
       </c>
       <c r="F152" t="s">
         <v>2033</v>
@@ -32539,7 +32635,7 @@
         <v>2463</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3589</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -32553,10 +32649,10 @@
         <v>2315</v>
       </c>
       <c r="D154" s="380" t="s">
-        <v>3022</v>
+        <v>3018</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3589</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -32573,12 +32669,12 @@
         <v>2776</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B156">
         <v>62491046</v>
@@ -32587,10 +32683,10 @@
         <v>2325</v>
       </c>
       <c r="D156" s="380" t="s">
-        <v>3376</v>
+        <v>3369</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -32607,7 +32703,7 @@
         <v>2631</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -32624,7 +32720,7 @@
         <v>2822</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -32641,7 +32737,7 @@
         <v>2749</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -32658,12 +32754,12 @@
         <v>2663</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3661</v>
+        <v>3653</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1164</v>
@@ -32672,27 +32768,27 @@
         <v>2778</v>
       </c>
       <c r="D161" s="380" t="s">
-        <v>3521</v>
+        <v>3514</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>2846</v>
+        <v>159</v>
       </c>
       <c r="B162">
-        <v>66935922</v>
+        <v>68017742</v>
       </c>
       <c r="C162" t="s">
         <v>2665</v>
       </c>
       <c r="D162" s="380" t="s">
-        <v>3161</v>
+        <v>3661</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -32703,13 +32799,13 @@
         <v>12369714760</v>
       </c>
       <c r="C163" t="s">
-        <v>3292</v>
+        <v>3285</v>
       </c>
       <c r="D163" s="380" t="s">
-        <v>3309</v>
+        <v>3302</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3011</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -32720,18 +32816,18 @@
         <v>2250</v>
       </c>
       <c r="C164" t="s">
-        <v>3146</v>
+        <v>3141</v>
       </c>
       <c r="D164" s="380" t="s">
         <v>2632</v>
       </c>
       <c r="E164" s="30" t="s">
-        <v>3238</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>3212</v>
+        <v>3206</v>
       </c>
       <c r="B165">
         <v>66315726</v>
@@ -32743,12 +32839,12 @@
         <v>2367</v>
       </c>
       <c r="E165" s="30" t="s">
-        <v>3238</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B166">
         <v>64568369</v>
@@ -32760,12 +32856,12 @@
         <v>2367</v>
       </c>
       <c r="E166" s="30" t="s">
-        <v>3238</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B167">
         <v>66935922</v>
@@ -32777,7 +32873,7 @@
         <v>2779</v>
       </c>
       <c r="E167" s="30" t="s">
-        <v>3238</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -32794,12 +32890,12 @@
         <v>2922</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3474</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>2652</v>
+        <v>1475</v>
       </c>
       <c r="B169">
         <v>66615857</v>
@@ -32808,10 +32904,10 @@
         <v>2413</v>
       </c>
       <c r="D169" s="380" t="s">
-        <v>2982</v>
+        <v>2979</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3474</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -32828,7 +32924,7 @@
         <v>2629</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3474</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -32845,7 +32941,7 @@
         <v>2415</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3474</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -32862,7 +32958,7 @@
         <v>2633</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3520</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -32879,7 +32975,7 @@
         <v>2430</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3520</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -32893,10 +32989,10 @@
         <v>2429</v>
       </c>
       <c r="D174" s="380" t="s">
-        <v>3012</v>
+        <v>3008</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3520</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -32907,13 +33003,13 @@
         <v>62640383</v>
       </c>
       <c r="C175" t="s">
-        <v>2987</v>
+        <v>2984</v>
       </c>
       <c r="D175" s="380" t="s">
-        <v>2988</v>
+        <v>2985</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3610</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -32924,30 +33020,25 @@
         <v>68918211</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>2989</v>
+        <v>2986</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>2988</v>
+        <v>2985</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3610</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" t="s">
-        <v>159</v>
-      </c>
-      <c r="B177">
-        <v>68017742</v>
-      </c>
+      <c r="A177" s="97"/>
       <c r="C177" s="3" t="s">
-        <v>2990</v>
+        <v>3662</v>
       </c>
       <c r="D177" s="220" t="s">
-        <v>2988</v>
+        <v>3104</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3610</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -32958,13 +33049,13 @@
         <v>63000428</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>2991</v>
+        <v>2987</v>
       </c>
       <c r="D178" s="220" t="s">
-        <v>3023</v>
+        <v>3019</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3610</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -32975,13 +33066,13 @@
         <v>68501487</v>
       </c>
       <c r="C179" s="22" t="s">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>2988</v>
+        <v>2985</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3610</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -32992,98 +33083,98 @@
         <v>63195211</v>
       </c>
       <c r="C180" t="s">
-        <v>3030</v>
+        <v>3026</v>
       </c>
       <c r="D180" s="380" t="s">
-        <v>3031</v>
+        <v>3027</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3035</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B181">
         <v>63950696</v>
       </c>
       <c r="C181" t="s">
-        <v>3032</v>
+        <v>3028</v>
       </c>
       <c r="D181" s="380" t="s">
-        <v>3031</v>
+        <v>3027</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3035</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B182" t="s">
-        <v>3080</v>
+        <v>3075</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>3033</v>
+        <v>3029</v>
       </c>
       <c r="D182" s="220" t="s">
-        <v>3031</v>
+        <v>3027</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3035</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B183">
         <v>66805512</v>
       </c>
       <c r="C183" t="s">
-        <v>3034</v>
+        <v>3030</v>
       </c>
       <c r="D183" s="380" t="s">
-        <v>3183</v>
+        <v>3177</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3035</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B184" t="s">
-        <v>3206</v>
+        <v>3200</v>
       </c>
       <c r="C184" t="s">
-        <v>3153</v>
+        <v>3148</v>
       </c>
       <c r="D184" s="380" t="s">
-        <v>3186</v>
+        <v>3180</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3035</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>3212</v>
+        <v>3206</v>
       </c>
       <c r="B185">
         <v>68201775</v>
       </c>
       <c r="C185" t="s">
-        <v>3100</v>
+        <v>3095</v>
       </c>
       <c r="D185" s="380" t="s">
-        <v>3189</v>
+        <v>3183</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -33091,16 +33182,16 @@
         <v>2671</v>
       </c>
       <c r="B186" t="s">
-        <v>3112</v>
+        <v>3107</v>
       </c>
       <c r="C186" t="s">
-        <v>3101</v>
+        <v>3096</v>
       </c>
       <c r="D186" s="380" t="s">
-        <v>3109</v>
+        <v>3104</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33111,30 +33202,30 @@
         <v>62724019</v>
       </c>
       <c r="C187" t="s">
-        <v>3102</v>
+        <v>3097</v>
       </c>
       <c r="D187" s="380" t="s">
-        <v>3109</v>
+        <v>3104</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="30" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B188" s="32" t="s">
         <v>2190</v>
       </c>
       <c r="C188" t="s">
-        <v>3103</v>
+        <v>3098</v>
       </c>
       <c r="D188" s="380" t="s">
-        <v>3109</v>
+        <v>3104</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33145,13 +33236,13 @@
         <v>65080956</v>
       </c>
       <c r="C189" t="s">
+        <v>3099</v>
+      </c>
+      <c r="D189" s="380" t="s">
         <v>3104</v>
       </c>
-      <c r="D189" s="380" t="s">
-        <v>3109</v>
-      </c>
       <c r="E189" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33162,47 +33253,47 @@
         <v>68726473</v>
       </c>
       <c r="C190" t="s">
+        <v>3100</v>
+      </c>
+      <c r="D190" s="380" t="s">
+        <v>3104</v>
+      </c>
+      <c r="E190" s="30" t="s">
         <v>3105</v>
-      </c>
-      <c r="D190" s="380" t="s">
-        <v>3109</v>
-      </c>
-      <c r="E190" s="30" t="s">
-        <v>3110</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3624</v>
+        <v>3617</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1917</v>
       </c>
       <c r="C191" t="s">
-        <v>3106</v>
+        <v>3101</v>
       </c>
       <c r="D191" s="380" t="s">
-        <v>3109</v>
+        <v>3104</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>3567</v>
+        <v>3560</v>
       </c>
       <c r="B192">
         <v>64046277</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>3187</v>
+        <v>3181</v>
       </c>
       <c r="D192" s="380" t="s">
-        <v>3188</v>
+        <v>3182</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -33213,13 +33304,13 @@
         <v>66520892</v>
       </c>
       <c r="C193" t="s">
-        <v>3107</v>
+        <v>3102</v>
       </c>
       <c r="D193" s="380" t="s">
-        <v>3109</v>
+        <v>3104</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33230,18 +33321,18 @@
         <v>62031509</v>
       </c>
       <c r="C194" t="s">
-        <v>3108</v>
+        <v>3103</v>
       </c>
       <c r="D194" s="380" t="s">
-        <v>3109</v>
+        <v>3104</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3110</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="399" customFormat="1" ht="23.5">
       <c r="C197" s="399" t="s">
-        <v>3139</v>
+        <v>3134</v>
       </c>
       <c r="D197" s="399">
         <v>51957149094</v>
@@ -33249,87 +33340,87 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>3054</v>
+        <v>3049</v>
       </c>
       <c r="B198">
         <v>60240509</v>
       </c>
       <c r="C198" t="s">
-        <v>3154</v>
+        <v>3149</v>
       </c>
       <c r="D198" s="380" t="s">
-        <v>3155</v>
+        <v>3150</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B199">
         <v>66003234</v>
       </c>
       <c r="C199" t="s">
+        <v>3135</v>
+      </c>
+      <c r="D199" s="380" t="s">
+        <v>3499</v>
+      </c>
+      <c r="E199" s="30" t="s">
         <v>3140</v>
-      </c>
-      <c r="D199" s="380" t="s">
-        <v>3506</v>
-      </c>
-      <c r="E199" s="30" t="s">
-        <v>3145</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B200">
         <v>65344753</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>3156</v>
+        <v>3151</v>
       </c>
       <c r="D200" s="380" t="s">
-        <v>3265</v>
+        <v>3258</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3450</v>
+        <v>3443</v>
       </c>
       <c r="B201">
         <v>65633205</v>
       </c>
       <c r="C201" t="s">
-        <v>3141</v>
+        <v>3136</v>
       </c>
       <c r="D201" s="380" t="s">
-        <v>3449</v>
+        <v>3442</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>3036</v>
+        <v>3031</v>
       </c>
       <c r="B202">
         <v>61248427</v>
       </c>
       <c r="C202" t="s">
-        <v>3142</v>
+        <v>3137</v>
       </c>
       <c r="D202" s="380" t="s">
-        <v>3254</v>
+        <v>3247</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33340,30 +33431,30 @@
         <v>69329372</v>
       </c>
       <c r="C203" t="s">
-        <v>3264</v>
+        <v>3257</v>
       </c>
       <c r="D203" s="380" t="s">
-        <v>3278</v>
+        <v>3271</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="30" t="s">
-        <v>3036</v>
+        <v>3031</v>
       </c>
       <c r="B204">
         <v>68168617</v>
       </c>
       <c r="C204" t="s">
-        <v>3143</v>
+        <v>3138</v>
       </c>
       <c r="D204" s="380" t="s">
-        <v>3260</v>
+        <v>3253</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33374,13 +33465,13 @@
         <v>68934853</v>
       </c>
       <c r="C205" t="s">
-        <v>3144</v>
+        <v>3139</v>
       </c>
       <c r="D205" s="380" t="s">
-        <v>3277</v>
+        <v>3270</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33388,16 +33479,16 @@
         <v>2957</v>
       </c>
       <c r="B206" t="s">
-        <v>3297</v>
+        <v>3290</v>
       </c>
       <c r="C206" t="s">
-        <v>3291</v>
+        <v>3284</v>
       </c>
       <c r="D206" s="380" t="s">
-        <v>3294</v>
+        <v>3287</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33408,30 +33499,30 @@
         <v>61430885</v>
       </c>
       <c r="C207" t="s">
-        <v>3295</v>
+        <v>3288</v>
       </c>
       <c r="D207" s="380" t="s">
-        <v>3296</v>
+        <v>3289</v>
       </c>
       <c r="E207" s="30" t="s">
-        <v>3145</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>3324</v>
+        <v>3317</v>
       </c>
       <c r="B208">
         <v>66496809</v>
       </c>
       <c r="C208" t="s">
-        <v>3320</v>
+        <v>3313</v>
       </c>
       <c r="D208" t="s">
-        <v>3322</v>
+        <v>3315</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>3323</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -33442,13 +33533,13 @@
         <v>65583706</v>
       </c>
       <c r="C209" t="s">
-        <v>3377</v>
+        <v>3370</v>
       </c>
       <c r="D209" s="380" t="s">
-        <v>3379</v>
+        <v>3372</v>
       </c>
       <c r="E209" s="30" t="s">
-        <v>3323</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -33459,41 +33550,44 @@
         <v>65574051</v>
       </c>
       <c r="C210" t="s">
-        <v>3321</v>
+        <v>3314</v>
       </c>
       <c r="D210" t="s">
-        <v>3326</v>
+        <v>3319</v>
       </c>
       <c r="E210" s="30" t="s">
-        <v>3323</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B211" t="s">
-        <v>3406</v>
+        <v>3399</v>
       </c>
       <c r="C211" t="s">
-        <v>3378</v>
+        <v>3371</v>
       </c>
       <c r="D211" s="380" t="s">
-        <v>3380</v>
+        <v>3373</v>
       </c>
       <c r="E211" s="30" t="s">
-        <v>3323</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="212" spans="1:5">
-      <c r="C212" s="7" t="s">
-        <v>3625</v>
+      <c r="A212" s="97" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>3663</v>
       </c>
       <c r="D212" t="s">
-        <v>3626</v>
+        <v>3618</v>
       </c>
       <c r="E212" s="30" t="s">
-        <v>3323</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -33504,30 +33598,30 @@
         <v>62863306</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>3431</v>
+        <v>3424</v>
       </c>
       <c r="D213" s="380" t="s">
-        <v>3433</v>
+        <v>3426</v>
       </c>
       <c r="E213" s="30" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>3359</v>
+        <v>3352</v>
       </c>
       <c r="B214">
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3454</v>
+        <v>3447</v>
       </c>
       <c r="D214" t="s">
-        <v>3505</v>
+        <v>3498</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33538,30 +33632,30 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3455</v>
+        <v>3448</v>
       </c>
       <c r="D215" t="s">
-        <v>3447</v>
+        <v>3440</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B216">
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>3432</v>
+        <v>3425</v>
       </c>
       <c r="D216" t="s">
-        <v>3448</v>
+        <v>3441</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33572,13 +33666,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
-        <v>3456</v>
+        <v>3449</v>
       </c>
       <c r="D217" s="380" t="s">
-        <v>3457</v>
+        <v>3450</v>
       </c>
       <c r="E217" s="30" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -33664,7 +33758,7 @@
         <v>234</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>3129</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -33688,7 +33782,7 @@
         <v>1379</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>3070</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -33696,23 +33790,23 @@
         <v>1298</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>3131</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="C258" s="1" t="s">
-        <v>3168</v>
+        <v>3162</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>3169</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="C259" s="1" t="s">
-        <v>3223</v>
+        <v>3217</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>3225</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -33720,10 +33814,7 @@
         <v>1719</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>3228</v>
-      </c>
-      <c r="E260" s="30" t="s">
-        <v>3226</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -36252,7 +36343,7 @@
     <hyperlink ref="C35" r:id="rId147" xr:uid="{0B9BC1FA-777F-4893-8CF4-82697BE54A32}"/>
     <hyperlink ref="C36" r:id="rId148" xr:uid="{BCA3DF1A-B691-43F0-A38B-8A9CC37966CE}"/>
     <hyperlink ref="C41" r:id="rId149" xr:uid="{4C471FD1-B3C4-4EDE-A5AF-F4B3D5022588}"/>
-    <hyperlink ref="C106" r:id="rId150" xr:uid="{DF5BCFDF-5038-49D7-BE66-F8A90983695E}"/>
+    <hyperlink ref="C112" r:id="rId150" xr:uid="{DF5BCFDF-5038-49D7-BE66-F8A90983695E}"/>
     <hyperlink ref="C74" r:id="rId151" xr:uid="{047F61C7-DCB9-4295-B31A-74FCE7EE225F}"/>
     <hyperlink ref="C97" r:id="rId152" xr:uid="{14D67631-2BA0-4065-BDD9-3DC867DED8C5}"/>
     <hyperlink ref="C14" r:id="rId153" xr:uid="{15C9990A-A335-486A-8DDD-2CAE4F944C80}"/>
@@ -36316,15 +36407,17 @@
     <hyperlink ref="C216" r:id="rId211" xr:uid="{3282A0CE-1A34-4BD6-A24E-B0F6E745A388}"/>
     <hyperlink ref="C40" r:id="rId212" xr:uid="{389D92AC-3F0B-46AB-B1BE-A42116881DAD}"/>
     <hyperlink ref="C13" r:id="rId213" xr:uid="{C07A4BC3-5D5F-4788-A303-499D5A7A8C5F}"/>
-    <hyperlink ref="C103" r:id="rId214" xr:uid="{6B571CD1-6955-4385-A8C3-F64B0AEF6E7A}"/>
+    <hyperlink ref="C106" r:id="rId214" xr:uid="{6B571CD1-6955-4385-A8C3-F64B0AEF6E7A}"/>
     <hyperlink ref="C56" r:id="rId215" xr:uid="{46CF7CFA-F5A8-4BC4-AC26-244003072524}"/>
     <hyperlink ref="C57" r:id="rId216" xr:uid="{E7928081-4BDD-48E5-A2F3-120BC2988EF3}"/>
     <hyperlink ref="C140" r:id="rId217" xr:uid="{7C4063D9-F6B8-4E86-84D8-6E0E13C1E3D7}"/>
+    <hyperlink ref="C212" r:id="rId218" xr:uid="{40426CF8-C3BE-4A74-801D-FF9EEC75E297}"/>
+    <hyperlink ref="C103" r:id="rId219" xr:uid="{71898969-7371-48D1-B4B7-FEB2ABB4A37E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId218"/>
-  <drawing r:id="rId219"/>
-  <legacyDrawing r:id="rId220"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId220"/>
+  <drawing r:id="rId221"/>
+  <legacyDrawing r:id="rId222"/>
 </worksheet>
 </file>
 
@@ -36349,7 +36442,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>3425</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36393,7 +36486,7 @@
     </row>
     <row r="6" spans="1:9" s="76" customFormat="1">
       <c r="A6" s="76" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36408,7 +36501,7 @@
         <v>684</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3092</v>
+        <v>3087</v>
       </c>
       <c r="G6" s="222" t="s">
         <v>1485</v>
@@ -36428,13 +36521,13 @@
         <v>1905</v>
       </c>
       <c r="D7" s="183" t="s">
-        <v>3313</v>
+        <v>3306</v>
       </c>
       <c r="E7" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3092</v>
+        <v>3087</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1485</v>
@@ -36460,7 +36553,7 @@
         <v>365</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3092</v>
+        <v>3087</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1485</v>
@@ -36486,7 +36579,7 @@
         <v>365</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3092</v>
+        <v>3087</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1485</v>
@@ -36512,7 +36605,7 @@
         <v>365</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3092</v>
+        <v>3087</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1485</v>
@@ -36538,7 +36631,7 @@
         <v>365</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3092</v>
+        <v>3087</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1485</v>
@@ -36561,7 +36654,7 @@
         <v>2673</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1470</v>
@@ -36588,7 +36681,7 @@
         <v>1906</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1470</v>
@@ -36603,19 +36696,19 @@
     </row>
     <row r="15" spans="1:9" s="183" customFormat="1">
       <c r="A15" s="193" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B15" s="193">
         <v>60389752</v>
       </c>
       <c r="C15" s="191" t="s">
-        <v>3040</v>
+        <v>3035</v>
       </c>
       <c r="D15" s="193" t="s">
-        <v>3041</v>
+        <v>3036</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1470</v>
@@ -36630,7 +36723,7 @@
     </row>
     <row r="16" spans="1:9" s="183" customFormat="1">
       <c r="A16" s="183" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36642,7 +36735,7 @@
         <v>2418</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1470</v>
@@ -36669,7 +36762,7 @@
         <v>1553</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1470</v>
@@ -36684,7 +36777,7 @@
     </row>
     <row r="18" spans="1:9" s="183" customFormat="1">
       <c r="A18" s="193" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B18" s="193">
         <v>60389752</v>
@@ -36696,7 +36789,7 @@
         <v>2238</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1470</v>
@@ -36711,7 +36804,7 @@
     </row>
     <row r="20" spans="1:9" s="76" customFormat="1">
       <c r="A20" s="195" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36726,7 +36819,7 @@
         <v>365</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>427</v>
@@ -36740,7 +36833,7 @@
     </row>
     <row r="21" spans="1:9" s="183" customFormat="1">
       <c r="A21" s="183" t="s">
-        <v>3203</v>
+        <v>3197</v>
       </c>
       <c r="B21" s="183">
         <v>62723048</v>
@@ -36755,7 +36848,7 @@
         <v>365</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>427</v>
@@ -36769,7 +36862,7 @@
     </row>
     <row r="22" spans="1:9" s="183" customFormat="1">
       <c r="A22" s="183" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B22" s="183">
         <v>66439962</v>
@@ -36784,7 +36877,7 @@
         <v>365</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>427</v>
@@ -36798,7 +36891,7 @@
     </row>
     <row r="23" spans="1:9" s="183" customFormat="1">
       <c r="A23" s="183" t="s">
-        <v>3620</v>
+        <v>3613</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -36813,7 +36906,7 @@
         <v>365</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>427</v>
@@ -36842,7 +36935,7 @@
         <v>365</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>427</v>
@@ -36856,7 +36949,7 @@
     </row>
     <row r="25" spans="1:9" s="183" customFormat="1">
       <c r="A25" s="183" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B25" s="183">
         <v>69757885</v>
@@ -36871,7 +36964,7 @@
         <v>365</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>427</v>
@@ -36885,7 +36978,7 @@
     </row>
     <row r="27" spans="1:9" s="76" customFormat="1">
       <c r="A27" s="195" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B27" s="195">
         <v>62747874</v>
@@ -36900,7 +36993,7 @@
         <v>365</v>
       </c>
       <c r="F27" s="195" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>427</v>
@@ -36929,7 +37022,7 @@
         <v>365</v>
       </c>
       <c r="F28" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>427</v>
@@ -36958,7 +37051,7 @@
         <v>365</v>
       </c>
       <c r="F29" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>427</v>
@@ -36972,22 +37065,22 @@
     </row>
     <row r="30" spans="1:9" s="183" customFormat="1">
       <c r="A30" s="183" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B30" s="183">
         <v>63950696</v>
       </c>
       <c r="C30" s="193" t="s">
-        <v>3065</v>
+        <v>3060</v>
       </c>
       <c r="D30" s="193" t="s">
-        <v>3066</v>
+        <v>3061</v>
       </c>
       <c r="E30" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F30" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>427</v>
@@ -37016,7 +37109,7 @@
         <v>365</v>
       </c>
       <c r="F31" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>427</v>
@@ -37030,7 +37123,7 @@
     </row>
     <row r="32" spans="1:9" s="183" customFormat="1">
       <c r="A32" s="193" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B32" s="193">
         <v>64967407</v>
@@ -37045,7 +37138,7 @@
         <v>365</v>
       </c>
       <c r="F32" s="193" t="s">
-        <v>3095</v>
+        <v>3090</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>427</v>
@@ -37059,7 +37152,7 @@
     </row>
     <row r="34" spans="1:9" s="76" customFormat="1">
       <c r="A34" s="76" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B34" s="76">
         <v>60389752</v>
@@ -37074,7 +37167,7 @@
         <v>365</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>3167</v>
+        <v>3161</v>
       </c>
       <c r="G34" s="76" t="s">
         <v>1486</v>
@@ -37101,7 +37194,7 @@
         <v>365</v>
       </c>
       <c r="F35" s="183" t="s">
-        <v>3167</v>
+        <v>3161</v>
       </c>
       <c r="G35" s="183" t="s">
         <v>381</v>
@@ -37130,7 +37223,7 @@
         <v>365</v>
       </c>
       <c r="F36" s="183" t="s">
-        <v>3167</v>
+        <v>3161</v>
       </c>
       <c r="G36" s="183" t="s">
         <v>381</v>
@@ -37159,7 +37252,7 @@
         <v>365</v>
       </c>
       <c r="F37" s="183" t="s">
-        <v>3167</v>
+        <v>3161</v>
       </c>
       <c r="G37" s="183" t="s">
         <v>381</v>
@@ -37188,7 +37281,7 @@
         <v>365</v>
       </c>
       <c r="F38" s="183" t="s">
-        <v>3167</v>
+        <v>3161</v>
       </c>
       <c r="G38" s="183" t="s">
         <v>381</v>
@@ -37202,7 +37295,7 @@
     </row>
     <row r="39" spans="1:9" s="183" customFormat="1">
       <c r="A39" s="183" t="s">
-        <v>3054</v>
+        <v>3049</v>
       </c>
       <c r="B39" s="183">
         <v>68241069</v>
@@ -37217,7 +37310,7 @@
         <v>365</v>
       </c>
       <c r="F39" s="183" t="s">
-        <v>3167</v>
+        <v>3161</v>
       </c>
       <c r="G39" s="183" t="s">
         <v>381</v>
@@ -37246,7 +37339,7 @@
         <v>2627</v>
       </c>
       <c r="F41" s="195" t="s">
-        <v>3208</v>
+        <v>3202</v>
       </c>
       <c r="G41" s="76" t="s">
         <v>1485</v>
@@ -37273,7 +37366,7 @@
         <v>2627</v>
       </c>
       <c r="F42" s="193" t="s">
-        <v>3208</v>
+        <v>3202</v>
       </c>
       <c r="G42" s="183" t="s">
         <v>1485</v>
@@ -37285,7 +37378,7 @@
     </row>
     <row r="43" spans="1:9" s="183" customFormat="1">
       <c r="A43" s="193" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B43" s="193">
         <v>63226030</v>
@@ -37300,7 +37393,7 @@
         <v>2627</v>
       </c>
       <c r="F43" s="193" t="s">
-        <v>3208</v>
+        <v>3202</v>
       </c>
       <c r="G43" s="183" t="s">
         <v>1485</v>
@@ -37327,7 +37420,7 @@
         <v>2627</v>
       </c>
       <c r="F44" s="193" t="s">
-        <v>3208</v>
+        <v>3202</v>
       </c>
       <c r="G44" s="183" t="s">
         <v>1485</v>
@@ -37354,7 +37447,7 @@
         <v>2627</v>
       </c>
       <c r="F45" s="193" t="s">
-        <v>3208</v>
+        <v>3202</v>
       </c>
       <c r="G45" s="183" t="s">
         <v>1485</v>
@@ -37381,7 +37474,7 @@
         <v>2627</v>
       </c>
       <c r="F46" s="193" t="s">
-        <v>3208</v>
+        <v>3202</v>
       </c>
       <c r="G46" s="183" t="s">
         <v>1485</v>
@@ -37402,13 +37495,13 @@
         <v>1720</v>
       </c>
       <c r="D48" s="195" t="s">
-        <v>3475</v>
+        <v>3468</v>
       </c>
       <c r="E48" s="76" t="s">
         <v>2627</v>
       </c>
       <c r="F48" s="195" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G48" s="76" t="s">
         <v>1485</v>
@@ -37435,7 +37528,7 @@
         <v>2627</v>
       </c>
       <c r="F49" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G49" s="183" t="s">
         <v>1485</v>
@@ -37462,7 +37555,7 @@
         <v>2627</v>
       </c>
       <c r="F50" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G50" s="183" t="s">
         <v>1485</v>
@@ -37489,7 +37582,7 @@
         <v>2627</v>
       </c>
       <c r="F51" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G51" s="183" t="s">
         <v>1485</v>
@@ -37507,7 +37600,7 @@
         <v>65174343</v>
       </c>
       <c r="C52" s="193" t="s">
-        <v>3149</v>
+        <v>3144</v>
       </c>
       <c r="D52" s="193" t="s">
         <v>2068</v>
@@ -37516,7 +37609,7 @@
         <v>2627</v>
       </c>
       <c r="F52" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G52" s="183" t="s">
         <v>1485</v>
@@ -37535,7 +37628,7 @@
         <v>2627</v>
       </c>
       <c r="F53" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G53" s="183" t="s">
         <v>1485</v>
@@ -37561,7 +37654,7 @@
         <v>2627</v>
       </c>
       <c r="F55" s="195" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G55" s="76" t="s">
         <v>1485</v>
@@ -37588,7 +37681,7 @@
         <v>2627</v>
       </c>
       <c r="F56" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G56" s="183" t="s">
         <v>1485</v>
@@ -37600,7 +37693,7 @@
     </row>
     <row r="57" spans="1:9" s="183" customFormat="1">
       <c r="A57" s="183" t="s">
-        <v>3212</v>
+        <v>3206</v>
       </c>
       <c r="B57" s="183">
         <v>64403333</v>
@@ -37615,7 +37708,7 @@
         <v>2627</v>
       </c>
       <c r="F57" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G57" s="183" t="s">
         <v>1485</v>
@@ -37642,7 +37735,7 @@
         <v>2627</v>
       </c>
       <c r="F58" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G58" s="183" t="s">
         <v>1485</v>
@@ -37654,7 +37747,7 @@
     </row>
     <row r="59" spans="1:9" s="183" customFormat="1">
       <c r="A59" s="183" t="s">
-        <v>3267</v>
+        <v>3260</v>
       </c>
       <c r="B59" s="183">
         <v>65003516</v>
@@ -37669,7 +37762,7 @@
         <v>2627</v>
       </c>
       <c r="F59" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G59" s="183" t="s">
         <v>1485</v>
@@ -37696,7 +37789,7 @@
         <v>2627</v>
       </c>
       <c r="F60" s="193" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="G60" s="183" t="s">
         <v>1485</v>
@@ -37708,7 +37801,7 @@
     </row>
     <row r="62" spans="1:9" s="76" customFormat="1">
       <c r="A62" s="76" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B62" s="76">
         <v>64147946</v>
@@ -37720,7 +37813,7 @@
         <v>2580</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F62" s="195" t="s">
         <v>2581</v>
@@ -37735,7 +37828,7 @@
     </row>
     <row r="63" spans="1:9" s="183" customFormat="1">
       <c r="A63" s="193" t="s">
-        <v>3263</v>
+        <v>3256</v>
       </c>
       <c r="B63" s="193">
         <v>62646186</v>
@@ -37747,7 +37840,7 @@
         <v>2585</v>
       </c>
       <c r="E63" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F63" s="193" t="s">
         <v>2581</v>
@@ -37774,7 +37867,7 @@
         <v>2387</v>
       </c>
       <c r="E64" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F64" s="193" t="s">
         <v>2581</v>
@@ -37795,13 +37888,13 @@
         <v>68632558</v>
       </c>
       <c r="C65" s="194" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="E65" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F65" s="183" t="s">
         <v>2581</v>
@@ -37827,7 +37920,7 @@
         <v>2128</v>
       </c>
       <c r="E66" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F66" s="183" t="s">
         <v>2581</v>
@@ -37853,7 +37946,7 @@
         <v>2575</v>
       </c>
       <c r="E67" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F67" s="183" t="s">
         <v>2581</v>
@@ -37879,7 +37972,7 @@
         <v>1781</v>
       </c>
       <c r="E69" s="76" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F69" s="195" t="s">
         <v>2579</v>
@@ -37891,7 +37984,7 @@
     </row>
     <row r="70" spans="1:9" s="183" customFormat="1">
       <c r="A70" s="193" t="s">
-        <v>3203</v>
+        <v>3197</v>
       </c>
       <c r="B70" s="193">
         <v>66082581</v>
@@ -37903,7 +37996,7 @@
         <v>2434</v>
       </c>
       <c r="E70" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F70" s="193" t="s">
         <v>2579</v>
@@ -37927,7 +38020,7 @@
         <v>1272</v>
       </c>
       <c r="E71" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F71" s="193" t="s">
         <v>2579</v>
@@ -37951,7 +38044,7 @@
         <v>2472</v>
       </c>
       <c r="E72" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F72" s="193" t="s">
         <v>2579</v>
@@ -37963,7 +38056,7 @@
     </row>
     <row r="73" spans="1:9" s="183" customFormat="1">
       <c r="A73" s="420" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B73" s="193">
         <v>60196388</v>
@@ -37975,7 +38068,7 @@
         <v>2384</v>
       </c>
       <c r="E73" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F73" s="193" t="s">
         <v>2579</v>
@@ -37987,7 +38080,7 @@
     </row>
     <row r="74" spans="1:9" s="183" customFormat="1">
       <c r="A74" s="183" t="s">
-        <v>3212</v>
+        <v>3206</v>
       </c>
       <c r="B74" s="183" t="s">
         <v>1481</v>
@@ -37999,7 +38092,7 @@
         <v>2639</v>
       </c>
       <c r="E74" s="183" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="F74" s="193" t="s">
         <v>2579</v>
@@ -38017,16 +38110,16 @@
         <v>63574980</v>
       </c>
       <c r="C76" s="76" t="s">
-        <v>3138</v>
+        <v>3133</v>
       </c>
       <c r="D76" s="76" t="s">
-        <v>3137</v>
+        <v>3132</v>
       </c>
       <c r="E76" s="76" t="s">
         <v>1381</v>
       </c>
       <c r="F76" s="195" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="G76" s="76" t="s">
         <v>1485</v>
@@ -38052,7 +38145,7 @@
         <v>1381</v>
       </c>
       <c r="F77" s="183" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="G77" s="183" t="s">
         <v>1485</v>
@@ -38063,13 +38156,13 @@
     </row>
     <row r="78" spans="1:9" s="183" customFormat="1">
       <c r="A78" s="183" t="s">
-        <v>3275</v>
+        <v>3268</v>
       </c>
       <c r="B78" s="183">
         <v>68483411</v>
       </c>
       <c r="C78" s="183" t="s">
-        <v>3274</v>
+        <v>3267</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>2236</v>
@@ -38078,7 +38171,7 @@
         <v>1381</v>
       </c>
       <c r="F78" s="183" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="G78" s="183" t="s">
         <v>1485</v>
@@ -38092,19 +38185,19 @@
         <v>2648</v>
       </c>
       <c r="B79" s="183" t="s">
-        <v>3646</v>
+        <v>3638</v>
       </c>
       <c r="C79" s="194" t="s">
         <v>2865</v>
       </c>
       <c r="D79" s="183" t="s">
-        <v>3645</v>
+        <v>3637</v>
       </c>
       <c r="E79" s="183" t="s">
         <v>1381</v>
       </c>
       <c r="F79" s="183" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="G79" s="183" t="s">
         <v>1485</v>
@@ -38130,7 +38223,7 @@
         <v>1381</v>
       </c>
       <c r="F80" s="183" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="G80" s="183" t="s">
         <v>1485</v>
@@ -38156,7 +38249,7 @@
         <v>1381</v>
       </c>
       <c r="F81" s="183" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="G81" s="183" t="s">
         <v>1485</v>
@@ -38182,7 +38275,7 @@
         <v>1710</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1485</v>
@@ -38206,7 +38299,7 @@
         <v>1710</v>
       </c>
       <c r="F84" s="193" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1485</v>
@@ -38214,8 +38307,8 @@
       <c r="I84" s="193"/>
     </row>
     <row r="85" spans="1:9" s="183" customFormat="1">
-      <c r="A85" s="49" t="s">
-        <v>85</v>
+      <c r="A85" s="183" t="s">
+        <v>2703</v>
       </c>
       <c r="B85" s="183">
         <v>65014102</v>
@@ -38230,7 +38323,7 @@
         <v>1710</v>
       </c>
       <c r="F85" s="193" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1485</v>
@@ -38254,7 +38347,7 @@
         <v>1710</v>
       </c>
       <c r="F86" s="193" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1485</v>
@@ -38278,7 +38371,7 @@
         <v>1710</v>
       </c>
       <c r="F87" s="193" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1485</v>
@@ -38302,7 +38395,7 @@
         <v>1710</v>
       </c>
       <c r="F88" s="193" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1485</v>
@@ -38311,7 +38404,7 @@
     </row>
     <row r="90" spans="1:9" s="76" customFormat="1">
       <c r="A90" s="195" t="s">
-        <v>3243</v>
+        <v>3236</v>
       </c>
       <c r="B90" s="195">
         <v>64476521</v>
@@ -38326,7 +38419,7 @@
         <v>2627</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1485</v>
@@ -38353,7 +38446,7 @@
         <v>2627</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1485</v>
@@ -38365,7 +38458,7 @@
     </row>
     <row r="92" spans="1:9" s="183" customFormat="1">
       <c r="A92" s="183" t="s">
-        <v>2846</v>
+        <v>2630</v>
       </c>
       <c r="B92" s="183">
         <v>60389752</v>
@@ -38380,7 +38473,7 @@
         <v>2627</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1485</v>
@@ -38407,7 +38500,7 @@
         <v>2627</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1485</v>
@@ -38434,7 +38527,7 @@
         <v>2627</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1485</v>
@@ -38445,7 +38538,7 @@
       <c r="I94" s="193"/>
     </row>
     <row r="95" spans="1:9" s="183" customFormat="1">
-      <c r="A95" s="193" t="s">
+      <c r="A95" s="276" t="s">
         <v>2265</v>
       </c>
       <c r="B95" s="193">
@@ -38461,7 +38554,7 @@
         <v>2627</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1485</v>
@@ -38473,7 +38566,7 @@
     </row>
     <row r="97" spans="1:9" s="76" customFormat="1">
       <c r="A97" s="195" t="s">
-        <v>3460</v>
+        <v>3453</v>
       </c>
       <c r="B97" s="195">
         <v>66082581</v>
@@ -38485,7 +38578,7 @@
         <v>2397</v>
       </c>
       <c r="E97" s="76" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="F97" s="195" t="s">
         <v>427</v>
@@ -38500,7 +38593,7 @@
     </row>
     <row r="98" spans="1:9" s="183" customFormat="1">
       <c r="A98" s="193" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B98" s="193" t="s">
         <v>2907</v>
@@ -38512,7 +38605,7 @@
         <v>2402</v>
       </c>
       <c r="E98" s="183" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="F98" s="193" t="s">
         <v>427</v>
@@ -38539,7 +38632,7 @@
         <v>2404</v>
       </c>
       <c r="E99" s="183" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="F99" s="193" t="s">
         <v>427</v>
@@ -38560,13 +38653,13 @@
         <v>69017426</v>
       </c>
       <c r="C100" s="194" t="s">
-        <v>3316</v>
+        <v>3309</v>
       </c>
       <c r="D100" s="193" t="s">
         <v>2592</v>
       </c>
       <c r="E100" s="183" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="F100" s="193" t="s">
         <v>427</v>
@@ -38593,7 +38686,7 @@
         <v>2408</v>
       </c>
       <c r="E101" s="183" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="F101" s="193" t="s">
         <v>427</v>
@@ -38614,13 +38707,13 @@
         <v>62723048</v>
       </c>
       <c r="C102" s="194" t="s">
-        <v>3337</v>
+        <v>3330</v>
       </c>
       <c r="D102" s="193" t="s">
-        <v>3336</v>
+        <v>3329</v>
       </c>
       <c r="E102" s="183" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="F102" s="193" t="s">
         <v>427</v>
@@ -38641,16 +38734,16 @@
         <v>68310153</v>
       </c>
       <c r="C104" s="195" t="s">
-        <v>3452</v>
+        <v>3445</v>
       </c>
       <c r="D104" s="195" t="s">
-        <v>3453</v>
+        <v>3446</v>
       </c>
       <c r="E104" s="76" t="s">
         <v>365</v>
       </c>
       <c r="F104" s="195" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G104" s="76" t="s">
         <v>1381</v>
@@ -38664,7 +38757,7 @@
     </row>
     <row r="105" spans="1:9" s="183" customFormat="1">
       <c r="A105" s="193" t="s">
-        <v>3459</v>
+        <v>3452</v>
       </c>
       <c r="B105" s="193">
         <v>63910392</v>
@@ -38677,7 +38770,7 @@
         <v>365</v>
       </c>
       <c r="F105" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G105" s="183" t="s">
         <v>1381</v>
@@ -38691,22 +38784,22 @@
     </row>
     <row r="106" spans="1:9" s="183" customFormat="1">
       <c r="A106" s="193" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B106" s="193">
         <v>68853797</v>
       </c>
       <c r="C106" s="193" t="s">
-        <v>3523</v>
+        <v>3516</v>
       </c>
       <c r="D106" s="193" t="s">
-        <v>3382</v>
+        <v>3375</v>
       </c>
       <c r="E106" s="183" t="s">
         <v>2627</v>
       </c>
       <c r="F106" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G106" s="183" t="s">
         <v>1381</v>
@@ -38725,7 +38818,7 @@
         <v>365</v>
       </c>
       <c r="F107" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G107" s="183" t="s">
         <v>1381</v>
@@ -38746,7 +38839,7 @@
         <v>365</v>
       </c>
       <c r="F108" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G108" s="183" t="s">
         <v>1381</v>
@@ -38767,7 +38860,7 @@
         <v>365</v>
       </c>
       <c r="F109" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G109" s="183" t="s">
         <v>1381</v>
@@ -38781,7 +38874,7 @@
     </row>
     <row r="111" spans="1:9" s="76" customFormat="1">
       <c r="A111" s="76" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B111" s="76">
         <v>62751201</v>
@@ -38796,7 +38889,7 @@
         <v>1381</v>
       </c>
       <c r="F111" s="76" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G111" s="222" t="s">
         <v>1485</v>
@@ -38823,7 +38916,7 @@
         <v>1381</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1485</v>
@@ -38841,16 +38934,16 @@
         <v>64543204</v>
       </c>
       <c r="C113" s="194" t="s">
-        <v>3395</v>
+        <v>3388</v>
       </c>
       <c r="D113" s="183" t="s">
-        <v>3394</v>
+        <v>3387</v>
       </c>
       <c r="E113" s="183" t="s">
         <v>1381</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1485</v>
@@ -38877,7 +38970,7 @@
         <v>1381</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1485</v>
@@ -38904,7 +38997,7 @@
         <v>1381</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1485</v>
@@ -38931,7 +39024,7 @@
         <v>1381</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1485</v>
@@ -38955,7 +39048,7 @@
         <v>1734</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>1567</v>
@@ -38981,7 +39074,7 @@
         <v>895</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F119" s="183" t="s">
         <v>1567</v>
@@ -38995,7 +39088,7 @@
     </row>
     <row r="120" spans="1:9" s="183" customFormat="1">
       <c r="A120" s="183" t="s">
-        <v>3488</v>
+        <v>3481</v>
       </c>
       <c r="B120" s="183">
         <v>69563253</v>
@@ -39007,7 +39100,7 @@
         <v>1021</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F120" s="183" t="s">
         <v>1567</v>
@@ -39021,19 +39114,19 @@
     </row>
     <row r="121" spans="1:9" s="183" customFormat="1">
       <c r="A121" s="183" t="s">
-        <v>3036</v>
+        <v>3031</v>
       </c>
       <c r="B121" s="183">
         <v>63062167</v>
       </c>
       <c r="C121" s="194" t="s">
-        <v>3230</v>
+        <v>3223</v>
       </c>
       <c r="D121" s="183" t="s">
         <v>1284</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F121" s="183" t="s">
         <v>1567</v>
@@ -39059,7 +39152,7 @@
         <v>950</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F122" s="183" t="s">
         <v>1567</v>
@@ -39085,7 +39178,7 @@
         <v>1991</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F123" s="183" t="s">
         <v>1567</v>
@@ -39111,7 +39204,7 @@
         <v>2422</v>
       </c>
       <c r="E125" s="76" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>427</v>
@@ -39137,7 +39230,7 @@
         <v>2424</v>
       </c>
       <c r="E126" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F126" s="193" t="s">
         <v>427</v>
@@ -39164,7 +39257,7 @@
         <v>2426</v>
       </c>
       <c r="E127" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F127" s="193" t="s">
         <v>427</v>
@@ -39179,7 +39272,7 @@
     </row>
     <row r="128" spans="1:9" s="183" customFormat="1">
       <c r="A128" s="49" t="s">
-        <v>3583</v>
+        <v>3576</v>
       </c>
       <c r="B128" s="183">
         <v>67836337</v>
@@ -39188,7 +39281,7 @@
         <v>2498</v>
       </c>
       <c r="E128" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F128" s="193" t="s">
         <v>427</v>
@@ -39215,7 +39308,7 @@
         <v>380</v>
       </c>
       <c r="E129" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F129" s="193" t="s">
         <v>427</v>
@@ -39242,7 +39335,7 @@
         <v>1706</v>
       </c>
       <c r="E130" s="183" t="s">
-        <v>3541</v>
+        <v>3534</v>
       </c>
       <c r="F130" s="193" t="s">
         <v>427</v>
@@ -39271,8 +39364,8 @@
       <c r="E132" s="76" t="s">
         <v>684</v>
       </c>
-      <c r="F132" s="76" t="s">
-        <v>2981</v>
+      <c r="F132" s="284" t="s">
+        <v>2978</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>427</v>
@@ -39286,7 +39379,7 @@
     </row>
     <row r="133" spans="1:9" s="183" customFormat="1">
       <c r="A133" s="183" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B133" s="183">
         <v>64403333</v>
@@ -39301,7 +39394,7 @@
         <v>365</v>
       </c>
       <c r="F133" s="183" t="s">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>427</v>
@@ -39330,7 +39423,7 @@
         <v>365</v>
       </c>
       <c r="F134" s="183" t="s">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>427</v>
@@ -39356,7 +39449,7 @@
         <v>365</v>
       </c>
       <c r="F135" s="183" t="s">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>427</v>
@@ -39370,7 +39463,7 @@
     </row>
     <row r="136" spans="1:9" s="183" customFormat="1">
       <c r="A136" s="183" t="s">
-        <v>3241</v>
+        <v>3234</v>
       </c>
       <c r="B136" s="183">
         <v>66230961</v>
@@ -39385,7 +39478,7 @@
         <v>365</v>
       </c>
       <c r="F136" s="183" t="s">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>427</v>
@@ -39399,7 +39492,7 @@
     </row>
     <row r="137" spans="1:9" s="183" customFormat="1">
       <c r="A137" s="183" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B137" s="183">
         <v>69888391</v>
@@ -39414,7 +39507,7 @@
         <v>365</v>
       </c>
       <c r="F137" s="183" t="s">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>427</v>
@@ -39443,7 +39536,7 @@
         <v>2485</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1485</v>
@@ -39470,7 +39563,7 @@
         <v>2485</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1485</v>
@@ -39497,7 +39590,7 @@
         <v>2485</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1485</v>
@@ -39524,7 +39617,7 @@
         <v>2485</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1485</v>
@@ -39536,7 +39629,7 @@
     </row>
     <row r="143" spans="1:9" s="183" customFormat="1">
       <c r="A143" s="183" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B143" s="183">
         <v>62385671</v>
@@ -39551,7 +39644,7 @@
         <v>2485</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1485</v>
@@ -39578,7 +39671,7 @@
         <v>2485</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1485</v>
@@ -39605,7 +39698,7 @@
         <v>2485</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1485</v>
@@ -39632,7 +39725,7 @@
         <v>2485</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1485</v>
@@ -39644,7 +39737,7 @@
     </row>
     <row r="148" spans="1:9" s="183" customFormat="1">
       <c r="A148" s="183" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B148" s="183">
         <v>60389752</v>
@@ -39659,7 +39752,7 @@
         <v>2485</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1485</v>
@@ -39686,7 +39779,7 @@
         <v>2485</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1485</v>
@@ -39698,22 +39791,22 @@
     </row>
     <row r="150" spans="1:9" s="183" customFormat="1">
       <c r="A150" s="183" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B150" s="183">
         <v>67433224</v>
       </c>
       <c r="C150" s="183" t="s">
-        <v>3017</v>
+        <v>3013</v>
       </c>
       <c r="D150" s="183" t="s">
-        <v>3019</v>
+        <v>3015</v>
       </c>
       <c r="E150" s="183" t="s">
         <v>2485</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1485</v>
@@ -39740,7 +39833,7 @@
         <v>2485</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3029</v>
+        <v>3025</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1485</v>
@@ -39767,7 +39860,7 @@
         <v>2627</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>1485</v>
@@ -39794,7 +39887,7 @@
         <v>2627</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>1485</v>
@@ -39806,7 +39899,7 @@
     </row>
     <row r="155" spans="1:9" s="183" customFormat="1">
       <c r="A155" s="183" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B155" s="183">
         <v>62560788</v>
@@ -39821,7 +39914,7 @@
         <v>2627</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>1485</v>
@@ -39833,7 +39926,7 @@
     </row>
     <row r="156" spans="1:9" s="183" customFormat="1">
       <c r="A156" s="193" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B156" s="193">
         <v>64403333</v>
@@ -39848,7 +39941,7 @@
         <v>2627</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>1485</v>
@@ -39860,22 +39953,22 @@
     </row>
     <row r="157" spans="1:9" s="183" customFormat="1">
       <c r="A157" s="193" t="s">
-        <v>3397</v>
+        <v>3390</v>
       </c>
       <c r="B157" s="193">
         <v>60125401</v>
       </c>
       <c r="C157" s="194" t="s">
-        <v>3396</v>
+        <v>3389</v>
       </c>
       <c r="D157" s="193" t="s">
-        <v>3398</v>
+        <v>3391</v>
       </c>
       <c r="E157" s="183" t="s">
         <v>2627</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>1485</v>
@@ -39887,7 +39980,7 @@
     </row>
     <row r="158" spans="1:9" s="183" customFormat="1">
       <c r="A158" s="193" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B158" s="193">
         <v>64720128</v>
@@ -39902,7 +39995,7 @@
         <v>2627</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>1485</v>
@@ -39914,7 +40007,7 @@
     </row>
     <row r="160" spans="1:9" s="76" customFormat="1">
       <c r="A160" s="76" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B160" s="76">
         <v>69661499</v>
@@ -39929,7 +40022,7 @@
         <v>365</v>
       </c>
       <c r="F160" s="195" t="s">
-        <v>3077</v>
+        <v>3072</v>
       </c>
       <c r="G160" s="76" t="s">
         <v>2491</v>
@@ -39958,7 +40051,7 @@
         <v>365</v>
       </c>
       <c r="F161" s="193" t="s">
-        <v>3077</v>
+        <v>3072</v>
       </c>
       <c r="G161" s="183" t="s">
         <v>2491</v>
@@ -39987,7 +40080,7 @@
         <v>365</v>
       </c>
       <c r="F162" s="193" t="s">
-        <v>3077</v>
+        <v>3072</v>
       </c>
       <c r="G162" s="183" t="s">
         <v>2491</v>
@@ -40001,7 +40094,7 @@
     </row>
     <row r="163" spans="1:9" s="183" customFormat="1">
       <c r="A163" s="235" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B163" s="183">
         <v>62747874</v>
@@ -40016,7 +40109,7 @@
         <v>365</v>
       </c>
       <c r="F163" s="193" t="s">
-        <v>3077</v>
+        <v>3072</v>
       </c>
       <c r="G163" s="183" t="s">
         <v>2491</v>
@@ -40045,7 +40138,7 @@
         <v>365</v>
       </c>
       <c r="F164" s="193" t="s">
-        <v>3077</v>
+        <v>3072</v>
       </c>
       <c r="G164" s="183" t="s">
         <v>2491</v>
@@ -40065,16 +40158,16 @@
         <v>64403333</v>
       </c>
       <c r="C165" s="194" t="s">
-        <v>3399</v>
+        <v>3392</v>
       </c>
       <c r="D165" s="423" t="s">
-        <v>3398</v>
+        <v>3391</v>
       </c>
       <c r="E165" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F165" s="193" t="s">
-        <v>3077</v>
+        <v>3072</v>
       </c>
       <c r="G165" s="183" t="s">
         <v>2491</v>
@@ -40109,7 +40202,7 @@
     </row>
     <row r="192" spans="1:9" s="387" customFormat="1" ht="23.5">
       <c r="B192" s="387" t="s">
-        <v>3018</v>
+        <v>3014</v>
       </c>
       <c r="C192" s="388"/>
       <c r="D192" s="389"/>
@@ -40135,7 +40228,7 @@
         <v>319</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>3017</v>
+        <v>3013</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40148,7 +40241,7 @@
         <v>316</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>3040</v>
+        <v>3035</v>
       </c>
       <c r="E195" s="30"/>
       <c r="F195"/>
@@ -40161,7 +40254,7 @@
         <v>444</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>3065</v>
+        <v>3060</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40172,7 +40265,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>3138</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40180,7 +40273,7 @@
         <v>1364</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>3149</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40188,7 +40281,7 @@
         <v>1717</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>3230</v>
+        <v>3223</v>
       </c>
       <c r="F199" s="405"/>
     </row>
@@ -40197,7 +40290,7 @@
         <v>1343</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>3274</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40205,7 +40298,7 @@
         <v>411</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>3316</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -40213,7 +40306,7 @@
         <v>716</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>3337</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -40221,7 +40314,7 @@
         <v>284</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>3395</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40229,7 +40322,7 @@
         <v>2495</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>3396</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40239,7 +40332,7 @@
         <v>470</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>3452</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40247,7 +40340,7 @@
         <v>222</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>3523</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41585,10 +41678,10 @@
         <v>712</v>
       </c>
       <c r="H3" t="s">
-        <v>3279</v>
+        <v>3272</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3492</v>
+        <v>3485</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41618,16 +41711,16 @@
         <v>2855</v>
       </c>
       <c r="I4" t="s">
-        <v>3387</v>
+        <v>3380</v>
       </c>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B5" t="s">
-        <v>3231</v>
+        <v>3224</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>485</v>
@@ -41636,7 +41729,7 @@
         <v>1573</v>
       </c>
       <c r="E5" t="s">
-        <v>3529</v>
+        <v>3522</v>
       </c>
       <c r="F5" t="s">
         <v>2253</v>
@@ -41645,10 +41738,10 @@
         <v>520</v>
       </c>
       <c r="H5" s="437" t="s">
-        <v>2980</v>
+        <v>2977</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3665</v>
+        <v>3657</v>
       </c>
       <c r="J5" t="s">
         <v>1436</v>
@@ -41676,7 +41769,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B7" s="180">
         <v>64403333</v>
@@ -41702,13 +41795,13 @@
         <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>3363</v>
+        <v>3356</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>2139</v>
       </c>
       <c r="D8" t="s">
-        <v>3362</v>
+        <v>3355</v>
       </c>
       <c r="E8" t="s">
         <v>2436</v>
@@ -41720,10 +41813,10 @@
         <v>253</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3655</v>
+        <v>3647</v>
       </c>
       <c r="I8" t="s">
-        <v>3098</v>
+        <v>3093</v>
       </c>
       <c r="J8"/>
     </row>
@@ -41741,7 +41834,7 @@
         <v>2927</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3097</v>
+        <v>3092</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>2140</v>
@@ -41750,10 +41843,10 @@
         <v>253</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>2985</v>
+        <v>2982</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3195</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -41787,7 +41880,7 @@
         <v>441</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3603</v>
+        <v>3596</v>
       </c>
       <c r="I12" s="49" t="s">
         <v>2766</v>
@@ -41832,34 +41925,34 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="10" t="s">
-        <v>3242</v>
+        <v>3235</v>
       </c>
       <c r="B16" s="10">
         <v>67663098</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>3200</v>
+        <v>3194</v>
       </c>
       <c r="D16" t="s">
-        <v>3199</v>
+        <v>3193</v>
       </c>
       <c r="E16" t="s">
-        <v>3258</v>
+        <v>3251</v>
       </c>
       <c r="F16" t="s">
-        <v>3259</v>
+        <v>3252</v>
       </c>
       <c r="G16" t="s">
         <v>122</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>3273</v>
+        <v>3266</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>3276</v>
+        <v>3269</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>3360</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="19" customFormat="1"/>
@@ -41985,15 +42078,15 @@
         <v>522</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>3000</v>
+        <v>2996</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3496</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>3036</v>
+        <v>3031</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>2535</v>
@@ -42013,8 +42106,8 @@
       <c r="G7" t="s">
         <v>522</v>
       </c>
-      <c r="H7" t="s">
-        <v>3089</v>
+      <c r="H7" s="49" t="s">
+        <v>3084</v>
       </c>
       <c r="I7" s="276" t="s">
         <v>2770</v>
@@ -42096,7 +42189,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>3241</v>
+        <v>3234</v>
       </c>
       <c r="B15" s="10">
         <v>68543713</v>
@@ -42105,7 +42198,7 @@
         <v>2296</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3533</v>
+        <v>3526</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>976</v>
@@ -42117,10 +42210,10 @@
         <v>522</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3534</v>
+        <v>3527</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3543</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42193,12 +42286,12 @@
         <v>2689</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>3175</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="10" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B19" s="10">
         <v>65188271</v>
@@ -42219,7 +42312,7 @@
         <v>522</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>3466</v>
+        <v>3459</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2750</v>
@@ -42256,10 +42349,10 @@
         <v>522</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>3289</v>
+        <v>3282</v>
       </c>
       <c r="I22" s="276" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -42285,10 +42378,10 @@
         <v>522</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>3284</v>
+        <v>3277</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>3285</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -42302,7 +42395,7 @@
         <v>2567</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3649</v>
+        <v>3641</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>976</v>
@@ -42314,10 +42407,10 @@
         <v>522</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>3240</v>
+        <v>3233</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3473</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42327,7 +42420,7 @@
         <v>2582</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3532</v>
+        <v>3525</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>976</v>
@@ -42515,13 +42608,13 @@
         <v>2600</v>
       </c>
       <c r="B4" t="s">
-        <v>3612</v>
+        <v>3605</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1929</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3611</v>
+        <v>3604</v>
       </c>
       <c r="E4" t="s">
         <v>1930</v>
@@ -42533,10 +42626,10 @@
         <v>980</v>
       </c>
       <c r="H4" t="s">
-        <v>3630</v>
+        <v>3622</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3640</v>
+        <v>3632</v>
       </c>
       <c r="J4" s="97"/>
     </row>
@@ -42586,10 +42679,10 @@
         <v>980</v>
       </c>
       <c r="H6" t="s">
-        <v>3663</v>
+        <v>3655</v>
       </c>
       <c r="I6" t="s">
-        <v>3587</v>
+        <v>3580</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2322</v>
@@ -42597,16 +42690,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="10" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>3051</v>
+        <v>3046</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>2394</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3050</v>
+        <v>3045</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>2395</v>
@@ -42618,13 +42711,13 @@
         <v>980</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>3052</v>
+        <v>3047</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3064</v>
+        <v>3059</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3522</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42632,73 +42725,73 @@
         <v>2576</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>3302</v>
+        <v>3295</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>3299</v>
+        <v>3292</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>3298</v>
+        <v>3291</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>3300</v>
+        <v>3293</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>3301</v>
+        <v>3294</v>
       </c>
       <c r="G8" t="s">
         <v>980</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3531</v>
+        <v>3524</v>
       </c>
       <c r="I8" s="279"/>
       <c r="J8" s="10" t="s">
-        <v>3542</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>3546</v>
+        <v>3539</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>3547</v>
+        <v>3540</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>3544</v>
+        <v>3537</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>3298</v>
+        <v>3291</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3545</v>
+        <v>3538</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>3301</v>
+        <v>3294</v>
       </c>
       <c r="G9" t="s">
         <v>980</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>3548</v>
+        <v>3541</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>3549</v>
+        <v>3542</v>
       </c>
       <c r="J9" t="s">
-        <v>3607</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="279"/>
       <c r="C10" s="3" t="s">
-        <v>3627</v>
+        <v>3619</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3628</v>
+        <v>3620</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>3629</v>
+        <v>3621</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2396</v>
@@ -42768,13 +42861,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>3026</v>
+        <v>3022</v>
       </c>
       <c r="B5">
         <v>68658411</v>
       </c>
       <c r="C5" t="s">
-        <v>3025</v>
+        <v>3021</v>
       </c>
       <c r="D5" t="s">
         <v>2829</v>
@@ -42869,7 +42962,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B10" s="10">
         <v>64676716</v>
@@ -42878,7 +42971,7 @@
         <v>1849</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3504</v>
+        <v>3497</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2802</v>
@@ -42919,7 +43012,7 @@
         <v>65124748</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>3369</v>
+        <v>3362</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>2829</v>
@@ -42940,7 +43033,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3400</v>
+        <v>3393</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2829</v>
@@ -43116,7 +43209,7 @@
     <row r="1" spans="1:9" s="422" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="421"/>
       <c r="B1" s="421" t="s">
-        <v>3388</v>
+        <v>3381</v>
       </c>
       <c r="C1" s="421"/>
     </row>
@@ -43125,25 +43218,25 @@
         <v>148</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3451</v>
+        <v>3444</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3615</v>
+        <v>3608</v>
       </c>
       <c r="E4" t="s">
-        <v>3389</v>
+        <v>3382</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>3616</v>
+        <v>3609</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>3403</v>
+        <v>3396</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3592</v>
+        <v>3585</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3609</v>
+        <v>3602</v>
       </c>
     </row>
   </sheetData>
@@ -43345,7 +43438,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="B27" t="s">
         <v>297</v>
@@ -43362,7 +43455,7 @@
         <v>2864</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>2863</v>
@@ -43373,7 +43466,7 @@
         <v>2864</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -43489,7 +43582,7 @@
         <v>2727</v>
       </c>
       <c r="C5" s="328" t="s">
-        <v>3237</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="328" customFormat="1">
@@ -43497,10 +43590,10 @@
         <v>2706</v>
       </c>
       <c r="B6" s="328" t="s">
-        <v>3236</v>
+        <v>3229</v>
       </c>
       <c r="C6" s="328" t="s">
-        <v>3236</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="328" customFormat="1">
@@ -43575,10 +43668,10 @@
         <v>2736</v>
       </c>
       <c r="H14" s="334" t="s">
-        <v>3244</v>
+        <v>3237</v>
       </c>
       <c r="I14" s="334" t="s">
-        <v>3247</v>
+        <v>3240</v>
       </c>
       <c r="L14" s="334"/>
       <c r="M14" s="334"/>
@@ -43606,10 +43699,10 @@
         <v>2737</v>
       </c>
       <c r="H15" s="335" t="s">
-        <v>3245</v>
+        <v>3238</v>
       </c>
       <c r="I15" s="335" t="s">
-        <v>3248</v>
+        <v>3241</v>
       </c>
       <c r="L15" s="335"/>
       <c r="M15" s="335"/>
@@ -43637,7 +43730,7 @@
         <v>2738</v>
       </c>
       <c r="H16" s="335" t="s">
-        <v>3246</v>
+        <v>3239</v>
       </c>
       <c r="I16" s="335" t="s">
         <v>1381</v>
@@ -43650,7 +43743,7 @@
         <v>2711</v>
       </c>
       <c r="B17" s="407" t="s">
-        <v>3233</v>
+        <v>3226</v>
       </c>
       <c r="C17" s="407"/>
       <c r="D17" s="407"/>
@@ -43667,7 +43760,7 @@
         <v>2706</v>
       </c>
       <c r="B18" s="407" t="s">
-        <v>3234</v>
+        <v>3227</v>
       </c>
       <c r="C18" s="407"/>
       <c r="D18" s="407"/>
@@ -43684,7 +43777,7 @@
         <v>2707</v>
       </c>
       <c r="B19" s="407" t="s">
-        <v>3235</v>
+        <v>3228</v>
       </c>
       <c r="C19" s="407"/>
       <c r="D19" s="407"/>
@@ -43813,7 +43906,7 @@
         <v>2717</v>
       </c>
       <c r="C29" s="347" t="s">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="D29" s="347"/>
       <c r="E29" s="347"/>
@@ -43832,7 +43925,7 @@
         <v>2718</v>
       </c>
       <c r="C30" s="348" t="s">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="D30" s="348"/>
       <c r="E30" s="348"/>
@@ -44586,7 +44679,7 @@
         <v>2364</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3044</v>
+        <v>3039</v>
       </c>
       <c r="L7" s="3"/>
     </row>
@@ -44642,10 +44735,10 @@
         <v>160</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>3255</v>
+        <v>3248</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3173</v>
+        <v>3167</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>828</v>
@@ -44653,7 +44746,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>3349</v>
+        <v>3342</v>
       </c>
       <c r="B10" s="4">
         <v>67916500</v>
@@ -44674,10 +44767,10 @@
         <v>247</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>3279</v>
+        <v>3272</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3086</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44703,10 +44796,10 @@
         <v>247</v>
       </c>
       <c r="H11" t="s">
-        <v>3352</v>
+        <v>3345</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -44732,10 +44825,10 @@
         <v>247</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3385</v>
+        <v>3378</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3442</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -44761,10 +44854,10 @@
         <v>247</v>
       </c>
       <c r="H13" s="220" t="s">
-        <v>3124</v>
+        <v>3119</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>3371</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1">
@@ -44790,25 +44883,25 @@
         <v>247</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>3317</v>
+        <v>3310</v>
       </c>
       <c r="I14" s="220" t="s">
-        <v>3334</v>
+        <v>3327</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="105" t="s">
-        <v>3216</v>
+        <v>3210</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3217</v>
+        <v>3211</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>343</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>3215</v>
+        <v>3209</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>1584</v>
@@ -44820,10 +44913,10 @@
         <v>901</v>
       </c>
       <c r="H15" t="s">
-        <v>3079</v>
+        <v>3074</v>
       </c>
       <c r="I15" t="s">
-        <v>3491</v>
+        <v>3484</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>503</v>
@@ -44831,16 +44924,16 @@
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1">
       <c r="A16" s="4" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>2964</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>2965</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>2784</v>
       </c>
       <c r="D16" t="s">
-        <v>3193</v>
+        <v>3187</v>
       </c>
       <c r="E16" t="s">
         <v>2786</v>
@@ -44852,10 +44945,10 @@
         <v>160</v>
       </c>
       <c r="H16" t="s">
-        <v>3266</v>
+        <v>3259</v>
       </c>
       <c r="I16" t="s">
-        <v>3194</v>
+        <v>3188</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>817</v>
@@ -44863,7 +44956,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -44898,19 +44991,19 @@
         <v>2309</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>3347</v>
+        <v>3340</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3348</v>
+        <v>3341</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>247</v>
       </c>
       <c r="H18" t="s">
-        <v>3562</v>
+        <v>3555</v>
       </c>
       <c r="I18" t="s">
-        <v>3340</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1">
@@ -44921,13 +45014,13 @@
         <v>64403333</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3117</v>
+        <v>3112</v>
       </c>
       <c r="D19" t="s">
         <v>2785</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>3116</v>
+        <v>3111</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>2616</v>
@@ -44940,7 +45033,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="4" t="s">
-        <v>3212</v>
+        <v>3206</v>
       </c>
       <c r="B20">
         <v>64403333</v>
@@ -45033,7 +45126,7 @@
         <v>160</v>
       </c>
       <c r="H23" t="s">
-        <v>3113</v>
+        <v>3108</v>
       </c>
       <c r="I23" s="308" t="s">
         <v>2744</v>
@@ -45051,10 +45144,10 @@
         <v>1689</v>
       </c>
       <c r="D24" t="s">
-        <v>3591</v>
+        <v>3584</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3593</v>
+        <v>3586</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2616</v>
@@ -45065,7 +45158,7 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1">
       <c r="A25" s="4" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2619</v>
@@ -45077,7 +45170,7 @@
         <v>2102</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3483</v>
+        <v>3476</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2622</v>
@@ -45086,7 +45179,7 @@
         <v>247</v>
       </c>
       <c r="H25" s="437" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="I25" s="308" t="s">
         <v>2887</v>
@@ -45114,11 +45207,11 @@
       <c r="G26" t="s">
         <v>247</v>
       </c>
-      <c r="H26" t="s">
-        <v>3150</v>
+      <c r="H26" s="49" t="s">
+        <v>3145</v>
       </c>
       <c r="I26" t="s">
-        <v>3009</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -45126,7 +45219,7 @@
         <v>2678</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>3135</v>
+        <v>3130</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>370</v>
@@ -45144,10 +45237,10 @@
         <v>160</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>3354</v>
+        <v>3347</v>
       </c>
       <c r="I27" t="s">
-        <v>3085</v>
+        <v>3080</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>825</v>
@@ -45155,7 +45248,7 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1">
       <c r="A28" t="s">
-        <v>3359</v>
+        <v>3352</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2609</v>
@@ -45167,7 +45260,7 @@
         <v>2103</v>
       </c>
       <c r="E28" t="s">
-        <v>3608</v>
+        <v>3601</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2622</v>
@@ -45179,7 +45272,7 @@
         <v>2853</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>3256</v>
+        <v>3249</v>
       </c>
       <c r="K28"/>
     </row>
@@ -45194,10 +45287,10 @@
         <v>353</v>
       </c>
       <c r="D29" s="75" t="s">
-        <v>3261</v>
+        <v>3254</v>
       </c>
       <c r="E29" t="s">
-        <v>3201</v>
+        <v>3195</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>2622</v>
@@ -45206,26 +45299,26 @@
         <v>253</v>
       </c>
       <c r="H29" t="s">
-        <v>3262</v>
+        <v>3255</v>
       </c>
       <c r="I29" t="s">
-        <v>3176</v>
+        <v>3170</v>
       </c>
       <c r="J29" s="4"/>
       <c r="L29" s="135"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3555</v>
+        <v>3548</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>407</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3554</v>
+        <v>3547</v>
       </c>
       <c r="E30" t="s">
         <v>2499</v>
@@ -45237,15 +45330,15 @@
         <v>160</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3559</v>
+        <v>3552</v>
       </c>
       <c r="I30" t="s">
-        <v>2999</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>3216</v>
+        <v>3210</v>
       </c>
       <c r="B31" s="4">
         <v>69409351</v>
@@ -45266,10 +45359,10 @@
         <v>160</v>
       </c>
       <c r="H31" t="s">
-        <v>3090</v>
+        <v>3085</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3662</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45295,10 +45388,10 @@
         <v>160</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3463</v>
+        <v>3456</v>
       </c>
       <c r="I32" s="49" t="s">
-        <v>2977</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -45306,7 +45399,7 @@
         <v>2652</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2984</v>
+        <v>2981</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>2783</v>
@@ -45324,10 +45417,10 @@
         <v>160</v>
       </c>
       <c r="H33" t="s">
-        <v>3134</v>
+        <v>3129</v>
       </c>
       <c r="I33" t="s">
-        <v>3493</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45356,7 +45449,7 @@
         <v>2788</v>
       </c>
       <c r="I34" t="s">
-        <v>3164</v>
+        <v>3158</v>
       </c>
       <c r="J34" s="4"/>
     </row>
@@ -45365,13 +45458,13 @@
         <v>148</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3423</v>
+        <v>3416</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2781</v>
       </c>
       <c r="D35" t="s">
-        <v>3422</v>
+        <v>3415</v>
       </c>
       <c r="E35" t="s">
         <v>2786</v>
@@ -45383,10 +45476,10 @@
         <v>2789</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3468</v>
+        <v>3461</v>
       </c>
       <c r="I35" t="s">
-        <v>3481</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -45412,10 +45505,10 @@
         <v>160</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="I36" t="s">
-        <v>3057</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45423,13 +45516,13 @@
         <v>2638</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3159</v>
+        <v>3154</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>2796</v>
       </c>
       <c r="D37" t="s">
-        <v>3331</v>
+        <v>3324</v>
       </c>
       <c r="E37" t="s">
         <v>2798</v>
@@ -45441,10 +45534,10 @@
         <v>160</v>
       </c>
       <c r="H37" t="s">
-        <v>3332</v>
+        <v>3325</v>
       </c>
       <c r="I37" t="s">
-        <v>3410</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45452,7 +45545,7 @@
         <v>158</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3574</v>
+        <v>3567</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2797</v>
@@ -45506,10 +45599,10 @@
         <v>2684</v>
       </c>
       <c r="J45" s="49" t="s">
-        <v>3111</v>
+        <v>3106</v>
       </c>
       <c r="K45" t="s">
-        <v>3405</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -45915,13 +46008,13 @@
         <v>158</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3577</v>
+        <v>3570</v>
       </c>
       <c r="C2" s="277" t="s">
         <v>257</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3576</v>
+        <v>3569</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1334</v>
@@ -45933,21 +46026,21 @@
         <v>62</v>
       </c>
       <c r="H2" s="301" t="s">
-        <v>3623</v>
+        <v>3616</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3590</v>
+        <v>3583</v>
       </c>
       <c r="J2" s="107" t="s">
-        <v>3374</v>
+        <v>3367</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>3339</v>
+        <v>3332</v>
       </c>
       <c r="M2" s="159"/>
     </row>
     <row r="4" spans="1:13" s="32" customFormat="1">
-      <c r="A4" s="107" t="s">
+      <c r="A4" s="397" t="s">
         <v>2846</v>
       </c>
       <c r="B4" s="32" t="s">
@@ -45969,16 +46062,16 @@
         <v>273</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>3043</v>
+        <v>3038</v>
       </c>
       <c r="I4" s="217" t="s">
-        <v>3081</v>
+        <v>3076</v>
       </c>
       <c r="J4" s="139" t="s">
-        <v>3353</v>
+        <v>3346</v>
       </c>
       <c r="K4" s="139" t="s">
-        <v>3147</v>
+        <v>3142</v>
       </c>
       <c r="M4" s="39"/>
     </row>
@@ -46005,14 +46098,14 @@
         <v>65</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>3239</v>
+        <v>3232</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>3430</v>
+        <v>3423</v>
       </c>
       <c r="J5" s="145"/>
       <c r="K5" s="217" t="s">
-        <v>3024</v>
+        <v>3020</v>
       </c>
       <c r="M5" s="36"/>
     </row>
@@ -46024,7 +46117,7 @@
         <v>2271</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="D6" s="30" t="s">
         <v>2534</v>
@@ -46039,22 +46132,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3467</v>
+        <v>3460</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3582</v>
+        <v>3575</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>3160</v>
+        <v>3155</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3056</v>
+        <v>3051</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3054</v>
+        <v>3049</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1245</v>
@@ -46075,16 +46168,16 @@
         <v>731</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3091</v>
+        <v>3086</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3443</v>
+        <v>3436</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>2871</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3469</v>
+        <v>3462</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46111,13 +46204,13 @@
         <v>65</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>3357</v>
+        <v>3350</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3540</v>
+        <v>3533</v>
       </c>
       <c r="J8" s="107" t="s">
-        <v>3370</v>
+        <v>3363</v>
       </c>
       <c r="K8" s="278" t="s">
         <v>2943</v>
@@ -46126,7 +46219,7 @@
     </row>
     <row r="9" spans="1:13" s="107" customFormat="1">
       <c r="A9" s="304" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>1732</v>
@@ -46147,22 +46240,22 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3491</v>
+        <v>3484</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3526</v>
+        <v>3519</v>
       </c>
       <c r="J9" s="217" t="s">
         <v>2909</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3494</v>
+        <v>3487</v>
       </c>
       <c r="M9" s="36"/>
     </row>
     <row r="10" spans="1:13" s="30" customFormat="1">
       <c r="A10" s="30" t="s">
-        <v>3038</v>
+        <v>3033</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>2048</v>
@@ -46183,22 +46276,22 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3114</v>
+        <v>3109</v>
       </c>
       <c r="I10" s="49" t="s">
         <v>2946</v>
       </c>
       <c r="J10" s="219" t="s">
-        <v>3280</v>
+        <v>3273</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3527</v>
+        <v>3520</v>
       </c>
       <c r="M10" s="34"/>
     </row>
     <row r="11" spans="1:13" s="30" customFormat="1">
       <c r="A11" s="107" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B11" s="107">
         <v>62657225</v>
@@ -46219,16 +46312,16 @@
         <v>610</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3663</v>
+        <v>3655</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>3350</v>
+        <v>3343</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3464</v>
+        <v>3457</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3098</v>
+        <v>3093</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -46243,7 +46336,7 @@
         <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3221</v>
+        <v>3215</v>
       </c>
       <c r="E12" s="106" t="s">
         <v>922</v>
@@ -46255,52 +46348,52 @@
         <v>248</v>
       </c>
       <c r="H12" s="106" t="s">
-        <v>3346</v>
+        <v>3339</v>
       </c>
       <c r="I12" s="106" t="s">
-        <v>3333</v>
+        <v>3326</v>
       </c>
       <c r="J12" s="106" t="s">
-        <v>3268</v>
+        <v>3261</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3220</v>
+        <v>3214</v>
       </c>
       <c r="M12" s="151"/>
     </row>
     <row r="13" spans="1:13" s="107" customFormat="1">
       <c r="A13" s="140" t="s">
-        <v>3036</v>
+        <v>3031</v>
       </c>
       <c r="B13" s="107" t="s">
-        <v>3062</v>
+        <v>3057</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>933</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3642</v>
+        <v>3634</v>
       </c>
       <c r="E13" s="140" t="s">
-        <v>3013</v>
+        <v>3009</v>
       </c>
       <c r="F13" s="140" t="s">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="G13" s="106" t="s">
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3643</v>
+        <v>3635</v>
       </c>
       <c r="I13" s="145" t="s">
-        <v>3644</v>
+        <v>3636</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3148</v>
+        <v>3143</v>
       </c>
       <c r="K13" t="s">
-        <v>3010</v>
+        <v>3006</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46327,7 +46420,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3392</v>
+        <v>3385</v>
       </c>
       <c r="I14" s="424" t="s">
         <v>2365</v>
@@ -46360,16 +46453,16 @@
         <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>3318</v>
+        <v>3311</v>
       </c>
       <c r="I15" t="s">
-        <v>3586</v>
+        <v>3579</v>
       </c>
       <c r="J15" t="s">
-        <v>3099</v>
+        <v>3094</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3482</v>
+        <v>3475</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46421,16 +46514,16 @@
         <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>3088</v>
+        <v>3083</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3595</v>
+        <v>3588</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3439</v>
+        <v>3432</v>
       </c>
       <c r="K17" s="220" t="s">
-        <v>3257</v>
+        <v>3250</v>
       </c>
       <c r="M17" s="34"/>
     </row>
@@ -46457,16 +46550,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3575</v>
+        <v>3568</v>
       </c>
       <c r="I18" t="s">
-        <v>3063</v>
+        <v>3058</v>
       </c>
       <c r="J18" t="s">
-        <v>3079</v>
+        <v>3074</v>
       </c>
       <c r="K18" t="s">
-        <v>3393</v>
+        <v>3386</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46481,7 +46574,7 @@
         <v>1750</v>
       </c>
       <c r="D19" s="134" t="s">
-        <v>3003</v>
+        <v>2999</v>
       </c>
       <c r="E19" t="s">
         <v>1753</v>
@@ -46493,16 +46586,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3602</v>
+        <v>3595</v>
       </c>
       <c r="I19" t="s">
-        <v>3381</v>
+        <v>3374</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="K19" t="s">
-        <v>3539</v>
+        <v>3532</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46517,7 +46610,7 @@
         <v>2643</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3514</v>
+        <v>3507</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2548</v>
@@ -46529,16 +46622,16 @@
         <v>65</v>
       </c>
       <c r="H20" s="318" t="s">
-        <v>3269</v>
+        <v>3262</v>
       </c>
       <c r="I20" t="s">
-        <v>3515</v>
+        <v>3508</v>
       </c>
       <c r="J20" t="s">
-        <v>3517</v>
+        <v>3510</v>
       </c>
       <c r="K20" t="s">
-        <v>3558</v>
+        <v>3551</v>
       </c>
       <c r="M20" s="36"/>
     </row>
@@ -46603,7 +46696,7 @@
     </row>
     <row r="31" spans="1:13" s="30" customFormat="1">
       <c r="A31" s="107" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B31" s="107">
         <v>64403333</v>
@@ -46698,7 +46791,7 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B35">
         <v>60389752</v>
@@ -46746,7 +46839,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="30" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B37" s="30">
         <v>64403333</v>
@@ -46808,10 +46901,10 @@
         <v>2227</v>
       </c>
       <c r="E39" s="140" t="s">
-        <v>3327</v>
+        <v>3320</v>
       </c>
       <c r="F39" s="140" t="s">
-        <v>3328</v>
+        <v>3321</v>
       </c>
       <c r="G39" s="106" t="s">
         <v>731</v>
@@ -46849,7 +46942,7 @@
         <v>372</v>
       </c>
       <c r="H43" s="32" t="s">
-        <v>3044</v>
+        <v>3039</v>
       </c>
       <c r="I43" s="139"/>
       <c r="K43" s="240"/>
@@ -46867,7 +46960,7 @@
         <v>2945</v>
       </c>
       <c r="B45" t="s">
-        <v>3180</v>
+        <v>3174</v>
       </c>
       <c r="C45" t="s">
         <v>2680</v>
@@ -46876,7 +46969,7 @@
         <v>2681</v>
       </c>
       <c r="E45" t="s">
-        <v>3120</v>
+        <v>3115</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2682</v>
@@ -46884,14 +46977,14 @@
       <c r="G45" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="H45" t="s">
-        <v>3004</v>
+      <c r="H45" s="49" t="s">
+        <v>3000</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>3165</v>
+        <v>3159</v>
       </c>
       <c r="J45" t="s">
-        <v>3426</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47430,7 +47523,7 @@
     </row>
     <row r="105" spans="2:5">
       <c r="D105" s="1" t="s">
-        <v>3007</v>
+        <v>3003</v>
       </c>
     </row>
   </sheetData>
@@ -47647,7 +47740,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="45" t="s">
-        <v>3123</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -47783,7 +47876,7 @@
         <v>6.83</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>3290</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -47792,7 +47885,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3525</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48044,7 +48137,7 @@
         <v>144</v>
       </c>
       <c r="B6" s="248" t="s">
-        <v>3338</v>
+        <v>3331</v>
       </c>
       <c r="C6" s="247" t="s">
         <v>1326</v>
@@ -48062,13 +48155,13 @@
         <v>360</v>
       </c>
       <c r="H6" s="248" t="s">
-        <v>3172</v>
+        <v>3166</v>
       </c>
       <c r="I6" s="245" t="s">
-        <v>3351</v>
+        <v>3344</v>
       </c>
       <c r="J6" s="296" t="s">
-        <v>3415</v>
+        <v>3408</v>
       </c>
       <c r="K6" s="248" t="s">
         <v>480</v>
@@ -48096,19 +48189,19 @@
         <v>1055</v>
       </c>
       <c r="F8" s="266" t="s">
-        <v>3157</v>
+        <v>3152</v>
       </c>
       <c r="G8" s="266" t="s">
         <v>696</v>
       </c>
       <c r="H8" s="296" t="s">
-        <v>3125</v>
+        <v>3120</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>3535</v>
+        <v>3528</v>
       </c>
       <c r="J8" s="266" t="s">
-        <v>3281</v>
+        <v>3274</v>
       </c>
       <c r="K8" s="266" t="s">
         <v>717</v>
@@ -48137,10 +48230,10 @@
         <v>253</v>
       </c>
       <c r="H9" s="106" t="s">
-        <v>3151</v>
+        <v>3146</v>
       </c>
       <c r="I9" s="106" t="s">
-        <v>3256</v>
+        <v>3249</v>
       </c>
       <c r="J9" s="106" t="s">
         <v>2308</v>
@@ -48163,7 +48256,7 @@
         <v>1454</v>
       </c>
       <c r="F10" s="264" t="s">
-        <v>3184</v>
+        <v>3178</v>
       </c>
       <c r="G10" s="264" t="s">
         <v>962</v>
@@ -48195,20 +48288,20 @@
         <v>696</v>
       </c>
       <c r="H11" s="265" t="s">
-        <v>3495</v>
+        <v>3488</v>
       </c>
       <c r="I11" s="296" t="s">
-        <v>3487</v>
+        <v>3480</v>
       </c>
       <c r="J11" s="265" t="s">
-        <v>3386</v>
+        <v>3379</v>
       </c>
       <c r="K11" s="246" t="s">
         <v>1239</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="263" t="s">
+      <c r="A12" s="443" t="s">
         <v>2846</v>
       </c>
       <c r="B12" s="263">
@@ -48230,13 +48323,13 @@
         <v>696</v>
       </c>
       <c r="H12" s="215" t="s">
-        <v>3516</v>
+        <v>3509</v>
       </c>
       <c r="I12" s="215" t="s">
-        <v>3185</v>
+        <v>3179</v>
       </c>
       <c r="J12" s="270" t="s">
-        <v>3421</v>
+        <v>3414</v>
       </c>
       <c r="K12" s="183" t="s">
         <v>1240</v>
@@ -48270,10 +48363,10 @@
     </row>
     <row r="14" spans="1:11" s="224" customFormat="1">
       <c r="A14" s="224" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B14" s="224" t="s">
-        <v>3580</v>
+        <v>3573</v>
       </c>
       <c r="C14" s="438" t="s">
         <v>338</v>
@@ -48282,22 +48375,22 @@
         <v>2525</v>
       </c>
       <c r="E14" s="224" t="s">
-        <v>3572</v>
+        <v>3565</v>
       </c>
       <c r="F14" s="224" t="s">
-        <v>3571</v>
+        <v>3564</v>
       </c>
       <c r="G14" s="224" t="s">
         <v>696</v>
       </c>
       <c r="H14" s="224" t="s">
-        <v>3578</v>
+        <v>3571</v>
       </c>
       <c r="I14" s="224" t="s">
-        <v>3579</v>
+        <v>3572</v>
       </c>
       <c r="J14" s="224" t="s">
-        <v>3581</v>
+        <v>3574</v>
       </c>
       <c r="K14" s="224" t="s">
         <v>1357</v>
@@ -48317,7 +48410,7 @@
         <v>2041</v>
       </c>
       <c r="E15" s="216" t="s">
-        <v>3157</v>
+        <v>3152</v>
       </c>
       <c r="F15" s="216" t="s">
         <v>1478</v>
@@ -48326,13 +48419,13 @@
         <v>696</v>
       </c>
       <c r="H15" s="273" t="s">
-        <v>3507</v>
+        <v>3500</v>
       </c>
       <c r="I15" s="215" t="s">
-        <v>3465</v>
+        <v>3458</v>
       </c>
       <c r="J15" s="263" t="s">
-        <v>3664</v>
+        <v>3656</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1241</v>
@@ -48343,31 +48436,31 @@
         <v>1460</v>
       </c>
       <c r="B16" s="265" t="s">
-        <v>3472</v>
+        <v>3465</v>
       </c>
       <c r="C16" s="271" t="s">
         <v>1343</v>
       </c>
       <c r="D16" s="260" t="s">
-        <v>3435</v>
+        <v>3428</v>
       </c>
       <c r="E16" s="260" t="s">
-        <v>3027</v>
+        <v>3023</v>
       </c>
       <c r="F16" s="260" t="s">
-        <v>3028</v>
+        <v>3024</v>
       </c>
       <c r="G16" s="260" t="s">
         <v>696</v>
       </c>
       <c r="H16" s="265" t="s">
-        <v>3470</v>
+        <v>3463</v>
       </c>
       <c r="I16" s="272" t="s">
-        <v>3305</v>
+        <v>3298</v>
       </c>
       <c r="J16" s="265" t="s">
-        <v>3436</v>
+        <v>3429</v>
       </c>
       <c r="K16" s="260" t="s">
         <v>1484</v>
@@ -48440,7 +48533,7 @@
         <v>696</v>
       </c>
       <c r="J19" s="265" t="s">
-        <v>3249</v>
+        <v>3242</v>
       </c>
       <c r="K19" s="265" t="s">
         <v>1701</v>
@@ -48469,7 +48562,7 @@
         <v>696</v>
       </c>
       <c r="I20" s="260" t="s">
-        <v>3375</v>
+        <v>3368</v>
       </c>
       <c r="J20" s="49"/>
       <c r="K20" s="265" t="s">
@@ -48499,13 +48592,13 @@
         <v>696</v>
       </c>
       <c r="H21" s="260" t="s">
-        <v>3440</v>
+        <v>3433</v>
       </c>
       <c r="I21" s="265" t="s">
-        <v>3015</v>
+        <v>3011</v>
       </c>
       <c r="J21" s="260" t="s">
-        <v>3329</v>
+        <v>3322</v>
       </c>
       <c r="K21" s="265" t="s">
         <v>1828</v>
@@ -48513,7 +48606,7 @@
     </row>
     <row r="22" spans="1:11" s="260" customFormat="1">
       <c r="A22" s="246" t="s">
-        <v>3267</v>
+        <v>3260</v>
       </c>
       <c r="B22" s="260" t="s">
         <v>2512</v>
@@ -48533,14 +48626,14 @@
       <c r="G22" s="260" t="s">
         <v>696</v>
       </c>
-      <c r="H22" s="260" t="s">
-        <v>2986</v>
-      </c>
-      <c r="I22" s="260" t="s">
-        <v>2978</v>
+      <c r="H22" s="49" t="s">
+        <v>2983</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>2975</v>
       </c>
       <c r="J22" s="260" t="s">
-        <v>3600</v>
+        <v>3593</v>
       </c>
       <c r="K22" s="260" t="s">
         <v>1873</v>
@@ -48569,13 +48662,13 @@
         <v>696</v>
       </c>
       <c r="H24" s="265" t="s">
-        <v>3039</v>
+        <v>3034</v>
       </c>
       <c r="I24" s="265" t="s">
-        <v>3356</v>
+        <v>3349</v>
       </c>
       <c r="J24" s="265" t="s">
-        <v>3325</v>
+        <v>3318</v>
       </c>
       <c r="K24" s="260" t="s">
         <v>1875</v>
@@ -48616,7 +48709,7 @@
         <v>642</v>
       </c>
       <c r="D27" s="256" t="s">
-        <v>3563</v>
+        <v>3556</v>
       </c>
       <c r="E27" s="272" t="s">
         <v>2529</v>
@@ -48628,7 +48721,7 @@
         <v>714</v>
       </c>
       <c r="H27" s="260" t="s">
-        <v>3562</v>
+        <v>3555</v>
       </c>
       <c r="I27" s="145"/>
       <c r="J27" s="145"/>
@@ -48638,7 +48731,7 @@
         <v>853</v>
       </c>
       <c r="D29" s="265" t="s">
-        <v>3508</v>
+        <v>3501</v>
       </c>
       <c r="E29" s="260" t="s">
         <v>1851</v>
@@ -49016,16 +49109,16 @@
         <v>575</v>
       </c>
       <c r="G2" s="49" t="s">
-        <v>3058</v>
+        <v>3053</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>3181</v>
+        <v>3175</v>
       </c>
       <c r="I2" t="s">
-        <v>3286</v>
+        <v>3279</v>
       </c>
       <c r="J2" t="s">
-        <v>3417</v>
+        <v>3410</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1207</v>
@@ -49051,7 +49144,7 @@
         <v>301</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>3162</v>
+        <v>3156</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>715</v>
@@ -49077,25 +49170,25 @@
         <v>316</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3408</v>
+        <v>3401</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3501</v>
+        <v>3494</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>326</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>3355</v>
+        <v>3348</v>
       </c>
       <c r="H4" t="s">
-        <v>3568</v>
+        <v>3561</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3416</v>
+        <v>3409</v>
       </c>
       <c r="J4" t="s">
-        <v>3409</v>
+        <v>3402</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>325</v>
@@ -49103,7 +49196,7 @@
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1">
       <c r="A5" s="4" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="B5" s="4">
         <v>64720128</v>
@@ -49121,13 +49214,13 @@
         <v>429</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3573</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2997</v>
+        <v>3566</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>2993</v>
       </c>
       <c r="I5" s="75" t="s">
-        <v>3179</v>
+        <v>3173</v>
       </c>
       <c r="J5" s="220" t="s">
         <v>2805</v>
@@ -49145,25 +49238,25 @@
         <v>330</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>3311</v>
+        <v>3304</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>3310</v>
+        <v>3303</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>167</v>
       </c>
       <c r="G6" t="s">
-        <v>3121</v>
+        <v>3116</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3444</v>
+        <v>3437</v>
       </c>
       <c r="I6" t="s">
-        <v>3209</v>
+        <v>3203</v>
       </c>
       <c r="J6" t="s">
-        <v>3312</v>
+        <v>3305</v>
       </c>
       <c r="L6" s="67" t="s">
         <v>428</v>
@@ -49189,16 +49282,16 @@
         <v>152</v>
       </c>
       <c r="G7" t="s">
-        <v>3374</v>
+        <v>3367</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>3283</v>
+        <v>3276</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3605</v>
+        <v>3598</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>2979</v>
+        <v>2976</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>440</v>
@@ -49206,10 +49299,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="4" t="s">
-        <v>3349</v>
+        <v>3342</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3446</v>
+        <v>3439</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>664</v>
@@ -49227,13 +49320,13 @@
         <v>2857</v>
       </c>
       <c r="H8" t="s">
-        <v>3372</v>
+        <v>3365</v>
       </c>
       <c r="I8" t="s">
-        <v>3482</v>
+        <v>3475</v>
       </c>
       <c r="J8" t="s">
-        <v>3055</v>
+        <v>3050</v>
       </c>
       <c r="L8" s="36"/>
     </row>
@@ -49257,16 +49350,16 @@
         <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>3663</v>
+        <v>3655</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3650</v>
+        <v>3642</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3445</v>
+        <v>3438</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3636</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49280,7 +49373,7 @@
         <v>2288</v>
       </c>
       <c r="D10" t="s">
-        <v>3518</v>
+        <v>3511</v>
       </c>
       <c r="E10" t="s">
         <v>2258</v>
@@ -49289,16 +49382,16 @@
         <v>1881</v>
       </c>
       <c r="G10" t="s">
-        <v>3163</v>
+        <v>3157</v>
       </c>
       <c r="H10" t="s">
-        <v>3367</v>
+        <v>3360</v>
       </c>
       <c r="I10" t="s">
-        <v>3196</v>
+        <v>3190</v>
       </c>
       <c r="J10" t="s">
-        <v>3190</v>
+        <v>3184</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>2289</v>
@@ -49312,7 +49405,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B12" s="4">
         <v>64403333</v>
@@ -49375,7 +49468,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="49" t="s">
-        <v>3557</v>
+        <v>3550</v>
       </c>
       <c r="B15">
         <v>69184177</v>
@@ -49395,10 +49488,10 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B16" t="s">
-        <v>3061</v>
+        <v>3056</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>716</v>
@@ -49407,22 +49500,22 @@
         <v>1199</v>
       </c>
       <c r="E16" t="s">
-        <v>3060</v>
+        <v>3055</v>
       </c>
       <c r="F16" t="s">
         <v>152</v>
       </c>
       <c r="G16" t="s">
-        <v>3087</v>
+        <v>3082</v>
       </c>
       <c r="H16" t="s">
-        <v>3093</v>
+        <v>3088</v>
       </c>
       <c r="I16" t="s">
-        <v>3096</v>
+        <v>3091</v>
       </c>
       <c r="J16" t="s">
-        <v>3119</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -49430,7 +49523,7 @@
     </row>
     <row r="20" spans="2:12" s="391" customFormat="1" ht="23.5">
       <c r="B20" s="391" t="s">
-        <v>3059</v>
+        <v>3054</v>
       </c>
       <c r="C20" s="392"/>
       <c r="D20" s="393"/>
@@ -49658,7 +49751,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3536</v>
+        <v>3529</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49673,19 +49766,19 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="30" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B8" s="30">
         <v>67129610</v>
       </c>
       <c r="C8" t="s">
-        <v>3115</v>
+        <v>3110</v>
       </c>
       <c r="D8" t="s">
+        <v>2966</v>
+      </c>
+      <c r="E8" s="30" t="s">
         <v>2967</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>2968</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -49702,7 +49795,7 @@
         <v>1606</v>
       </c>
       <c r="E9" t="s">
-        <v>3330</v>
+        <v>3323</v>
       </c>
       <c r="F9" t="s">
         <v>1793</v>
@@ -49722,7 +49815,7 @@
         <v>2306</v>
       </c>
       <c r="E10" t="s">
-        <v>3319</v>
+        <v>3312</v>
       </c>
       <c r="F10" t="s">
         <v>1742</v>
@@ -49742,7 +49835,7 @@
         <v>2133</v>
       </c>
       <c r="E11" t="s">
-        <v>3556</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49759,7 +49852,7 @@
         <v>2900</v>
       </c>
       <c r="E12" t="s">
-        <v>3250</v>
+        <v>3243</v>
       </c>
       <c r="F12" t="s">
         <v>1742</v>
@@ -49767,7 +49860,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>3202</v>
+        <v>3196</v>
       </c>
       <c r="B13">
         <v>62271547</v>
@@ -49779,10 +49872,10 @@
         <v>2518</v>
       </c>
       <c r="E13" t="s">
-        <v>3390</v>
+        <v>3383</v>
       </c>
       <c r="F13" t="s">
-        <v>3391</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -49796,7 +49889,7 @@
         <v>2004</v>
       </c>
       <c r="D14" t="s">
-        <v>3524</v>
+        <v>3517</v>
       </c>
       <c r="E14" t="s">
         <v>2858</v>
@@ -49807,7 +49900,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>3054</v>
+        <v>3049</v>
       </c>
       <c r="B15">
         <v>62806425</v>
@@ -49819,27 +49912,27 @@
         <v>1796</v>
       </c>
       <c r="E15" t="s">
-        <v>3204</v>
+        <v>3198</v>
       </c>
       <c r="F15" t="s">
         <v>2904</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="30" customFormat="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="217" t="s">
         <v>2846</v>
       </c>
       <c r="B16" s="30">
         <v>65790414</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>3565</v>
+        <v>3558</v>
       </c>
       <c r="E16" t="s">
-        <v>3566</v>
+        <v>3559</v>
       </c>
       <c r="F16" t="s">
         <v>2904</v>
@@ -49847,19 +49940,19 @@
     </row>
     <row r="17" spans="1:7" s="30" customFormat="1">
       <c r="A17" s="30" t="s">
-        <v>3349</v>
+        <v>3342</v>
       </c>
       <c r="B17" s="30">
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>3425</v>
+        <v>3418</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>3584</v>
+        <v>3577</v>
       </c>
       <c r="E17" t="s">
-        <v>3585</v>
+        <v>3578</v>
       </c>
       <c r="F17" t="s">
         <v>2904</v>
@@ -49876,13 +49969,13 @@
         <v>64276131</v>
       </c>
       <c r="C18" s="30" t="s">
+        <v>2968</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>2969</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>2970</v>
-      </c>
       <c r="E18" t="s">
-        <v>3585</v>
+        <v>3578</v>
       </c>
       <c r="F18" t="s">
         <v>2904</v>
@@ -49890,7 +49983,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>3128</v>
+        <v>3123</v>
       </c>
       <c r="B21">
         <v>64245493</v>
@@ -49910,7 +50003,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="B22">
         <v>65324947</v>
@@ -49919,7 +50012,7 @@
         <v>1868</v>
       </c>
       <c r="D22" t="s">
-        <v>3047</v>
+        <v>3042</v>
       </c>
       <c r="E22" t="s">
         <v>2602</v>
@@ -49939,7 +50032,7 @@
         <v>2628</v>
       </c>
       <c r="D23" t="s">
-        <v>3068</v>
+        <v>3063</v>
       </c>
       <c r="E23" t="s">
         <v>2636</v>
@@ -49961,7 +50054,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -49973,13 +50066,13 @@
         <v>2875</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3537</v>
+        <v>3530</v>
       </c>
       <c r="F26" t="s">
-        <v>3538</v>
+        <v>3531</v>
       </c>
       <c r="G26" t="s">
-        <v>3550</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -49996,13 +50089,13 @@
         <v>426</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3537</v>
+        <v>3530</v>
       </c>
       <c r="F27" t="s">
-        <v>3572</v>
+        <v>3565</v>
       </c>
       <c r="G27" t="s">
-        <v>3614</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -50018,7 +50111,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50030,10 +50123,10 @@
         <v>2903</v>
       </c>
       <c r="E30" t="s">
-        <v>3551</v>
+        <v>3544</v>
       </c>
       <c r="F30" t="s">
-        <v>3552</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="307" customFormat="1" ht="15.5">
@@ -50128,7 +50221,7 @@
         <v>364</v>
       </c>
       <c r="D46" t="s">
-        <v>3067</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="30" customFormat="1">
@@ -50139,10 +50232,10 @@
         <v>2668</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>3251</v>
+        <v>3244</v>
       </c>
       <c r="F47" s="408" t="s">
-        <v>3252</v>
+        <v>3245</v>
       </c>
       <c r="G47" s="30" t="s">
         <v>412</v>
@@ -50172,13 +50265,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="97" t="s">
-        <v>3046</v>
+        <v>3041</v>
       </c>
       <c r="C51" t="s">
         <v>1411</v>
       </c>
       <c r="D51" t="s">
-        <v>3045</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -50238,12 +50331,12 @@
     </row>
     <row r="60" spans="1:5" s="403" customFormat="1" ht="18">
       <c r="C60" s="403" t="s">
-        <v>3210</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="30" t="s">
-        <v>3158</v>
+        <v>3153</v>
       </c>
       <c r="B61" s="30">
         <v>65036571</v>
@@ -50255,7 +50348,7 @@
         <v>2676</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3211</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="76" customFormat="1">
@@ -52097,12 +52190,12 @@
     </row>
     <row r="252" spans="1:6" s="433" customFormat="1" ht="21">
       <c r="C252" s="433" t="s">
-        <v>3499</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B253">
         <v>64476521</v>
@@ -52114,30 +52207,30 @@
         <v>2342</v>
       </c>
       <c r="E253" t="s">
-        <v>3497</v>
+        <v>3490</v>
       </c>
       <c r="F253" t="s">
-        <v>3498</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="D254" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="E254" t="s">
-        <v>3497</v>
+        <v>3490</v>
       </c>
       <c r="F254" t="s">
-        <v>3498</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52148,21 +52241,21 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>3413</v>
+        <v>3406</v>
       </c>
       <c r="D255" s="252" t="s">
         <v>2837</v>
       </c>
       <c r="E255" t="s">
-        <v>3497</v>
+        <v>3490</v>
       </c>
       <c r="F255" t="s">
-        <v>3498</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>3037</v>
+        <v>3032</v>
       </c>
       <c r="B256">
         <v>61915064</v>
@@ -55548,7 +55641,7 @@
         <v>1379</v>
       </c>
       <c r="D456" t="s">
-        <v>3073</v>
+        <v>3068</v>
       </c>
       <c r="E456" s="76" t="s">
         <v>1456</v>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc549f2659ed9bd7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60878" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{812F74AF-BF18-4913-B17B-BBAEBF0A4B73}"/>
+  <xr:revisionPtr revIDLastSave="60880" documentId="8_{85679C33-06E3-462F-8559-6705F1C3B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A809AE04-EC81-4436-81B0-1D5D1B686919}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,6 @@
     <author>tc={A1BAE17A-7373-4E96-9A79-0A588580086C}</author>
     <author>tc={6CB69787-04DC-427D-92C4-EA68685283A6}</author>
     <author>tc={D6ECFDFD-E9B9-4F9B-B2EF-5C67AA00056B}</author>
-    <author>tc={A3554D91-2D1C-4186-8090-CCD5996EDC8F}</author>
     <author>tc={5775AADF-97AE-4D86-A7DF-2817E0EA08FF}</author>
   </authors>
   <commentList>
@@ -214,15 +213,7 @@
     https://netflix-server-a9i0.onrender.com/cliente/68259581-kenneth</t>
       </text>
     </comment>
-    <comment ref="K97" authorId="15" shapeId="0" xr:uid="{A3554D91-2D1C-4186-8090-CCD5996EDC8F}">
-      <text>
-        <t>[Comentario encadenado]
-Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    https://netflix-server-a9i0.onrender.com/cliente/62624989-maria</t>
-      </text>
-    </comment>
-    <comment ref="H103" authorId="16" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
+    <comment ref="H103" authorId="15" shapeId="0" xr:uid="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -11092,9 +11083,6 @@
     <t>60432412 pantalla hasta el 16 de septiembre 110n005</t>
   </si>
   <si>
-    <t>62624989-maria 1 pantalla hasta el 03 de septiembre</t>
-  </si>
-  <si>
     <t>62657225 1 pantalla hasta el 18 de septiembre</t>
   </si>
   <si>
@@ -12416,6 +12404,9 @@
   </si>
   <si>
     <t xml:space="preserve">68259581-kenneth 1 pantalla hasta el 04 de octubre </t>
+  </si>
+  <si>
+    <t>040926-0234t</t>
   </si>
 </sst>
 </file>
@@ -30264,15 +30255,6 @@
       </x:ext>
     </extLst>
   </threadedComment>
-  <threadedComment ref="K97" dT="2026-08-16T18:15:52.84" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{A3554D91-2D1C-4186-8090-CCD5996EDC8F}">
-    <text>https://netflix-server-a9i0.onrender.com/cliente/62624989-maria</text>
-    <extLst>
-      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
-        <xltc2:checksum>3957755351</xltc2:checksum>
-        <xltc2:hyperlink startIndex="0" length="49" url="https://netflix-server-a9i0.onrender.com/cliente/"/>
-      </x:ext>
-    </extLst>
-  </threadedComment>
   <threadedComment ref="H103" dT="2026-08-28T21:46:31.74" personId="{0912E1D7-9EEC-46AD-AFB7-0C0A7E0E5337}" id="{5775AADF-97AE-4D86-A7DF-2817E0EA08FF}">
     <text>https://netflix-server-a9i0.onrender.com/cliente/280826-0425s</text>
     <extLst>
@@ -30362,7 +30344,7 @@
   <sheetData>
     <row r="1" spans="1:11" s="30" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="B1" s="30">
         <v>60389752</v>
@@ -30394,7 +30376,7 @@
         <v>2193</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="148" customFormat="1">
@@ -30413,7 +30395,7 @@
     </row>
     <row r="4" spans="1:11" s="30" customFormat="1">
       <c r="A4" s="30" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="B4" s="30">
         <v>60389752</v>
@@ -30425,7 +30407,7 @@
         <v>2069</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="F4" s="30" t="s">
         <v>2144</v>
@@ -30445,7 +30427,7 @@
         <v>2207</v>
       </c>
       <c r="D5" s="148" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="148" customFormat="1">
@@ -30476,7 +30458,7 @@
         <v>3045</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
       <c r="F7" s="30" t="s">
         <v>2149</v>
@@ -30501,7 +30483,7 @@
     </row>
     <row r="9" spans="1:11" s="148" customFormat="1">
       <c r="A9" s="148" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B9" s="148" t="s">
         <v>1234</v>
@@ -30518,7 +30500,7 @@
     </row>
     <row r="10" spans="1:11" s="433" customFormat="1">
       <c r="A10" s="433" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B10" s="433">
         <v>60389752</v>
@@ -30555,7 +30537,7 @@
         <v>2212</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="F13" s="30" t="s">
         <v>2211</v>
@@ -30604,10 +30586,10 @@
         <v>1573</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="F16" s="32" t="s">
         <v>1574</v>
@@ -30616,16 +30598,16 @@
         <v>201</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="I16" s="32" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="J16" s="32" t="s">
+        <v>3549</v>
+      </c>
+      <c r="K16" s="30" t="s">
         <v>3550</v>
-      </c>
-      <c r="K16" s="30" t="s">
-        <v>3551</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="164" customFormat="1">
@@ -30676,7 +30658,7 @@
         <v>2101</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
       <c r="F19" s="30" t="s">
         <v>1397</v>
@@ -30696,7 +30678,7 @@
         <v>1733</v>
       </c>
       <c r="D20" s="253" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="E20" s="253" t="s">
         <v>1734</v>
@@ -30784,7 +30766,7 @@
         <v>1570</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="F25" s="30" t="s">
         <v>1397</v>
@@ -30832,7 +30814,7 @@
     </row>
     <row r="28" spans="1:11" s="30" customFormat="1">
       <c r="A28" s="30" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B28" s="30">
         <v>60389752</v>
@@ -30844,7 +30826,7 @@
         <v>2066</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="F28" s="305" t="s">
         <v>2224</v>
@@ -30886,13 +30868,13 @@
         <v>3140</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="C31" s="252" t="s">
         <v>1956</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="E31" s="30" t="s">
         <v>3226</v>
@@ -30904,13 +30886,13 @@
         <v>201</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="I31" s="192" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
       <c r="J31" s="431" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="K31" s="30" t="s">
         <v>3054</v>
@@ -31010,7 +30992,7 @@
         <v>2064</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
       <c r="E37" s="30" t="s">
         <v>3197</v>
@@ -31025,13 +31007,13 @@
         <v>3069</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="147" customFormat="1">
@@ -31068,7 +31050,7 @@
         <v>2589</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="C40" s="252" t="s">
         <v>1713</v>
@@ -31086,13 +31068,13 @@
         <v>201</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
       <c r="K40" s="30" t="s">
         <v>3048</v>
@@ -31100,7 +31082,7 @@
     </row>
     <row r="41" spans="1:11" s="163" customFormat="1">
       <c r="A41" s="163" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B41" s="163">
         <v>68381893</v>
@@ -31132,7 +31114,7 @@
     </row>
     <row r="43" spans="1:11" s="30" customFormat="1">
       <c r="A43" s="30" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B43" s="30">
         <v>60389752</v>
@@ -31144,7 +31126,7 @@
         <v>2093</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="F43" s="30" t="s">
         <v>2187</v>
@@ -31155,7 +31137,7 @@
     </row>
     <row r="44" spans="1:11" s="164" customFormat="1">
       <c r="A44" s="164" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B44" s="164">
         <v>68381893</v>
@@ -31253,7 +31235,7 @@
         <v>2055</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="E49" s="30" t="s">
         <v>3131</v>
@@ -31265,16 +31247,16 @@
         <v>201</v>
       </c>
       <c r="H49" s="30" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="J49" s="440" t="s">
         <v>2989</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="50" spans="1:11" s="164" customFormat="1">
@@ -31302,7 +31284,7 @@
         <v>2063</v>
       </c>
       <c r="D51" s="164" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="139" customFormat="1">
@@ -31328,16 +31310,16 @@
         <v>201</v>
       </c>
       <c r="H52" s="140" t="s">
-        <v>3445</v>
+        <v>3444</v>
       </c>
       <c r="I52" s="140" t="s">
         <v>3060</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="K52" s="270" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="164" customFormat="1">
@@ -31390,7 +31372,7 @@
         <v>2059</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="F55" s="30" t="s">
         <v>2170</v>
@@ -31407,10 +31389,10 @@
         <v>60433915</v>
       </c>
       <c r="C56" s="408" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="D56" s="376" t="s">
-        <v>3471</v>
+        <v>3470</v>
       </c>
       <c r="E56" s="164"/>
     </row>
@@ -31419,13 +31401,13 @@
         <v>2589</v>
       </c>
       <c r="B57" s="163" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
       <c r="C57" s="408" t="s">
-        <v>3470</v>
+        <v>3469</v>
       </c>
       <c r="D57" s="376" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="E57" s="164"/>
     </row>
@@ -31443,7 +31425,7 @@
         <v>2945</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="F58" s="30" t="s">
         <v>2183</v>
@@ -31452,13 +31434,13 @@
         <v>201</v>
       </c>
       <c r="H58" s="30" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
       <c r="K58" s="30" t="s">
         <v>3198</v>
@@ -31476,7 +31458,7 @@
         <v>159</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="C61" s="134" t="s">
         <v>2136</v>
@@ -31485,7 +31467,7 @@
         <v>3040</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="F61" s="30" t="s">
         <v>2137</v>
@@ -31497,10 +31479,10 @@
         <v>3088</v>
       </c>
       <c r="I61" s="30" t="s">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>3623</v>
+        <v>3622</v>
       </c>
       <c r="K61" s="30" t="s">
         <v>2991</v>
@@ -31508,7 +31490,7 @@
     </row>
     <row r="62" spans="1:11" s="147" customFormat="1">
       <c r="A62" s="147" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="B62" s="147">
         <v>60196388</v>
@@ -31517,7 +31499,7 @@
         <v>1511</v>
       </c>
       <c r="D62" s="377" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="E62" s="148" t="s">
         <v>1417</v>
@@ -31534,7 +31516,7 @@
         <v>2121</v>
       </c>
       <c r="D63" s="376" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="E63" s="164"/>
     </row>
@@ -31549,7 +31531,7 @@
         <v>1712</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="E64" s="30" t="s">
         <v>3130</v>
@@ -31561,7 +31543,7 @@
         <v>201</v>
       </c>
       <c r="H64" s="443" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="I64" s="32" t="s">
         <v>3037</v>
@@ -31570,7 +31552,7 @@
         <v>3036</v>
       </c>
       <c r="K64" s="30" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="65" spans="1:11" s="164" customFormat="1">
@@ -31618,7 +31600,7 @@
         <v>1716</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="E67" s="30" t="s">
         <v>3169</v>
@@ -31630,7 +31612,7 @@
         <v>201</v>
       </c>
       <c r="H67" s="30" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="I67" s="30" t="s">
         <v>3076</v>
@@ -31639,12 +31621,12 @@
         <v>3145</v>
       </c>
       <c r="K67" s="30" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="147" customFormat="1">
       <c r="A68" s="147" t="s">
-        <v>3459</v>
+        <v>3458</v>
       </c>
       <c r="B68" s="147">
         <v>68741448</v>
@@ -31653,7 +31635,7 @@
         <v>1932</v>
       </c>
       <c r="D68" s="377" t="s">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="E68" s="148"/>
     </row>
@@ -31682,10 +31664,10 @@
         <v>1715</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="F70" s="30" t="s">
         <v>2198</v>
@@ -31694,13 +31676,13 @@
         <v>201</v>
       </c>
       <c r="H70" s="32" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="I70" s="30" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="J70" s="32" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="71" spans="1:11" s="164" customFormat="1">
@@ -31734,7 +31716,7 @@
     </row>
     <row r="73" spans="1:11" s="30" customFormat="1">
       <c r="A73" s="30" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
       <c r="B73" s="30">
         <v>60389752</v>
@@ -31746,7 +31728,7 @@
         <v>2961</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="F73" s="30" t="s">
         <v>2088</v>
@@ -31781,7 +31763,7 @@
         <v>2003</v>
       </c>
       <c r="D75" s="148" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
       <c r="E75" s="148"/>
     </row>
@@ -31799,7 +31781,7 @@
         <v>3219</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="F76" s="30" t="s">
         <v>2169</v>
@@ -31814,10 +31796,10 @@
         <v>3222</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="K76" s="30" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="77" spans="1:11" s="152" customFormat="1">
@@ -31839,7 +31821,7 @@
         <v>2062</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="E79" s="30" t="s">
         <v>3196</v>
@@ -31851,16 +31833,16 @@
         <v>201</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="K79" s="30" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="80" spans="1:11" s="147" customFormat="1">
@@ -31897,10 +31879,10 @@
     </row>
     <row r="82" spans="1:11" s="30" customFormat="1">
       <c r="A82" s="30" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
       <c r="C82" s="134" t="s">
         <v>1957</v>
@@ -31918,13 +31900,13 @@
         <v>201</v>
       </c>
       <c r="H82" s="30" t="s">
+        <v>3437</v>
+      </c>
+      <c r="I82" s="30" t="s">
+        <v>3647</v>
+      </c>
+      <c r="J82" s="30" t="s">
         <v>3438</v>
-      </c>
-      <c r="I82" s="30" t="s">
-        <v>3648</v>
-      </c>
-      <c r="J82" s="30" t="s">
-        <v>3439</v>
       </c>
       <c r="K82" s="30" t="s">
         <v>3080</v>
@@ -31969,7 +31951,7 @@
         <v>700</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="E85" s="30" t="s">
         <v>1844</v>
@@ -31981,16 +31963,16 @@
         <v>498</v>
       </c>
       <c r="H85" s="30" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="I85" s="32" t="s">
         <v>3091</v>
       </c>
       <c r="J85" s="145" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="K85" s="215" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="86" spans="1:11" s="147" customFormat="1">
@@ -32013,7 +31995,7 @@
     </row>
     <row r="87" spans="1:11" s="147" customFormat="1">
       <c r="A87" s="147" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B87" s="147" t="s">
         <v>922</v>
@@ -32058,10 +32040,10 @@
         <v>3236</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="K88" s="30" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="89" spans="1:11" s="147" customFormat="1">
@@ -32084,7 +32066,7 @@
     </row>
     <row r="90" spans="1:11" s="148" customFormat="1">
       <c r="A90" s="226" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B90" s="148">
         <v>67381873</v>
@@ -32111,7 +32093,7 @@
         <v>46</v>
       </c>
       <c r="D91" s="106" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="E91" s="106" t="s">
         <v>1148</v>
@@ -32123,16 +32105,16 @@
         <v>66</v>
       </c>
       <c r="H91" s="30" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
       <c r="I91" s="31" t="s">
         <v>3163</v>
       </c>
       <c r="J91" s="32" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="K91" s="30" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="414" customFormat="1">
@@ -32163,7 +32145,7 @@
         <v>1770</v>
       </c>
       <c r="D93" s="148" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="94" spans="1:11" s="32" customFormat="1">
@@ -32250,13 +32232,13 @@
         <v>3086</v>
       </c>
       <c r="I97" s="30" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="J97" s="440" t="s">
+        <v>3677</v>
+      </c>
+      <c r="K97" s="139" t="s">
         <v>3678</v>
-      </c>
-      <c r="K97" s="139" t="s">
-        <v>3237</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="394" customFormat="1">
@@ -32281,7 +32263,7 @@
         <v>2999</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="F100" s="30" t="s">
         <v>1958</v>
@@ -32312,19 +32294,19 @@
     </row>
     <row r="103" spans="1:13" s="30" customFormat="1">
       <c r="A103" s="30" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="C103" s="252" t="s">
         <v>3087</v>
       </c>
       <c r="D103" s="30" t="s">
+        <v>3508</v>
+      </c>
+      <c r="E103" s="30" t="s">
         <v>3509</v>
-      </c>
-      <c r="E103" s="30" t="s">
-        <v>3510</v>
       </c>
       <c r="F103" s="30" t="s">
         <v>1958</v>
@@ -32333,16 +32315,16 @@
         <v>201</v>
       </c>
       <c r="H103" s="30" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="I103" s="30" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="J103" s="30" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="K103" s="30" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -32386,13 +32368,13 @@
         <v>3085</v>
       </c>
       <c r="D106" s="30" t="s">
+        <v>3333</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>3335</v>
+      </c>
+      <c r="F106" s="30" t="s">
         <v>3334</v>
-      </c>
-      <c r="E106" s="30" t="s">
-        <v>3336</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>3335</v>
       </c>
       <c r="G106" s="30" t="s">
         <v>59</v>
@@ -32411,7 +32393,7 @@
         <v>158</v>
       </c>
       <c r="B112" s="285" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="C112" s="134" t="s">
         <v>2049</v>
@@ -32490,7 +32472,7 @@
         <v>2039</v>
       </c>
       <c r="E127" s="30" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="F127" t="s">
         <v>2037</v>
@@ -32510,7 +32492,7 @@
         <v>2009</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -32524,10 +32506,10 @@
         <v>2848</v>
       </c>
       <c r="D129" s="379" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="E129" s="30" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -32544,7 +32526,7 @@
         <v>2718</v>
       </c>
       <c r="E130" s="30" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -32561,7 +32543,7 @@
         <v>2015</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>3430</v>
+        <v>3429</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="121" customFormat="1" ht="23.5">
@@ -32600,7 +32582,7 @@
         <v>2435</v>
       </c>
       <c r="E136" s="30" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
       <c r="F136" t="s">
         <v>1374</v>
@@ -32646,7 +32628,7 @@
         <v>2026</v>
       </c>
       <c r="D140" s="379" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
       <c r="E140" s="30" t="s">
         <v>2025</v>
@@ -32677,7 +32659,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="C143" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -32718,10 +32700,10 @@
         <v>2299</v>
       </c>
       <c r="D152" s="379" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="E152" s="30" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
       <c r="F152" t="s">
         <v>2027</v>
@@ -32741,7 +32723,7 @@
         <v>2440</v>
       </c>
       <c r="E153" s="30" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -32758,7 +32740,7 @@
         <v>2923</v>
       </c>
       <c r="E154" s="30" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -32775,7 +32757,7 @@
         <v>2719</v>
       </c>
       <c r="E155" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -32792,7 +32774,7 @@
         <v>3229</v>
       </c>
       <c r="E156" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -32809,7 +32791,7 @@
         <v>2590</v>
       </c>
       <c r="E157" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -32826,7 +32808,7 @@
         <v>2760</v>
       </c>
       <c r="E158" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -32843,12 +32825,12 @@
         <v>2699</v>
       </c>
       <c r="E159" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B160">
         <v>65133588</v>
@@ -32860,12 +32842,12 @@
         <v>2615</v>
       </c>
       <c r="E160" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="4" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>1162</v>
@@ -32874,10 +32856,10 @@
         <v>2720</v>
       </c>
       <c r="D161" s="379" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="E161" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -32891,10 +32873,10 @@
         <v>2617</v>
       </c>
       <c r="D162" s="379" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="E162" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -32911,7 +32893,7 @@
         <v>3164</v>
       </c>
       <c r="E163" s="30" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -32987,10 +32969,10 @@
         <v>2850</v>
       </c>
       <c r="D168" s="379" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="E168" s="30" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -33007,7 +32989,7 @@
         <v>2895</v>
       </c>
       <c r="E169" s="30" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -33024,7 +33006,7 @@
         <v>2588</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -33041,7 +33023,7 @@
         <v>2395</v>
       </c>
       <c r="E171" s="30" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -33055,10 +33037,10 @@
         <v>2407</v>
       </c>
       <c r="D172" s="379" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="E172" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -33072,10 +33054,10 @@
         <v>2408</v>
       </c>
       <c r="D173" s="379" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -33089,10 +33071,10 @@
         <v>2409</v>
       </c>
       <c r="D174" s="379" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -33106,15 +33088,15 @@
         <v>2899</v>
       </c>
       <c r="D175" s="379" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="E175" s="30" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B176">
         <v>66935922</v>
@@ -33123,10 +33105,10 @@
         <v>2900</v>
       </c>
       <c r="D176" s="220" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -33137,13 +33119,13 @@
         <v>63503223</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="D177" s="220" t="s">
         <v>2983</v>
       </c>
       <c r="E177" s="30" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -33160,7 +33142,7 @@
         <v>2924</v>
       </c>
       <c r="E178" s="30" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -33169,10 +33151,10 @@
         <v>2902</v>
       </c>
       <c r="D179" s="220" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="E179" s="30" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -33181,15 +33163,15 @@
         <v>2929</v>
       </c>
       <c r="D180" s="379" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="E180" s="30" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B181">
         <v>63950696</v>
@@ -33201,12 +33183,12 @@
         <v>2930</v>
       </c>
       <c r="E181" s="30" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="4" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B182" t="s">
         <v>2967</v>
@@ -33218,7 +33200,7 @@
         <v>2930</v>
       </c>
       <c r="E182" s="30" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -33235,7 +33217,7 @@
         <v>3046</v>
       </c>
       <c r="E183" s="30" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -33252,7 +33234,7 @@
         <v>3049</v>
       </c>
       <c r="E184" s="30" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -33269,7 +33251,7 @@
         <v>3052</v>
       </c>
       <c r="E185" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -33286,7 +33268,7 @@
         <v>2983</v>
       </c>
       <c r="E186" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -33303,7 +33285,7 @@
         <v>2983</v>
       </c>
       <c r="E187" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -33320,7 +33302,7 @@
         <v>2983</v>
       </c>
       <c r="E188" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -33337,7 +33319,7 @@
         <v>2983</v>
       </c>
       <c r="E189" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -33354,12 +33336,12 @@
         <v>2983</v>
       </c>
       <c r="E190" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="4" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>1911</v>
@@ -33371,12 +33353,12 @@
         <v>2983</v>
       </c>
       <c r="E191" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="B192">
         <v>64046277</v>
@@ -33388,7 +33370,7 @@
         <v>3051</v>
       </c>
       <c r="E192" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -33405,7 +33387,7 @@
         <v>2983</v>
       </c>
       <c r="E193" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -33422,24 +33404,24 @@
         <v>2983</v>
       </c>
       <c r="E194" s="30" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="445" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="B195">
         <v>64730396</v>
       </c>
       <c r="C195" s="21" t="s">
+        <v>3536</v>
+      </c>
+      <c r="D195" t="s">
         <v>3537</v>
       </c>
-      <c r="D195" t="s">
-        <v>3538</v>
-      </c>
       <c r="E195" s="30" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="397" customFormat="1" ht="23.5">
@@ -33464,7 +33446,7 @@
         <v>3021</v>
       </c>
       <c r="E198" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -33478,27 +33460,27 @@
         <v>3009</v>
       </c>
       <c r="D199" s="379" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="E199" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="97"/>
       <c r="C200" s="22" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="D200" s="379" t="s">
         <v>3124</v>
       </c>
       <c r="E200" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="B201">
         <v>65633205</v>
@@ -33507,10 +33489,10 @@
         <v>3010</v>
       </c>
       <c r="D201" s="379" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="E201" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -33527,7 +33509,7 @@
         <v>3113</v>
       </c>
       <c r="E202" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -33544,7 +33526,7 @@
         <v>3136</v>
       </c>
       <c r="E203" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -33561,7 +33543,7 @@
         <v>3119</v>
       </c>
       <c r="E204" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -33578,7 +33560,7 @@
         <v>3135</v>
       </c>
       <c r="E205" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -33595,7 +33577,7 @@
         <v>3151</v>
       </c>
       <c r="E206" s="30" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -33609,10 +33591,10 @@
         <v>3152</v>
       </c>
       <c r="D207" s="379" t="s">
+        <v>3577</v>
+      </c>
+      <c r="E207" s="30" t="s">
         <v>3578</v>
-      </c>
-      <c r="E207" s="30" t="s">
-        <v>3579</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -33671,7 +33653,7 @@
         <v>2935</v>
       </c>
       <c r="B211" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="C211" t="s">
         <v>3231</v>
@@ -33691,10 +33673,10 @@
         <v>64881871</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="D212" t="s">
-        <v>3465</v>
+        <v>3464</v>
       </c>
       <c r="E212" s="30" t="s">
         <v>3178</v>
@@ -33708,13 +33690,13 @@
         <v>68069608</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="D213" s="379" t="s">
+        <v>3284</v>
+      </c>
+      <c r="E213" s="30" t="s">
         <v>3285</v>
-      </c>
-      <c r="E213" s="30" t="s">
-        <v>3286</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -33725,13 +33707,13 @@
         <v>63258169</v>
       </c>
       <c r="C214" s="22" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="D214" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="E214" s="30" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -33742,13 +33724,13 @@
         <v>69243886</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="D215" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="E215" s="30" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -33759,13 +33741,13 @@
         <v>67752170</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="D216" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="E216" s="30" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -33776,13 +33758,13 @@
         <v>64457890</v>
       </c>
       <c r="C217" t="s">
+        <v>3306</v>
+      </c>
+      <c r="D217" s="379" t="s">
         <v>3307</v>
       </c>
-      <c r="D217" s="379" t="s">
-        <v>3308</v>
-      </c>
       <c r="E217" s="30" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="231" spans="3:4">
@@ -36552,7 +36534,7 @@
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="18" spans="4:4">
@@ -36601,7 +36583,7 @@
     </row>
     <row r="6" spans="1:9" s="76" customFormat="1">
       <c r="A6" s="76" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B6" s="76">
         <v>64966680</v>
@@ -36616,7 +36598,7 @@
         <v>684</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="G6" s="222" t="s">
         <v>1483</v>
@@ -36642,7 +36624,7 @@
         <v>365</v>
       </c>
       <c r="F7" s="183" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="G7" s="183" t="s">
         <v>1483</v>
@@ -36668,7 +36650,7 @@
         <v>365</v>
       </c>
       <c r="F8" s="183" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="G8" s="183" t="s">
         <v>1483</v>
@@ -36694,7 +36676,7 @@
         <v>365</v>
       </c>
       <c r="F9" s="183" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="G9" s="183" t="s">
         <v>1483</v>
@@ -36720,7 +36702,7 @@
         <v>365</v>
       </c>
       <c r="F10" s="183" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="G10" s="183" t="s">
         <v>1483</v>
@@ -36746,7 +36728,7 @@
         <v>365</v>
       </c>
       <c r="F11" s="183" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="G11" s="183" t="s">
         <v>1483</v>
@@ -36769,7 +36751,7 @@
         <v>2625</v>
       </c>
       <c r="E13" s="195" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="F13" s="195" t="s">
         <v>1468</v>
@@ -36796,7 +36778,7 @@
         <v>1900</v>
       </c>
       <c r="E14" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="F14" s="193" t="s">
         <v>1468</v>
@@ -36823,7 +36805,7 @@
         <v>2939</v>
       </c>
       <c r="E15" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="F15" s="193" t="s">
         <v>1468</v>
@@ -36838,7 +36820,7 @@
     </row>
     <row r="16" spans="1:9" s="183" customFormat="1">
       <c r="A16" s="183" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B16" s="183">
         <v>63666666</v>
@@ -36850,7 +36832,7 @@
         <v>2398</v>
       </c>
       <c r="E16" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="F16" s="193" t="s">
         <v>1468</v>
@@ -36877,7 +36859,7 @@
         <v>1549</v>
       </c>
       <c r="E17" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="F17" s="193" t="s">
         <v>1468</v>
@@ -36904,7 +36886,7 @@
         <v>2229</v>
       </c>
       <c r="E18" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>1468</v>
@@ -36919,7 +36901,7 @@
     </row>
     <row r="20" spans="1:9" s="76" customFormat="1">
       <c r="A20" s="195" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B20" s="195">
         <v>67539485</v>
@@ -36934,7 +36916,7 @@
         <v>365</v>
       </c>
       <c r="F20" s="195" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G20" s="76" t="s">
         <v>427</v>
@@ -36963,7 +36945,7 @@
         <v>365</v>
       </c>
       <c r="F21" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G21" s="183" t="s">
         <v>427</v>
@@ -36992,7 +36974,7 @@
         <v>365</v>
       </c>
       <c r="F22" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G22" s="183" t="s">
         <v>427</v>
@@ -37006,7 +36988,7 @@
     </row>
     <row r="23" spans="1:9" s="183" customFormat="1">
       <c r="A23" s="183" t="s">
-        <v>3460</v>
+        <v>3459</v>
       </c>
       <c r="B23" s="183">
         <v>60389752</v>
@@ -37021,7 +37003,7 @@
         <v>365</v>
       </c>
       <c r="F23" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G23" s="183" t="s">
         <v>427</v>
@@ -37050,7 +37032,7 @@
         <v>365</v>
       </c>
       <c r="F24" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G24" s="183" t="s">
         <v>427</v>
@@ -37079,7 +37061,7 @@
         <v>365</v>
       </c>
       <c r="F25" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G25" s="183" t="s">
         <v>427</v>
@@ -37093,7 +37075,7 @@
     </row>
     <row r="27" spans="1:9" s="76" customFormat="1">
       <c r="A27" s="195" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B27" s="195">
         <v>62747874</v>
@@ -37108,7 +37090,7 @@
         <v>365</v>
       </c>
       <c r="F27" s="195" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G27" s="76" t="s">
         <v>427</v>
@@ -37137,7 +37119,7 @@
         <v>365</v>
       </c>
       <c r="F28" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G28" s="183" t="s">
         <v>427</v>
@@ -37166,7 +37148,7 @@
         <v>365</v>
       </c>
       <c r="F29" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G29" s="183" t="s">
         <v>427</v>
@@ -37180,7 +37162,7 @@
     </row>
     <row r="30" spans="1:9" s="183" customFormat="1">
       <c r="A30" s="183" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B30" s="183">
         <v>63950696</v>
@@ -37195,7 +37177,7 @@
         <v>365</v>
       </c>
       <c r="F30" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G30" s="183" t="s">
         <v>427</v>
@@ -37224,7 +37206,7 @@
         <v>365</v>
       </c>
       <c r="F31" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G31" s="183" t="s">
         <v>427</v>
@@ -37253,7 +37235,7 @@
         <v>365</v>
       </c>
       <c r="F32" s="193" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="G32" s="183" t="s">
         <v>427</v>
@@ -37267,7 +37249,7 @@
     </row>
     <row r="34" spans="1:9" s="76" customFormat="1">
       <c r="A34" s="76" t="s">
-        <v>3575</v>
+        <v>3574</v>
       </c>
       <c r="B34" s="76">
         <v>60389752</v>
@@ -37493,7 +37475,7 @@
     </row>
     <row r="43" spans="1:9" s="183" customFormat="1">
       <c r="A43" s="193" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B43" s="193">
         <v>63226030</v>
@@ -37610,7 +37592,7 @@
         <v>1715</v>
       </c>
       <c r="D48" s="195" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="E48" s="76" t="s">
         <v>2586</v>
@@ -37664,7 +37646,7 @@
         <v>2732</v>
       </c>
       <c r="D50" s="193" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="E50" s="183" t="s">
         <v>2586</v>
@@ -37738,10 +37720,10 @@
       <c r="A53" s="279"/>
       <c r="B53" s="193"/>
       <c r="C53" s="193" t="s">
+        <v>3655</v>
+      </c>
+      <c r="D53" s="193" t="s">
         <v>3656</v>
-      </c>
-      <c r="D53" s="193" t="s">
-        <v>3657</v>
       </c>
       <c r="E53" s="183" t="s">
         <v>2586</v>
@@ -37839,7 +37821,7 @@
     </row>
     <row r="58" spans="1:9" s="183" customFormat="1">
       <c r="A58" s="193" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="B58" s="193">
         <v>69872571</v>
@@ -38223,7 +38205,7 @@
     </row>
     <row r="76" spans="1:9" s="76" customFormat="1">
       <c r="A76" s="76" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B76" s="76">
         <v>63574980</v>
@@ -38238,7 +38220,7 @@
         <v>1379</v>
       </c>
       <c r="F76" s="195" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="G76" s="76" t="s">
         <v>1483</v>
@@ -38264,7 +38246,7 @@
         <v>1379</v>
       </c>
       <c r="F77" s="183" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="G77" s="183" t="s">
         <v>1483</v>
@@ -38290,7 +38272,7 @@
         <v>1379</v>
       </c>
       <c r="F78" s="183" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="G78" s="183" t="s">
         <v>1483</v>
@@ -38304,19 +38286,19 @@
         <v>2604</v>
       </c>
       <c r="B79" s="183" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
       <c r="C79" s="194" t="s">
         <v>2798</v>
       </c>
       <c r="D79" s="183" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
       <c r="E79" s="183" t="s">
         <v>1379</v>
       </c>
       <c r="F79" s="183" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="G79" s="183" t="s">
         <v>1483</v>
@@ -38327,7 +38309,7 @@
     </row>
     <row r="80" spans="1:9" s="183" customFormat="1">
       <c r="A80" s="183" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B80" s="183">
         <v>69904406</v>
@@ -38336,13 +38318,13 @@
         <v>2799</v>
       </c>
       <c r="D80" s="183" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="E80" s="183" t="s">
         <v>1379</v>
       </c>
       <c r="F80" s="183" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="G80" s="183" t="s">
         <v>1483</v>
@@ -38368,7 +38350,7 @@
         <v>1379</v>
       </c>
       <c r="F81" s="183" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="G81" s="183" t="s">
         <v>1483</v>
@@ -38394,7 +38376,7 @@
         <v>1705</v>
       </c>
       <c r="F83" s="195" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>1483</v>
@@ -38418,7 +38400,7 @@
         <v>1705</v>
       </c>
       <c r="F84" s="193" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="G84" s="183" t="s">
         <v>1483</v>
@@ -38442,7 +38424,7 @@
         <v>1705</v>
       </c>
       <c r="F85" s="193" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="G85" s="183" t="s">
         <v>1483</v>
@@ -38466,7 +38448,7 @@
         <v>1705</v>
       </c>
       <c r="F86" s="193" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="G86" s="183" t="s">
         <v>1483</v>
@@ -38490,7 +38472,7 @@
         <v>1705</v>
       </c>
       <c r="F87" s="193" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="G87" s="183" t="s">
         <v>1483</v>
@@ -38514,7 +38496,7 @@
         <v>1705</v>
       </c>
       <c r="F88" s="193" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="G88" s="183" t="s">
         <v>1483</v>
@@ -38538,7 +38520,7 @@
         <v>2586</v>
       </c>
       <c r="F90" s="195" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="G90" s="76" t="s">
         <v>1483</v>
@@ -38550,7 +38532,7 @@
     </row>
     <row r="91" spans="1:9" s="183" customFormat="1">
       <c r="A91" s="193" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B91" s="193">
         <v>66319486</v>
@@ -38559,13 +38541,13 @@
         <v>2778</v>
       </c>
       <c r="D91" s="193" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="E91" s="183" t="s">
         <v>2586</v>
       </c>
       <c r="F91" s="193" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="G91" s="183" t="s">
         <v>1483</v>
@@ -38592,7 +38574,7 @@
         <v>2586</v>
       </c>
       <c r="F92" s="193" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="G92" s="183" t="s">
         <v>1483</v>
@@ -38619,7 +38601,7 @@
         <v>2586</v>
       </c>
       <c r="F93" s="193" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="G93" s="183" t="s">
         <v>1483</v>
@@ -38646,7 +38628,7 @@
         <v>2586</v>
       </c>
       <c r="F94" s="193" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="G94" s="183" t="s">
         <v>1483</v>
@@ -38658,7 +38640,7 @@
     </row>
     <row r="95" spans="1:9" s="183" customFormat="1">
       <c r="A95" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B95" s="193">
         <v>67381873</v>
@@ -38667,13 +38649,13 @@
         <v>2366</v>
       </c>
       <c r="D95" s="193" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="E95" s="183" t="s">
         <v>2586</v>
       </c>
       <c r="F95" s="193" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="G95" s="183" t="s">
         <v>1483</v>
@@ -38685,7 +38667,7 @@
     </row>
     <row r="97" spans="1:9" s="76" customFormat="1">
       <c r="A97" s="195" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="B97" s="195">
         <v>66082581</v>
@@ -38697,7 +38679,7 @@
         <v>2380</v>
       </c>
       <c r="E97" s="76" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="F97" s="195" t="s">
         <v>427</v>
@@ -38712,7 +38694,7 @@
     </row>
     <row r="98" spans="1:9" s="183" customFormat="1">
       <c r="A98" s="193" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B98" s="193" t="s">
         <v>2838</v>
@@ -38724,7 +38706,7 @@
         <v>2385</v>
       </c>
       <c r="E98" s="183" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="F98" s="193" t="s">
         <v>427</v>
@@ -38739,7 +38721,7 @@
     </row>
     <row r="99" spans="1:9" s="183" customFormat="1">
       <c r="A99" s="193" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="B99" s="193">
         <v>62723048</v>
@@ -38748,10 +38730,10 @@
         <v>2386</v>
       </c>
       <c r="D99" s="193" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="E99" s="183" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="F99" s="193" t="s">
         <v>427</v>
@@ -38778,7 +38760,7 @@
         <v>2558</v>
       </c>
       <c r="E100" s="183" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="F100" s="193" t="s">
         <v>427</v>
@@ -38805,7 +38787,7 @@
         <v>2389</v>
       </c>
       <c r="E101" s="183" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="F101" s="193" t="s">
         <v>427</v>
@@ -38832,7 +38814,7 @@
         <v>3191</v>
       </c>
       <c r="E102" s="183" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="F102" s="193" t="s">
         <v>427</v>
@@ -38853,16 +38835,16 @@
         <v>68310153</v>
       </c>
       <c r="C104" s="195" t="s">
+        <v>3302</v>
+      </c>
+      <c r="D104" s="195" t="s">
         <v>3303</v>
-      </c>
-      <c r="D104" s="195" t="s">
-        <v>3304</v>
       </c>
       <c r="E104" s="76" t="s">
         <v>365</v>
       </c>
       <c r="F104" s="195" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G104" s="76" t="s">
         <v>1379</v>
@@ -38876,7 +38858,7 @@
     </row>
     <row r="105" spans="1:9" s="183" customFormat="1">
       <c r="A105" s="193" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="B105" s="193">
         <v>63910392</v>
@@ -38889,7 +38871,7 @@
         <v>365</v>
       </c>
       <c r="F105" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G105" s="183" t="s">
         <v>1379</v>
@@ -38909,7 +38891,7 @@
         <v>68853797</v>
       </c>
       <c r="C106" s="193" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="D106" s="193" t="s">
         <v>3235</v>
@@ -38918,7 +38900,7 @@
         <v>2586</v>
       </c>
       <c r="F106" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G106" s="183" t="s">
         <v>1379</v>
@@ -38936,16 +38918,16 @@
       </c>
       <c r="B107" s="193"/>
       <c r="C107" s="194" t="s">
+        <v>3657</v>
+      </c>
+      <c r="D107" s="183" t="s">
         <v>3658</v>
-      </c>
-      <c r="D107" s="183" t="s">
-        <v>3659</v>
       </c>
       <c r="E107" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F107" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G107" s="183" t="s">
         <v>1379</v>
@@ -38963,16 +38945,16 @@
       </c>
       <c r="B108" s="193"/>
       <c r="C108" s="193" t="s">
+        <v>3659</v>
+      </c>
+      <c r="D108" s="193" t="s">
         <v>3660</v>
-      </c>
-      <c r="D108" s="193" t="s">
-        <v>3661</v>
       </c>
       <c r="E108" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F108" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G108" s="183" t="s">
         <v>1379</v>
@@ -38990,16 +38972,16 @@
       </c>
       <c r="B109" s="193"/>
       <c r="C109" s="193" t="s">
+        <v>3661</v>
+      </c>
+      <c r="D109" s="193" t="s">
         <v>3662</v>
-      </c>
-      <c r="D109" s="193" t="s">
-        <v>3663</v>
       </c>
       <c r="E109" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F109" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G109" s="183" t="s">
         <v>1379</v>
@@ -39013,7 +38995,7 @@
     </row>
     <row r="111" spans="1:9" s="76" customFormat="1">
       <c r="A111" s="76" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B111" s="76">
         <v>62751201</v>
@@ -39028,7 +39010,7 @@
         <v>1379</v>
       </c>
       <c r="F111" s="76" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G111" s="222" t="s">
         <v>1483</v>
@@ -39055,7 +39037,7 @@
         <v>1379</v>
       </c>
       <c r="F112" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G112" s="183" t="s">
         <v>1483</v>
@@ -39073,16 +39055,16 @@
         <v>64543204</v>
       </c>
       <c r="C113" s="194" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="D113" s="183" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="E113" s="183" t="s">
         <v>1379</v>
       </c>
       <c r="F113" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G113" s="183" t="s">
         <v>1483</v>
@@ -39109,7 +39091,7 @@
         <v>1379</v>
       </c>
       <c r="F114" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G114" s="183" t="s">
         <v>1483</v>
@@ -39136,7 +39118,7 @@
         <v>1379</v>
       </c>
       <c r="F115" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G115" s="183" t="s">
         <v>1483</v>
@@ -39163,7 +39145,7 @@
         <v>1379</v>
       </c>
       <c r="F116" s="193" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="G116" s="183" t="s">
         <v>1483</v>
@@ -39187,7 +39169,7 @@
         <v>1729</v>
       </c>
       <c r="E118" s="76" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>1563</v>
@@ -39213,7 +39195,7 @@
         <v>894</v>
       </c>
       <c r="E119" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F119" s="183" t="s">
         <v>1563</v>
@@ -39227,7 +39209,7 @@
     </row>
     <row r="120" spans="1:9" s="183" customFormat="1">
       <c r="A120" s="183" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="B120" s="183">
         <v>69563253</v>
@@ -39239,7 +39221,7 @@
         <v>1020</v>
       </c>
       <c r="E120" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F120" s="183" t="s">
         <v>1563</v>
@@ -39265,7 +39247,7 @@
         <v>1282</v>
       </c>
       <c r="E121" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F121" s="183" t="s">
         <v>1563</v>
@@ -39291,7 +39273,7 @@
         <v>949</v>
       </c>
       <c r="E122" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F122" s="183" t="s">
         <v>1563</v>
@@ -39317,7 +39299,7 @@
         <v>1985</v>
       </c>
       <c r="E123" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F123" s="183" t="s">
         <v>1563</v>
@@ -39343,7 +39325,7 @@
         <v>2402</v>
       </c>
       <c r="E125" s="76" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>427</v>
@@ -39369,7 +39351,7 @@
         <v>2404</v>
       </c>
       <c r="E126" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F126" s="193" t="s">
         <v>427</v>
@@ -39396,7 +39378,7 @@
         <v>2406</v>
       </c>
       <c r="E127" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F127" s="193" t="s">
         <v>427</v>
@@ -39414,13 +39396,13 @@
         <v>1192</v>
       </c>
       <c r="C128" s="183" t="s">
+        <v>3663</v>
+      </c>
+      <c r="D128" s="183" t="s">
         <v>3664</v>
       </c>
-      <c r="D128" s="183" t="s">
-        <v>3665</v>
-      </c>
       <c r="E128" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F128" s="193" t="s">
         <v>427</v>
@@ -39447,7 +39429,7 @@
         <v>380</v>
       </c>
       <c r="E129" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F129" s="193" t="s">
         <v>427</v>
@@ -39474,7 +39456,7 @@
         <v>1701</v>
       </c>
       <c r="E130" s="183" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="F130" s="193" t="s">
         <v>427</v>
@@ -39504,7 +39486,7 @@
         <v>684</v>
       </c>
       <c r="F132" s="76" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G132" s="76" t="s">
         <v>427</v>
@@ -39533,7 +39515,7 @@
         <v>365</v>
       </c>
       <c r="F133" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G133" s="183" t="s">
         <v>427</v>
@@ -39562,7 +39544,7 @@
         <v>365</v>
       </c>
       <c r="F134" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G134" s="183" t="s">
         <v>427</v>
@@ -39588,7 +39570,7 @@
         <v>365</v>
       </c>
       <c r="F135" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G135" s="183" t="s">
         <v>427</v>
@@ -39617,7 +39599,7 @@
         <v>365</v>
       </c>
       <c r="F136" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G136" s="183" t="s">
         <v>427</v>
@@ -39646,7 +39628,7 @@
         <v>365</v>
       </c>
       <c r="F137" s="183" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G137" s="183" t="s">
         <v>427</v>
@@ -39675,7 +39657,7 @@
         <v>2461</v>
       </c>
       <c r="F139" s="195" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G139" s="76" t="s">
         <v>1483</v>
@@ -39702,7 +39684,7 @@
         <v>2461</v>
       </c>
       <c r="F140" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G140" s="183" t="s">
         <v>1483</v>
@@ -39729,7 +39711,7 @@
         <v>2461</v>
       </c>
       <c r="F141" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G141" s="183" t="s">
         <v>1483</v>
@@ -39756,7 +39738,7 @@
         <v>2461</v>
       </c>
       <c r="F142" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G142" s="183" t="s">
         <v>1483</v>
@@ -39783,7 +39765,7 @@
         <v>2461</v>
       </c>
       <c r="F143" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G143" s="183" t="s">
         <v>1483</v>
@@ -39810,7 +39792,7 @@
         <v>2461</v>
       </c>
       <c r="F144" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G144" s="183" t="s">
         <v>1483</v>
@@ -39828,16 +39810,16 @@
         <v>2234</v>
       </c>
       <c r="C146" s="195" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
       <c r="D146" s="195" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
       <c r="E146" s="76" t="s">
         <v>2461</v>
       </c>
       <c r="F146" s="195" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G146" s="76" t="s">
         <v>1483</v>
@@ -39851,16 +39833,16 @@
       <c r="A147" s="279"/>
       <c r="B147" s="193"/>
       <c r="C147" s="193" t="s">
+        <v>3665</v>
+      </c>
+      <c r="D147" s="193" t="s">
         <v>3666</v>
-      </c>
-      <c r="D147" s="193" t="s">
-        <v>3667</v>
       </c>
       <c r="E147" s="183" t="s">
         <v>2461</v>
       </c>
       <c r="F147" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G147" s="183" t="s">
         <v>1483</v>
@@ -39887,7 +39869,7 @@
         <v>2461</v>
       </c>
       <c r="F148" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G148" s="183" t="s">
         <v>1483</v>
@@ -39914,7 +39896,7 @@
         <v>2461</v>
       </c>
       <c r="F149" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G149" s="183" t="s">
         <v>1483</v>
@@ -39941,7 +39923,7 @@
         <v>2461</v>
       </c>
       <c r="F150" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G150" s="183" t="s">
         <v>1483</v>
@@ -39968,7 +39950,7 @@
         <v>2461</v>
       </c>
       <c r="F151" s="193" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
       <c r="G151" s="183" t="s">
         <v>1483</v>
@@ -39995,7 +39977,7 @@
         <v>2586</v>
       </c>
       <c r="F153" s="195" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="G153" s="76" t="s">
         <v>1483</v>
@@ -40016,7 +39998,7 @@
         <v>2586</v>
       </c>
       <c r="F154" s="193" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="G154" s="183" t="s">
         <v>1483</v>
@@ -40043,7 +40025,7 @@
         <v>2586</v>
       </c>
       <c r="F155" s="193" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="G155" s="183" t="s">
         <v>1483</v>
@@ -40055,7 +40037,7 @@
     </row>
     <row r="156" spans="1:9" s="183" customFormat="1">
       <c r="A156" s="193" t="s">
-        <v>3464</v>
+        <v>3463</v>
       </c>
       <c r="B156" s="193">
         <v>64403333</v>
@@ -40070,7 +40052,7 @@
         <v>2586</v>
       </c>
       <c r="F156" s="193" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="G156" s="183" t="s">
         <v>1483</v>
@@ -40082,22 +40064,22 @@
     </row>
     <row r="157" spans="1:9" s="183" customFormat="1">
       <c r="A157" s="193" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="B157" s="193">
         <v>60125401</v>
       </c>
       <c r="C157" s="194" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="D157" s="193" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="E157" s="183" t="s">
         <v>2586</v>
       </c>
       <c r="F157" s="193" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="G157" s="183" t="s">
         <v>1483</v>
@@ -40124,7 +40106,7 @@
         <v>2586</v>
       </c>
       <c r="F158" s="193" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="G158" s="183" t="s">
         <v>1483</v>
@@ -40151,7 +40133,7 @@
         <v>365</v>
       </c>
       <c r="F160" s="195" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="G160" s="76" t="s">
         <v>2467</v>
@@ -40165,22 +40147,22 @@
     </row>
     <row r="161" spans="1:9" s="183" customFormat="1">
       <c r="A161" s="193" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B161" s="193">
         <v>65963732</v>
       </c>
       <c r="C161" s="194" t="s">
+        <v>3645</v>
+      </c>
+      <c r="D161" s="193" t="s">
         <v>3646</v>
-      </c>
-      <c r="D161" s="193" t="s">
-        <v>3647</v>
       </c>
       <c r="E161" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F161" s="193" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="G161" s="183" t="s">
         <v>2467</v>
@@ -40194,7 +40176,7 @@
     </row>
     <row r="162" spans="1:9" s="183" customFormat="1">
       <c r="A162" s="183" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B162" s="183">
         <v>60071688</v>
@@ -40203,13 +40185,13 @@
         <v>2449</v>
       </c>
       <c r="D162" s="183" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="E162" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F162" s="193" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="G162" s="183" t="s">
         <v>2467</v>
@@ -40238,7 +40220,7 @@
         <v>365</v>
       </c>
       <c r="F163" s="193" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="G163" s="183" t="s">
         <v>2467</v>
@@ -40267,7 +40249,7 @@
         <v>365</v>
       </c>
       <c r="F164" s="193" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="G164" s="183" t="s">
         <v>2467</v>
@@ -40287,16 +40269,16 @@
         <v>64403333</v>
       </c>
       <c r="C165" s="194" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="D165" s="420" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="E165" s="183" t="s">
         <v>365</v>
       </c>
       <c r="F165" s="193" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="G165" s="183" t="s">
         <v>2467</v>
@@ -40357,7 +40339,7 @@
         <v>319</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="E194" s="30"/>
       <c r="F194"/>
@@ -40383,7 +40365,7 @@
         <v>444</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="E196" s="30"/>
       <c r="F196"/>
@@ -40394,7 +40376,7 @@
         <v>26</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -40402,7 +40384,7 @@
         <v>1362</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -40410,7 +40392,7 @@
         <v>1712</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="F199" s="402"/>
     </row>
@@ -40419,7 +40401,7 @@
         <v>1341</v>
       </c>
       <c r="D200" s="444" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -40443,7 +40425,7 @@
         <v>284</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -40451,7 +40433,7 @@
         <v>2469</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -40461,7 +40443,7 @@
         <v>470</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -40469,7 +40451,7 @@
         <v>222</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -40477,7 +40459,7 @@
         <v>432</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -40485,7 +40467,7 @@
         <v>1069</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -41834,7 +41816,7 @@
         <v>3137</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="J3"/>
     </row>
@@ -41861,10 +41843,10 @@
         <v>520</v>
       </c>
       <c r="H4" s="445" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="I4" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="J4"/>
     </row>
@@ -41882,7 +41864,7 @@
         <v>1569</v>
       </c>
       <c r="E5" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="F5" t="s">
         <v>2243</v>
@@ -41894,7 +41876,7 @@
         <v>2894</v>
       </c>
       <c r="I5" s="220" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="J5" t="s">
         <v>1434</v>
@@ -41966,10 +41948,10 @@
         <v>253</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="I8" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="J8"/>
     </row>
@@ -42033,7 +42015,7 @@
         <v>441</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="I12" s="49" t="s">
         <v>2713</v>
@@ -42234,7 +42216,7 @@
         <v>2909</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -42248,7 +42230,7 @@
         <v>1778</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1751</v>
@@ -42260,10 +42242,10 @@
         <v>522</v>
       </c>
       <c r="H7" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -42279,7 +42261,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B11" s="10">
         <v>64403333</v>
@@ -42311,7 +42293,7 @@
         <v>2221</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>975</v>
@@ -42323,10 +42305,10 @@
         <v>522</v>
       </c>
       <c r="H12" s="10" t="s">
+        <v>3563</v>
+      </c>
+      <c r="I12" s="49" t="s">
         <v>3564</v>
-      </c>
-      <c r="I12" s="49" t="s">
-        <v>3565</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -42351,7 +42333,7 @@
         <v>2282</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>975</v>
@@ -42363,10 +42345,10 @@
         <v>522</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -42415,7 +42397,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B18" s="10">
         <v>60345107</v>
@@ -42424,7 +42406,7 @@
         <v>2423</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>975</v>
@@ -42436,7 +42418,7 @@
         <v>522</v>
       </c>
       <c r="H18" s="441" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>3038</v>
@@ -42465,7 +42447,7 @@
         <v>522</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>2700</v>
@@ -42505,7 +42487,7 @@
         <v>3146</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -42548,7 +42530,7 @@
         <v>2533</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>975</v>
@@ -42563,7 +42545,7 @@
         <v>3099</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -42573,7 +42555,7 @@
         <v>2548</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>975</v>
@@ -42692,13 +42674,13 @@
         <v>2564</v>
       </c>
       <c r="B4" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1923</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
       <c r="E4" t="s">
         <v>1924</v>
@@ -42710,13 +42692,13 @@
         <v>979</v>
       </c>
       <c r="H4" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
       <c r="J4" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -42765,10 +42747,10 @@
         <v>979</v>
       </c>
       <c r="H6" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="I6" t="s">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="J6" s="49" t="s">
         <v>2308</v>
@@ -42800,10 +42782,10 @@
         <v>2948</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -42829,30 +42811,30 @@
         <v>979</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
+        <v>3391</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>3392</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>3393</v>
-      </c>
       <c r="C9" s="22" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>3154</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>3157</v>
@@ -42861,13 +42843,13 @@
         <v>979</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>3393</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>3394</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>3395</v>
-      </c>
       <c r="J9" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -42875,16 +42857,16 @@
         <v>1472</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>3559</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>3560</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>3561</v>
-      </c>
       <c r="E10" s="10" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>2379</v>
@@ -42893,7 +42875,7 @@
         <v>979</v>
       </c>
       <c r="H10" s="446" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="I10" s="279"/>
       <c r="J10" s="97"/>
@@ -43066,7 +43048,7 @@
         <v>1843</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>2742</v>
@@ -43128,7 +43110,7 @@
         <v>63132287</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>2767</v>
@@ -43304,7 +43286,7 @@
     <row r="1" spans="1:10" s="419" customFormat="1" ht="42.5" customHeight="1">
       <c r="A1" s="418"/>
       <c r="B1" s="418" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="C1" s="418"/>
     </row>
@@ -43313,28 +43295,28 @@
         <v>148</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>3454</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3241</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>3455</v>
       </c>
-      <c r="E4" t="s">
-        <v>3242</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>3456</v>
-      </c>
       <c r="G4" s="10" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>3434</v>
+        <v>3433</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>3449</v>
+        <v>3448</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
     </row>
   </sheetData>
@@ -44730,7 +44712,7 @@
         <v>51</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>1188</v>
@@ -44773,7 +44755,7 @@
         <v>2349</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="L7" s="3"/>
     </row>
@@ -44803,7 +44785,7 @@
         <v>2877</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1">
@@ -44864,7 +44846,7 @@
         <v>3137</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -44919,10 +44901,10 @@
         <v>247</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -45007,10 +44989,10 @@
         <v>900</v>
       </c>
       <c r="H15" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="I15" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>503</v>
@@ -45050,7 +45032,7 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="B17">
         <v>65325884</v>
@@ -45094,7 +45076,7 @@
         <v>247</v>
       </c>
       <c r="H18" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="I18" t="s">
         <v>3195</v>
@@ -45220,7 +45202,7 @@
         <v>160</v>
       </c>
       <c r="H23" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
       <c r="I23" s="308" t="s">
         <v>2694</v>
@@ -45238,10 +45220,10 @@
         <v>1684</v>
       </c>
       <c r="D24" t="s">
-        <v>3433</v>
+        <v>3432</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>2578</v>
@@ -45264,7 +45246,7 @@
         <v>2094</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>2582</v>
@@ -45305,7 +45287,7 @@
         <v>3017</v>
       </c>
       <c r="I26" s="49" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1">
@@ -45334,7 +45316,7 @@
         <v>3209</v>
       </c>
       <c r="I27" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>824</v>
@@ -45354,7 +45336,7 @@
         <v>2095</v>
       </c>
       <c r="E28" t="s">
-        <v>3448</v>
+        <v>3447</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>2582</v>
@@ -45403,19 +45385,19 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="C30" s="22" t="s">
         <v>407</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="E30" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1379</v>
@@ -45424,7 +45406,7 @@
         <v>160</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="I30" t="s">
         <v>2908</v>
@@ -45453,10 +45435,10 @@
         <v>160</v>
       </c>
       <c r="H31" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -45482,7 +45464,7 @@
         <v>160</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="I32" s="49" t="s">
         <v>2893</v>
@@ -45514,7 +45496,7 @@
         <v>3003</v>
       </c>
       <c r="I33" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -45522,13 +45504,13 @@
         <v>1472</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>2722</v>
       </c>
       <c r="D34" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="E34" t="s">
         <v>2728</v>
@@ -45540,7 +45522,7 @@
         <v>160</v>
       </c>
       <c r="H34" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="I34" s="49" t="s">
         <v>3028</v>
@@ -45552,13 +45534,13 @@
         <v>148</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>2723</v>
       </c>
       <c r="D35" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="E35" t="s">
         <v>2728</v>
@@ -45570,10 +45552,10 @@
         <v>2729</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="I35" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -45602,7 +45584,7 @@
         <v>2891</v>
       </c>
       <c r="I36" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -45631,7 +45613,7 @@
         <v>3187</v>
       </c>
       <c r="I37" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -45639,7 +45621,7 @@
         <v>158</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>2737</v>
@@ -45657,10 +45639,10 @@
         <v>160</v>
       </c>
       <c r="H38" s="97" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
       <c r="I38" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="262" customFormat="1" ht="15.5">
@@ -45670,7 +45652,7 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="4" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B45" t="s">
         <v>2621</v>
@@ -45700,7 +45682,7 @@
         <v>2984</v>
       </c>
       <c r="K45" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1">
@@ -46106,13 +46088,13 @@
         <v>158</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="C2" s="277" t="s">
         <v>257</v>
       </c>
       <c r="D2" s="106" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>1332</v>
@@ -46124,10 +46106,10 @@
         <v>62</v>
       </c>
       <c r="H2" s="301" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>3432</v>
+        <v>3431</v>
       </c>
       <c r="J2" s="107" t="s">
         <v>3227</v>
@@ -46148,7 +46130,7 @@
         <v>1211</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>2498</v>
@@ -46163,7 +46145,7 @@
         <v>2941</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
       <c r="J4" s="139" t="s">
         <v>3208</v>
@@ -46175,10 +46157,10 @@
     </row>
     <row r="5" spans="1:13" s="30" customFormat="1">
       <c r="A5" s="30" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>1139</v>
@@ -46199,13 +46181,13 @@
         <v>3098</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="J5" s="145" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="M5" s="36"/>
     </row>
@@ -46232,22 +46214,22 @@
         <v>65</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
       <c r="J6" s="217" t="s">
         <v>3025</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="M6" s="36"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="107" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>1243</v>
@@ -46268,16 +46250,16 @@
         <v>730</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="J7" s="30" t="s">
         <v>2804</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="M7" s="36"/>
     </row>
@@ -46307,7 +46289,7 @@
         <v>3212</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="J8" s="107" t="s">
         <v>3224</v>
@@ -46340,16 +46322,16 @@
         <v>65</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="I9" s="107" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
       <c r="K9" s="107" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="M9" s="36"/>
     </row>
@@ -46376,7 +46358,7 @@
         <v>65</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="I10" s="49" t="s">
         <v>2867</v>
@@ -46385,7 +46367,7 @@
         <v>3138</v>
       </c>
       <c r="K10" s="107" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="M10" s="34"/>
     </row>
@@ -46412,16 +46394,16 @@
         <v>610</v>
       </c>
       <c r="H11" s="139" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="I11" s="30" t="s">
         <v>3205</v>
       </c>
       <c r="J11" s="107" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="K11" s="107" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="M11" s="36"/>
     </row>
@@ -46457,7 +46439,7 @@
         <v>3127</v>
       </c>
       <c r="K12" s="107" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="M12" s="151"/>
     </row>
@@ -46472,7 +46454,7 @@
         <v>932</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
       <c r="E13" s="140" t="s">
         <v>2916</v>
@@ -46484,16 +46466,16 @@
         <v>65</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="J13" s="107" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
       <c r="K13" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="M13" s="36"/>
     </row>
@@ -46520,13 +46502,13 @@
         <v>65</v>
       </c>
       <c r="H14" s="107" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I14" s="421" t="s">
         <v>2350</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="M14" s="36"/>
     </row>
@@ -46556,13 +46538,13 @@
         <v>3173</v>
       </c>
       <c r="I15" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="J15" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="K15" s="107" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="M15" s="36"/>
     </row>
@@ -46617,10 +46599,10 @@
         <v>2969</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>3437</v>
+        <v>3436</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="K17" s="220" t="s">
         <v>3116</v>
@@ -46650,16 +46632,16 @@
         <v>66</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="I18" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="J18" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="K18" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="M18" s="36"/>
     </row>
@@ -46686,16 +46668,16 @@
         <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="I19" t="s">
         <v>3234</v>
       </c>
       <c r="J19" s="220" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="K19" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="M19" s="36"/>
     </row>
@@ -46710,7 +46692,7 @@
         <v>2599</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>3363</v>
+        <v>3362</v>
       </c>
       <c r="E20" s="107" t="s">
         <v>2518</v>
@@ -46725,13 +46707,13 @@
         <v>3128</v>
       </c>
       <c r="I20" t="s">
+        <v>3363</v>
+      </c>
+      <c r="J20" t="s">
         <v>3364</v>
       </c>
-      <c r="J20" t="s">
-        <v>3365</v>
-      </c>
       <c r="K20" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="M20" s="36"/>
     </row>
@@ -46876,7 +46858,7 @@
         <v>2249</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
       <c r="E34" s="32" t="s">
         <v>2516</v>
@@ -47066,7 +47048,7 @@
         <v>2633</v>
       </c>
       <c r="E45" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="F45" s="30" t="s">
         <v>2634</v>
@@ -47075,13 +47057,13 @@
         <v>372</v>
       </c>
       <c r="H45" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
       <c r="I45" s="30" t="s">
         <v>3029</v>
       </c>
       <c r="J45" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -47982,7 +47964,7 @@
       </c>
       <c r="B24" s="87"/>
       <c r="F24" s="2" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -48252,13 +48234,13 @@
         <v>360</v>
       </c>
       <c r="H6" s="248" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
       <c r="I6" s="245" t="s">
         <v>3206</v>
       </c>
       <c r="J6" s="296" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="K6" s="248" t="s">
         <v>480</v>
@@ -48295,7 +48277,7 @@
         <v>2994</v>
       </c>
       <c r="I8" s="296" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="J8" s="266" t="s">
         <v>3139</v>
@@ -48321,7 +48303,7 @@
         <v>1263</v>
       </c>
       <c r="F9" s="106" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
       <c r="G9" s="106" t="s">
         <v>253</v>
@@ -48385,13 +48367,13 @@
         <v>696</v>
       </c>
       <c r="H11" s="265" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="I11" s="296" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="J11" s="265" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="K11" s="246" t="s">
         <v>1237</v>
@@ -48402,7 +48384,7 @@
         <v>2630</v>
       </c>
       <c r="B12" s="263" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
       <c r="C12" s="194" t="s">
         <v>496</v>
@@ -48420,13 +48402,13 @@
         <v>696</v>
       </c>
       <c r="H12" s="145" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="I12" s="215" t="s">
         <v>3048</v>
       </c>
       <c r="J12" s="270" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="K12" s="183" t="s">
         <v>1238</v>
@@ -48463,7 +48445,7 @@
         <v>2879</v>
       </c>
       <c r="B14" s="224" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="C14" s="435" t="s">
         <v>338</v>
@@ -48472,22 +48454,22 @@
         <v>2496</v>
       </c>
       <c r="E14" s="224" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="F14" s="224" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="G14" s="224" t="s">
         <v>696</v>
       </c>
       <c r="H14" s="224" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="I14" s="215" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="J14" s="224" t="s">
-        <v>3424</v>
+        <v>3423</v>
       </c>
       <c r="K14" s="224" t="s">
         <v>1355</v>
@@ -48516,13 +48498,13 @@
         <v>696</v>
       </c>
       <c r="H15" s="442" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
       <c r="I15" s="215" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="J15" s="263" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
       <c r="K15" s="183" t="s">
         <v>1239</v>
@@ -48533,13 +48515,13 @@
         <v>1458</v>
       </c>
       <c r="B16" s="265" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="C16" s="271" t="s">
         <v>1341</v>
       </c>
       <c r="D16" s="260" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="E16" s="260" t="s">
         <v>2927</v>
@@ -48551,13 +48533,13 @@
         <v>696</v>
       </c>
       <c r="H16" s="265" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="I16" s="272" t="s">
         <v>3161</v>
       </c>
       <c r="J16" s="265" t="s">
-        <v>3576</v>
+        <v>3575</v>
       </c>
       <c r="K16" s="260" t="s">
         <v>1482</v>
@@ -48689,7 +48671,7 @@
         <v>696</v>
       </c>
       <c r="H21" s="260" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="I21" s="217" t="s">
         <v>2918</v>
@@ -48724,13 +48706,13 @@
         <v>696</v>
       </c>
       <c r="H22" s="260" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="I22" s="260" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="J22" s="260" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="K22" s="260" t="s">
         <v>1867</v>
@@ -48802,13 +48784,13 @@
         <v>1472</v>
       </c>
       <c r="B27" s="265" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="C27" s="271" t="s">
         <v>642</v>
       </c>
       <c r="D27" s="256" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="E27" s="272" t="s">
         <v>2500</v>
@@ -48820,13 +48802,13 @@
         <v>253</v>
       </c>
       <c r="H27" s="260" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="I27" s="265" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="J27" s="265" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="260" customFormat="1">
@@ -48834,7 +48816,7 @@
         <v>852</v>
       </c>
       <c r="D29" s="265" t="s">
-        <v>3358</v>
+        <v>3357</v>
       </c>
       <c r="E29" s="260" t="s">
         <v>1845</v>
@@ -49222,7 +49204,7 @@
         <v>3143</v>
       </c>
       <c r="J2" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="L2" s="36" t="s">
         <v>1205</v>
@@ -49274,10 +49256,10 @@
         <v>316</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>326</v>
@@ -49286,13 +49268,13 @@
         <v>3210</v>
       </c>
       <c r="H4" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="J4" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="L4" s="127" t="s">
         <v>325</v>
@@ -49318,7 +49300,7 @@
         <v>429</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>2907</v>
@@ -49351,10 +49333,10 @@
         <v>167</v>
       </c>
       <c r="G6" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="I6" t="s">
         <v>3071</v>
@@ -49368,7 +49350,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="4" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="B7" s="4">
         <v>69561522</v>
@@ -49377,25 +49359,25 @@
         <v>439</v>
       </c>
       <c r="D7" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="E7" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="F7" t="s">
         <v>152</v>
       </c>
       <c r="G7" t="s">
+        <v>3532</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>3533</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>3534</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>3446</v>
+        <v>3445</v>
       </c>
       <c r="J7" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="L7" s="83" t="s">
         <v>440</v>
@@ -49406,7 +49388,7 @@
         <v>3204</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>664</v>
@@ -49424,10 +49406,10 @@
         <v>2790</v>
       </c>
       <c r="H8" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="I8" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="J8" s="49" t="s">
         <v>2950</v>
@@ -49454,16 +49436,16 @@
         <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
       <c r="H9" s="220" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="J9" s="220" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -49477,7 +49459,7 @@
         <v>2276</v>
       </c>
       <c r="D10" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="E10" t="s">
         <v>2247</v>
@@ -49541,7 +49523,7 @@
         <v>1522</v>
       </c>
       <c r="E13" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="F13" t="s">
         <v>619</v>
@@ -49572,16 +49554,16 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="B15" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>284</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="E15" t="s">
         <v>2210</v>
@@ -49859,7 +49841,7 @@
     </row>
     <row r="2" spans="1:14" ht="43.15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="52" t="s">
@@ -49883,7 +49865,7 @@
         <v>2823</v>
       </c>
       <c r="E4" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -49960,7 +49942,7 @@
         <v>2125</v>
       </c>
       <c r="E11" t="s">
-        <v>3402</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -49997,10 +49979,10 @@
         <v>2489</v>
       </c>
       <c r="E13" t="s">
+        <v>3242</v>
+      </c>
+      <c r="F13" t="s">
         <v>3243</v>
-      </c>
-      <c r="F13" t="s">
-        <v>3244</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -50014,7 +49996,7 @@
         <v>1998</v>
       </c>
       <c r="D14" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="E14" t="s">
         <v>2791</v>
@@ -50054,10 +50036,10 @@
         <v>2886</v>
       </c>
       <c r="D16" s="30" t="s">
+        <v>3408</v>
+      </c>
+      <c r="E16" t="s">
         <v>3409</v>
-      </c>
-      <c r="E16" t="s">
-        <v>3410</v>
       </c>
       <c r="F16" t="s">
         <v>2835</v>
@@ -50071,13 +50053,13 @@
         <v>68582631</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="D17" s="30" t="s">
+        <v>3425</v>
+      </c>
+      <c r="E17" t="s">
         <v>3426</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3427</v>
       </c>
       <c r="F17" t="s">
         <v>2835</v>
@@ -50100,7 +50082,7 @@
         <v>2890</v>
       </c>
       <c r="E18" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="F18" t="s">
         <v>2835</v>
@@ -50120,10 +50102,10 @@
         <v>2944</v>
       </c>
       <c r="E19" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
       <c r="F19" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -50179,7 +50161,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B26">
         <v>68927207</v>
@@ -50191,13 +50173,13 @@
         <v>2808</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>3382</v>
+      </c>
+      <c r="F26" t="s">
         <v>3383</v>
       </c>
-      <c r="F26" t="s">
-        <v>3384</v>
-      </c>
       <c r="G26" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -50214,21 +50196,21 @@
         <v>426</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="F27" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="G27" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="B29" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="C29" s="56" t="s">
         <v>1505</v>
@@ -50237,15 +50219,15 @@
         <v>1203</v>
       </c>
       <c r="E29" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="F29" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="B30">
         <v>63926844</v>
@@ -50257,10 +50239,10 @@
         <v>2834</v>
       </c>
       <c r="E30" t="s">
+        <v>3396</v>
+      </c>
+      <c r="F30" t="s">
         <v>3397</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3398</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -50274,10 +50256,10 @@
         <v>1608</v>
       </c>
       <c r="D31" t="s">
+        <v>3669</v>
+      </c>
+      <c r="E31" t="s">
         <v>3670</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3671</v>
       </c>
       <c r="F31" t="s">
         <v>1351</v>
@@ -52321,7 +52303,7 @@
     </row>
     <row r="252" spans="1:6" s="430" customFormat="1" ht="21">
       <c r="C252" s="430" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -52338,30 +52320,30 @@
         <v>2328</v>
       </c>
       <c r="E253" t="s">
+        <v>3346</v>
+      </c>
+      <c r="F253" t="s">
         <v>3347</v>
-      </c>
-      <c r="F253" t="s">
-        <v>3348</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="B254">
         <v>64738222</v>
       </c>
       <c r="C254" s="22" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="D254" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="E254" t="s">
+        <v>3346</v>
+      </c>
+      <c r="F254" t="s">
         <v>3347</v>
-      </c>
-      <c r="F254" t="s">
-        <v>3348</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -52372,16 +52354,16 @@
         <v>60433915</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="D255" s="252" t="s">
         <v>2773</v>
       </c>
       <c r="E255" t="s">
+        <v>3346</v>
+      </c>
+      <c r="F255" t="s">
         <v>3347</v>
-      </c>
-      <c r="F255" t="s">
-        <v>3348</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -57137,7 +57119,7 @@
         <v>2823</v>
       </c>
       <c r="E537" s="76" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
       <c r="F537" s="76"/>
       <c r="G537" s="76"/>
